--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -41205,13 +41205,13 @@
         <v>44562</v>
       </c>
       <c r="B314" t="n">
-        <v>59751.403989751</v>
+        <v>53032.8666853723</v>
       </c>
       <c r="C314" t="n">
         <v>3088.559712</v>
       </c>
       <c r="D314" t="n">
-        <v>111363.393024108</v>
+        <v>115336.716178298</v>
       </c>
       <c r="E314" t="n">
         <v>29853.94119</v>
@@ -41220,52 +41220,52 @@
         <v>82508.82319714</v>
       </c>
       <c r="G314" t="n">
-        <v>205159.802464815</v>
+        <v>207349.14293882</v>
       </c>
       <c r="H314" t="n">
-        <v>74279.836042</v>
+        <v>74311.0846521677</v>
       </c>
       <c r="I314" t="n">
         <v>28728.5886093913</v>
       </c>
       <c r="J314" t="n">
-        <v>60146.39212058</v>
+        <v>60146.5576270659</v>
       </c>
       <c r="K314" t="n">
-        <v>264942.749060519</v>
+        <v>264942.615541379</v>
       </c>
       <c r="L314" t="n">
-        <v>29760.93067823</v>
+        <v>29761.5484081397</v>
       </c>
       <c r="M314" t="n">
-        <v>38500.478171</v>
+        <v>38573.2978820278</v>
       </c>
       <c r="N314" t="n">
-        <v>384256.597267264</v>
+        <v>384230.54596256</v>
       </c>
       <c r="O314" t="n">
         <v>55531.294064</v>
       </c>
       <c r="P314" t="n">
-        <v>328725.303203264</v>
+        <v>328699.25189856</v>
       </c>
       <c r="Q314" t="n">
-        <v>77438.2309000213</v>
+        <v>77946.3089544499</v>
       </c>
       <c r="R314" t="n">
-        <v>1560486.53553508</v>
+        <v>1560491.35534237</v>
       </c>
       <c r="S314" t="n">
         <v>273549.788159</v>
       </c>
       <c r="T314" t="n">
-        <v>1834036.32369408</v>
+        <v>1834041.14350137</v>
       </c>
       <c r="U314" t="n">
-        <v>1.1031514768604</v>
+        <v>1.1034637497928</v>
       </c>
       <c r="V314" t="n">
-        <v>12.8426306420735</v>
+        <v>12.8429791742277</v>
       </c>
       <c r="W314" t="n">
         <v>0.801966565643886</v>
@@ -41274,16 +41274,16 @@
         <v>16.8395535352565</v>
       </c>
       <c r="Y314" t="n">
-        <v>1.05811505802944</v>
+        <v>1.0583806365424</v>
       </c>
       <c r="Z314" t="n">
-        <v>13.4213381250935</v>
+        <v>13.4216361938859</v>
       </c>
       <c r="AA314" t="n">
-        <v>0.850848216785575</v>
+        <v>0.850848608752165</v>
       </c>
       <c r="AB314" t="n">
-        <v>0.149151783214425</v>
+        <v>0.149151391247835</v>
       </c>
     </row>
     <row r="315">
@@ -41291,13 +41291,13 @@
         <v>44593</v>
       </c>
       <c r="B315" t="n">
-        <v>60069.5788977393</v>
+        <v>53351.0415933606</v>
       </c>
       <c r="C315" t="n">
         <v>3025.956532</v>
       </c>
       <c r="D315" t="n">
-        <v>109290.492122159</v>
+        <v>113263.815276349</v>
       </c>
       <c r="E315" t="n">
         <v>27629.892877</v>
@@ -41306,52 +41306,52 @@
         <v>81291.41599814</v>
       </c>
       <c r="G315" t="n">
-        <v>202381.045162179</v>
+        <v>204570.385636184</v>
       </c>
       <c r="H315" t="n">
-        <v>72262.15648</v>
+        <v>72293.4050901677</v>
       </c>
       <c r="I315" t="n">
         <v>28399.3051571157</v>
       </c>
       <c r="J315" t="n">
-        <v>59894.93844158</v>
+        <v>59895.1039480659</v>
       </c>
       <c r="K315" t="n">
-        <v>267706.810830886</v>
+        <v>267706.677311746</v>
       </c>
       <c r="L315" t="n">
-        <v>29544.08892123</v>
+        <v>29544.7066511397</v>
       </c>
       <c r="M315" t="n">
-        <v>39255.511554</v>
+        <v>39328.3312650278</v>
       </c>
       <c r="N315" t="n">
-        <v>390961.365120067</v>
+        <v>390935.313815364</v>
       </c>
       <c r="O315" t="n">
         <v>56340.032166</v>
       </c>
       <c r="P315" t="n">
-        <v>334621.332954067</v>
+        <v>334595.281649364</v>
       </c>
       <c r="Q315" t="n">
-        <v>79855.880029398</v>
+        <v>80363.9580838267</v>
       </c>
       <c r="R315" t="n">
-        <v>1584410.79660356</v>
+        <v>1584415.61641085</v>
       </c>
       <c r="S315" t="n">
         <v>258119.00664</v>
       </c>
       <c r="T315" t="n">
-        <v>1842529.80324356</v>
+        <v>1842534.62305085</v>
       </c>
       <c r="U315" t="n">
-        <v>1.53312832399892</v>
+        <v>1.53312358870639</v>
       </c>
       <c r="V315" t="n">
-        <v>13.6633265572515</v>
+        <v>13.6636723232176</v>
       </c>
       <c r="W315" t="n">
         <v>-5.64094076725473</v>
@@ -41360,16 +41360,16 @@
         <v>10.6896235039097</v>
       </c>
       <c r="Y315" t="n">
-        <v>0.463103126134956</v>
+        <v>0.463101909113273</v>
       </c>
       <c r="Z315" t="n">
-        <v>13.2371543740824</v>
+        <v>13.2374505870724</v>
       </c>
       <c r="AA315" t="n">
-        <v>0.859910539202345</v>
+        <v>0.859910905656357</v>
       </c>
       <c r="AB315" t="n">
-        <v>0.140089460797655</v>
+        <v>0.140089094343643</v>
       </c>
     </row>
     <row r="316">
@@ -41377,13 +41377,13 @@
         <v>44621</v>
       </c>
       <c r="B316" t="n">
-        <v>58480.0178154955</v>
+        <v>51761.4805111168</v>
       </c>
       <c r="C316" t="n">
         <v>3042.460377</v>
       </c>
       <c r="D316" t="n">
-        <v>114929.569942505</v>
+        <v>118902.893096695</v>
       </c>
       <c r="E316" t="n">
         <v>29364.979116</v>
@@ -41392,52 +41392,52 @@
         <v>87992.29630114</v>
       </c>
       <c r="G316" t="n">
-        <v>204039.661354251</v>
+        <v>206229.001828256</v>
       </c>
       <c r="H316" t="n">
-        <v>72920.598888</v>
+        <v>72951.8474981677</v>
       </c>
       <c r="I316" t="n">
         <v>27621.6836080496</v>
       </c>
       <c r="J316" t="n">
-        <v>58984.75099258</v>
+        <v>58984.9164990659</v>
       </c>
       <c r="K316" t="n">
-        <v>271895.463055362</v>
+        <v>271895.329536222</v>
       </c>
       <c r="L316" t="n">
-        <v>28928.68059723</v>
+        <v>28929.2983271397</v>
       </c>
       <c r="M316" t="n">
-        <v>40771.894664</v>
+        <v>40844.7143750278</v>
       </c>
       <c r="N316" t="n">
-        <v>399715.866972354</v>
+        <v>399689.81566765</v>
       </c>
       <c r="O316" t="n">
         <v>56191.318388</v>
       </c>
       <c r="P316" t="n">
-        <v>343524.548584354</v>
+        <v>343498.49727965</v>
       </c>
       <c r="Q316" t="n">
-        <v>80726.4667860365</v>
+        <v>81234.5448404652</v>
       </c>
       <c r="R316" t="n">
-        <v>1612388.58535036</v>
+        <v>1612393.40515765</v>
       </c>
       <c r="S316" t="n">
         <v>266741.672092</v>
       </c>
       <c r="T316" t="n">
-        <v>1879130.25744236</v>
+        <v>1879135.07724965</v>
       </c>
       <c r="U316" t="n">
-        <v>1.76581659294235</v>
+        <v>1.76581122131159</v>
       </c>
       <c r="V316" t="n">
-        <v>14.1915310467052</v>
+        <v>14.1918723919484</v>
       </c>
       <c r="W316" t="n">
         <v>3.34057749727283</v>
@@ -41446,16 +41446,16 @@
         <v>16.0090898824449</v>
       </c>
       <c r="Y316" t="n">
-        <v>1.98642399891524</v>
+        <v>1.98641880271391</v>
       </c>
       <c r="Z316" t="n">
-        <v>14.446056532499</v>
+        <v>14.4463500767785</v>
       </c>
       <c r="AA316" t="n">
-        <v>0.858050461890249</v>
+        <v>0.858050825977656</v>
       </c>
       <c r="AB316" t="n">
-        <v>0.141949538109751</v>
+        <v>0.141949174022344</v>
       </c>
     </row>
     <row r="317">
@@ -41463,13 +41463,13 @@
         <v>44652</v>
       </c>
       <c r="B317" t="n">
-        <v>59842.6549764806</v>
+        <v>53124.1176721019</v>
       </c>
       <c r="C317" t="n">
         <v>2953.653841</v>
       </c>
       <c r="D317" t="n">
-        <v>117322.997897435</v>
+        <v>121296.321051625</v>
       </c>
       <c r="E317" t="n">
         <v>29377.542547</v>
@@ -41478,52 +41478,52 @@
         <v>85669.47730014</v>
       </c>
       <c r="G317" t="n">
-        <v>202955.979678191</v>
+        <v>205145.320152196</v>
       </c>
       <c r="H317" t="n">
-        <v>76058.409097</v>
+        <v>76089.6577071677</v>
       </c>
       <c r="I317" t="n">
         <v>28426.790062059</v>
       </c>
       <c r="J317" t="n">
-        <v>59527.19205758</v>
+        <v>59527.3575640659</v>
       </c>
       <c r="K317" t="n">
-        <v>275369.908905373</v>
+        <v>275369.775386233</v>
       </c>
       <c r="L317" t="n">
-        <v>29237.49039723</v>
+        <v>29238.1081271397</v>
       </c>
       <c r="M317" t="n">
-        <v>42477.309911</v>
+        <v>42550.1296220278</v>
       </c>
       <c r="N317" t="n">
-        <v>402989.555126419</v>
+        <v>402963.503821715</v>
       </c>
       <c r="O317" t="n">
         <v>57349.428334</v>
       </c>
       <c r="P317" t="n">
-        <v>345640.126792419</v>
+        <v>345614.075487715</v>
       </c>
       <c r="Q317" t="n">
-        <v>81580.5116385628</v>
+        <v>82088.5896929914</v>
       </c>
       <c r="R317" t="n">
-        <v>1624956.46850589</v>
+        <v>1624961.28831318</v>
       </c>
       <c r="S317" t="n">
         <v>271822.560056</v>
       </c>
       <c r="T317" t="n">
-        <v>1896779.02856189</v>
+        <v>1896783.84836918</v>
       </c>
       <c r="U317" t="n">
-        <v>0.779457462656308</v>
+        <v>0.779455132682294</v>
       </c>
       <c r="V317" t="n">
-        <v>14.1252070972309</v>
+        <v>14.1255456056868</v>
       </c>
       <c r="W317" t="n">
         <v>1.90479722352779</v>
@@ -41532,16 +41532,16 @@
         <v>17.3656897559533</v>
       </c>
       <c r="Y317" t="n">
-        <v>0.939198921928552</v>
+        <v>0.939196512970386</v>
       </c>
       <c r="Z317" t="n">
-        <v>14.5785644691908</v>
+        <v>14.5788556188671</v>
       </c>
       <c r="AA317" t="n">
-        <v>0.856692553026542</v>
+        <v>0.856692917176774</v>
       </c>
       <c r="AB317" t="n">
-        <v>0.143307446973458</v>
+        <v>0.143307082823226</v>
       </c>
     </row>
     <row r="318">
@@ -41549,13 +41549,13 @@
         <v>44682</v>
       </c>
       <c r="B318" t="n">
-        <v>62035.3533357207</v>
+        <v>55316.816031342</v>
       </c>
       <c r="C318" t="n">
         <v>3016.1436</v>
       </c>
       <c r="D318" t="n">
-        <v>119557.505286598</v>
+        <v>123530.828440787</v>
       </c>
       <c r="E318" t="n">
         <v>30598.601441</v>
@@ -41564,52 +41564,52 @@
         <v>86760.52349114</v>
       </c>
       <c r="G318" t="n">
-        <v>207342.586799492</v>
+        <v>209531.927273497</v>
       </c>
       <c r="H318" t="n">
-        <v>75179.981141</v>
+        <v>75211.2297511677</v>
       </c>
       <c r="I318" t="n">
         <v>28761.8233561185</v>
       </c>
       <c r="J318" t="n">
-        <v>60329.83180258</v>
+        <v>60329.9973090659</v>
       </c>
       <c r="K318" t="n">
-        <v>279708.803989455</v>
+        <v>279708.670470315</v>
       </c>
       <c r="L318" t="n">
-        <v>29237.91604823</v>
+        <v>29238.5337781397</v>
       </c>
       <c r="M318" t="n">
-        <v>44236.291465</v>
+        <v>44309.1111760278</v>
       </c>
       <c r="N318" t="n">
-        <v>413145.830919373</v>
+        <v>413119.77961467</v>
       </c>
       <c r="O318" t="n">
         <v>60142.33963</v>
       </c>
       <c r="P318" t="n">
-        <v>353003.491289373</v>
+        <v>352977.43998467</v>
       </c>
       <c r="Q318" t="n">
-        <v>82531.4210982901</v>
+        <v>83039.4991527188</v>
       </c>
       <c r="R318" t="n">
-        <v>1654530.60394537</v>
+        <v>1654535.42375266</v>
       </c>
       <c r="S318" t="n">
         <v>281057.840748</v>
       </c>
       <c r="T318" t="n">
-        <v>1935588.44469337</v>
+        <v>1935593.26450066</v>
       </c>
       <c r="U318" t="n">
-        <v>1.81999555143004</v>
+        <v>1.81999015313048</v>
       </c>
       <c r="V318" t="n">
-        <v>14.6659639040573</v>
+        <v>14.6662979370738</v>
       </c>
       <c r="W318" t="n">
         <v>3.39754017845222</v>
@@ -41618,16 +41618,16 @@
         <v>19.7147481805512</v>
       </c>
       <c r="Y318" t="n">
-        <v>2.0460694444153</v>
+        <v>2.04606424526705</v>
       </c>
       <c r="Z318" t="n">
-        <v>15.3724832911907</v>
+        <v>15.3727705801221</v>
       </c>
       <c r="AA318" t="n">
-        <v>0.854794627691361</v>
+        <v>0.854794989266246</v>
       </c>
       <c r="AB318" t="n">
-        <v>0.145205372308639</v>
+        <v>0.145205010733754</v>
       </c>
     </row>
     <row r="319">
@@ -41635,13 +41635,13 @@
         <v>44713</v>
       </c>
       <c r="B319" t="n">
-        <v>62387.7895519757</v>
+        <v>54548.499239595</v>
       </c>
       <c r="C319" t="n">
         <v>3339.735301</v>
       </c>
       <c r="D319" t="n">
-        <v>121261.461775464</v>
+        <v>125966.60744254</v>
       </c>
       <c r="E319" t="n">
         <v>32041.873818</v>
@@ -41650,52 +41650,52 @@
         <v>88870.89337714</v>
       </c>
       <c r="G319" t="n">
-        <v>212945.846370579</v>
+        <v>215538.428308989</v>
       </c>
       <c r="H319" t="n">
-        <v>77665.76672</v>
+        <v>77702.7708238766</v>
       </c>
       <c r="I319" t="n">
         <v>28408.448078981</v>
       </c>
       <c r="J319" t="n">
-        <v>59834.07078458</v>
+        <v>59834.2667747109</v>
       </c>
       <c r="K319" t="n">
-        <v>283523.810542522</v>
+        <v>283523.736007522</v>
       </c>
       <c r="L319" t="n">
-        <v>29772.80719123</v>
+        <v>29773.5386970993</v>
       </c>
       <c r="M319" t="n">
-        <v>45371.846148</v>
+        <v>45276.8355336994</v>
       </c>
       <c r="N319" t="n">
-        <v>421042.560620673</v>
+        <v>421073.930528191</v>
       </c>
       <c r="O319" t="n">
         <v>60877.840124</v>
       </c>
       <c r="P319" t="n">
-        <v>360164.720496673</v>
+        <v>360196.090404191</v>
       </c>
       <c r="Q319" t="n">
-        <v>84454.0743447733</v>
+        <v>85104.9927736929</v>
       </c>
       <c r="R319" t="n">
-        <v>1678914.47869159</v>
+        <v>1679029.42067923</v>
       </c>
       <c r="S319" t="n">
         <v>293049.066554</v>
       </c>
       <c r="T319" t="n">
-        <v>1971963.54524559</v>
+        <v>1972078.48723323</v>
       </c>
       <c r="U319" t="n">
-        <v>1.47376389944525</v>
+        <v>1.48041538276724</v>
       </c>
       <c r="V319" t="n">
-        <v>14.996387585435</v>
+        <v>15.0042604780259</v>
       </c>
       <c r="W319" t="n">
         <v>4.26646194039164</v>
@@ -41704,16 +41704,16 @@
         <v>22.7852461933471</v>
       </c>
       <c r="Y319" t="n">
-        <v>1.87927865822648</v>
+        <v>1.88496330307184</v>
       </c>
       <c r="Z319" t="n">
-        <v>16.0907641006653</v>
+        <v>16.0975308095145</v>
       </c>
       <c r="AA319" t="n">
-        <v>0.851392249486284</v>
+        <v>0.851400911043282</v>
       </c>
       <c r="AB319" t="n">
-        <v>0.148607750513716</v>
+        <v>0.148599088956718</v>
       </c>
     </row>
     <row r="320">
@@ -41721,13 +41721,13 @@
         <v>44743</v>
       </c>
       <c r="B320" t="n">
-        <v>62365.2764381016</v>
+        <v>54160.253295989</v>
       </c>
       <c r="C320" t="n">
         <v>3436.997793</v>
       </c>
       <c r="D320" t="n">
-        <v>121616.116244675</v>
+        <v>126391.780859079</v>
       </c>
       <c r="E320" t="n">
         <v>32685.603062</v>
@@ -41736,52 +41736,52 @@
         <v>89664.14552314</v>
       </c>
       <c r="G320" t="n">
-        <v>217662.352587013</v>
+        <v>220293.791164961</v>
       </c>
       <c r="H320" t="n">
-        <v>78577.98496</v>
+        <v>78615.5436674185</v>
       </c>
       <c r="I320" t="n">
         <v>29027.4446516128</v>
       </c>
       <c r="J320" t="n">
-        <v>61348.16475958</v>
+        <v>61348.363687137</v>
       </c>
       <c r="K320" t="n">
-        <v>287216.423924145</v>
+        <v>287216.371756145</v>
       </c>
       <c r="L320" t="n">
-        <v>30354.08258523</v>
+        <v>30354.8250546331</v>
       </c>
       <c r="M320" t="n">
-        <v>47235.089684</v>
+        <v>47410.6364722354</v>
       </c>
       <c r="N320" t="n">
-        <v>429295.091251454</v>
+        <v>429330.941105179</v>
       </c>
       <c r="O320" t="n">
         <v>62329.819894</v>
       </c>
       <c r="P320" t="n">
-        <v>366965.271357454</v>
+        <v>367001.121211179</v>
       </c>
       <c r="Q320" t="n">
-        <v>83461.2602970882</v>
+        <v>84067.4137447353</v>
       </c>
       <c r="R320" t="n">
-        <v>1702003.67084549</v>
+        <v>1702097.59877544</v>
       </c>
       <c r="S320" t="n">
         <v>301237.454167</v>
       </c>
       <c r="T320" t="n">
-        <v>2003241.12501249</v>
+        <v>2003335.05294244</v>
       </c>
       <c r="U320" t="n">
-        <v>1.37524528181425</v>
+        <v>1.37389957627334</v>
       </c>
       <c r="V320" t="n">
-        <v>16.0512544812111</v>
+        <v>16.0576589645199</v>
       </c>
       <c r="W320" t="n">
         <v>2.79420361555429</v>
@@ -41790,16 +41790,16 @@
         <v>21.9254441578109</v>
       </c>
       <c r="Y320" t="n">
-        <v>1.58611348786406</v>
+        <v>1.58495546255204</v>
       </c>
       <c r="Z320" t="n">
-        <v>16.8981640720886</v>
+        <v>16.9036451908762</v>
       </c>
       <c r="AA320" t="n">
-        <v>0.849624965059999</v>
+        <v>0.84963201551106</v>
       </c>
       <c r="AB320" t="n">
-        <v>0.150375034940001</v>
+        <v>0.15036798448894</v>
       </c>
     </row>
     <row r="321">
@@ -41807,13 +41807,13 @@
         <v>44774</v>
       </c>
       <c r="B321" t="n">
-        <v>62607.9427573849</v>
+        <v>54516.2168351685</v>
       </c>
       <c r="C321" t="n">
         <v>3397.6616</v>
       </c>
       <c r="D321" t="n">
-        <v>120374.886859805</v>
+        <v>125171.884143127</v>
       </c>
       <c r="E321" t="n">
         <v>35512.612282</v>
@@ -41822,52 +41822,52 @@
         <v>84297.50612114</v>
       </c>
       <c r="G321" t="n">
-        <v>223355.130031731</v>
+        <v>225998.323121876</v>
       </c>
       <c r="H321" t="n">
-        <v>78381.604223</v>
+        <v>78419.3307033957</v>
       </c>
       <c r="I321" t="n">
         <v>30244.6131245909</v>
       </c>
       <c r="J321" t="n">
-        <v>62788.08905058</v>
+        <v>62788.2888667371</v>
       </c>
       <c r="K321" t="n">
-        <v>292424.505731569</v>
+        <v>292424.44863057</v>
       </c>
       <c r="L321" t="n">
-        <v>30742.99537723</v>
+        <v>30743.741163209</v>
       </c>
       <c r="M321" t="n">
-        <v>48877.262599</v>
+        <v>48926.384704577</v>
       </c>
       <c r="N321" t="n">
-        <v>437016.697235</v>
+        <v>437055.361683373</v>
       </c>
       <c r="O321" t="n">
         <v>64244.414608</v>
       </c>
       <c r="P321" t="n">
-        <v>372772.282627</v>
+        <v>372810.947075373</v>
       </c>
       <c r="Q321" t="n">
-        <v>84445.1732215086</v>
+        <v>85054.1735920519</v>
       </c>
       <c r="R321" t="n">
-        <v>1719524.67341054</v>
+        <v>1719647.20421619</v>
       </c>
       <c r="S321" t="n">
         <v>311958.704039</v>
       </c>
       <c r="T321" t="n">
-        <v>2031483.37744954</v>
+        <v>2031605.90825519</v>
       </c>
       <c r="U321" t="n">
-        <v>1.02943388813854</v>
+        <v>1.0310575288615</v>
       </c>
       <c r="V321" t="n">
-        <v>16.1782399917979</v>
+        <v>16.1865186827438</v>
       </c>
       <c r="W321" t="n">
         <v>3.55906934004839</v>
@@ -41876,16 +41876,16 @@
         <v>25.862031708732</v>
       </c>
       <c r="Y321" t="n">
-        <v>1.40982790760495</v>
+        <v>1.41118956967392</v>
       </c>
       <c r="Z321" t="n">
-        <v>17.567300235875</v>
+        <v>17.5743914167214</v>
       </c>
       <c r="AA321" t="n">
-        <v>0.846437973600033</v>
+        <v>0.846447235277574</v>
       </c>
       <c r="AB321" t="n">
-        <v>0.153562026399967</v>
+        <v>0.153552764722426</v>
       </c>
     </row>
     <row r="322">
@@ -41893,13 +41893,13 @@
         <v>44805</v>
       </c>
       <c r="B322" t="n">
-        <v>62804.9753541374</v>
+        <v>54742.8136785258</v>
       </c>
       <c r="C322" t="n">
         <v>3798.460005</v>
       </c>
       <c r="D322" t="n">
-        <v>114919.643820101</v>
+        <v>119627.914176783</v>
       </c>
       <c r="E322" t="n">
         <v>36189.776506</v>
@@ -41908,52 +41908,52 @@
         <v>86400.14876</v>
       </c>
       <c r="G322" t="n">
-        <v>230855.158921852</v>
+        <v>233449.462595232</v>
       </c>
       <c r="H322" t="n">
-        <v>79163.43139</v>
+        <v>79200.4600683206</v>
       </c>
       <c r="I322" t="n">
         <v>30544.1119120083</v>
       </c>
       <c r="J322" t="n">
-        <v>62656.378634</v>
+        <v>62656.5747542881</v>
       </c>
       <c r="K322" t="n">
-        <v>296443.337254835</v>
+        <v>296443.285086835</v>
       </c>
       <c r="L322" t="n">
-        <v>31198.76896</v>
+        <v>31199.5009516627</v>
       </c>
       <c r="M322" t="n">
-        <v>50401.743505</v>
+        <v>50567.3542726374</v>
       </c>
       <c r="N322" t="n">
-        <v>445537.338794872</v>
+        <v>445565.816684563</v>
       </c>
       <c r="O322" t="n">
         <v>65773.067975</v>
       </c>
       <c r="P322" t="n">
-        <v>379764.270819872</v>
+        <v>379792.748709563</v>
       </c>
       <c r="Q322" t="n">
-        <v>85567.4240917834</v>
+        <v>86142.5210395142</v>
       </c>
       <c r="R322" t="n">
-        <v>1740988.25639646</v>
+        <v>1741064.23686793</v>
       </c>
       <c r="S322" t="n">
         <v>321029.780308</v>
       </c>
       <c r="T322" t="n">
-        <v>2062018.03670446</v>
+        <v>2062094.01717593</v>
       </c>
       <c r="U322" t="n">
-        <v>1.24822768279047</v>
+        <v>1.24543177224001</v>
       </c>
       <c r="V322" t="n">
-        <v>16.4006939047954</v>
+        <v>16.4057738813949</v>
       </c>
       <c r="W322" t="n">
         <v>2.90778111062608</v>
@@ -41962,16 +41962,16 @@
         <v>29.3046222061123</v>
       </c>
       <c r="Y322" t="n">
-        <v>1.50307207008793</v>
+        <v>1.50069010908367</v>
       </c>
       <c r="Z322" t="n">
-        <v>18.2377263347827</v>
+        <v>18.2420831144194</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.844312816574062</v>
+        <v>0.844318553065949</v>
       </c>
       <c r="AB322" t="n">
-        <v>0.155687183425938</v>
+        <v>0.155681446934051</v>
       </c>
     </row>
     <row r="323">
@@ -41979,13 +41979,13 @@
         <v>44835</v>
       </c>
       <c r="B323" t="n">
-        <v>63071.8906228081</v>
+        <v>54838.1374500293</v>
       </c>
       <c r="C323" t="n">
         <v>4001.717958</v>
       </c>
       <c r="D323" t="n">
-        <v>120047.152322909</v>
+        <v>124852.539164</v>
       </c>
       <c r="E323" t="n">
         <v>35492.682164</v>
@@ -41994,52 +41994,52 @@
         <v>86292.555056</v>
       </c>
       <c r="G323" t="n">
-        <v>232820.011463036</v>
+        <v>235467.827282738</v>
       </c>
       <c r="H323" t="n">
-        <v>79274.196984</v>
+        <v>79311.9894449389</v>
       </c>
       <c r="I323" t="n">
         <v>31200.1514017623</v>
       </c>
       <c r="J323" t="n">
-        <v>62492.651924</v>
+        <v>62492.8520896192</v>
       </c>
       <c r="K323" t="n">
-        <v>299908.973433703</v>
+        <v>299908.926247703</v>
       </c>
       <c r="L323" t="n">
-        <v>30463.375736</v>
+        <v>30464.122826298</v>
       </c>
       <c r="M323" t="n">
-        <v>51447.444839</v>
+        <v>51635.6377146828</v>
       </c>
       <c r="N323" t="n">
-        <v>454006.897549817</v>
+        <v>454055.796049339</v>
       </c>
       <c r="O323" t="n">
         <v>67776.563931</v>
       </c>
       <c r="P323" t="n">
-        <v>386230.333618817</v>
+        <v>386279.232118339</v>
       </c>
       <c r="Q323" t="n">
-        <v>88348.1204846508</v>
+        <v>88900.015277027</v>
       </c>
       <c r="R323" t="n">
-        <v>1761050.8122655</v>
+        <v>1761146.83895148</v>
       </c>
       <c r="S323" t="n">
         <v>331823.907224</v>
       </c>
       <c r="T323" t="n">
-        <v>2092874.7194895</v>
+        <v>2092970.74617548</v>
       </c>
       <c r="U323" t="n">
-        <v>1.15236595050716</v>
+        <v>1.15346703804962</v>
       </c>
       <c r="V323" t="n">
-        <v>16.643537771693</v>
+        <v>16.6498981176265</v>
       </c>
       <c r="W323" t="n">
         <v>3.36234442351238</v>
@@ -42048,16 +42048,16 @@
         <v>31.5009527851203</v>
       </c>
       <c r="Y323" t="n">
-        <v>1.49643127440129</v>
+        <v>1.49734826551837</v>
       </c>
       <c r="Z323" t="n">
-        <v>18.7711364307553</v>
+        <v>18.7765859679467</v>
       </c>
       <c r="AA323" t="n">
-        <v>0.841450659165619</v>
+        <v>0.841457933499382</v>
       </c>
       <c r="AB323" t="n">
-        <v>0.158549340834381</v>
+        <v>0.158542066500618</v>
       </c>
     </row>
     <row r="324">
@@ -42065,13 +42065,13 @@
         <v>44866</v>
       </c>
       <c r="B324" t="n">
-        <v>64022.5505953227</v>
+        <v>55552.3508663087</v>
       </c>
       <c r="C324" t="n">
         <v>4189.60955967</v>
       </c>
       <c r="D324" t="n">
-        <v>120817.215540406</v>
+        <v>125746.310394769</v>
       </c>
       <c r="E324" t="n">
         <v>35726.64306728</v>
@@ -42080,52 +42080,52 @@
         <v>87050.52811038</v>
       </c>
       <c r="G324" t="n">
-        <v>238381.826525611</v>
+        <v>241097.806687831</v>
       </c>
       <c r="H324" t="n">
-        <v>80375.4433986</v>
+        <v>80414.2087739814</v>
       </c>
       <c r="I324" t="n">
         <v>31688.6038252217</v>
       </c>
       <c r="J324" t="n">
-        <v>62931.36618875</v>
+        <v>62931.5715073552</v>
       </c>
       <c r="K324" t="n">
-        <v>304073.367457054</v>
+        <v>304073.325303054</v>
       </c>
       <c r="L324" t="n">
-        <v>30553.5810255</v>
+        <v>30554.3473486006</v>
       </c>
       <c r="M324" t="n">
-        <v>53459.44929427</v>
+        <v>53645.1065357086</v>
       </c>
       <c r="N324" t="n">
-        <v>467305.251387952</v>
+        <v>467365.052578717</v>
       </c>
       <c r="O324" t="n">
         <v>73328.01964821</v>
       </c>
       <c r="P324" t="n">
-        <v>393977.231739742</v>
+        <v>394037.032930507</v>
       </c>
       <c r="Q324" t="n">
-        <v>88096.748813383</v>
+        <v>88683.2020186275</v>
       </c>
       <c r="R324" t="n">
-        <v>1793198.39880701</v>
+        <v>1793304.68178588</v>
       </c>
       <c r="S324" t="n">
         <v>342779.03737034</v>
       </c>
       <c r="T324" t="n">
-        <v>2135977.43617735</v>
+        <v>2136083.71915622</v>
       </c>
       <c r="U324" t="n">
-        <v>1.82547751135886</v>
+        <v>1.82596034147562</v>
       </c>
       <c r="V324" t="n">
-        <v>16.607393800604</v>
+        <v>16.6143051279728</v>
       </c>
       <c r="W324" t="n">
         <v>3.30148910546841</v>
@@ -42134,16 +42134,16 @@
         <v>31.1805586483905</v>
       </c>
       <c r="Y324" t="n">
-        <v>2.05949817666884</v>
+        <v>2.05989372090014</v>
       </c>
       <c r="Z324" t="n">
-        <v>18.7240022434615</v>
+        <v>18.7299097687041</v>
       </c>
       <c r="AA324" t="n">
-        <v>0.839521227347891</v>
+        <v>0.839529212129503</v>
       </c>
       <c r="AB324" t="n">
-        <v>0.160478772652109</v>
+        <v>0.160470787870497</v>
       </c>
     </row>
     <row r="325">
@@ -42151,13 +42151,13 @@
         <v>44896</v>
       </c>
       <c r="B325" t="n">
-        <v>64055.7602851346</v>
+        <v>55680.284894821</v>
       </c>
       <c r="C325" t="n">
         <v>4189.5002289</v>
       </c>
       <c r="D325" t="n">
-        <v>123373.511138676</v>
+        <v>128318.648595272</v>
       </c>
       <c r="E325" t="n">
         <v>35527.31431429</v>
@@ -42166,52 +42166,52 @@
         <v>87157.09103496</v>
       </c>
       <c r="G325" t="n">
-        <v>237064.883501782</v>
+        <v>239789.703296977</v>
       </c>
       <c r="H325" t="n">
-        <v>81480.66083823</v>
+        <v>81519.5523823129</v>
       </c>
       <c r="I325" t="n">
         <v>32063.1061748284</v>
       </c>
       <c r="J325" t="n">
-        <v>65312.76203509</v>
+        <v>65312.9680219406</v>
       </c>
       <c r="K325" t="n">
-        <v>306627.003205703</v>
+        <v>306626.966130703</v>
       </c>
       <c r="L325" t="n">
-        <v>31900.42639778</v>
+        <v>31901.1952150133</v>
       </c>
       <c r="M325" t="n">
-        <v>54780.71419277</v>
+        <v>54887.9276673326</v>
       </c>
       <c r="N325" t="n">
-        <v>467605.507805088</v>
+        <v>467625.95442717</v>
       </c>
       <c r="O325" t="n">
         <v>70652.67624779</v>
       </c>
       <c r="P325" t="n">
-        <v>396952.831557298</v>
+        <v>396973.27817938</v>
       </c>
       <c r="Q325" t="n">
-        <v>88235.9772213212</v>
+        <v>88794.6581565029</v>
       </c>
       <c r="R325" t="n">
-        <v>1797110.55706986</v>
+        <v>1797151.65585841</v>
       </c>
       <c r="S325" t="n">
         <v>349869.16910978</v>
       </c>
       <c r="T325" t="n">
-        <v>2146979.72617964</v>
+        <v>2147020.82496819</v>
       </c>
       <c r="U325" t="n">
-        <v>0.218166504356199</v>
+        <v>0.214518710155898</v>
       </c>
       <c r="V325" t="n">
-        <v>16.4339048973577</v>
+        <v>16.4365676675579</v>
       </c>
       <c r="W325" t="n">
         <v>2.06842629404427</v>
@@ -42220,16 +42220,16 @@
         <v>28.9253430766853</v>
       </c>
       <c r="Y325" t="n">
-        <v>0.515093924492893</v>
+        <v>0.512016720781561</v>
       </c>
       <c r="Z325" t="n">
-        <v>18.3017595630288</v>
+        <v>18.3040241670875</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.837041232926619</v>
+        <v>0.837044352322496</v>
       </c>
       <c r="AB325" t="n">
-        <v>0.162958767073381</v>
+        <v>0.162955647677504</v>
       </c>
     </row>
     <row r="326">
@@ -42237,13 +42237,13 @@
         <v>44927</v>
       </c>
       <c r="B326" t="n">
-        <v>59371.8055340402</v>
+        <v>51053.3612685873</v>
       </c>
       <c r="C326" t="n">
         <v>4808.16031675</v>
       </c>
       <c r="D326" t="n">
-        <v>122345.671989556</v>
+        <v>127286.581830255</v>
       </c>
       <c r="E326" t="n">
         <v>35396.0294751</v>
@@ -42252,52 +42252,52 @@
         <v>87431.24651272</v>
       </c>
       <c r="G326" t="n">
-        <v>236931.408200642</v>
+        <v>239653.898537539</v>
       </c>
       <c r="H326" t="n">
-        <v>78648.05973497</v>
+        <v>78686.9180305312</v>
       </c>
       <c r="I326" t="n">
         <v>32473.7981358284</v>
       </c>
       <c r="J326" t="n">
-        <v>66040.63454885</v>
+        <v>66040.8403596017</v>
       </c>
       <c r="K326" t="n">
-        <v>308727.189613053</v>
+        <v>308727.157671053</v>
       </c>
       <c r="L326" t="n">
-        <v>34610.51770819</v>
+        <v>34611.2858681586</v>
       </c>
       <c r="M326" t="n">
-        <v>56820.92656797</v>
+        <v>56926.6483927774</v>
       </c>
       <c r="N326" t="n">
-        <v>474834.356468918</v>
+        <v>474878.430821528</v>
       </c>
       <c r="O326" t="n">
         <v>71176.02520721</v>
       </c>
       <c r="P326" t="n">
-        <v>403658.331261708</v>
+        <v>403702.405614318</v>
       </c>
       <c r="Q326" t="n">
-        <v>88405.4739274312</v>
+        <v>88891.9951713034</v>
       </c>
       <c r="R326" t="n">
-        <v>1810876.40492429</v>
+        <v>1810941.55293461</v>
       </c>
       <c r="S326" t="n">
         <v>350803.23027865</v>
       </c>
       <c r="T326" t="n">
-        <v>2161679.63520294</v>
+        <v>2161744.78321326</v>
       </c>
       <c r="U326" t="n">
-        <v>0.76599894203897</v>
+        <v>0.767319609964123</v>
       </c>
       <c r="V326" t="n">
-        <v>16.0456283144632</v>
+        <v>16.0494447300088</v>
       </c>
       <c r="W326" t="n">
         <v>0.266974415392673</v>
@@ -42306,16 +42306,16 @@
         <v>28.2410900917045</v>
       </c>
       <c r="Y326" t="n">
-        <v>0.684678520437276</v>
+        <v>0.685785534720429</v>
       </c>
       <c r="Z326" t="n">
-        <v>17.8646031856621</v>
+        <v>17.8678455973059</v>
       </c>
       <c r="AA326" t="n">
-        <v>0.83771728957158</v>
+        <v>0.837722180248674</v>
       </c>
       <c r="AB326" t="n">
-        <v>0.16228271042842</v>
+        <v>0.162277819751326</v>
       </c>
     </row>
     <row r="327">
@@ -42323,13 +42323,13 @@
         <v>44958</v>
       </c>
       <c r="B327" t="n">
-        <v>59094.2040670098</v>
+        <v>50870.0446823573</v>
       </c>
       <c r="C327" t="n">
         <v>4760.009642</v>
       </c>
       <c r="D327" t="n">
-        <v>118721.318964155</v>
+        <v>123653.153329244</v>
       </c>
       <c r="E327" t="n">
         <v>34968.697149</v>
@@ -42338,52 +42338,52 @@
         <v>89523.259123</v>
       </c>
       <c r="G327" t="n">
-        <v>238409.224211766</v>
+        <v>241126.713871572</v>
       </c>
       <c r="H327" t="n">
-        <v>77442.021086</v>
+        <v>77480.8080065463</v>
       </c>
       <c r="I327" t="n">
         <v>32025.2646905055</v>
       </c>
       <c r="J327" t="n">
-        <v>67507.32362</v>
+        <v>67507.529052718</v>
       </c>
       <c r="K327" t="n">
         <v>311957.939422696</v>
       </c>
       <c r="L327" t="n">
-        <v>34750.303148</v>
+        <v>34751.0698970105</v>
       </c>
       <c r="M327" t="n">
-        <v>58660.051077</v>
+        <v>58728.3660049674</v>
       </c>
       <c r="N327" t="n">
-        <v>481478.90757438</v>
+        <v>481511.490664279</v>
       </c>
       <c r="O327" t="n">
         <v>72475.559153</v>
       </c>
       <c r="P327" t="n">
-        <v>409003.34842138</v>
+        <v>409035.931511279</v>
       </c>
       <c r="Q327" t="n">
-        <v>89604.8855759717</v>
+        <v>90060.5684175926</v>
       </c>
       <c r="R327" t="n">
-        <v>1834363.27837986</v>
+        <v>1834417.36607177</v>
       </c>
       <c r="S327" t="n">
         <v>346019.038546</v>
       </c>
       <c r="T327" t="n">
-        <v>2180382.31692586</v>
+        <v>2180436.40461777</v>
       </c>
       <c r="U327" t="n">
-        <v>1.29698931366653</v>
+        <v>1.29633190530722</v>
       </c>
       <c r="V327" t="n">
-        <v>15.7757370949577</v>
+        <v>15.7787986353759</v>
       </c>
       <c r="W327" t="n">
         <v>-1.36378212049241</v>
@@ -42392,16 +42392,16 @@
         <v>34.0540718214504</v>
       </c>
       <c r="Y327" t="n">
-        <v>0.865192113500712</v>
+        <v>0.864654400910525</v>
       </c>
       <c r="Z327" t="n">
-        <v>18.3363391510711</v>
+        <v>18.3389651048958</v>
       </c>
       <c r="AA327" t="n">
-        <v>0.841303501748329</v>
+        <v>0.841307438358122</v>
       </c>
       <c r="AB327" t="n">
-        <v>0.158696498251671</v>
+        <v>0.158692561641878</v>
       </c>
     </row>
     <row r="328">
@@ -42409,13 +42409,13 @@
         <v>44986</v>
       </c>
       <c r="B328" t="n">
-        <v>58457.7086814553</v>
+        <v>50349.3008854772</v>
       </c>
       <c r="C328" t="n">
         <v>4774.23830511</v>
       </c>
       <c r="D328" t="n">
-        <v>118498.15248464</v>
+        <v>123442.232567556</v>
       </c>
       <c r="E328" t="n">
         <v>36267.39931458</v>
@@ -42424,52 +42424,52 @@
         <v>91291.28418439</v>
       </c>
       <c r="G328" t="n">
-        <v>245347.07063997</v>
+        <v>248071.307811779</v>
       </c>
       <c r="H328" t="n">
-        <v>75053.89433261</v>
+        <v>75092.7775608685</v>
       </c>
       <c r="I328" t="n">
         <v>31656.9011918792</v>
       </c>
       <c r="J328" t="n">
-        <v>69703.72463315</v>
+        <v>69703.9305759563</v>
       </c>
       <c r="K328" t="n">
         <v>316897.81103141</v>
       </c>
       <c r="L328" t="n">
-        <v>35112.59590065</v>
+        <v>35113.3645534941</v>
       </c>
       <c r="M328" t="n">
-        <v>60332.71536325</v>
+        <v>60334.3670268745</v>
       </c>
       <c r="N328" t="n">
-        <v>487326.515728954</v>
+        <v>487324.456526539</v>
       </c>
       <c r="O328" t="n">
         <v>71730.31727735</v>
       </c>
       <c r="P328" t="n">
-        <v>415596.198451604</v>
+        <v>415594.139249189</v>
       </c>
       <c r="Q328" t="n">
-        <v>91762.0501310279</v>
+        <v>92184.4590411835</v>
       </c>
       <c r="R328" t="n">
-        <v>1859625.70369352</v>
+        <v>1859645.41314513</v>
       </c>
       <c r="S328" t="n">
         <v>350182.87395851</v>
       </c>
       <c r="T328" t="n">
-        <v>2209808.57765203</v>
+        <v>2209828.28710364</v>
       </c>
       <c r="U328" t="n">
-        <v>1.37717678997424</v>
+        <v>1.37526211537031</v>
       </c>
       <c r="V328" t="n">
-        <v>15.3335939356977</v>
+        <v>15.3344715499694</v>
       </c>
       <c r="W328" t="n">
         <v>1.20335442523822</v>
@@ -42478,16 +42478,16 @@
         <v>31.2816520988632</v>
       </c>
       <c r="Y328" t="n">
-        <v>1.34959178937282</v>
+        <v>1.3479816436573</v>
       </c>
       <c r="Z328" t="n">
-        <v>17.5974134257065</v>
+        <v>17.59816065687</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.84153248498538</v>
+        <v>0.841533898356652</v>
       </c>
       <c r="AB328" t="n">
-        <v>0.15846751501462</v>
+        <v>0.158466101643348</v>
       </c>
     </row>
     <row r="329">
@@ -42552,10 +42552,10 @@
         <v>2234358.60840149</v>
       </c>
       <c r="U329" t="n">
-        <v>1.12031738486689</v>
+        <v>1.1192456611997</v>
       </c>
       <c r="V329" t="n">
-        <v>15.7236793841311</v>
+        <v>15.7233361354411</v>
       </c>
       <c r="W329" t="n">
         <v>1.0612514128741</v>
@@ -42564,10 +42564,10 @@
         <v>30.194931054703</v>
       </c>
       <c r="Y329" t="n">
-        <v>1.11095734706326</v>
+        <v>1.11005553874979</v>
       </c>
       <c r="Z329" t="n">
-        <v>17.7975175155511</v>
+        <v>17.79721818712</v>
       </c>
       <c r="AA329" t="n">
         <v>0.841610387282807</v>
@@ -42581,13 +42581,13 @@
         <v>45047</v>
       </c>
       <c r="B330" t="n">
-        <v>59332.7775534677</v>
+        <v>50887.9583563286</v>
       </c>
       <c r="C330" t="n">
         <v>4883.710808</v>
       </c>
       <c r="D330" t="n">
-        <v>122834.211100723</v>
+        <v>127955.566193593</v>
       </c>
       <c r="E330" t="n">
         <v>36789.346255</v>
@@ -42596,52 +42596,52 @@
         <v>93610.49583814</v>
       </c>
       <c r="G330" t="n">
-        <v>253645.976769588</v>
+        <v>256467.894230479</v>
       </c>
       <c r="H330" t="n">
-        <v>74244.190984</v>
+        <v>74284.4684098768</v>
       </c>
       <c r="I330" t="n">
         <v>31475.0252350713</v>
       </c>
       <c r="J330" t="n">
-        <v>69716.873592</v>
+        <v>69717.0869190947</v>
       </c>
       <c r="K330" t="n">
         <v>324645.955466881</v>
       </c>
       <c r="L330" t="n">
-        <v>35988.356257</v>
+        <v>35989.152470672</v>
       </c>
       <c r="M330" t="n">
-        <v>62308.273573</v>
+        <v>62384.3757074063</v>
       </c>
       <c r="N330" t="n">
-        <v>503647.545147007</v>
+        <v>503647.206393066</v>
       </c>
       <c r="O330" t="n">
         <v>75813.881765</v>
       </c>
       <c r="P330" t="n">
-        <v>427833.663382007</v>
+        <v>427833.324628066</v>
       </c>
       <c r="Q330" t="n">
-        <v>95155.5484280226</v>
+        <v>95546.1546815455</v>
       </c>
       <c r="R330" t="n">
-        <v>1911442.04413091</v>
+        <v>1911447.81533422</v>
       </c>
       <c r="S330" t="n">
         <v>360483.788024</v>
       </c>
       <c r="T330" t="n">
-        <v>2271925.83215491</v>
+        <v>2271931.60335822</v>
       </c>
       <c r="U330" t="n">
-        <v>1.6476096298055</v>
+        <v>1.64791653370735</v>
       </c>
       <c r="V330" t="n">
-        <v>15.527753888197</v>
+        <v>15.5277661567896</v>
       </c>
       <c r="W330" t="n">
         <v>1.86058444534238</v>
@@ -42650,16 +42650,16 @@
         <v>28.259644728152</v>
       </c>
       <c r="Y330" t="n">
-        <v>1.68134262835691</v>
+        <v>1.6816009218686</v>
       </c>
       <c r="Z330" t="n">
-        <v>17.3764928378056</v>
+        <v>17.3764987214051</v>
       </c>
       <c r="AA330" t="n">
-        <v>0.841331181272725</v>
+        <v>0.841331584326237</v>
       </c>
       <c r="AB330" t="n">
-        <v>0.158668818727275</v>
+        <v>0.158668415673763</v>
       </c>
     </row>
     <row r="331">
@@ -42667,13 +42667,13 @@
         <v>45078</v>
       </c>
       <c r="B331" t="n">
-        <v>60913.0509992767</v>
+        <v>52139.8189985152</v>
       </c>
       <c r="C331" t="n">
         <v>5436.19738317</v>
       </c>
       <c r="D331" t="n">
-        <v>129940.4963372</v>
+        <v>135228.109965993</v>
       </c>
       <c r="E331" t="n">
         <v>38488.3141894</v>
@@ -42682,52 +42682,52 @@
         <v>103142.07613795</v>
       </c>
       <c r="G331" t="n">
-        <v>273589.165625003</v>
+        <v>276502.693188501</v>
       </c>
       <c r="H331" t="n">
-        <v>78222.59327748</v>
+        <v>78264.1782607778</v>
       </c>
       <c r="I331" t="n">
         <v>32704.2347153109</v>
       </c>
       <c r="J331" t="n">
-        <v>73233.39601769</v>
+        <v>73233.6162701882</v>
       </c>
       <c r="K331" t="n">
         <v>328863.214975899</v>
       </c>
       <c r="L331" t="n">
-        <v>36516.48652541</v>
+        <v>36517.3085871861</v>
       </c>
       <c r="M331" t="n">
-        <v>66737.61411966</v>
+        <v>66852.4045071575</v>
       </c>
       <c r="N331" t="n">
-        <v>515264.661118221</v>
+        <v>515274.205515687</v>
       </c>
       <c r="O331" t="n">
         <v>77403.79127953</v>
       </c>
       <c r="P331" t="n">
-        <v>437860.869838691</v>
+        <v>437870.414236157</v>
       </c>
       <c r="Q331" t="n">
-        <v>96885.9355045209</v>
+        <v>97295.7847427785</v>
       </c>
       <c r="R331" t="n">
-        <v>1981423.50334287</v>
+        <v>1981437.76825266</v>
       </c>
       <c r="S331" t="n">
         <v>373778.59470154</v>
       </c>
       <c r="T331" t="n">
-        <v>2355202.09804441</v>
+        <v>2355216.3629542</v>
       </c>
       <c r="U331" t="n">
-        <v>3.66118655947969</v>
+        <v>3.6616198651598</v>
       </c>
       <c r="V331" t="n">
-        <v>18.0181318638119</v>
+        <v>18.0109022420286</v>
       </c>
       <c r="W331" t="n">
         <v>3.68804565398511</v>
@@ -42736,16 +42736,16 @@
         <v>27.5481267000262</v>
       </c>
       <c r="Y331" t="n">
-        <v>3.66544826027697</v>
+        <v>3.66581280320566</v>
       </c>
       <c r="Z331" t="n">
-        <v>19.434362958829</v>
+        <v>19.4281251076628</v>
       </c>
       <c r="AA331" t="n">
-        <v>0.841296594032462</v>
+        <v>0.841297555256154</v>
       </c>
       <c r="AB331" t="n">
-        <v>0.158703405967538</v>
+        <v>0.158702444743845</v>
       </c>
     </row>
     <row r="332">
@@ -42753,13 +42753,13 @@
         <v>45108</v>
       </c>
       <c r="B332" t="n">
-        <v>61290.8464709959</v>
+        <v>52392.2497194948</v>
       </c>
       <c r="C332" t="n">
         <v>4630.012584</v>
       </c>
       <c r="D332" t="n">
-        <v>130116.787446419</v>
+        <v>135478.07170587</v>
       </c>
       <c r="E332" t="n">
         <v>40919.795296</v>
@@ -42768,52 +42768,52 @@
         <v>111435.211581</v>
       </c>
       <c r="G332" t="n">
-        <v>274079.7695935</v>
+        <v>277033.890405316</v>
       </c>
       <c r="H332" t="n">
-        <v>79521.981454</v>
+        <v>79564.1458275786</v>
       </c>
       <c r="I332" t="n">
         <v>33129.1515374015</v>
       </c>
       <c r="J332" t="n">
-        <v>72931.560997</v>
+        <v>72931.7843182058</v>
       </c>
       <c r="K332" t="n">
         <v>333488.188171627</v>
       </c>
       <c r="L332" t="n">
-        <v>36978.717617</v>
+        <v>36979.5511323001</v>
       </c>
       <c r="M332" t="n">
-        <v>69015.906947</v>
+        <v>69129.0470336903</v>
       </c>
       <c r="N332" t="n">
-        <v>526347.089888982</v>
+        <v>526369.195490555</v>
       </c>
       <c r="O332" t="n">
         <v>80329.811074</v>
       </c>
       <c r="P332" t="n">
-        <v>446017.278814982</v>
+        <v>446039.384416555</v>
       </c>
       <c r="Q332" t="n">
-        <v>99619.2026346803</v>
+        <v>100028.058721675</v>
       </c>
       <c r="R332" t="n">
-        <v>2015197.40524059</v>
+        <v>2015223.64214727</v>
       </c>
       <c r="S332" t="n">
         <v>384653.906868</v>
       </c>
       <c r="T332" t="n">
-        <v>2399851.31210859</v>
+        <v>2399877.54901527</v>
       </c>
       <c r="U332" t="n">
-        <v>1.70452716649099</v>
+        <v>1.70511910270097</v>
       </c>
       <c r="V332" t="n">
-        <v>18.4014723211209</v>
+        <v>18.3964799431655</v>
       </c>
       <c r="W332" t="n">
         <v>2.90955991611661</v>
@@ -42822,16 +42822,16 @@
         <v>27.6912620084605</v>
       </c>
       <c r="Y332" t="n">
-        <v>1.89576996815901</v>
+        <v>1.89626680433927</v>
       </c>
       <c r="Z332" t="n">
-        <v>19.7984247699398</v>
+        <v>19.7941175885878</v>
       </c>
       <c r="AA332" t="n">
-        <v>0.839717608783841</v>
+        <v>0.839719361087472</v>
       </c>
       <c r="AB332" t="n">
-        <v>0.160282391216158</v>
+        <v>0.160280638912528</v>
       </c>
     </row>
     <row r="333">
@@ -42839,13 +42839,13 @@
         <v>45139</v>
       </c>
       <c r="B333" t="n">
-        <v>62333.62345642</v>
+        <v>53376.8619494601</v>
       </c>
       <c r="C333" t="n">
         <v>4870.425066</v>
       </c>
       <c r="D333" t="n">
-        <v>127066.271413687</v>
+        <v>132491.583769656</v>
       </c>
       <c r="E333" t="n">
         <v>41528.425931</v>
@@ -42854,52 +42854,52 @@
         <v>106210.534506</v>
       </c>
       <c r="G333" t="n">
-        <v>276122.150527114</v>
+        <v>279111.551455281</v>
       </c>
       <c r="H333" t="n">
-        <v>80859.598162</v>
+        <v>80902.2660911542</v>
       </c>
       <c r="I333" t="n">
         <v>34340.6406501273</v>
       </c>
       <c r="J333" t="n">
-        <v>75976.971063</v>
+        <v>75977.1970512593</v>
       </c>
       <c r="K333" t="n">
         <v>340547.95213893</v>
       </c>
       <c r="L333" t="n">
-        <v>37606.106285</v>
+        <v>37606.9497547057</v>
       </c>
       <c r="M333" t="n">
-        <v>71309.070086</v>
+        <v>71430.9152028874</v>
       </c>
       <c r="N333" t="n">
-        <v>534666.796824491</v>
+        <v>534685.412545399</v>
       </c>
       <c r="O333" t="n">
         <v>82557.472932</v>
       </c>
       <c r="P333" t="n">
-        <v>452109.323892491</v>
+        <v>452127.939613399</v>
       </c>
       <c r="Q333" t="n">
-        <v>101799.467560926</v>
+        <v>102161.024366522</v>
       </c>
       <c r="R333" t="n">
-        <v>2039992.23833619</v>
+        <v>2040014.56086478</v>
       </c>
       <c r="S333" t="n">
         <v>389912.592159</v>
       </c>
       <c r="T333" t="n">
-        <v>2429904.83049519</v>
+        <v>2429927.15302378</v>
       </c>
       <c r="U333" t="n">
-        <v>1.23039226981525</v>
+        <v>1.23018201052343</v>
       </c>
       <c r="V333" t="n">
-        <v>18.6369855507816</v>
+        <v>18.6298303432892</v>
       </c>
       <c r="W333" t="n">
         <v>1.36712124772584</v>
@@ -42908,16 +42908,16 @@
         <v>24.9885280040958</v>
       </c>
       <c r="Y333" t="n">
-        <v>1.25230751734331</v>
+        <v>1.25213071895443</v>
       </c>
       <c r="Z333" t="n">
-        <v>19.612341280678</v>
+        <v>19.60622594914</v>
       </c>
       <c r="AA333" t="n">
-        <v>0.839535858661781</v>
+        <v>0.839537332765801</v>
       </c>
       <c r="AB333" t="n">
-        <v>0.160464141338219</v>
+        <v>0.160462667234199</v>
       </c>
     </row>
     <row r="334">
@@ -42925,13 +42925,13 @@
         <v>45170</v>
       </c>
       <c r="B334" t="n">
-        <v>61651.8189607785</v>
+        <v>52888.1739259939</v>
       </c>
       <c r="C334" t="n">
         <v>5226.12889303</v>
       </c>
       <c r="D334" t="n">
-        <v>118996.480271511</v>
+        <v>124337.152546714</v>
       </c>
       <c r="E334" t="n">
         <v>40355.92111146</v>
@@ -42940,52 +42940,52 @@
         <v>107949.4324657</v>
       </c>
       <c r="G334" t="n">
-        <v>280269.327248142</v>
+        <v>283212.090652163</v>
       </c>
       <c r="H334" t="n">
-        <v>80786.29521166</v>
+        <v>80828.2974801605</v>
       </c>
       <c r="I334" t="n">
         <v>34751.9532140549</v>
       </c>
       <c r="J334" t="n">
-        <v>77017.52984834</v>
+        <v>77017.7523109655</v>
       </c>
       <c r="K334" t="n">
         <v>346129.001582067</v>
       </c>
       <c r="L334" t="n">
-        <v>37547.14503268</v>
+        <v>37547.9753434486</v>
       </c>
       <c r="M334" t="n">
-        <v>72566.50183175</v>
+        <v>72684.3479605505</v>
       </c>
       <c r="N334" t="n">
-        <v>543817.997395346</v>
+        <v>543824.887461824</v>
       </c>
       <c r="O334" t="n">
         <v>84253.94924605</v>
       </c>
       <c r="P334" t="n">
-        <v>459564.048149296</v>
+        <v>459570.938215774</v>
       </c>
       <c r="Q334" t="n">
-        <v>104832.956939014</v>
+        <v>105150.072173718</v>
       </c>
       <c r="R334" t="n">
-        <v>2067586.92025923</v>
+        <v>2067598.50744202</v>
       </c>
       <c r="S334" t="n">
         <v>388129.56714165</v>
       </c>
       <c r="T334" t="n">
-        <v>2455716.48740088</v>
+        <v>2455728.07458367</v>
       </c>
       <c r="U334" t="n">
-        <v>1.35268563303694</v>
+        <v>1.35214459280875</v>
       </c>
       <c r="V334" t="n">
-        <v>18.7593835089255</v>
+        <v>18.7548663432146</v>
       </c>
       <c r="W334" t="n">
         <v>-0.457288390579313</v>
@@ -42994,16 +42994,16 @@
         <v>20.9014212853629</v>
       </c>
       <c r="Y334" t="n">
-        <v>1.06224970549289</v>
+        <v>1.06179815011276</v>
       </c>
       <c r="Z334" t="n">
-        <v>19.092871337131</v>
+        <v>19.0890451225317</v>
       </c>
       <c r="AA334" t="n">
-        <v>0.841948543680445</v>
+        <v>0.841949289435293</v>
       </c>
       <c r="AB334" t="n">
-        <v>0.158051456319555</v>
+        <v>0.158050710564707</v>
       </c>
     </row>
     <row r="335">
@@ -43011,13 +43011,13 @@
         <v>45200</v>
       </c>
       <c r="B335" t="n">
-        <v>62324.8803008017</v>
+        <v>53584.9154706664</v>
       </c>
       <c r="C335" t="n">
         <v>5750.238811</v>
       </c>
       <c r="D335" t="n">
-        <v>125507.263222355</v>
+        <v>130910.221840202</v>
       </c>
       <c r="E335" t="n">
         <v>43822.184047</v>
@@ -43026,52 +43026,52 @@
         <v>117011.426804</v>
       </c>
       <c r="G335" t="n">
-        <v>283062.988193715</v>
+        <v>286040.071990424</v>
       </c>
       <c r="H335" t="n">
-        <v>80772.52423</v>
+        <v>80815.0163558729</v>
       </c>
       <c r="I335" t="n">
         <v>35957.6352862915</v>
       </c>
       <c r="J335" t="n">
-        <v>79001.577104</v>
+        <v>79001.8021611272</v>
       </c>
       <c r="K335" t="n">
         <v>350416.183395263</v>
       </c>
       <c r="L335" t="n">
-        <v>38134.832015</v>
+        <v>38135.6720093849</v>
       </c>
       <c r="M335" t="n">
-        <v>74435.50496</v>
+        <v>74535.0663460225</v>
       </c>
       <c r="N335" t="n">
-        <v>551989.41452442</v>
+        <v>551995.54234337</v>
       </c>
       <c r="O335" t="n">
         <v>86653.36741</v>
       </c>
       <c r="P335" t="n">
-        <v>465336.04711442</v>
+        <v>465342.17493337</v>
       </c>
       <c r="Q335" t="n">
-        <v>106277.636400905</v>
+        <v>106492.601699341</v>
       </c>
       <c r="R335" t="n">
-        <v>2111984.32942017</v>
+        <v>2111994.74650434</v>
       </c>
       <c r="S335" t="n">
         <v>394469.374399</v>
       </c>
       <c r="T335" t="n">
-        <v>2506453.70381917</v>
+        <v>2506464.12090334</v>
       </c>
       <c r="U335" t="n">
-        <v>2.14730557278702</v>
+        <v>2.14723694675314</v>
       </c>
       <c r="V335" t="n">
-        <v>19.9275066176659</v>
+        <v>19.921559054198</v>
       </c>
       <c r="W335" t="n">
         <v>1.63342548315477</v>
@@ -43080,16 +43080,16 @@
         <v>18.8791301082206</v>
       </c>
       <c r="Y335" t="n">
-        <v>2.06608607624701</v>
+        <v>2.06602867983514</v>
       </c>
       <c r="Z335" t="n">
-        <v>19.7612872131471</v>
+        <v>19.7562902149227</v>
       </c>
       <c r="AA335" t="n">
-        <v>0.842618527604187</v>
+        <v>0.842619181695355</v>
       </c>
       <c r="AB335" t="n">
-        <v>0.157381472395813</v>
+        <v>0.157380818304645</v>
       </c>
     </row>
     <row r="336">
@@ -43097,13 +43097,13 @@
         <v>45231</v>
       </c>
       <c r="B336" t="n">
-        <v>63464.5161942354</v>
+        <v>54671.4255309624</v>
       </c>
       <c r="C336" t="n">
         <v>6083.341165</v>
       </c>
       <c r="D336" t="n">
-        <v>126772.923385103</v>
+        <v>132241.411257139</v>
       </c>
       <c r="E336" t="n">
         <v>39622.095577</v>
@@ -43112,52 +43112,52 @@
         <v>116229.539582</v>
       </c>
       <c r="G336" t="n">
-        <v>285595.45205324</v>
+        <v>288608.643119069</v>
       </c>
       <c r="H336" t="n">
-        <v>81299.850025</v>
+        <v>81342.857512458</v>
       </c>
       <c r="I336" t="n">
         <v>36543.0165539194</v>
       </c>
       <c r="J336" t="n">
-        <v>80513.287947</v>
+        <v>80513.5157337105</v>
       </c>
       <c r="K336" t="n">
         <v>354766.789647027</v>
       </c>
       <c r="L336" t="n">
-        <v>39305.068332</v>
+        <v>39305.9185141745</v>
       </c>
       <c r="M336" t="n">
-        <v>75104.358023</v>
+        <v>75240.8933267922</v>
       </c>
       <c r="N336" t="n">
-        <v>565217.441285818</v>
+        <v>565226.642001196</v>
       </c>
       <c r="O336" t="n">
         <v>93257.27568</v>
       </c>
       <c r="P336" t="n">
-        <v>471960.165605818</v>
+        <v>471969.366321196</v>
       </c>
       <c r="Q336" t="n">
-        <v>109153.620163446</v>
+        <v>109279.054786244</v>
       </c>
       <c r="R336" t="n">
-        <v>2152675.76602261</v>
+        <v>2152688.81111089</v>
       </c>
       <c r="S336" t="n">
         <v>392212.975197</v>
       </c>
       <c r="T336" t="n">
-        <v>2544888.74121961</v>
+        <v>2544901.78630789</v>
       </c>
       <c r="U336" t="n">
-        <v>1.9266921650696</v>
+        <v>1.92680709428406</v>
       </c>
       <c r="V336" t="n">
-        <v>20.0467147112528</v>
+        <v>20.0403273897166</v>
       </c>
       <c r="W336" t="n">
         <v>-0.572008715616457</v>
@@ -43166,16 +43166,16 @@
         <v>14.4215171983377</v>
       </c>
       <c r="Y336" t="n">
-        <v>1.53344294139051</v>
+        <v>1.53354141732931</v>
       </c>
       <c r="Z336" t="n">
-        <v>19.1439899184545</v>
+        <v>19.1386724914113</v>
       </c>
       <c r="AA336" t="n">
-        <v>0.845882073803731</v>
+        <v>0.84588286380748</v>
       </c>
       <c r="AB336" t="n">
-        <v>0.154117926196269</v>
+        <v>0.15411713619252</v>
       </c>
     </row>
     <row r="337">
@@ -43183,13 +43183,13 @@
         <v>45261</v>
       </c>
       <c r="B337" t="n">
-        <v>64117.1951522631</v>
+        <v>54769.119180229</v>
       </c>
       <c r="C337" t="n">
         <v>6497.74565</v>
       </c>
       <c r="D337" t="n">
-        <v>133239.243281053</v>
+        <v>138704.669245382</v>
       </c>
       <c r="E337" t="n">
         <v>47821.236131</v>
@@ -43198,52 +43198,52 @@
         <v>119930.451317</v>
       </c>
       <c r="G337" t="n">
-        <v>291809.046470635</v>
+        <v>294820.550394942</v>
       </c>
       <c r="H337" t="n">
-        <v>87664.795245</v>
+        <v>87707.7786517687</v>
       </c>
       <c r="I337" t="n">
         <v>37459.3765924975</v>
       </c>
       <c r="J337" t="n">
-        <v>76595.207663</v>
+        <v>76595.4353221685</v>
       </c>
       <c r="K337" t="n">
         <v>357839.911195908</v>
       </c>
       <c r="L337" t="n">
-        <v>38880.967749</v>
+        <v>38881.8174551417</v>
       </c>
       <c r="M337" t="n">
-        <v>76011.189106</v>
+        <v>76043.4830678689</v>
       </c>
       <c r="N337" t="n">
-        <v>562656.255697516</v>
+        <v>563254.094816159</v>
       </c>
       <c r="O337" t="n">
         <v>89992.530956</v>
       </c>
       <c r="P337" t="n">
-        <v>472663.724741516</v>
+        <v>473261.563860159</v>
       </c>
       <c r="Q337" t="n">
-        <v>111720.150220058</v>
+        <v>111931.044881086</v>
       </c>
       <c r="R337" t="n">
-        <v>2166974.45740545</v>
+        <v>2167586.23895431</v>
       </c>
       <c r="S337" t="n">
         <v>407924.569763</v>
       </c>
       <c r="T337" t="n">
-        <v>2574899.02716845</v>
+        <v>2575510.80871731</v>
       </c>
       <c r="U337" t="n">
-        <v>0.664228752352214</v>
+        <v>0.692038150917607</v>
       </c>
       <c r="V337" t="n">
-        <v>20.5810320840048</v>
+        <v>20.6123162665956</v>
       </c>
       <c r="W337" t="n">
         <v>4.00588342548036</v>
@@ -43252,16 +43252,16 @@
         <v>16.5934600070473</v>
       </c>
       <c r="Y337" t="n">
-        <v>1.17923764063879</v>
+        <v>1.20275849441835</v>
       </c>
       <c r="Z337" t="n">
-        <v>19.9312222547276</v>
+        <v>19.9574209418981</v>
       </c>
       <c r="AA337" t="n">
-        <v>0.841576479132238</v>
+        <v>0.841614110730073</v>
       </c>
       <c r="AB337" t="n">
-        <v>0.158423520867762</v>
+        <v>0.158385889269927</v>
       </c>
     </row>
     <row r="338">
@@ -43269,13 +43269,13 @@
         <v>45292</v>
       </c>
       <c r="B338" t="n">
-        <v>64525.7107728722</v>
+        <v>52816.5494637829</v>
       </c>
       <c r="C338" t="n">
         <v>6255.706649</v>
       </c>
       <c r="D338" t="n">
-        <v>137668.237170824</v>
+        <v>139212.329701824</v>
       </c>
       <c r="E338" t="n">
         <v>50406.784387</v>
@@ -43284,22 +43284,22 @@
         <v>116641.724077</v>
       </c>
       <c r="G338" t="n">
-        <v>296536.767593208</v>
+        <v>305012.297253208</v>
       </c>
       <c r="H338" t="n">
-        <v>88050.559314</v>
+        <v>88057.563379</v>
       </c>
       <c r="I338" t="n">
         <v>37710.6644326297</v>
       </c>
       <c r="J338" t="n">
-        <v>78614.696482</v>
+        <v>78996.396801</v>
       </c>
       <c r="K338" t="n">
         <v>361342.266114257</v>
       </c>
       <c r="L338" t="n">
-        <v>39633.955902</v>
+        <v>41020.699736</v>
       </c>
       <c r="M338" t="n">
         <v>76751.380266</v>
@@ -43314,22 +43314,22 @@
         <v>482612.359350618</v>
       </c>
       <c r="Q338" t="n">
-        <v>111966.715480413</v>
+        <v>111998.582919413</v>
       </c>
       <c r="R338" t="n">
-        <v>2195921.40247144</v>
+        <v>2196039.17901035</v>
       </c>
       <c r="S338" t="n">
         <v>416755.322833</v>
       </c>
       <c r="T338" t="n">
-        <v>2612676.72530444</v>
+        <v>2612794.50184335</v>
       </c>
       <c r="U338" t="n">
-        <v>1.33582308582687</v>
+        <v>1.31265550337536</v>
       </c>
       <c r="V338" t="n">
-        <v>21.2629087496036</v>
+        <v>21.2650499654003</v>
       </c>
       <c r="W338" t="n">
         <v>2.16480048630818</v>
@@ -43338,16 +43338,16 @@
         <v>18.8003093648718</v>
       </c>
       <c r="Y338" t="n">
-        <v>1.46715260433092</v>
+        <v>1.44762324428409</v>
       </c>
       <c r="Z338" t="n">
-        <v>20.86327144675</v>
+        <v>20.8650772344939</v>
       </c>
       <c r="AA338" t="n">
-        <v>0.840487221860777</v>
+        <v>0.840494412193927</v>
       </c>
       <c r="AB338" t="n">
-        <v>0.159512778139223</v>
+        <v>0.159505587806073</v>
       </c>
     </row>
     <row r="339">
@@ -43355,13 +43355,13 @@
         <v>45323</v>
       </c>
       <c r="B339" t="n">
-        <v>64713.9939527485</v>
+        <v>53354.268192406</v>
       </c>
       <c r="C339" t="n">
         <v>6410.64736634</v>
       </c>
       <c r="D339" t="n">
-        <v>137094.348668569</v>
+        <v>138613.374656569</v>
       </c>
       <c r="E339" t="n">
         <v>52924.560269</v>
@@ -43370,22 +43370,22 @@
         <v>118772.06285235</v>
       </c>
       <c r="G339" t="n">
-        <v>300182.250412806</v>
+        <v>308357.084549806</v>
       </c>
       <c r="H339" t="n">
-        <v>87134.33162029</v>
+        <v>87141.17821129</v>
       </c>
       <c r="I339" t="n">
         <v>38407.3802974497</v>
       </c>
       <c r="J339" t="n">
-        <v>79454.42046368</v>
+        <v>79832.92754468</v>
       </c>
       <c r="K339" t="n">
         <v>365226.243577909</v>
       </c>
       <c r="L339" t="n">
-        <v>39967.98098955</v>
+        <v>41334.02730655</v>
       </c>
       <c r="M339" t="n">
         <v>77326.28101124</v>
@@ -43400,22 +43400,22 @@
         <v>487858.106439314</v>
       </c>
       <c r="Q339" t="n">
-        <v>114460.867803499</v>
+        <v>114491.335242499</v>
       </c>
       <c r="R339" t="n">
-        <v>2223243.38676406</v>
+        <v>2223359.38855672</v>
       </c>
       <c r="S339" t="n">
         <v>419669.256598</v>
       </c>
       <c r="T339" t="n">
-        <v>2642912.64336206</v>
+        <v>2643028.64515472</v>
       </c>
       <c r="U339" t="n">
-        <v>1.24421503710783</v>
+        <v>1.24406749239681</v>
       </c>
       <c r="V339" t="n">
-        <v>21.1997325157785</v>
+        <v>21.2024825799502</v>
       </c>
       <c r="W339" t="n">
         <v>0.69919533245355</v>
@@ -43424,16 +43424,16 @@
         <v>21.2850189866674</v>
       </c>
       <c r="Y339" t="n">
-        <v>1.15727742987779</v>
+        <v>1.15715733824586</v>
       </c>
       <c r="Z339" t="n">
-        <v>21.2132671800568</v>
+        <v>21.2155804937609</v>
       </c>
       <c r="AA339" t="n">
-        <v>0.841209561862727</v>
+        <v>0.841216531130924</v>
       </c>
       <c r="AB339" t="n">
-        <v>0.158790438137273</v>
+        <v>0.158783468869076</v>
       </c>
     </row>
     <row r="340">
@@ -43441,13 +43441,13 @@
         <v>45352</v>
       </c>
       <c r="B340" t="n">
-        <v>64484.8246267541</v>
+        <v>53367.8066335358</v>
       </c>
       <c r="C340" t="n">
         <v>6651.27565459</v>
       </c>
       <c r="D340" t="n">
-        <v>134680.62099463</v>
+        <v>136186.72884363</v>
       </c>
       <c r="E340" t="n">
         <v>53860.664244</v>
@@ -43456,22 +43456,22 @@
         <v>122098.48315727</v>
       </c>
       <c r="G340" t="n">
-        <v>307174.84778779</v>
+        <v>315206.05940279</v>
       </c>
       <c r="H340" t="n">
-        <v>89052.63888833</v>
+        <v>89059.23522033</v>
       </c>
       <c r="I340" t="n">
         <v>38166.5574633913</v>
       </c>
       <c r="J340" t="n">
-        <v>81162.04383327</v>
+        <v>81537.59303427</v>
       </c>
       <c r="K340" t="n">
         <v>369211.80439435</v>
       </c>
       <c r="L340" t="n">
-        <v>40490.74773654</v>
+        <v>41773.13885854</v>
       </c>
       <c r="M340" t="n">
         <v>76391.51066969</v>
@@ -43486,22 +43486,22 @@
         <v>493472.324757012</v>
       </c>
       <c r="Q340" t="n">
-        <v>119667.944140133</v>
+        <v>119697.732580133</v>
       </c>
       <c r="R340" t="n">
-        <v>2252246.35882776</v>
+        <v>2252360.98539354</v>
       </c>
       <c r="S340" t="n">
         <v>425860.436649</v>
       </c>
       <c r="T340" t="n">
-        <v>2678106.79547676</v>
+        <v>2678221.42204254</v>
       </c>
       <c r="U340" t="n">
-        <v>1.30453427799995</v>
+        <v>1.30440436153034</v>
       </c>
       <c r="V340" t="n">
-        <v>21.1128860154187</v>
+        <v>21.1177662941795</v>
       </c>
       <c r="W340" t="n">
         <v>1.47525222628604</v>
@@ -43510,16 +43510,16 @@
         <v>21.6108691538857</v>
       </c>
       <c r="Y340" t="n">
-        <v>1.33164265580619</v>
+        <v>1.33153217814515</v>
       </c>
       <c r="Z340" t="n">
-        <v>21.1918001658908</v>
+        <v>21.1959063820664</v>
       </c>
       <c r="AA340" t="n">
-        <v>0.840984520345393</v>
+        <v>0.840991326130079</v>
       </c>
       <c r="AB340" t="n">
-        <v>0.159015479654607</v>
+        <v>0.159008673869921</v>
       </c>
     </row>
     <row r="341">
@@ -43527,13 +43527,13 @@
         <v>45383</v>
       </c>
       <c r="B341" t="n">
-        <v>65329.8152793935</v>
+        <v>53915.1274412853</v>
       </c>
       <c r="C341" t="n">
         <v>6768.418033</v>
       </c>
       <c r="D341" t="n">
-        <v>134849.222608947</v>
+        <v>136378.093855947</v>
       </c>
       <c r="E341" t="n">
         <v>52541.068035</v>
@@ -43542,22 +43542,22 @@
         <v>122338.932081</v>
       </c>
       <c r="G341" t="n">
-        <v>311371.263108139</v>
+        <v>319731.895231139</v>
       </c>
       <c r="H341" t="n">
-        <v>90237.738512</v>
+        <v>90243.839333</v>
       </c>
       <c r="I341" t="n">
         <v>40167.0825526046</v>
       </c>
       <c r="J341" t="n">
-        <v>79842.49668</v>
+        <v>80222.477039</v>
       </c>
       <c r="K341" t="n">
         <v>371551.455377862</v>
       </c>
       <c r="L341" t="n">
-        <v>40436.593106</v>
+        <v>41660.616838</v>
       </c>
       <c r="M341" t="n">
         <v>74263.45515</v>
@@ -43572,22 +43572,22 @@
         <v>496473.136918076</v>
       </c>
       <c r="Q341" t="n">
-        <v>122478.65270778</v>
+        <v>122508.44114578</v>
       </c>
       <c r="R341" t="n">
-        <v>2269323.58177688</v>
+        <v>2269438.29065877</v>
       </c>
       <c r="S341" t="n">
         <v>427475.643533</v>
       </c>
       <c r="T341" t="n">
-        <v>2696799.22530988</v>
+        <v>2696913.93419177</v>
       </c>
       <c r="U341" t="n">
-        <v>0.758230682988059</v>
+        <v>0.758195749969448</v>
       </c>
       <c r="V341" t="n">
-        <v>20.6792108986225</v>
+        <v>20.6853109442313</v>
       </c>
       <c r="W341" t="n">
         <v>0.379280803051252</v>
@@ -43596,16 +43596,16 @@
         <v>20.7902278354922</v>
       </c>
       <c r="Y341" t="n">
-        <v>0.697971786064855</v>
+        <v>0.697944986750487</v>
       </c>
       <c r="Z341" t="n">
-        <v>20.6967948282584</v>
+        <v>20.7019286900056</v>
       </c>
       <c r="AA341" t="n">
-        <v>0.841487775759843</v>
+        <v>0.841494517821493</v>
       </c>
       <c r="AB341" t="n">
-        <v>0.158512224240157</v>
+        <v>0.158505482178507</v>
       </c>
     </row>
     <row r="342">
@@ -43613,13 +43613,13 @@
         <v>45413</v>
       </c>
       <c r="B342" t="n">
-        <v>66863.7615850048</v>
+        <v>54371.0220076264</v>
       </c>
       <c r="C342" t="n">
         <v>6892.82016855</v>
       </c>
       <c r="D342" t="n">
-        <v>136415.517916056</v>
+        <v>137953.058630056</v>
       </c>
       <c r="E342" t="n">
         <v>60065.331241</v>
@@ -43628,22 +43628,22 @@
         <v>126620.83684834</v>
       </c>
       <c r="G342" t="n">
-        <v>314469.893289514</v>
+        <v>323866.476032514</v>
       </c>
       <c r="H342" t="n">
-        <v>94749.83142624</v>
+        <v>94755.73120224</v>
       </c>
       <c r="I342" t="n">
         <v>37770.6702862179</v>
       </c>
       <c r="J342" t="n">
-        <v>82055.49949905</v>
+        <v>82469.68201605</v>
       </c>
       <c r="K342" t="n">
         <v>376162.278529878</v>
       </c>
       <c r="L342" t="n">
-        <v>40011.21689556</v>
+        <v>41234.17830656</v>
       </c>
       <c r="M342" t="n">
         <v>72507.65826652</v>
@@ -43658,22 +43658,22 @@
         <v>502656.543250154</v>
       </c>
       <c r="Q342" t="n">
-        <v>125976.181981167</v>
+        <v>126005.970420167</v>
       </c>
       <c r="R342" t="n">
-        <v>2297114.1605544</v>
+        <v>2297228.37657703</v>
       </c>
       <c r="S342" t="n">
         <v>444970.300879</v>
       </c>
       <c r="T342" t="n">
-        <v>2742084.4614334</v>
+        <v>2742198.67745603</v>
       </c>
       <c r="U342" t="n">
-        <v>1.22461948576627</v>
+        <v>1.22453587007167</v>
       </c>
       <c r="V342" t="n">
-        <v>20.1770238133929</v>
+        <v>20.1826363318923</v>
       </c>
       <c r="W342" t="n">
         <v>4.09255067760357</v>
@@ -43682,16 +43682,16 @@
         <v>23.4369798758814</v>
       </c>
       <c r="Y342" t="n">
-        <v>1.67922163795209</v>
+        <v>1.67913194003462</v>
       </c>
       <c r="Z342" t="n">
-        <v>20.6942771909308</v>
+        <v>20.6989978660752</v>
       </c>
       <c r="AA342" t="n">
-        <v>0.837725530654736</v>
+        <v>0.837732289590408</v>
       </c>
       <c r="AB342" t="n">
-        <v>0.162274469345264</v>
+        <v>0.162267710409592</v>
       </c>
     </row>
     <row r="343">
@@ -43699,13 +43699,13 @@
         <v>45444</v>
       </c>
       <c r="B343" t="n">
-        <v>66651.2406869287</v>
+        <v>54078.3514519649</v>
       </c>
       <c r="C343" t="n">
         <v>6774.500191</v>
       </c>
       <c r="D343" t="n">
-        <v>137974.601567481</v>
+        <v>139475.261757481</v>
       </c>
       <c r="E343" t="n">
         <v>60702.538991</v>
@@ -43714,22 +43714,22 @@
         <v>128122.88663514</v>
       </c>
       <c r="G343" t="n">
-        <v>311014.782386187</v>
+        <v>320528.257791187</v>
       </c>
       <c r="H343" t="n">
-        <v>95956.95697768</v>
+        <v>95962.58636468</v>
       </c>
       <c r="I343" t="n">
         <v>38452.5717678225</v>
       </c>
       <c r="J343" t="n">
-        <v>82285.13605982</v>
+        <v>82704.63153882</v>
       </c>
       <c r="K343" t="n">
         <v>380337.639127461</v>
       </c>
       <c r="L343" t="n">
-        <v>40055.18495056</v>
+        <v>41270.13752156</v>
       </c>
       <c r="M343" t="n">
         <v>72220.01594863</v>
@@ -43744,22 +43744,22 @@
         <v>509144.985392889</v>
       </c>
       <c r="Q343" t="n">
-        <v>128404.339015897</v>
+        <v>128444.610209897</v>
       </c>
       <c r="R343" t="n">
-        <v>2315609.58467539</v>
+        <v>2315731.17966642</v>
       </c>
       <c r="S343" t="n">
         <v>451882.844638</v>
       </c>
       <c r="T343" t="n">
-        <v>2767492.42931339</v>
+        <v>2767614.02430442</v>
       </c>
       <c r="U343" t="n">
-        <v>0.805159118278964</v>
+        <v>0.805440298320081</v>
       </c>
       <c r="V343" t="n">
-        <v>16.865959284762</v>
+        <v>16.8712546399354</v>
       </c>
       <c r="W343" t="n">
         <v>1.55348429891724</v>
@@ -43768,16 +43768,16 @@
         <v>20.8958594857006</v>
       </c>
       <c r="Y343" t="n">
-        <v>0.926593189864744</v>
+        <v>0.926823685582612</v>
       </c>
       <c r="Z343" t="n">
-        <v>17.5055181723602</v>
+        <v>17.5099692680863</v>
       </c>
       <c r="AA343" t="n">
-        <v>0.836717585980854</v>
+        <v>0.836724759785978</v>
       </c>
       <c r="AB343" t="n">
-        <v>0.163282414019146</v>
+        <v>0.163275240214022</v>
       </c>
     </row>
     <row r="344">
@@ -43785,13 +43785,13 @@
         <v>45474</v>
       </c>
       <c r="B344" t="n">
-        <v>66134.3818207768</v>
+        <v>57595.138967735</v>
       </c>
       <c r="C344" t="n">
         <v>6715.555045</v>
       </c>
       <c r="D344" t="n">
-        <v>136950.727220283</v>
+        <v>142348.352455283</v>
       </c>
       <c r="E344" t="n">
         <v>63356.441081</v>
@@ -43800,22 +43800,22 @@
         <v>129520.748044</v>
       </c>
       <c r="G344" t="n">
-        <v>313973.129231332</v>
+        <v>317147.594416332</v>
       </c>
       <c r="H344" t="n">
-        <v>93676.0036</v>
+        <v>93722.550079</v>
       </c>
       <c r="I344" t="n">
         <v>42743.2431276385</v>
       </c>
       <c r="J344" t="n">
-        <v>81977.037465</v>
+        <v>81977.506865</v>
       </c>
       <c r="K344" t="n">
         <v>385005.781642503</v>
       </c>
       <c r="L344" t="n">
-        <v>40575.783205</v>
+        <v>40576.628305</v>
       </c>
       <c r="M344" t="n">
         <v>71214.880668</v>
@@ -43830,22 +43830,22 @@
         <v>516179.814362678</v>
       </c>
       <c r="Q344" t="n">
-        <v>129443.608040054</v>
+        <v>129483.879234054</v>
       </c>
       <c r="R344" t="n">
-        <v>2333545.92922694</v>
+        <v>2333666.9089669</v>
       </c>
       <c r="S344" t="n">
         <v>465309.596483</v>
       </c>
       <c r="T344" t="n">
-        <v>2798855.52570994</v>
+        <v>2798976.5054499</v>
       </c>
       <c r="U344" t="n">
-        <v>0.774584138460055</v>
+        <v>0.774516898073752</v>
       </c>
       <c r="V344" t="n">
-        <v>15.7973865566955</v>
+        <v>15.8018822407384</v>
       </c>
       <c r="W344" t="n">
         <v>2.97129045820628</v>
@@ -43854,16 +43854,16 @@
         <v>20.9683791519836</v>
       </c>
       <c r="Y344" t="n">
-        <v>1.13326764923933</v>
+        <v>1.13319562880019</v>
       </c>
       <c r="Z344" t="n">
-        <v>16.6262056148293</v>
+        <v>16.6299716666124</v>
       </c>
       <c r="AA344" t="n">
-        <v>0.833750048114766</v>
+        <v>0.833757233911398</v>
       </c>
       <c r="AB344" t="n">
-        <v>0.166249951885234</v>
+        <v>0.166242766088602</v>
       </c>
     </row>
     <row r="345">
@@ -43871,13 +43871,13 @@
         <v>45505</v>
       </c>
       <c r="B345" t="n">
-        <v>66400.5104783855</v>
+        <v>57781.1573892972</v>
       </c>
       <c r="C345" t="n">
         <v>6777.656182</v>
       </c>
       <c r="D345" t="n">
-        <v>136541.464920557</v>
+        <v>142121.568536557</v>
       </c>
       <c r="E345" t="n">
         <v>68321.233391</v>
@@ -43886,22 +43886,22 @@
         <v>131665.512344</v>
       </c>
       <c r="G345" t="n">
-        <v>317885.529673089</v>
+        <v>320960.222121089</v>
       </c>
       <c r="H345" t="n">
-        <v>94304.968817</v>
+        <v>94348.854118</v>
       </c>
       <c r="I345" t="n">
         <v>43347.7988621676</v>
       </c>
       <c r="J345" t="n">
-        <v>82471.048465</v>
+        <v>82471.280901</v>
       </c>
       <c r="K345" t="n">
         <v>390241.185639029</v>
       </c>
       <c r="L345" t="n">
-        <v>39347.92079</v>
+        <v>39348.788325</v>
       </c>
       <c r="M345" t="n">
         <v>72070.902872</v>
@@ -43916,22 +43916,22 @@
         <v>521994.069898705</v>
       </c>
       <c r="Q345" t="n">
-        <v>132139.296215038</v>
+        <v>132179.739012038</v>
       </c>
       <c r="R345" t="n">
-        <v>2363189.61125768</v>
+        <v>2363310.48230159</v>
       </c>
       <c r="S345" t="n">
         <v>475438.891945</v>
       </c>
       <c r="T345" t="n">
-        <v>2838628.50320268</v>
+        <v>2838749.37424659</v>
       </c>
       <c r="U345" t="n">
-        <v>1.27032777283085</v>
+        <v>1.27025725997074</v>
       </c>
       <c r="V345" t="n">
-        <v>15.8430687552561</v>
+        <v>15.8477261701387</v>
       </c>
       <c r="W345" t="n">
         <v>2.17689373667798</v>
@@ -43940,16 +43940,16 @@
         <v>21.9347365296486</v>
       </c>
       <c r="Y345" t="n">
-        <v>1.42104432070123</v>
+        <v>1.42097901569538</v>
       </c>
       <c r="Z345" t="n">
-        <v>16.8205629939917</v>
+        <v>16.8244640879079</v>
       </c>
       <c r="AA345" t="n">
-        <v>0.832511055459146</v>
+        <v>0.83251818696704</v>
       </c>
       <c r="AB345" t="n">
-        <v>0.167488944540854</v>
+        <v>0.16748181303296</v>
       </c>
     </row>
     <row r="346">
@@ -43957,13 +43957,13 @@
         <v>45536</v>
       </c>
       <c r="B346" t="n">
-        <v>65045.3377945544</v>
+        <v>56467.3331015758</v>
       </c>
       <c r="C346" t="n">
         <v>6833.88831513</v>
       </c>
       <c r="D346" t="n">
-        <v>126621.783361655</v>
+        <v>132120.979628655</v>
       </c>
       <c r="E346" t="n">
         <v>67441.001115</v>
@@ -43972,22 +43972,22 @@
         <v>134053.66517845</v>
       </c>
       <c r="G346" t="n">
-        <v>322962.582337027</v>
+        <v>326077.461620027</v>
       </c>
       <c r="H346" t="n">
-        <v>98078.29439759</v>
+        <v>98120.93645459</v>
       </c>
       <c r="I346" t="n">
         <v>44027.7551998754</v>
       </c>
       <c r="J346" t="n">
-        <v>82765.1440308</v>
+        <v>82765.3704898</v>
       </c>
       <c r="K346" t="n">
         <v>395473.107325401</v>
       </c>
       <c r="L346" t="n">
-        <v>38746.67330491</v>
+        <v>38747.51495591</v>
       </c>
       <c r="M346" t="n">
         <v>72800.74817706</v>
@@ -44002,22 +44002,22 @@
         <v>526098.693641364</v>
       </c>
       <c r="Q346" t="n">
-        <v>133121.216144385</v>
+        <v>133161.808123385</v>
       </c>
       <c r="R346" t="n">
-        <v>2375450.21227557</v>
+        <v>2375570.58527859</v>
       </c>
       <c r="S346" t="n">
         <v>482569.416605</v>
       </c>
       <c r="T346" t="n">
-        <v>2858019.62888057</v>
+        <v>2858140.00188359</v>
       </c>
       <c r="U346" t="n">
-        <v>0.518815797068606</v>
+        <v>0.518768188471741</v>
       </c>
       <c r="V346" t="n">
-        <v>14.8899806339333</v>
+        <v>14.8951586455524</v>
       </c>
       <c r="W346" t="n">
         <v>1.4997773175075</v>
@@ -44026,16 +44026,16 @@
         <v>24.3320420443217</v>
       </c>
       <c r="Y346" t="n">
-        <v>0.683116006762097</v>
+        <v>0.68306937600453</v>
       </c>
       <c r="Z346" t="n">
-        <v>16.3823121905038</v>
+        <v>16.3866647722441</v>
       </c>
       <c r="AA346" t="n">
-        <v>0.831152518433187</v>
+        <v>0.831159629588832</v>
       </c>
       <c r="AB346" t="n">
-        <v>0.168847481566813</v>
+        <v>0.168840370411168</v>
       </c>
     </row>
     <row r="347">
@@ -44043,13 +44043,13 @@
         <v>45566</v>
       </c>
       <c r="B347" t="n">
-        <v>64443.2351582777</v>
+        <v>55869.7741980947</v>
       </c>
       <c r="C347" t="n">
         <v>7132.334922</v>
       </c>
       <c r="D347" t="n">
-        <v>128213.032861852</v>
+        <v>133635.736264852</v>
       </c>
       <c r="E347" t="n">
         <v>76662.276711</v>
@@ -44058,22 +44058,22 @@
         <v>134653.420885</v>
       </c>
       <c r="G347" t="n">
-        <v>326508.128639001</v>
+        <v>329695.258227001</v>
       </c>
       <c r="H347" t="n">
-        <v>98579.080283</v>
+        <v>98621.250341</v>
       </c>
       <c r="I347" t="n">
         <v>43554.0193344107</v>
       </c>
       <c r="J347" t="n">
-        <v>83999.477322</v>
+        <v>83999.697752</v>
       </c>
       <c r="K347" t="n">
         <v>400544.092701107</v>
       </c>
       <c r="L347" t="n">
-        <v>39224.026696</v>
+        <v>39224.915205</v>
       </c>
       <c r="M347" t="n">
         <v>79583.362434</v>
@@ -44088,22 +44088,22 @@
         <v>530042.47700918</v>
       </c>
       <c r="Q347" t="n">
-        <v>127310.915455358</v>
+        <v>127349.007434358</v>
       </c>
       <c r="R347" t="n">
-        <v>2394816.45066937</v>
+        <v>2394934.19367618</v>
       </c>
       <c r="S347" t="n">
         <v>495586.25425</v>
       </c>
       <c r="T347" t="n">
-        <v>2890402.70491937</v>
+        <v>2890520.44792618</v>
       </c>
       <c r="U347" t="n">
-        <v>0.815266019625316</v>
+        <v>0.815113999036354</v>
       </c>
       <c r="V347" t="n">
-        <v>13.391771771661</v>
+        <v>13.3967874513018</v>
       </c>
       <c r="W347" t="n">
         <v>2.69740211399569</v>
@@ -44112,16 +44112,16 @@
         <v>25.6336451987073</v>
       </c>
       <c r="Y347" t="n">
-        <v>1.13305995912576</v>
+        <v>1.13292022158664</v>
       </c>
       <c r="Z347" t="n">
-        <v>15.3184158364927</v>
+        <v>15.322634137066</v>
       </c>
       <c r="AA347" t="n">
-        <v>0.828540758903066</v>
+        <v>0.828547743156233</v>
       </c>
       <c r="AB347" t="n">
-        <v>0.171459241096934</v>
+        <v>0.171452256843767</v>
       </c>
     </row>
     <row r="348">
@@ -44129,13 +44129,13 @@
         <v>45597</v>
       </c>
       <c r="B348" t="n">
-        <v>64968.8025404715</v>
+        <v>56291.0890624354</v>
       </c>
       <c r="C348" t="n">
         <v>7106.822706</v>
       </c>
       <c r="D348" t="n">
-        <v>131241.544760918</v>
+        <v>136741.789836918</v>
       </c>
       <c r="E348" t="n">
         <v>78661.065971</v>
@@ -44144,22 +44144,22 @@
         <v>136587.953516</v>
       </c>
       <c r="G348" t="n">
-        <v>334337.622296701</v>
+        <v>337548.356260701</v>
       </c>
       <c r="H348" t="n">
-        <v>98854.101489</v>
+        <v>98898.093325</v>
       </c>
       <c r="I348" t="n">
         <v>43280.5439099321</v>
       </c>
       <c r="J348" t="n">
-        <v>84936.749584</v>
+        <v>84936.963919</v>
       </c>
       <c r="K348" t="n">
         <v>404725.833123555</v>
       </c>
       <c r="L348" t="n">
-        <v>39394.057234</v>
+        <v>39394.919563</v>
       </c>
       <c r="M348" t="n">
         <v>86754.282913</v>
@@ -44174,22 +44174,22 @@
         <v>532734.306584586</v>
       </c>
       <c r="Q348" t="n">
-        <v>121533.256942086</v>
+        <v>121573.848921086</v>
       </c>
       <c r="R348" t="n">
-        <v>2424021.96479983</v>
+        <v>2424140.8908408</v>
       </c>
       <c r="S348" t="n">
         <v>507713.315146</v>
       </c>
       <c r="T348" t="n">
-        <v>2931735.27994583</v>
+        <v>2931854.2059868</v>
       </c>
       <c r="U348" t="n">
-        <v>1.21953037871885</v>
+        <v>1.21951981986548</v>
       </c>
       <c r="V348" t="n">
-        <v>12.6050658933454</v>
+        <v>12.6099080521457</v>
       </c>
       <c r="W348" t="n">
         <v>2.44701316713325</v>
@@ -44198,16 +44198,16 @@
         <v>29.4483730149383</v>
       </c>
       <c r="Y348" t="n">
-        <v>1.42999364607992</v>
+        <v>1.42997632451525</v>
       </c>
       <c r="Z348" t="n">
-        <v>15.2009214572122</v>
+        <v>15.2050040500894</v>
       </c>
       <c r="AA348" t="n">
-        <v>0.826821569253217</v>
+        <v>0.826828593963077</v>
       </c>
       <c r="AB348" t="n">
-        <v>0.173178430746783</v>
+        <v>0.173171406036923</v>
       </c>
     </row>
     <row r="349">
@@ -44215,13 +44215,13 @@
         <v>45627</v>
       </c>
       <c r="B349" t="n">
-        <v>64712.6042541354</v>
+        <v>56063.9364753494</v>
       </c>
       <c r="C349" t="n">
         <v>7067.423195</v>
       </c>
       <c r="D349" t="n">
-        <v>131294.462649587</v>
+        <v>136822.857440587</v>
       </c>
       <c r="E349" t="n">
         <v>78164.025838</v>
@@ -44230,22 +44230,22 @@
         <v>139354.782648</v>
       </c>
       <c r="G349" t="n">
-        <v>332965.957948841</v>
+        <v>336120.901138841</v>
       </c>
       <c r="H349" t="n">
-        <v>101334.266883</v>
+        <v>101376.678533</v>
       </c>
       <c r="I349" t="n">
         <v>43101.1639328241</v>
       </c>
       <c r="J349" t="n">
-        <v>88034.250698</v>
+        <v>88034.464924</v>
       </c>
       <c r="K349" t="n">
         <v>407593.561885463</v>
       </c>
       <c r="L349" t="n">
-        <v>40662.473639</v>
+        <v>40663.303996</v>
       </c>
       <c r="M349" t="n">
         <v>85228.937841</v>
@@ -44260,22 +44260,22 @@
         <v>531373.91985314</v>
       </c>
       <c r="Q349" t="n">
-        <v>118861.488049128</v>
+        <v>118900.346694128</v>
       </c>
       <c r="R349" t="n">
-        <v>2417026.65517626</v>
+        <v>2417143.64025647</v>
       </c>
       <c r="S349" t="n">
         <v>513795.798564</v>
       </c>
       <c r="T349" t="n">
-        <v>2930822.45374026</v>
+        <v>2930939.43882047</v>
       </c>
       <c r="U349" t="n">
-        <v>-0.288582765550682</v>
+        <v>-0.288648675939718</v>
       </c>
       <c r="V349" t="n">
-        <v>11.5392314346983</v>
+        <v>11.5131475194526</v>
       </c>
       <c r="W349" t="n">
         <v>1.19801534380695</v>
@@ -44284,16 +44284,16 @@
         <v>25.9536288443008</v>
       </c>
       <c r="Y349" t="n">
-        <v>-0.0311360378209891</v>
+        <v>-0.0312009773356881</v>
       </c>
       <c r="Z349" t="n">
-        <v>13.8228110235147</v>
+        <v>13.8003159955744</v>
       </c>
       <c r="AA349" t="n">
-        <v>0.824692281203079</v>
+        <v>0.824699278409256</v>
       </c>
       <c r="AB349" t="n">
-        <v>0.175307718796921</v>
+        <v>0.175300721590744</v>
       </c>
     </row>
     <row r="350">
@@ -44301,13 +44301,13 @@
         <v>45658</v>
       </c>
       <c r="B350" t="n">
-        <v>65013.1184242625</v>
+        <v>56187.2558752682</v>
       </c>
       <c r="C350" t="n">
         <v>6893.230735</v>
       </c>
       <c r="D350" t="n">
-        <v>128614.055518884</v>
+        <v>134345.468413397</v>
       </c>
       <c r="E350" t="n">
         <v>81557.257005</v>
@@ -44316,70 +44316,70 @@
         <v>135852.986465</v>
       </c>
       <c r="G350" t="n">
-        <v>332660.403017857</v>
+        <v>336545.175755702</v>
       </c>
       <c r="H350" t="n">
-        <v>105116.937985</v>
+        <v>105159.552971</v>
       </c>
       <c r="I350" t="n">
-        <v>43517.691821208</v>
+        <v>43573.5555490643</v>
       </c>
       <c r="J350" t="n">
-        <v>96411.287404</v>
+        <v>96411.489385</v>
       </c>
       <c r="K350" t="n">
-        <v>411449.593468321</v>
+        <v>411866.216940539</v>
       </c>
       <c r="L350" t="n">
-        <v>40991.655388</v>
+        <v>40992.90423</v>
       </c>
       <c r="M350" t="n">
-        <v>84454.835359</v>
+        <v>84500.688026</v>
       </c>
       <c r="N350" t="n">
-        <v>651490.133567439</v>
+        <v>652150.668878434</v>
       </c>
       <c r="O350" t="n">
         <v>113373.067652</v>
       </c>
       <c r="P350" t="n">
-        <v>538117.065915439</v>
+        <v>538777.601226434</v>
       </c>
       <c r="Q350" t="n">
-        <v>118875.538225669</v>
+        <v>119063.832243568</v>
       </c>
       <c r="R350" t="n">
-        <v>2426944.63947708</v>
+        <v>2429805.61971041</v>
       </c>
       <c r="S350" t="n">
-        <v>527444.218475</v>
+        <v>527445.331641</v>
       </c>
       <c r="T350" t="n">
-        <v>2954388.85795208</v>
+        <v>2957250.95135141</v>
       </c>
       <c r="U350" t="n">
-        <v>0.410338226083651</v>
+        <v>0.523840587834878</v>
       </c>
       <c r="V350" t="n">
-        <v>10.5205603782371</v>
+        <v>10.6449121187994</v>
       </c>
       <c r="W350" t="n">
-        <v>2.65638994112949</v>
+        <v>2.65660659646281</v>
       </c>
       <c r="X350" t="n">
-        <v>26.5596837227091</v>
+        <v>26.5599508257163</v>
       </c>
       <c r="Y350" t="n">
-        <v>0.804088428548244</v>
+        <v>0.897716008131577</v>
       </c>
       <c r="Z350" t="n">
-        <v>13.0790055018315</v>
+        <v>13.1834497227026</v>
       </c>
       <c r="AA350" t="n">
-        <v>0.8214709559795</v>
+        <v>0.821643363949222</v>
       </c>
       <c r="AB350" t="n">
-        <v>0.1785290440205</v>
+        <v>0.178356636050778</v>
       </c>
     </row>
     <row r="351">
@@ -44387,13 +44387,13 @@
         <v>45689</v>
       </c>
       <c r="B351" t="n">
-        <v>64211.6376068987</v>
+        <v>55603.7998202537</v>
       </c>
       <c r="C351" t="n">
         <v>6875.929713</v>
       </c>
       <c r="D351" t="n">
-        <v>128511.828243697</v>
+        <v>134064.707404712</v>
       </c>
       <c r="E351" t="n">
         <v>82209.963379</v>
@@ -44402,70 +44402,70 @@
         <v>138342.617992</v>
       </c>
       <c r="G351" t="n">
-        <v>338890.458065332</v>
+        <v>342743.396186531</v>
       </c>
       <c r="H351" t="n">
-        <v>110815.097146</v>
+        <v>110855.892095</v>
       </c>
       <c r="I351" t="n">
-        <v>43254.3754176461</v>
+        <v>43310.6882697384</v>
       </c>
       <c r="J351" t="n">
-        <v>96199.113691</v>
+        <v>96199.315672</v>
       </c>
       <c r="K351" t="n">
-        <v>415705.517224504</v>
+        <v>416125.526909094</v>
       </c>
       <c r="L351" t="n">
-        <v>41138.258983</v>
+        <v>41139.465155</v>
       </c>
       <c r="M351" t="n">
-        <v>83306.781155</v>
+        <v>83306.781156</v>
       </c>
       <c r="N351" t="n">
-        <v>656764.006620688</v>
+        <v>657430.928528174</v>
       </c>
       <c r="O351" t="n">
-        <v>115639.616</v>
+        <v>115639.615998</v>
       </c>
       <c r="P351" t="n">
-        <v>541124.390620688</v>
+        <v>541791.312530174</v>
       </c>
       <c r="Q351" t="n">
-        <v>118657.694695661</v>
+        <v>118897.27024396</v>
       </c>
       <c r="R351" t="n">
-        <v>2441123.34123912</v>
+        <v>2444012.14364864</v>
       </c>
       <c r="S351" t="n">
-        <v>540523.945315</v>
+        <v>540525.067404</v>
       </c>
       <c r="T351" t="n">
-        <v>2981647.28655412</v>
+        <v>2984537.21105264</v>
       </c>
       <c r="U351" t="n">
-        <v>0.584220238542077</v>
+        <v>0.584677384190257</v>
       </c>
       <c r="V351" t="n">
-        <v>9.80009457228976</v>
+        <v>9.92429547052023</v>
       </c>
       <c r="W351" t="n">
-        <v>2.47983130383294</v>
+        <v>2.47982776192293</v>
       </c>
       <c r="X351" t="n">
-        <v>28.7976035453954</v>
+        <v>28.7978709199963</v>
       </c>
       <c r="Y351" t="n">
-        <v>0.922641869863128</v>
+        <v>0.922690030373019</v>
       </c>
       <c r="Z351" t="n">
-        <v>12.816717345646</v>
+        <v>12.9211072503503</v>
       </c>
       <c r="AA351" t="n">
-        <v>0.818716335848134</v>
+        <v>0.818891496677517</v>
       </c>
       <c r="AB351" t="n">
-        <v>0.181283664151866</v>
+        <v>0.181108503322483</v>
       </c>
     </row>
     <row r="352">
@@ -44473,13 +44473,13 @@
         <v>45717</v>
       </c>
       <c r="B352" t="n">
-        <v>64046.6246199656</v>
+        <v>51860.1576638232</v>
       </c>
       <c r="C352" t="n">
         <v>6968.828491</v>
       </c>
       <c r="D352" t="n">
-        <v>129512.482531877</v>
+        <v>131041.905800869</v>
       </c>
       <c r="E352" t="n">
         <v>84118.414109</v>
@@ -44488,70 +44488,70 @@
         <v>143296.735446</v>
       </c>
       <c r="G352" t="n">
-        <v>344647.589437345</v>
+        <v>354649.908672175</v>
       </c>
       <c r="H352" t="n">
-        <v>111414.841814</v>
+        <v>111420.035632</v>
       </c>
       <c r="I352" t="n">
-        <v>43708.0071278938</v>
+        <v>43764.8033764584</v>
       </c>
       <c r="J352" t="n">
-        <v>98406.291937</v>
+        <v>98795.262769</v>
       </c>
       <c r="K352" t="n">
-        <v>421286.750060302</v>
+        <v>421710.40140327</v>
       </c>
       <c r="L352" t="n">
-        <v>41535.259101</v>
+        <v>42641.849268</v>
       </c>
       <c r="M352" t="n">
-        <v>83010.845826</v>
+        <v>83011.017076</v>
       </c>
       <c r="N352" t="n">
-        <v>659134.662264811</v>
+        <v>659808.229135207</v>
       </c>
       <c r="O352" t="n">
-        <v>115329.381414</v>
+        <v>115329.23839</v>
       </c>
       <c r="P352" t="n">
-        <v>543805.280850812</v>
+        <v>544478.990745207</v>
       </c>
       <c r="Q352" t="n">
-        <v>118211.73028332</v>
+        <v>118486.585763801</v>
       </c>
       <c r="R352" t="n">
-        <v>2454255.99097133</v>
+        <v>2457173.63000081</v>
       </c>
       <c r="S352" t="n">
-        <v>554177.734343</v>
+        <v>554208.733741</v>
       </c>
       <c r="T352" t="n">
-        <v>3008433.72531433</v>
+        <v>3011382.36374181</v>
       </c>
       <c r="U352" t="n">
-        <v>0.537975673344926</v>
+        <v>0.538519679060356</v>
       </c>
       <c r="V352" t="n">
-        <v>8.96925113683851</v>
+        <v>9.09324242141758</v>
       </c>
       <c r="W352" t="n">
-        <v>2.52602852220414</v>
+        <v>2.53155073875095</v>
       </c>
       <c r="X352" t="n">
-        <v>30.1313028051396</v>
+        <v>30.1385820439071</v>
       </c>
       <c r="Y352" t="n">
-        <v>0.89837717831367</v>
+        <v>0.89947455135615</v>
       </c>
       <c r="Z352" t="n">
-        <v>12.334344933349</v>
+        <v>12.4396339659318</v>
       </c>
       <c r="AA352" t="n">
-        <v>0.815791941939789</v>
+        <v>0.815962017838092</v>
       </c>
       <c r="AB352" t="n">
-        <v>0.184208058060212</v>
+        <v>0.184037982161908</v>
       </c>
     </row>
     <row r="353">
@@ -44559,13 +44559,13 @@
         <v>45748</v>
       </c>
       <c r="B353" t="n">
-        <v>64889.1712548394</v>
+        <v>52470.8294596228</v>
       </c>
       <c r="C353" t="n">
         <v>6411.516967</v>
       </c>
       <c r="D353" t="n">
-        <v>130306.746023981</v>
+        <v>131792.531747491</v>
       </c>
       <c r="E353" t="n">
         <v>85037.741267</v>
@@ -44574,70 +44574,70 @@
         <v>143395.517307</v>
       </c>
       <c r="G353" t="n">
-        <v>339067.145059747</v>
+        <v>349365.598178433</v>
       </c>
       <c r="H353" t="n">
-        <v>103482.003046</v>
+        <v>103486.929883</v>
       </c>
       <c r="I353" t="n">
-        <v>43424.2504521845</v>
+        <v>43481.5992589647</v>
       </c>
       <c r="J353" t="n">
-        <v>97498.514575</v>
+        <v>97880.880871</v>
       </c>
       <c r="K353" t="n">
-        <v>422772.75482109</v>
+        <v>423200.617677549</v>
       </c>
       <c r="L353" t="n">
-        <v>41613.832216</v>
+        <v>42709.621253</v>
       </c>
       <c r="M353" t="n">
-        <v>82388.602239</v>
+        <v>82388.773489</v>
       </c>
       <c r="N353" t="n">
-        <v>658332.204944438</v>
+        <v>659013.32200794</v>
       </c>
       <c r="O353" t="n">
         <v>114943.965362</v>
       </c>
       <c r="P353" t="n">
-        <v>543388.239582438</v>
+        <v>544069.35664594</v>
       </c>
       <c r="Q353" t="n">
-        <v>116727.127108614</v>
+        <v>116973.134959521</v>
       </c>
       <c r="R353" t="n">
-        <v>2471897.35585533</v>
+        <v>2474838.90229346</v>
       </c>
       <c r="S353" t="n">
-        <v>521781.976371</v>
+        <v>521783.034041</v>
       </c>
       <c r="T353" t="n">
-        <v>2993679.33222633</v>
+        <v>2996621.93633446</v>
       </c>
       <c r="U353" t="n">
-        <v>0.718807041682012</v>
+        <v>0.718926496563776</v>
       </c>
       <c r="V353" t="n">
-        <v>8.92661477213572</v>
+        <v>9.05072468725605</v>
       </c>
       <c r="W353" t="n">
-        <v>-5.84573431309118</v>
+        <v>-5.85080994323587</v>
       </c>
       <c r="X353" t="n">
-        <v>22.0612178178334</v>
+        <v>22.0614652401172</v>
       </c>
       <c r="Y353" t="n">
-        <v>-0.490434373336701</v>
+        <v>-0.490154541152521</v>
       </c>
       <c r="Z353" t="n">
-        <v>11.0086099154208</v>
+        <v>11.1129983920867</v>
       </c>
       <c r="AA353" t="n">
-        <v>0.825705455238934</v>
+        <v>0.825876254954184</v>
       </c>
       <c r="AB353" t="n">
-        <v>0.174294544761066</v>
+        <v>0.174123745045815</v>
       </c>
     </row>
     <row r="354">
@@ -44645,13 +44645,13 @@
         <v>45778</v>
       </c>
       <c r="B354" t="n">
-        <v>66116.0572907987</v>
+        <v>53076.2116268135</v>
       </c>
       <c r="C354" t="n">
         <v>6321.940797</v>
       </c>
       <c r="D354" t="n">
-        <v>131559.518335264</v>
+        <v>133031.421027753</v>
       </c>
       <c r="E354" t="n">
         <v>88481.43403</v>
@@ -44660,70 +44660,70 @@
         <v>145533.564979</v>
       </c>
       <c r="G354" t="n">
-        <v>339981.192011201</v>
+        <v>350920.297337854</v>
       </c>
       <c r="H354" t="n">
-        <v>106134.737468</v>
+        <v>106139.483397</v>
       </c>
       <c r="I354" t="n">
-        <v>43988.1836516877</v>
+        <v>44046.078038894</v>
       </c>
       <c r="J354" t="n">
-        <v>97696.684712</v>
+        <v>98077.570587</v>
       </c>
       <c r="K354" t="n">
-        <v>427395.217219555</v>
+        <v>427827.19606753</v>
       </c>
       <c r="L354" t="n">
-        <v>42155.077803</v>
+        <v>43253.707605</v>
       </c>
       <c r="M354" t="n">
-        <v>82398.585541</v>
+        <v>82398.716312</v>
       </c>
       <c r="N354" t="n">
-        <v>662860.692519482</v>
+        <v>663547.804303664</v>
       </c>
       <c r="O354" t="n">
         <v>117552.728298</v>
       </c>
       <c r="P354" t="n">
-        <v>545307.964221481</v>
+        <v>545995.076005664</v>
       </c>
       <c r="Q354" t="n">
-        <v>115126.006009248</v>
+        <v>115380.125120584</v>
       </c>
       <c r="R354" t="n">
-        <v>2495939.74432272</v>
+        <v>2498912.45153976</v>
       </c>
       <c r="S354" t="n">
-        <v>522669.840564</v>
+        <v>522670.903994</v>
       </c>
       <c r="T354" t="n">
-        <v>3018609.58488672</v>
+        <v>3021583.35553376</v>
       </c>
       <c r="U354" t="n">
-        <v>0.972628916424734</v>
+        <v>0.972731971522833</v>
       </c>
       <c r="V354" t="n">
-        <v>8.65545070343074</v>
+        <v>8.77945253589671</v>
       </c>
       <c r="W354" t="n">
-        <v>0.170159996551655</v>
+        <v>0.170160755539284</v>
       </c>
       <c r="X354" t="n">
-        <v>17.4617361049741</v>
+        <v>17.4619750939578</v>
       </c>
       <c r="Y354" t="n">
-        <v>0.832762961350553</v>
+        <v>0.832985265729813</v>
       </c>
       <c r="Z354" t="n">
-        <v>10.0844859938691</v>
+        <v>10.1883455919729</v>
       </c>
       <c r="AA354" t="n">
-        <v>0.826850798069133</v>
+        <v>0.827020855460838</v>
       </c>
       <c r="AB354" t="n">
-        <v>0.173149201930867</v>
+        <v>0.172979144539162</v>
       </c>
     </row>
     <row r="355">
@@ -44731,13 +44731,13 @@
         <v>45809</v>
       </c>
       <c r="B355" t="n">
-        <v>66512.6649895395</v>
+        <v>53389.3722416668</v>
       </c>
       <c r="C355" t="n">
         <v>6178.655729</v>
       </c>
       <c r="D355" t="n">
-        <v>134252.223716591</v>
+        <v>135721.234981652</v>
       </c>
       <c r="E355" t="n">
         <v>89575.840551</v>
@@ -44746,70 +44746,70 @@
         <v>149654.82713</v>
       </c>
       <c r="G355" t="n">
-        <v>342141.853772286</v>
+        <v>353165.782287319</v>
       </c>
       <c r="H355" t="n">
-        <v>108003.832434</v>
+        <v>108008.470441</v>
       </c>
       <c r="I355" t="n">
-        <v>45156.2278046418</v>
+        <v>45216.1515209182</v>
       </c>
       <c r="J355" t="n">
-        <v>98332.268192</v>
+        <v>98711.202837</v>
       </c>
       <c r="K355" t="n">
-        <v>431496.880512051</v>
+        <v>431944.176405803</v>
       </c>
       <c r="L355" t="n">
-        <v>42867.135968</v>
+        <v>43961.321842</v>
       </c>
       <c r="M355" t="n">
         <v>85840.520052</v>
       </c>
       <c r="N355" t="n">
-        <v>665650.695445349</v>
+        <v>666362.977171977</v>
       </c>
       <c r="O355" t="n">
         <v>118965.746702</v>
       </c>
       <c r="P355" t="n">
-        <v>546684.948743349</v>
+        <v>547397.230469977</v>
       </c>
       <c r="Q355" t="n">
-        <v>110382.498574734</v>
+        <v>110640.235229777</v>
       </c>
       <c r="R355" t="n">
-        <v>2512296.22958654</v>
+        <v>2515332.08459509</v>
       </c>
       <c r="S355" t="n">
-        <v>529400.59073</v>
+        <v>529401.660998</v>
       </c>
       <c r="T355" t="n">
-        <v>3041696.82031654</v>
+        <v>3044733.74559309</v>
       </c>
       <c r="U355" t="n">
-        <v>0.655323723300083</v>
+        <v>0.657071160905032</v>
       </c>
       <c r="V355" t="n">
-        <v>8.49394674356241</v>
+        <v>8.61934695534996</v>
       </c>
       <c r="W355" t="n">
-        <v>1.28776325772635</v>
+        <v>1.28776194591409</v>
       </c>
       <c r="X355" t="n">
-        <v>17.1543901282862</v>
+        <v>17.1546269746309</v>
       </c>
       <c r="Y355" t="n">
-        <v>0.764830123955518</v>
+        <v>0.766167513364646</v>
       </c>
       <c r="Z355" t="n">
-        <v>9.90804484589627</v>
+        <v>10.012946850792</v>
       </c>
       <c r="AA355" t="n">
-        <v>0.825952216146609</v>
+        <v>0.826125466056186</v>
       </c>
       <c r="AB355" t="n">
-        <v>0.174047783853391</v>
+        <v>0.173874533943813</v>
       </c>
     </row>
     <row r="356">
@@ -44817,85 +44817,85 @@
         <v>45839</v>
       </c>
       <c r="B356" t="n">
-        <v>68070.1674446749</v>
+        <v>55050.0153759063</v>
       </c>
       <c r="C356" t="n">
         <v>6275.368771</v>
       </c>
       <c r="D356" t="n">
-        <v>139084.467045784</v>
+        <v>140676.937099506</v>
       </c>
       <c r="E356" t="n">
         <v>91779.81108</v>
       </c>
       <c r="F356" t="n">
-        <v>156404.270707</v>
+        <v>156392.561302</v>
       </c>
       <c r="G356" t="n">
-        <v>357213.413706896</v>
+        <v>368169.706410001</v>
       </c>
       <c r="H356" t="n">
-        <v>108202.361585</v>
+        <v>108206.890821</v>
       </c>
       <c r="I356" t="n">
-        <v>45839.2214590548</v>
+        <v>45899.6074662502</v>
       </c>
       <c r="J356" t="n">
-        <v>98534.477326</v>
+        <v>98909.639319</v>
       </c>
       <c r="K356" t="n">
-        <v>435663.234973264</v>
+        <v>436110.618236552</v>
       </c>
       <c r="L356" t="n">
-        <v>44807.806343</v>
+        <v>45765.551871</v>
       </c>
       <c r="M356" t="n">
-        <v>85521.930717</v>
+        <v>85543.723316</v>
       </c>
       <c r="N356" t="n">
-        <v>668824.109517368</v>
+        <v>669546.793506908</v>
       </c>
       <c r="O356" t="n">
-        <v>119869.107652</v>
+        <v>119869.809303</v>
       </c>
       <c r="P356" t="n">
-        <v>548955.001865368</v>
+        <v>549676.984203908</v>
       </c>
       <c r="Q356" t="n">
-        <v>103000.008096586</v>
+        <v>103258.865448388</v>
       </c>
       <c r="R356" t="n">
-        <v>2536480.53467199</v>
+        <v>2539545.12926642</v>
       </c>
       <c r="S356" t="n">
-        <v>541564.223618</v>
+        <v>541587.754264</v>
       </c>
       <c r="T356" t="n">
-        <v>3078044.75829</v>
+        <v>3081132.88353042</v>
       </c>
       <c r="U356" t="n">
-        <v>0.962637478838824</v>
+        <v>0.962618209325994</v>
       </c>
       <c r="V356" t="n">
-        <v>8.69640502478905</v>
+        <v>8.82209108371259</v>
       </c>
       <c r="W356" t="n">
-        <v>2.29762359562677</v>
+        <v>2.30186154743592</v>
       </c>
       <c r="X356" t="n">
-        <v>16.3879334772727</v>
+        <v>16.3929904643148</v>
       </c>
       <c r="Y356" t="n">
-        <v>1.19498885394083</v>
+        <v>1.1954785205772</v>
       </c>
       <c r="Z356" t="n">
-        <v>9.97512125993838</v>
+        <v>10.0806983385224</v>
       </c>
       <c r="AA356" t="n">
-        <v>0.824055767168615</v>
+        <v>0.824224473680136</v>
       </c>
       <c r="AB356" t="n">
-        <v>0.175944232831385</v>
+        <v>0.175775526319864</v>
       </c>
     </row>
     <row r="357">
@@ -44903,85 +44903,85 @@
         <v>45870</v>
       </c>
       <c r="B357" t="n">
-        <v>68605.245346184</v>
+        <v>55562.6837495287</v>
       </c>
       <c r="C357" t="n">
         <v>6617.180884</v>
       </c>
       <c r="D357" t="n">
-        <v>140149.195368457</v>
+        <v>141593.631793468</v>
       </c>
       <c r="E357" t="n">
         <v>95045.312543</v>
       </c>
       <c r="F357" t="n">
-        <v>160117.77529</v>
+        <v>160116.321812</v>
       </c>
       <c r="G357" t="n">
-        <v>361477.802878349</v>
+        <v>372395.245461208</v>
       </c>
       <c r="H357" t="n">
-        <v>110979.386667</v>
+        <v>110984.162932</v>
       </c>
       <c r="I357" t="n">
-        <v>48213.3173009031</v>
+        <v>48274.2692020237</v>
       </c>
       <c r="J357" t="n">
-        <v>100172.788306</v>
+        <v>100545.655692</v>
       </c>
       <c r="K357" t="n">
-        <v>442531.703151104</v>
+        <v>442994.56035912</v>
       </c>
       <c r="L357" t="n">
-        <v>45419.587844</v>
+        <v>46585.72267</v>
       </c>
       <c r="M357" t="n">
-        <v>86611.613312</v>
+        <v>86612.140228</v>
       </c>
       <c r="N357" t="n">
-        <v>674883.987823901</v>
+        <v>675561.208646148</v>
       </c>
       <c r="O357" t="n">
-        <v>123676.921688</v>
+        <v>123658.163247</v>
       </c>
       <c r="P357" t="n">
-        <v>551207.066135901</v>
+        <v>551903.045399148</v>
       </c>
       <c r="Q357" t="n">
-        <v>103525.746577413</v>
+        <v>103741.920181466</v>
       </c>
       <c r="R357" t="n">
-        <v>2559379.99843521</v>
+        <v>2562348.48455711</v>
       </c>
       <c r="S357" t="n">
-        <v>559854.632681</v>
+        <v>559842.740243</v>
       </c>
       <c r="T357" t="n">
-        <v>3119234.63111621</v>
+        <v>3122191.22480011</v>
       </c>
       <c r="U357" t="n">
-        <v>0.90280463225314</v>
+        <v>0.897930697426808</v>
       </c>
       <c r="V357" t="n">
-        <v>8.30193168770428</v>
+        <v>8.42199972225757</v>
       </c>
       <c r="W357" t="n">
-        <v>3.3773296435293</v>
+        <v>3.37064230778408</v>
       </c>
       <c r="X357" t="n">
-        <v>17.7553292686383</v>
+        <v>17.7528279086945</v>
       </c>
       <c r="Y357" t="n">
-        <v>1.33818303698419</v>
+        <v>1.33257288217459</v>
       </c>
       <c r="Z357" t="n">
-        <v>9.88527127085996</v>
+        <v>9.98474374402107</v>
       </c>
       <c r="AA357" t="n">
-        <v>0.820515383134017</v>
+        <v>0.820689157090677</v>
       </c>
       <c r="AB357" t="n">
-        <v>0.179484616865983</v>
+        <v>0.179310842909323</v>
       </c>
     </row>
     <row r="358">
@@ -44989,13 +44989,13 @@
         <v>45901</v>
       </c>
       <c r="B358" t="n">
-        <v>67957.5834376285</v>
+        <v>54887.6033892498</v>
       </c>
       <c r="C358" t="n">
         <v>6511.33062</v>
       </c>
       <c r="D358" t="n">
-        <v>137517.644521597</v>
+        <v>138992.141443604</v>
       </c>
       <c r="E358" t="n">
         <v>95094.906327</v>
@@ -45004,70 +45004,70 @@
         <v>160881.731691</v>
       </c>
       <c r="G358" t="n">
-        <v>358909.253889198</v>
+        <v>370684.549087124</v>
       </c>
       <c r="H358" t="n">
-        <v>111665.575169</v>
+        <v>111670.235433</v>
       </c>
       <c r="I358" t="n">
-        <v>48011.2537886496</v>
+        <v>48135.8360546402</v>
       </c>
       <c r="J358" t="n">
-        <v>101016.828703</v>
+        <v>101386.31433</v>
       </c>
       <c r="K358" t="n">
-        <v>447039.711355287</v>
+        <v>447979.685709741</v>
       </c>
       <c r="L358" t="n">
-        <v>46664.719259</v>
+        <v>47834.102053</v>
       </c>
       <c r="M358" t="n">
         <v>91307.80519</v>
       </c>
       <c r="N358" t="n">
-        <v>675678.286682471</v>
+        <v>677159.168255376</v>
       </c>
       <c r="O358" t="n">
         <v>123781.770953</v>
       </c>
       <c r="P358" t="n">
-        <v>551896.515729471</v>
+        <v>553377.397302376</v>
       </c>
       <c r="Q358" t="n">
-        <v>102004.854684167</v>
+        <v>102548.959329308</v>
       </c>
       <c r="R358" t="n">
-        <v>2572463.72030247</v>
+        <v>2578756.85121842</v>
       </c>
       <c r="S358" t="n">
-        <v>553476.051698</v>
+        <v>553476.68595</v>
       </c>
       <c r="T358" t="n">
-        <v>3125939.77200047</v>
+        <v>3132233.53716842</v>
       </c>
       <c r="U358" t="n">
-        <v>0.511206693623301</v>
+        <v>0.640364367305946</v>
       </c>
       <c r="V358" t="n">
-        <v>8.29373341561956</v>
+        <v>8.55315633216616</v>
       </c>
       <c r="W358" t="n">
-        <v>-1.13932807029831</v>
+        <v>-1.13711473515524</v>
       </c>
       <c r="X358" t="n">
-        <v>14.6935617246212</v>
+        <v>14.6936931569039</v>
       </c>
       <c r="Y358" t="n">
-        <v>0.214961093896848</v>
+        <v>0.321643091189916</v>
       </c>
       <c r="Z358" t="n">
-        <v>9.37432830805447</v>
+        <v>9.5899268441783</v>
       </c>
       <c r="AA358" t="n">
-        <v>0.822940909912734</v>
+        <v>0.823296481765421</v>
       </c>
       <c r="AB358" t="n">
-        <v>0.177059090087266</v>
+        <v>0.176703518234579</v>
       </c>
     </row>
     <row r="359">
@@ -45075,13 +45075,13 @@
         <v>45931</v>
       </c>
       <c r="B359" t="n">
-        <v>68481.3640357164</v>
+        <v>55510.3895955422</v>
       </c>
       <c r="C359" t="n">
         <v>6264.321892</v>
       </c>
       <c r="D359" t="n">
-        <v>146802.393909597</v>
+        <v>148286.846526018</v>
       </c>
       <c r="E359" t="n">
         <v>102005.896279</v>
@@ -45090,70 +45090,70 @@
         <v>165606.831831</v>
       </c>
       <c r="G359" t="n">
-        <v>375073.821822198</v>
+        <v>387123.794505757</v>
       </c>
       <c r="H359" t="n">
-        <v>111555.080666</v>
+        <v>111559.635803</v>
       </c>
       <c r="I359" t="n">
-        <v>48237.8809156496</v>
+        <v>48389.4949085512</v>
       </c>
       <c r="J359" t="n">
-        <v>106543.343541</v>
+        <v>106910.8339</v>
       </c>
       <c r="K359" t="n">
-        <v>454417.294107287</v>
+        <v>455561.030740054</v>
       </c>
       <c r="L359" t="n">
-        <v>46462.403884</v>
+        <v>47614.549448</v>
       </c>
       <c r="M359" t="n">
-        <v>86443.623947</v>
+        <v>86443.630292</v>
       </c>
       <c r="N359" t="n">
-        <v>675438.484359471</v>
+        <v>677239.551930214</v>
       </c>
       <c r="O359" t="n">
         <v>123805.478146</v>
       </c>
       <c r="P359" t="n">
-        <v>551633.006213471</v>
+        <v>553434.073784214</v>
       </c>
       <c r="Q359" t="n">
-        <v>101534.974802167</v>
+        <v>102196.891390117</v>
       </c>
       <c r="R359" t="n">
-        <v>2581391.17127056</v>
+        <v>2589038.22189047</v>
       </c>
       <c r="S359" t="n">
         <v>588915.029081</v>
       </c>
       <c r="T359" t="n">
-        <v>3170306.20035156</v>
+        <v>3177953.25097147</v>
       </c>
       <c r="U359" t="n">
-        <v>0.347038945491462</v>
+        <v>0.398694846595937</v>
       </c>
       <c r="V359" t="n">
-        <v>7.79077329909956</v>
+        <v>8.10477501748548</v>
       </c>
       <c r="W359" t="n">
-        <v>6.40298297898843</v>
+        <v>6.402861047376</v>
       </c>
       <c r="X359" t="n">
         <v>18.8319942352396</v>
       </c>
       <c r="Y359" t="n">
-        <v>1.41929888568184</v>
+        <v>1.45965213833892</v>
       </c>
       <c r="Z359" t="n">
-        <v>9.68389266159368</v>
+        <v>9.94398096202724</v>
       </c>
       <c r="AA359" t="n">
-        <v>0.814240331417926</v>
+        <v>0.814687321501355</v>
       </c>
       <c r="AB359" t="n">
-        <v>0.185759668582074</v>
+        <v>0.185312678498645</v>
       </c>
     </row>
     <row r="360">
@@ -45161,13 +45161,13 @@
         <v>45962</v>
       </c>
       <c r="B360" t="n">
-        <v>67965.6327138443</v>
+        <v>54975.2837555481</v>
       </c>
       <c r="C360" t="n">
         <v>6829.098867</v>
       </c>
       <c r="D360" t="n">
-        <v>145093.491368597</v>
+        <v>146587.708812178</v>
       </c>
       <c r="E360" t="n">
         <v>102159.336742</v>
@@ -45176,52 +45176,52 @@
         <v>165496.968242</v>
       </c>
       <c r="G360" t="n">
-        <v>375739.097054198</v>
+        <v>388311.401596094</v>
       </c>
       <c r="H360" t="n">
-        <v>109339.325921</v>
+        <v>109343.76519</v>
       </c>
       <c r="I360" t="n">
-        <v>48432.1849316496</v>
+        <v>48620.5796719043</v>
       </c>
       <c r="J360" t="n">
-        <v>106033.576029</v>
+        <v>106396.319323</v>
       </c>
       <c r="K360" t="n">
-        <v>457387.759304287</v>
+        <v>458810.049569084</v>
       </c>
       <c r="L360" t="n">
-        <v>46772.409791</v>
+        <v>47913.671221</v>
       </c>
       <c r="M360" t="n">
-        <v>85979.144611</v>
+        <v>85979.144612</v>
       </c>
       <c r="N360" t="n">
-        <v>681495.422503471</v>
+        <v>683734.828707729</v>
       </c>
       <c r="O360" t="n">
         <v>129629.544688</v>
       </c>
       <c r="P360" t="n">
-        <v>551865.877815471</v>
+        <v>554105.284019729</v>
       </c>
       <c r="Q360" t="n">
-        <v>102544.687114167</v>
+        <v>103369.731606775</v>
       </c>
       <c r="R360" t="n">
-        <v>2599720.92456469</v>
+        <v>2609220.08349204</v>
       </c>
       <c r="S360" t="n">
         <v>583042.633132</v>
       </c>
       <c r="T360" t="n">
-        <v>3182763.55769669</v>
+        <v>3192262.71662404</v>
       </c>
       <c r="U360" t="n">
-        <v>0.710072673143358</v>
+        <v>0.779511921876486</v>
       </c>
       <c r="V360" t="n">
-        <v>7.24824124187997</v>
+        <v>7.63483646311702</v>
       </c>
       <c r="W360" t="n">
         <v>-0.997155049373399</v>
@@ -45230,16 +45230,16 @@
         <v>14.8369790074026</v>
       </c>
       <c r="Y360" t="n">
-        <v>0.392938617214522</v>
+        <v>0.450273006634094</v>
       </c>
       <c r="Z360" t="n">
-        <v>8.56244693946202</v>
+        <v>8.88204161398929</v>
       </c>
       <c r="AA360" t="n">
-        <v>0.81681245792762</v>
+        <v>0.817357565811941</v>
       </c>
       <c r="AB360" t="n">
-        <v>0.18318754207238</v>
+        <v>0.182642434188059</v>
       </c>
     </row>
     <row r="361">
@@ -45247,13 +45247,13 @@
         <v>45992</v>
       </c>
       <c r="B361" t="n">
-        <v>71643.452190932</v>
+        <v>58642.5451262784</v>
       </c>
       <c r="C361" t="n">
         <v>6792.944137</v>
       </c>
       <c r="D361" t="n">
-        <v>145416.198460597</v>
+        <v>146934.314206673</v>
       </c>
       <c r="E361" t="n">
         <v>109565.342563</v>
@@ -45262,52 +45262,52 @@
         <v>167401.351336</v>
       </c>
       <c r="G361" t="n">
-        <v>363402.935898198</v>
+        <v>376309.878111897</v>
       </c>
       <c r="H361" t="n">
-        <v>111732.464004</v>
+        <v>111736.78418</v>
       </c>
       <c r="I361" t="n">
-        <v>48695.1639476496</v>
+        <v>48902.1027905668</v>
       </c>
       <c r="J361" t="n">
-        <v>112655.268559</v>
+        <v>113013.780635</v>
       </c>
       <c r="K361" t="n">
-        <v>459794.177036287</v>
+        <v>461356.466416015</v>
       </c>
       <c r="L361" t="n">
-        <v>46905.693154</v>
+        <v>47954.55983</v>
       </c>
       <c r="M361" t="n">
         <v>84025.302035</v>
       </c>
       <c r="N361" t="n">
-        <v>673590.862483471</v>
+        <v>676050.698294629</v>
       </c>
       <c r="O361" t="n">
         <v>125578.277228</v>
       </c>
       <c r="P361" t="n">
-        <v>548012.585255471</v>
+        <v>550472.421066629</v>
       </c>
       <c r="Q361" t="n">
-        <v>99823.2794081669</v>
+        <v>100730.333392454</v>
       </c>
       <c r="R361" t="n">
-        <v>2584121.25209177</v>
+        <v>2594553.05574414</v>
       </c>
       <c r="S361" t="n">
         <v>590914.045605</v>
       </c>
       <c r="T361" t="n">
-        <v>3175035.29769677</v>
+        <v>3185467.10134914</v>
       </c>
       <c r="U361" t="n">
-        <v>-0.600051810388991</v>
+        <v>-0.562123058943731</v>
       </c>
       <c r="V361" t="n">
-        <v>6.91322938279011</v>
+        <v>7.3396306505328</v>
       </c>
       <c r="W361" t="n">
         <v>1.35005778749251</v>
@@ -45316,16 +45316,16 @@
         <v>15.0095129731572</v>
       </c>
       <c r="Y361" t="n">
-        <v>-0.242816026381332</v>
+        <v>-0.212877694542846</v>
       </c>
       <c r="Z361" t="n">
-        <v>8.33257038975028</v>
+        <v>8.68416655620494</v>
       </c>
       <c r="AA361" t="n">
-        <v>0.813887409052221</v>
+        <v>0.814496892667725</v>
       </c>
       <c r="AB361" t="n">
-        <v>0.186112590947779</v>
+        <v>0.185503107332275</v>
       </c>
     </row>
     <row r="362">
@@ -45333,85 +45333,85 @@
         <v>46023</v>
       </c>
       <c r="B362" t="n">
-        <v>71338.5330609224</v>
+        <v>58850.3722232784</v>
       </c>
       <c r="C362" t="n">
-        <v>6772.006653</v>
+        <v>6770.43739</v>
       </c>
       <c r="D362" t="n">
-        <v>145844.241355597</v>
+        <v>147317.833824673</v>
       </c>
       <c r="E362" t="n">
-        <v>111389.600907</v>
+        <v>111629.220653</v>
       </c>
       <c r="F362" t="n">
-        <v>168095.770937</v>
+        <v>166121.723833</v>
       </c>
       <c r="G362" t="n">
-        <v>363373.687045198</v>
+        <v>375622.078352897</v>
       </c>
       <c r="H362" t="n">
-        <v>110191.325048</v>
+        <v>112264.706558</v>
       </c>
       <c r="I362" t="n">
-        <v>48382.0873346496</v>
+        <v>48558.3089095668</v>
       </c>
       <c r="J362" t="n">
-        <v>113032.494184</v>
+        <v>113376.854688</v>
       </c>
       <c r="K362" t="n">
-        <v>460998.570025287</v>
+        <v>462525.406099015</v>
       </c>
       <c r="L362" t="n">
-        <v>47031.356846</v>
+        <v>48112.946054</v>
       </c>
       <c r="M362" t="n">
-        <v>83475.453981</v>
+        <v>83431.795498</v>
       </c>
       <c r="N362" t="n">
-        <v>677287.559285471</v>
+        <v>680067.373106629</v>
       </c>
       <c r="O362" t="n">
-        <v>123697.740921</v>
+        <v>123980.352047</v>
       </c>
       <c r="P362" t="n">
-        <v>553589.818364471</v>
+        <v>556087.021059629</v>
       </c>
       <c r="Q362" t="n">
-        <v>100382.997607167</v>
+        <v>101097.079339454</v>
       </c>
       <c r="R362" t="n">
-        <v>2594776.70009276</v>
+        <v>2605613.05922614</v>
       </c>
       <c r="S362" t="n">
-        <v>590106.543463</v>
+        <v>590200.45041</v>
       </c>
       <c r="T362" t="n">
-        <v>3184883.24355576</v>
+        <v>3195813.50963614</v>
       </c>
       <c r="U362" t="n">
-        <v>0.412343189870246</v>
+        <v>0.426277792142815</v>
       </c>
       <c r="V362" t="n">
-        <v>6.91536419437435</v>
+        <v>7.23545283168325</v>
       </c>
       <c r="W362" t="n">
-        <v>-0.136653062827985</v>
+        <v>-0.120761251201829</v>
       </c>
       <c r="X362" t="n">
-        <v>11.880370054899</v>
+        <v>11.8979380429352</v>
       </c>
       <c r="Y362" t="n">
-        <v>0.310168074859951</v>
+        <v>0.324800349770316</v>
       </c>
       <c r="Z362" t="n">
-        <v>7.80176194420998</v>
+        <v>8.06703800959865</v>
       </c>
       <c r="AA362" t="n">
-        <v>0.814716428096066</v>
+        <v>0.815320747399557</v>
       </c>
       <c r="AB362" t="n">
-        <v>0.185283571903934</v>
+        <v>0.184679252600443</v>
       </c>
     </row>
     <row r="363">
@@ -45419,85 +45419,85 @@
         <v>46054</v>
       </c>
       <c r="B363" t="n">
-        <v>70880.5865787603</v>
+        <v>57973.2475572784</v>
       </c>
       <c r="C363" t="n">
-        <v>6662.90896</v>
+        <v>6666.545969</v>
       </c>
       <c r="D363" t="n">
-        <v>143866.555455597</v>
+        <v>145474.863034673</v>
       </c>
       <c r="E363" t="n">
-        <v>113758.33006</v>
+        <v>113485.59868</v>
       </c>
       <c r="F363" t="n">
-        <v>168898.076247</v>
+        <v>169155.843628</v>
       </c>
       <c r="G363" t="n">
-        <v>359789.614165198</v>
+        <v>371614.953204897</v>
       </c>
       <c r="H363" t="n">
-        <v>106135.06502</v>
+        <v>105893.576773</v>
       </c>
       <c r="I363" t="n">
-        <v>47851.3100846496</v>
+        <v>47970.8255175668</v>
       </c>
       <c r="J363" t="n">
-        <v>112768.313421</v>
+        <v>113084.754742</v>
       </c>
       <c r="K363" t="n">
-        <v>460511.790020287</v>
+        <v>462183.210062015</v>
       </c>
       <c r="L363" t="n">
-        <v>46874.314026</v>
+        <v>47851.46972</v>
       </c>
       <c r="M363" t="n">
-        <v>82870.224519</v>
+        <v>82868.53079</v>
       </c>
       <c r="N363" t="n">
-        <v>680377.124616471</v>
+        <v>683670.093517629</v>
       </c>
       <c r="O363" t="n">
-        <v>125456.273013</v>
+        <v>125530.159585</v>
       </c>
       <c r="P363" t="n">
-        <v>554920.851603471</v>
+        <v>558139.933932629</v>
       </c>
       <c r="Q363" t="n">
-        <v>101718.039337167</v>
+        <v>102571.458437454</v>
       </c>
       <c r="R363" t="n">
-        <v>2605780.3084786</v>
+        <v>2618569.74193914</v>
       </c>
       <c r="S363" t="n">
-        <v>577559.068649</v>
+        <v>575565.323212</v>
       </c>
       <c r="T363" t="n">
-        <v>3183339.3771276</v>
+        <v>3194135.06515114</v>
       </c>
       <c r="U363" t="n">
-        <v>0.424067642716386</v>
+        <v>0.497260430405122</v>
       </c>
       <c r="V363" t="n">
-        <v>6.74513100005452</v>
+        <v>7.14225576759655</v>
       </c>
       <c r="W363" t="n">
-        <v>-2.12630667342985</v>
+        <v>-2.47968756849192</v>
       </c>
       <c r="X363" t="n">
-        <v>6.85170817222855</v>
+        <v>6.48263289180817</v>
       </c>
       <c r="Y363" t="n">
-        <v>-0.0484748202712271</v>
+        <v>-0.0525201010615706</v>
       </c>
       <c r="Z363" t="n">
-        <v>6.76445170034117</v>
+        <v>7.02279245580524</v>
       </c>
       <c r="AA363" t="n">
-        <v>0.818568176299775</v>
+        <v>0.81980557757511</v>
       </c>
       <c r="AB363" t="n">
-        <v>0.181431823700225</v>
+        <v>0.180194422424891</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14329,7 +14329,9 @@
       </c>
       <c r="D314"/>
       <c r="E314"/>
-      <c r="F314"/>
+      <c r="F314" t="n">
+        <v>129.96287646414</v>
+      </c>
       <c r="G314" t="n">
         <v>4.89226213151006</v>
       </c>
@@ -14346,8 +14348,12 @@
       <c r="L314"/>
       <c r="M314"/>
       <c r="N314"/>
-      <c r="O314"/>
-      <c r="P314"/>
+      <c r="O314" t="n">
+        <v>3.48006152430886</v>
+      </c>
+      <c r="P314" t="n">
+        <v>-2.09683553036542</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45419,85 +45425,85 @@
         <v>46054</v>
       </c>
       <c r="B363" t="n">
-        <v>57973.2475572784</v>
+        <v>57549.7794852784</v>
       </c>
       <c r="C363" t="n">
-        <v>6666.545969</v>
+        <v>6622.99956</v>
       </c>
       <c r="D363" t="n">
-        <v>145474.863034673</v>
+        <v>145130.179789673</v>
       </c>
       <c r="E363" t="n">
-        <v>113485.59868</v>
+        <v>113137.980913</v>
       </c>
       <c r="F363" t="n">
-        <v>169155.843628</v>
+        <v>169773.175196</v>
       </c>
       <c r="G363" t="n">
-        <v>371614.953204897</v>
+        <v>370377.506594897</v>
       </c>
       <c r="H363" t="n">
-        <v>105893.576773</v>
+        <v>104869.268935</v>
       </c>
       <c r="I363" t="n">
-        <v>47970.8255175668</v>
+        <v>47973.2077435668</v>
       </c>
       <c r="J363" t="n">
-        <v>113084.754742</v>
+        <v>112965.661497</v>
       </c>
       <c r="K363" t="n">
-        <v>462183.210062015</v>
+        <v>462467.834094015</v>
       </c>
       <c r="L363" t="n">
-        <v>47851.46972</v>
+        <v>47820.907982</v>
       </c>
       <c r="M363" t="n">
-        <v>82868.53079</v>
+        <v>82962.31583</v>
       </c>
       <c r="N363" t="n">
-        <v>683670.093517629</v>
+        <v>683333.497783629</v>
       </c>
       <c r="O363" t="n">
-        <v>125530.159585</v>
+        <v>125281.41503</v>
       </c>
       <c r="P363" t="n">
-        <v>558139.933932629</v>
+        <v>558052.082753629</v>
       </c>
       <c r="Q363" t="n">
-        <v>102571.458437454</v>
+        <v>103106.758983454</v>
       </c>
       <c r="R363" t="n">
-        <v>2618569.74193914</v>
+        <v>2619744.14868014</v>
       </c>
       <c r="S363" t="n">
-        <v>575565.323212</v>
+        <v>571680.423491</v>
       </c>
       <c r="T363" t="n">
-        <v>3194135.06515114</v>
+        <v>3191424.57217114</v>
       </c>
       <c r="U363" t="n">
-        <v>0.497260430405122</v>
+        <v>0.542332615503427</v>
       </c>
       <c r="V363" t="n">
-        <v>7.14225576759655</v>
+        <v>7.19030817781274</v>
       </c>
       <c r="W363" t="n">
-        <v>-2.47968756849192</v>
+        <v>-3.13792151567058</v>
       </c>
       <c r="X363" t="n">
-        <v>6.48263289180817</v>
+        <v>5.76390586964468</v>
       </c>
       <c r="Y363" t="n">
-        <v>-0.0525201010615706</v>
+        <v>-0.137333966821473</v>
       </c>
       <c r="Z363" t="n">
-        <v>7.02279245580524</v>
+        <v>6.9319745906447</v>
       </c>
       <c r="AA363" t="n">
-        <v>0.81980557757511</v>
+        <v>0.820869830834798</v>
       </c>
       <c r="AB363" t="n">
-        <v>0.180194422424891</v>
+        <v>0.179130169165202</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14327,8 +14327,12 @@
       <c r="C314" t="n">
         <v>137.7394</v>
       </c>
-      <c r="D314"/>
-      <c r="E314"/>
+      <c r="D314" t="n">
+        <v>174.258530673772</v>
+      </c>
+      <c r="E314" t="n">
+        <v>152.015922353681</v>
+      </c>
       <c r="F314" t="n">
         <v>129.96287646414</v>
       </c>
@@ -14344,10 +14348,18 @@
       <c r="J314" t="n">
         <v>0.396441574249873</v>
       </c>
-      <c r="K314"/>
-      <c r="L314"/>
-      <c r="M314"/>
-      <c r="N314"/>
+      <c r="K314" t="n">
+        <v>4.51117024012211</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0.0983850932327002</v>
+      </c>
+      <c r="M314" t="n">
+        <v>3.61702837827826</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0.99462644080861</v>
+      </c>
       <c r="O314" t="n">
         <v>3.48006152430886</v>
       </c>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45437,85 +45437,85 @@
         <v>46054</v>
       </c>
       <c r="B363" t="n">
-        <v>57549.7794852784</v>
+        <v>57413.8573832784</v>
       </c>
       <c r="C363" t="n">
-        <v>6622.99956</v>
+        <v>6612.302284</v>
       </c>
       <c r="D363" t="n">
-        <v>145130.179789673</v>
+        <v>144624.292892673</v>
       </c>
       <c r="E363" t="n">
-        <v>113137.980913</v>
+        <v>112826.32214</v>
       </c>
       <c r="F363" t="n">
-        <v>169773.175196</v>
+        <v>170120.697888</v>
       </c>
       <c r="G363" t="n">
-        <v>370377.506594897</v>
+        <v>369888.947772897</v>
       </c>
       <c r="H363" t="n">
-        <v>104869.268935</v>
+        <v>104518.737961</v>
       </c>
       <c r="I363" t="n">
-        <v>47973.2077435668</v>
+        <v>47899.5585025668</v>
       </c>
       <c r="J363" t="n">
-        <v>112965.661497</v>
+        <v>112780.197267</v>
       </c>
       <c r="K363" t="n">
-        <v>462467.834094015</v>
+        <v>462523.116982015</v>
       </c>
       <c r="L363" t="n">
-        <v>47820.907982</v>
+        <v>47756.054429</v>
       </c>
       <c r="M363" t="n">
-        <v>82962.31583</v>
+        <v>83007.088108</v>
       </c>
       <c r="N363" t="n">
-        <v>683333.497783629</v>
+        <v>684785.548571629</v>
       </c>
       <c r="O363" t="n">
-        <v>125281.41503</v>
+        <v>126450.669804</v>
       </c>
       <c r="P363" t="n">
-        <v>558052.082753629</v>
+        <v>558334.878767629</v>
       </c>
       <c r="Q363" t="n">
-        <v>103106.758983454</v>
+        <v>101791.159385454</v>
       </c>
       <c r="R363" t="n">
-        <v>2619744.14868014</v>
+        <v>2621902.49303914</v>
       </c>
       <c r="S363" t="n">
-        <v>571680.423491</v>
+        <v>569430.9371</v>
       </c>
       <c r="T363" t="n">
-        <v>3191424.57217114</v>
+        <v>3191333.43013914</v>
       </c>
       <c r="U363" t="n">
-        <v>0.542332615503427</v>
+        <v>0.625167031433183</v>
       </c>
       <c r="V363" t="n">
-        <v>7.19030817781274</v>
+        <v>7.27861970132988</v>
       </c>
       <c r="W363" t="n">
-        <v>-3.13792151567058</v>
+        <v>-3.51906090474379</v>
       </c>
       <c r="X363" t="n">
-        <v>5.76390586964468</v>
+        <v>5.34773897440637</v>
       </c>
       <c r="Y363" t="n">
-        <v>-0.137333966821473</v>
+        <v>-0.140185886425837</v>
       </c>
       <c r="Z363" t="n">
-        <v>6.9319745906447</v>
+        <v>6.92892078278253</v>
       </c>
       <c r="AA363" t="n">
-        <v>0.820869830834798</v>
+        <v>0.82156958852301</v>
       </c>
       <c r="AB363" t="n">
-        <v>0.179130169165202</v>
+        <v>0.17843041147699</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45437,85 +45437,85 @@
         <v>46054</v>
       </c>
       <c r="B363" t="n">
-        <v>57413.8573832784</v>
+        <v>57442.1229722784</v>
       </c>
       <c r="C363" t="n">
-        <v>6612.302284</v>
+        <v>6562.121351</v>
       </c>
       <c r="D363" t="n">
-        <v>144624.292892673</v>
+        <v>149229.906240673</v>
       </c>
       <c r="E363" t="n">
-        <v>112826.32214</v>
+        <v>111357.96756</v>
       </c>
       <c r="F363" t="n">
-        <v>170120.697888</v>
+        <v>174444.064677</v>
       </c>
       <c r="G363" t="n">
-        <v>369888.947772897</v>
+        <v>369624.112691897</v>
       </c>
       <c r="H363" t="n">
-        <v>104518.737961</v>
+        <v>103878.862811</v>
       </c>
       <c r="I363" t="n">
-        <v>47899.5585025668</v>
+        <v>49315.5566525668</v>
       </c>
       <c r="J363" t="n">
-        <v>112780.197267</v>
+        <v>113339.3614</v>
       </c>
       <c r="K363" t="n">
-        <v>462523.116982015</v>
+        <v>463729.956696015</v>
       </c>
       <c r="L363" t="n">
-        <v>47756.054429</v>
+        <v>48585.400534</v>
       </c>
       <c r="M363" t="n">
-        <v>83007.088108</v>
+        <v>83313.000864</v>
       </c>
       <c r="N363" t="n">
-        <v>684785.548571629</v>
+        <v>682865.682473629</v>
       </c>
       <c r="O363" t="n">
-        <v>126450.669804</v>
+        <v>123451.201212</v>
       </c>
       <c r="P363" t="n">
-        <v>558334.878767629</v>
+        <v>559414.481261629</v>
       </c>
       <c r="Q363" t="n">
-        <v>101791.159385454</v>
+        <v>101210.616282454</v>
       </c>
       <c r="R363" t="n">
-        <v>2621902.49303914</v>
+        <v>2637025.21563814</v>
       </c>
       <c r="S363" t="n">
-        <v>569430.9371</v>
+        <v>560739.200042</v>
       </c>
       <c r="T363" t="n">
-        <v>3191333.43013914</v>
+        <v>3197764.41568014</v>
       </c>
       <c r="U363" t="n">
-        <v>0.625167031433183</v>
+        <v>1.20555722196638</v>
       </c>
       <c r="V363" t="n">
-        <v>7.27861970132988</v>
+        <v>7.89738596394034</v>
       </c>
       <c r="W363" t="n">
-        <v>-3.51906090474379</v>
+        <v>-4.99173634102346</v>
       </c>
       <c r="X363" t="n">
-        <v>5.34773897440637</v>
+        <v>3.73972158869211</v>
       </c>
       <c r="Y363" t="n">
-        <v>-0.140185886425837</v>
+        <v>0.0610456786078739</v>
       </c>
       <c r="Z363" t="n">
-        <v>6.92892078278253</v>
+        <v>7.14439759162191</v>
       </c>
       <c r="AA363" t="n">
-        <v>0.82156958852301</v>
+        <v>0.824646494503337</v>
       </c>
       <c r="AB363" t="n">
-        <v>0.17843041147699</v>
+        <v>0.175353505496663</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45518,6 +45518,92 @@
         <v>0.175353505496663</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B364" t="n">
+        <v>57383.5821242784</v>
+      </c>
+      <c r="C364" t="n">
+        <v>6545.1168</v>
+      </c>
+      <c r="D364" t="n">
+        <v>148807.990047673</v>
+      </c>
+      <c r="E364" t="n">
+        <v>111054.692287</v>
+      </c>
+      <c r="F364" t="n">
+        <v>174090.447078</v>
+      </c>
+      <c r="G364" t="n">
+        <v>367842.070083897</v>
+      </c>
+      <c r="H364" t="n">
+        <v>103354.203762</v>
+      </c>
+      <c r="I364" t="n">
+        <v>49333.2908315668</v>
+      </c>
+      <c r="J364" t="n">
+        <v>112954.480537</v>
+      </c>
+      <c r="K364" t="n">
+        <v>463155.180369015</v>
+      </c>
+      <c r="L364" t="n">
+        <v>48399.774693</v>
+      </c>
+      <c r="M364" t="n">
+        <v>82862.037167</v>
+      </c>
+      <c r="N364" t="n">
+        <v>681408.799605629</v>
+      </c>
+      <c r="O364" t="n">
+        <v>123332.46088</v>
+      </c>
+      <c r="P364" t="n">
+        <v>558076.338725629</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>99229.1136174537</v>
+      </c>
+      <c r="R364" t="n">
+        <v>2630004.33772014</v>
+      </c>
+      <c r="S364" t="n">
+        <v>557825.240889</v>
+      </c>
+      <c r="T364" t="n">
+        <v>3187829.57860914</v>
+      </c>
+      <c r="U364" t="n">
+        <v>-0.266242350523027</v>
+      </c>
+      <c r="V364" t="n">
+        <v>7.03371978313454</v>
+      </c>
+      <c r="W364" t="n">
+        <v>-0.519663892373079</v>
+      </c>
+      <c r="X364" t="n">
+        <v>0.652553257973376</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>-0.310680706254796</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>5.85934277200477</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>0.825014095912749</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>0.174985904087251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45523,85 +45523,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57383.5821242784</v>
+        <v>57700.9186292784</v>
       </c>
       <c r="C364" t="n">
-        <v>6545.1168</v>
+        <v>6539.69096</v>
       </c>
       <c r="D364" t="n">
-        <v>148807.990047673</v>
+        <v>147630.026676673</v>
       </c>
       <c r="E364" t="n">
-        <v>111054.692287</v>
+        <v>111343.47525</v>
       </c>
       <c r="F364" t="n">
-        <v>174090.447078</v>
+        <v>173835.487481</v>
       </c>
       <c r="G364" t="n">
-        <v>367842.070083897</v>
+        <v>367836.755627897</v>
       </c>
       <c r="H364" t="n">
-        <v>103354.203762</v>
+        <v>103480.78445</v>
       </c>
       <c r="I364" t="n">
-        <v>49333.2908315668</v>
+        <v>50210.7366405668</v>
       </c>
       <c r="J364" t="n">
-        <v>112954.480537</v>
+        <v>113043.270956</v>
       </c>
       <c r="K364" t="n">
-        <v>463155.180369015</v>
+        <v>463302.759533015</v>
       </c>
       <c r="L364" t="n">
-        <v>48399.774693</v>
+        <v>48395.878986</v>
       </c>
       <c r="M364" t="n">
-        <v>82862.037167</v>
+        <v>82717.315535</v>
       </c>
       <c r="N364" t="n">
-        <v>681408.799605629</v>
+        <v>680227.009958629</v>
       </c>
       <c r="O364" t="n">
-        <v>123332.46088</v>
+        <v>122169.286874</v>
       </c>
       <c r="P364" t="n">
-        <v>558076.338725629</v>
+        <v>558057.723084629</v>
       </c>
       <c r="Q364" t="n">
-        <v>99229.1136174537</v>
+        <v>99228.6365274537</v>
       </c>
       <c r="R364" t="n">
-        <v>2630004.33772014</v>
+        <v>2627448.81388514</v>
       </c>
       <c r="S364" t="n">
-        <v>557825.240889</v>
+        <v>558270.943285</v>
       </c>
       <c r="T364" t="n">
-        <v>3187829.57860914</v>
+        <v>3185719.75717014</v>
       </c>
       <c r="U364" t="n">
-        <v>-0.266242350523027</v>
+        <v>-0.363151694424835</v>
       </c>
       <c r="V364" t="n">
-        <v>7.03371978313454</v>
+        <v>6.92971720864006</v>
       </c>
       <c r="W364" t="n">
-        <v>-0.519663892373079</v>
+        <v>-0.440179098735205</v>
       </c>
       <c r="X364" t="n">
-        <v>0.652553257973376</v>
+        <v>0.732974653174345</v>
       </c>
       <c r="Y364" t="n">
-        <v>-0.310680706254796</v>
+        <v>-0.376658719789968</v>
       </c>
       <c r="Z364" t="n">
-        <v>5.85934277200477</v>
+        <v>5.78928121275533</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.825014095912749</v>
+        <v>0.82475830084285</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.174985904087251</v>
+        <v>0.17524169915715</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="368">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -1116,6 +1116,9 @@
   <si>
     <t xml:space="preserve">126.6108</t>
   </si>
+  <si>
+    <t xml:space="preserve">126.974</t>
+  </si>
 </sst>
 </file>
 
@@ -14367,6 +14370,38 @@
         <v>-2.09683553036542</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B315" t="n">
+        <v>134.54</v>
+      </c>
+      <c r="C315" t="n">
+        <v>137.7744</v>
+      </c>
+      <c r="D315"/>
+      <c r="E315"/>
+      <c r="F315"/>
+      <c r="G315" t="n">
+        <v>4.76226814126008</v>
+      </c>
+      <c r="H315" t="n">
+        <v>0.33028305608398</v>
+      </c>
+      <c r="I315" t="n">
+        <v>4.67238597099018</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0.0254103038056064</v>
+      </c>
+      <c r="K315"/>
+      <c r="L315"/>
+      <c r="M315"/>
+      <c r="N315"/>
+      <c r="O315"/>
+      <c r="P315"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -45523,85 +45558,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57700.9186292784</v>
+        <v>57387.6969802784</v>
       </c>
       <c r="C364" t="n">
-        <v>6539.69096</v>
+        <v>6542.638972</v>
       </c>
       <c r="D364" t="n">
-        <v>147630.026676673</v>
+        <v>147076.172498673</v>
       </c>
       <c r="E364" t="n">
-        <v>111343.47525</v>
+        <v>112295.537496</v>
       </c>
       <c r="F364" t="n">
-        <v>173835.487481</v>
+        <v>173016.358873</v>
       </c>
       <c r="G364" t="n">
-        <v>367836.755627897</v>
+        <v>371427.565263897</v>
       </c>
       <c r="H364" t="n">
-        <v>103480.78445</v>
+        <v>106091.630069</v>
       </c>
       <c r="I364" t="n">
-        <v>50210.7366405668</v>
+        <v>49339.9698875668</v>
       </c>
       <c r="J364" t="n">
-        <v>113043.270956</v>
+        <v>113458.516269</v>
       </c>
       <c r="K364" t="n">
-        <v>463302.759533015</v>
+        <v>464112.884212015</v>
       </c>
       <c r="L364" t="n">
-        <v>48395.878986</v>
+        <v>48700.712507</v>
       </c>
       <c r="M364" t="n">
-        <v>82717.315535</v>
+        <v>82620.275371</v>
       </c>
       <c r="N364" t="n">
-        <v>680227.009958629</v>
+        <v>680718.582196629</v>
       </c>
       <c r="O364" t="n">
-        <v>122169.286874</v>
+        <v>122278.707368</v>
       </c>
       <c r="P364" t="n">
-        <v>558057.723084629</v>
+        <v>558439.874828629</v>
       </c>
       <c r="Q364" t="n">
-        <v>99228.6365274537</v>
+        <v>99953.8252244537</v>
       </c>
       <c r="R364" t="n">
-        <v>2627448.81388514</v>
+        <v>2628884.67241614</v>
       </c>
       <c r="S364" t="n">
-        <v>558270.943285</v>
+        <v>564576.275601</v>
       </c>
       <c r="T364" t="n">
-        <v>3185719.75717014</v>
+        <v>3193460.94801714</v>
       </c>
       <c r="U364" t="n">
-        <v>-0.363151694424835</v>
+        <v>-0.308701758850261</v>
       </c>
       <c r="V364" t="n">
-        <v>6.92971720864006</v>
+        <v>6.9881525798108</v>
       </c>
       <c r="W364" t="n">
-        <v>-0.440179098735205</v>
+        <v>0.684288802836086</v>
       </c>
       <c r="X364" t="n">
-        <v>0.732974653174345</v>
+        <v>1.87069261612267</v>
       </c>
       <c r="Y364" t="n">
-        <v>-0.376658719789968</v>
+        <v>-0.134577382933465</v>
       </c>
       <c r="Z364" t="n">
-        <v>5.78928121275533</v>
+        <v>6.04634557429928</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.82475830084285</v>
+        <v>0.823208648926315</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.17524169915715</v>
+        <v>0.176791351073685</v>
       </c>
     </row>
   </sheetData>
@@ -60373,6 +60408,53 @@
         <v>146.7419</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B315" t="n">
+        <v>137.7744</v>
+      </c>
+      <c r="C315" t="n">
+        <v>134.54</v>
+      </c>
+      <c r="D315" t="n">
+        <v>153.6376</v>
+      </c>
+      <c r="E315" t="n">
+        <v>140.7433</v>
+      </c>
+      <c r="F315" t="n">
+        <v>96.6646</v>
+      </c>
+      <c r="G315" t="s">
+        <v>367</v>
+      </c>
+      <c r="H315" t="n">
+        <v>125.4768</v>
+      </c>
+      <c r="I315" t="n">
+        <v>135.818</v>
+      </c>
+      <c r="J315" t="n">
+        <v>139.9806</v>
+      </c>
+      <c r="K315" t="n">
+        <v>98.2367</v>
+      </c>
+      <c r="L315" t="n">
+        <v>121.8781</v>
+      </c>
+      <c r="M315" t="n">
+        <v>132.7154</v>
+      </c>
+      <c r="N315" t="n">
+        <v>152.7057</v>
+      </c>
+      <c r="O315" t="n">
+        <v>147.3267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -41258,13 +41258,13 @@
         <v>44562</v>
       </c>
       <c r="B314" t="n">
-        <v>53032.8666853723</v>
+        <v>59751.403989751</v>
       </c>
       <c r="C314" t="n">
         <v>3088.559712</v>
       </c>
       <c r="D314" t="n">
-        <v>115336.716178298</v>
+        <v>111363.393024108</v>
       </c>
       <c r="E314" t="n">
         <v>29853.94119</v>
@@ -41273,52 +41273,52 @@
         <v>82508.82319714</v>
       </c>
       <c r="G314" t="n">
-        <v>207349.14293882</v>
+        <v>205159.802464815</v>
       </c>
       <c r="H314" t="n">
-        <v>74311.0846521677</v>
+        <v>74279.836042</v>
       </c>
       <c r="I314" t="n">
         <v>28728.5886093913</v>
       </c>
       <c r="J314" t="n">
-        <v>60146.5576270659</v>
+        <v>60146.39212058</v>
       </c>
       <c r="K314" t="n">
-        <v>264942.615541379</v>
+        <v>264942.749060519</v>
       </c>
       <c r="L314" t="n">
-        <v>29761.5484081397</v>
+        <v>29760.93067823</v>
       </c>
       <c r="M314" t="n">
-        <v>38573.2978820278</v>
+        <v>38500.478171</v>
       </c>
       <c r="N314" t="n">
-        <v>384230.54596256</v>
+        <v>384256.597267264</v>
       </c>
       <c r="O314" t="n">
         <v>55531.294064</v>
       </c>
       <c r="P314" t="n">
-        <v>328699.25189856</v>
+        <v>328725.303203264</v>
       </c>
       <c r="Q314" t="n">
-        <v>77946.3089544499</v>
+        <v>77438.2309000213</v>
       </c>
       <c r="R314" t="n">
-        <v>1560491.35534237</v>
+        <v>1560486.53553508</v>
       </c>
       <c r="S314" t="n">
         <v>273549.788159</v>
       </c>
       <c r="T314" t="n">
-        <v>1834041.14350137</v>
+        <v>1834036.32369408</v>
       </c>
       <c r="U314" t="n">
-        <v>1.1034637497928</v>
+        <v>1.1031514768604</v>
       </c>
       <c r="V314" t="n">
-        <v>12.8429791742277</v>
+        <v>12.8426306420735</v>
       </c>
       <c r="W314" t="n">
         <v>0.801966565643886</v>
@@ -41327,16 +41327,16 @@
         <v>16.8395535352565</v>
       </c>
       <c r="Y314" t="n">
-        <v>1.0583806365424</v>
+        <v>1.05811505802944</v>
       </c>
       <c r="Z314" t="n">
-        <v>13.4216361938859</v>
+        <v>13.4213381250935</v>
       </c>
       <c r="AA314" t="n">
-        <v>0.850848608752165</v>
+        <v>0.850848216785575</v>
       </c>
       <c r="AB314" t="n">
-        <v>0.149151391247835</v>
+        <v>0.149151783214425</v>
       </c>
     </row>
     <row r="315">
@@ -41344,13 +41344,13 @@
         <v>44593</v>
       </c>
       <c r="B315" t="n">
-        <v>53351.0415933606</v>
+        <v>60069.5788977393</v>
       </c>
       <c r="C315" t="n">
         <v>3025.956532</v>
       </c>
       <c r="D315" t="n">
-        <v>113263.815276349</v>
+        <v>109290.492122159</v>
       </c>
       <c r="E315" t="n">
         <v>27629.892877</v>
@@ -41359,52 +41359,52 @@
         <v>81291.41599814</v>
       </c>
       <c r="G315" t="n">
-        <v>204570.385636184</v>
+        <v>202381.045162179</v>
       </c>
       <c r="H315" t="n">
-        <v>72293.4050901677</v>
+        <v>72262.15648</v>
       </c>
       <c r="I315" t="n">
         <v>28399.3051571157</v>
       </c>
       <c r="J315" t="n">
-        <v>59895.1039480659</v>
+        <v>59894.93844158</v>
       </c>
       <c r="K315" t="n">
-        <v>267706.677311746</v>
+        <v>267706.810830886</v>
       </c>
       <c r="L315" t="n">
-        <v>29544.7066511397</v>
+        <v>29544.08892123</v>
       </c>
       <c r="M315" t="n">
-        <v>39328.3312650278</v>
+        <v>39255.511554</v>
       </c>
       <c r="N315" t="n">
-        <v>390935.313815364</v>
+        <v>390961.365120067</v>
       </c>
       <c r="O315" t="n">
         <v>56340.032166</v>
       </c>
       <c r="P315" t="n">
-        <v>334595.281649364</v>
+        <v>334621.332954067</v>
       </c>
       <c r="Q315" t="n">
-        <v>80363.9580838267</v>
+        <v>79855.880029398</v>
       </c>
       <c r="R315" t="n">
-        <v>1584415.61641085</v>
+        <v>1584410.79660356</v>
       </c>
       <c r="S315" t="n">
         <v>258119.00664</v>
       </c>
       <c r="T315" t="n">
-        <v>1842534.62305085</v>
+        <v>1842529.80324356</v>
       </c>
       <c r="U315" t="n">
-        <v>1.53312358870639</v>
+        <v>1.53312832399892</v>
       </c>
       <c r="V315" t="n">
-        <v>13.6636723232176</v>
+        <v>13.6633265572515</v>
       </c>
       <c r="W315" t="n">
         <v>-5.64094076725473</v>
@@ -41413,16 +41413,16 @@
         <v>10.6896235039097</v>
       </c>
       <c r="Y315" t="n">
-        <v>0.463101909113273</v>
+        <v>0.463103126134956</v>
       </c>
       <c r="Z315" t="n">
-        <v>13.2374505870724</v>
+        <v>13.2371543740824</v>
       </c>
       <c r="AA315" t="n">
-        <v>0.859910905656357</v>
+        <v>0.859910539202345</v>
       </c>
       <c r="AB315" t="n">
-        <v>0.140089094343643</v>
+        <v>0.140089460797655</v>
       </c>
     </row>
     <row r="316">
@@ -41430,13 +41430,13 @@
         <v>44621</v>
       </c>
       <c r="B316" t="n">
-        <v>51761.4805111168</v>
+        <v>58480.0178154955</v>
       </c>
       <c r="C316" t="n">
         <v>3042.460377</v>
       </c>
       <c r="D316" t="n">
-        <v>118902.893096695</v>
+        <v>114929.569942505</v>
       </c>
       <c r="E316" t="n">
         <v>29364.979116</v>
@@ -41445,52 +41445,52 @@
         <v>87992.29630114</v>
       </c>
       <c r="G316" t="n">
-        <v>206229.001828256</v>
+        <v>204039.661354251</v>
       </c>
       <c r="H316" t="n">
-        <v>72951.8474981677</v>
+        <v>72920.598888</v>
       </c>
       <c r="I316" t="n">
         <v>27621.6836080496</v>
       </c>
       <c r="J316" t="n">
-        <v>58984.9164990659</v>
+        <v>58984.75099258</v>
       </c>
       <c r="K316" t="n">
-        <v>271895.329536222</v>
+        <v>271895.463055362</v>
       </c>
       <c r="L316" t="n">
-        <v>28929.2983271397</v>
+        <v>28928.68059723</v>
       </c>
       <c r="M316" t="n">
-        <v>40844.7143750278</v>
+        <v>40771.894664</v>
       </c>
       <c r="N316" t="n">
-        <v>399689.81566765</v>
+        <v>399715.866972354</v>
       </c>
       <c r="O316" t="n">
         <v>56191.318388</v>
       </c>
       <c r="P316" t="n">
-        <v>343498.49727965</v>
+        <v>343524.548584354</v>
       </c>
       <c r="Q316" t="n">
-        <v>81234.5448404652</v>
+        <v>80726.4667860365</v>
       </c>
       <c r="R316" t="n">
-        <v>1612393.40515765</v>
+        <v>1612388.58535036</v>
       </c>
       <c r="S316" t="n">
         <v>266741.672092</v>
       </c>
       <c r="T316" t="n">
-        <v>1879135.07724965</v>
+        <v>1879130.25744236</v>
       </c>
       <c r="U316" t="n">
-        <v>1.76581122131159</v>
+        <v>1.76581659294235</v>
       </c>
       <c r="V316" t="n">
-        <v>14.1918723919484</v>
+        <v>14.1915310467052</v>
       </c>
       <c r="W316" t="n">
         <v>3.34057749727283</v>
@@ -41499,16 +41499,16 @@
         <v>16.0090898824449</v>
       </c>
       <c r="Y316" t="n">
-        <v>1.98641880271391</v>
+        <v>1.98642399891524</v>
       </c>
       <c r="Z316" t="n">
-        <v>14.4463500767785</v>
+        <v>14.446056532499</v>
       </c>
       <c r="AA316" t="n">
-        <v>0.858050825977656</v>
+        <v>0.858050461890249</v>
       </c>
       <c r="AB316" t="n">
-        <v>0.141949174022344</v>
+        <v>0.141949538109751</v>
       </c>
     </row>
     <row r="317">
@@ -41516,13 +41516,13 @@
         <v>44652</v>
       </c>
       <c r="B317" t="n">
-        <v>53124.1176721019</v>
+        <v>59842.6549764806</v>
       </c>
       <c r="C317" t="n">
         <v>2953.653841</v>
       </c>
       <c r="D317" t="n">
-        <v>121296.321051625</v>
+        <v>117322.997897435</v>
       </c>
       <c r="E317" t="n">
         <v>29377.542547</v>
@@ -41531,52 +41531,52 @@
         <v>85669.47730014</v>
       </c>
       <c r="G317" t="n">
-        <v>205145.320152196</v>
+        <v>202955.979678191</v>
       </c>
       <c r="H317" t="n">
-        <v>76089.6577071677</v>
+        <v>76058.409097</v>
       </c>
       <c r="I317" t="n">
         <v>28426.790062059</v>
       </c>
       <c r="J317" t="n">
-        <v>59527.3575640659</v>
+        <v>59527.19205758</v>
       </c>
       <c r="K317" t="n">
-        <v>275369.775386233</v>
+        <v>275369.908905373</v>
       </c>
       <c r="L317" t="n">
-        <v>29238.1081271397</v>
+        <v>29237.49039723</v>
       </c>
       <c r="M317" t="n">
-        <v>42550.1296220278</v>
+        <v>42477.309911</v>
       </c>
       <c r="N317" t="n">
-        <v>402963.503821715</v>
+        <v>402989.555126419</v>
       </c>
       <c r="O317" t="n">
         <v>57349.428334</v>
       </c>
       <c r="P317" t="n">
-        <v>345614.075487715</v>
+        <v>345640.126792419</v>
       </c>
       <c r="Q317" t="n">
-        <v>82088.5896929914</v>
+        <v>81580.5116385628</v>
       </c>
       <c r="R317" t="n">
-        <v>1624961.28831318</v>
+        <v>1624956.46850589</v>
       </c>
       <c r="S317" t="n">
         <v>271822.560056</v>
       </c>
       <c r="T317" t="n">
-        <v>1896783.84836918</v>
+        <v>1896779.02856189</v>
       </c>
       <c r="U317" t="n">
-        <v>0.779455132682294</v>
+        <v>0.779457462656308</v>
       </c>
       <c r="V317" t="n">
-        <v>14.1255456056868</v>
+        <v>14.1252070972309</v>
       </c>
       <c r="W317" t="n">
         <v>1.90479722352779</v>
@@ -41585,16 +41585,16 @@
         <v>17.3656897559533</v>
       </c>
       <c r="Y317" t="n">
-        <v>0.939196512970386</v>
+        <v>0.939198921928552</v>
       </c>
       <c r="Z317" t="n">
-        <v>14.5788556188671</v>
+        <v>14.5785644691908</v>
       </c>
       <c r="AA317" t="n">
-        <v>0.856692917176774</v>
+        <v>0.856692553026542</v>
       </c>
       <c r="AB317" t="n">
-        <v>0.143307082823226</v>
+        <v>0.143307446973458</v>
       </c>
     </row>
     <row r="318">
@@ -41602,13 +41602,13 @@
         <v>44682</v>
       </c>
       <c r="B318" t="n">
-        <v>55316.816031342</v>
+        <v>62035.3533357207</v>
       </c>
       <c r="C318" t="n">
         <v>3016.1436</v>
       </c>
       <c r="D318" t="n">
-        <v>123530.828440787</v>
+        <v>119557.505286598</v>
       </c>
       <c r="E318" t="n">
         <v>30598.601441</v>
@@ -41617,52 +41617,52 @@
         <v>86760.52349114</v>
       </c>
       <c r="G318" t="n">
-        <v>209531.927273497</v>
+        <v>207342.586799492</v>
       </c>
       <c r="H318" t="n">
-        <v>75211.2297511677</v>
+        <v>75179.981141</v>
       </c>
       <c r="I318" t="n">
         <v>28761.8233561185</v>
       </c>
       <c r="J318" t="n">
-        <v>60329.9973090659</v>
+        <v>60329.83180258</v>
       </c>
       <c r="K318" t="n">
-        <v>279708.670470315</v>
+        <v>279708.803989455</v>
       </c>
       <c r="L318" t="n">
-        <v>29238.5337781397</v>
+        <v>29237.91604823</v>
       </c>
       <c r="M318" t="n">
-        <v>44309.1111760278</v>
+        <v>44236.291465</v>
       </c>
       <c r="N318" t="n">
-        <v>413119.77961467</v>
+        <v>413145.830919373</v>
       </c>
       <c r="O318" t="n">
         <v>60142.33963</v>
       </c>
       <c r="P318" t="n">
-        <v>352977.43998467</v>
+        <v>353003.491289373</v>
       </c>
       <c r="Q318" t="n">
-        <v>83039.4991527188</v>
+        <v>82531.4210982901</v>
       </c>
       <c r="R318" t="n">
-        <v>1654535.42375266</v>
+        <v>1654530.60394537</v>
       </c>
       <c r="S318" t="n">
         <v>281057.840748</v>
       </c>
       <c r="T318" t="n">
-        <v>1935593.26450066</v>
+        <v>1935588.44469337</v>
       </c>
       <c r="U318" t="n">
-        <v>1.81999015313048</v>
+        <v>1.81999555143004</v>
       </c>
       <c r="V318" t="n">
-        <v>14.6662979370738</v>
+        <v>14.6659639040573</v>
       </c>
       <c r="W318" t="n">
         <v>3.39754017845222</v>
@@ -41671,16 +41671,16 @@
         <v>19.7147481805512</v>
       </c>
       <c r="Y318" t="n">
-        <v>2.04606424526705</v>
+        <v>2.0460694444153</v>
       </c>
       <c r="Z318" t="n">
-        <v>15.3727705801221</v>
+        <v>15.3724832911907</v>
       </c>
       <c r="AA318" t="n">
-        <v>0.854794989266246</v>
+        <v>0.854794627691361</v>
       </c>
       <c r="AB318" t="n">
-        <v>0.145205010733754</v>
+        <v>0.145205372308639</v>
       </c>
     </row>
     <row r="319">
@@ -41688,13 +41688,13 @@
         <v>44713</v>
       </c>
       <c r="B319" t="n">
-        <v>54548.499239595</v>
+        <v>62387.7895519757</v>
       </c>
       <c r="C319" t="n">
         <v>3339.735301</v>
       </c>
       <c r="D319" t="n">
-        <v>125966.60744254</v>
+        <v>121261.461775464</v>
       </c>
       <c r="E319" t="n">
         <v>32041.873818</v>
@@ -41703,52 +41703,52 @@
         <v>88870.89337714</v>
       </c>
       <c r="G319" t="n">
-        <v>215538.428308989</v>
+        <v>212945.846370579</v>
       </c>
       <c r="H319" t="n">
-        <v>77702.7708238766</v>
+        <v>77665.76672</v>
       </c>
       <c r="I319" t="n">
         <v>28408.448078981</v>
       </c>
       <c r="J319" t="n">
-        <v>59834.2667747109</v>
+        <v>59834.07078458</v>
       </c>
       <c r="K319" t="n">
-        <v>283523.736007522</v>
+        <v>283523.810542522</v>
       </c>
       <c r="L319" t="n">
-        <v>29773.5386970993</v>
+        <v>29772.80719123</v>
       </c>
       <c r="M319" t="n">
-        <v>45276.8355336994</v>
+        <v>45371.846148</v>
       </c>
       <c r="N319" t="n">
-        <v>421073.930528191</v>
+        <v>421042.560620673</v>
       </c>
       <c r="O319" t="n">
         <v>60877.840124</v>
       </c>
       <c r="P319" t="n">
-        <v>360196.090404191</v>
+        <v>360164.720496673</v>
       </c>
       <c r="Q319" t="n">
-        <v>85104.9927736929</v>
+        <v>84454.0743447733</v>
       </c>
       <c r="R319" t="n">
-        <v>1679029.42067923</v>
+        <v>1678914.47869159</v>
       </c>
       <c r="S319" t="n">
         <v>293049.066554</v>
       </c>
       <c r="T319" t="n">
-        <v>1972078.48723323</v>
+        <v>1971963.54524559</v>
       </c>
       <c r="U319" t="n">
-        <v>1.48041538276724</v>
+        <v>1.47376389944525</v>
       </c>
       <c r="V319" t="n">
-        <v>15.0042604780259</v>
+        <v>14.996387585435</v>
       </c>
       <c r="W319" t="n">
         <v>4.26646194039164</v>
@@ -41757,16 +41757,16 @@
         <v>22.7852461933471</v>
       </c>
       <c r="Y319" t="n">
-        <v>1.88496330307184</v>
+        <v>1.87927865822648</v>
       </c>
       <c r="Z319" t="n">
-        <v>16.0975308095145</v>
+        <v>16.0907641006653</v>
       </c>
       <c r="AA319" t="n">
-        <v>0.851400911043282</v>
+        <v>0.851392249486284</v>
       </c>
       <c r="AB319" t="n">
-        <v>0.148599088956718</v>
+        <v>0.148607750513716</v>
       </c>
     </row>
     <row r="320">
@@ -41774,13 +41774,13 @@
         <v>44743</v>
       </c>
       <c r="B320" t="n">
-        <v>54160.253295989</v>
+        <v>62365.2764381016</v>
       </c>
       <c r="C320" t="n">
         <v>3436.997793</v>
       </c>
       <c r="D320" t="n">
-        <v>126391.780859079</v>
+        <v>121616.116244675</v>
       </c>
       <c r="E320" t="n">
         <v>32685.603062</v>
@@ -41789,52 +41789,52 @@
         <v>89664.14552314</v>
       </c>
       <c r="G320" t="n">
-        <v>220293.791164961</v>
+        <v>217662.352587013</v>
       </c>
       <c r="H320" t="n">
-        <v>78615.5436674185</v>
+        <v>78577.98496</v>
       </c>
       <c r="I320" t="n">
         <v>29027.4446516128</v>
       </c>
       <c r="J320" t="n">
-        <v>61348.363687137</v>
+        <v>61348.16475958</v>
       </c>
       <c r="K320" t="n">
-        <v>287216.371756145</v>
+        <v>287216.423924145</v>
       </c>
       <c r="L320" t="n">
-        <v>30354.8250546331</v>
+        <v>30354.08258523</v>
       </c>
       <c r="M320" t="n">
-        <v>47410.6364722354</v>
+        <v>47235.089684</v>
       </c>
       <c r="N320" t="n">
-        <v>429330.941105179</v>
+        <v>429295.091251454</v>
       </c>
       <c r="O320" t="n">
         <v>62329.819894</v>
       </c>
       <c r="P320" t="n">
-        <v>367001.121211179</v>
+        <v>366965.271357454</v>
       </c>
       <c r="Q320" t="n">
-        <v>84067.4137447353</v>
+        <v>83461.2602970882</v>
       </c>
       <c r="R320" t="n">
-        <v>1702097.59877544</v>
+        <v>1702003.67084549</v>
       </c>
       <c r="S320" t="n">
         <v>301237.454167</v>
       </c>
       <c r="T320" t="n">
-        <v>2003335.05294244</v>
+        <v>2003241.12501249</v>
       </c>
       <c r="U320" t="n">
-        <v>1.37389957627334</v>
+        <v>1.37524528181425</v>
       </c>
       <c r="V320" t="n">
-        <v>16.0576589645199</v>
+        <v>16.0512544812111</v>
       </c>
       <c r="W320" t="n">
         <v>2.79420361555429</v>
@@ -41843,16 +41843,16 @@
         <v>21.9254441578109</v>
       </c>
       <c r="Y320" t="n">
-        <v>1.58495546255204</v>
+        <v>1.58611348786406</v>
       </c>
       <c r="Z320" t="n">
-        <v>16.9036451908762</v>
+        <v>16.8981640720886</v>
       </c>
       <c r="AA320" t="n">
-        <v>0.84963201551106</v>
+        <v>0.849624965059999</v>
       </c>
       <c r="AB320" t="n">
-        <v>0.15036798448894</v>
+        <v>0.150375034940001</v>
       </c>
     </row>
     <row r="321">
@@ -41860,13 +41860,13 @@
         <v>44774</v>
       </c>
       <c r="B321" t="n">
-        <v>54516.2168351685</v>
+        <v>62607.9427573849</v>
       </c>
       <c r="C321" t="n">
         <v>3397.6616</v>
       </c>
       <c r="D321" t="n">
-        <v>125171.884143127</v>
+        <v>120374.886859805</v>
       </c>
       <c r="E321" t="n">
         <v>35512.612282</v>
@@ -41875,52 +41875,52 @@
         <v>84297.50612114</v>
       </c>
       <c r="G321" t="n">
-        <v>225998.323121876</v>
+        <v>223355.130031731</v>
       </c>
       <c r="H321" t="n">
-        <v>78419.3307033957</v>
+        <v>78381.604223</v>
       </c>
       <c r="I321" t="n">
         <v>30244.6131245909</v>
       </c>
       <c r="J321" t="n">
-        <v>62788.2888667371</v>
+        <v>62788.08905058</v>
       </c>
       <c r="K321" t="n">
-        <v>292424.44863057</v>
+        <v>292424.505731569</v>
       </c>
       <c r="L321" t="n">
-        <v>30743.741163209</v>
+        <v>30742.99537723</v>
       </c>
       <c r="M321" t="n">
-        <v>48926.384704577</v>
+        <v>48877.262599</v>
       </c>
       <c r="N321" t="n">
-        <v>437055.361683373</v>
+        <v>437016.697235</v>
       </c>
       <c r="O321" t="n">
         <v>64244.414608</v>
       </c>
       <c r="P321" t="n">
-        <v>372810.947075373</v>
+        <v>372772.282627</v>
       </c>
       <c r="Q321" t="n">
-        <v>85054.1735920519</v>
+        <v>84445.1732215086</v>
       </c>
       <c r="R321" t="n">
-        <v>1719647.20421619</v>
+        <v>1719524.67341054</v>
       </c>
       <c r="S321" t="n">
         <v>311958.704039</v>
       </c>
       <c r="T321" t="n">
-        <v>2031605.90825519</v>
+        <v>2031483.37744954</v>
       </c>
       <c r="U321" t="n">
-        <v>1.0310575288615</v>
+        <v>1.02943388813854</v>
       </c>
       <c r="V321" t="n">
-        <v>16.1865186827438</v>
+        <v>16.1782399917979</v>
       </c>
       <c r="W321" t="n">
         <v>3.55906934004839</v>
@@ -41929,16 +41929,16 @@
         <v>25.862031708732</v>
       </c>
       <c r="Y321" t="n">
-        <v>1.41118956967392</v>
+        <v>1.40982790760495</v>
       </c>
       <c r="Z321" t="n">
-        <v>17.5743914167214</v>
+        <v>17.567300235875</v>
       </c>
       <c r="AA321" t="n">
-        <v>0.846447235277574</v>
+        <v>0.846437973600033</v>
       </c>
       <c r="AB321" t="n">
-        <v>0.153552764722426</v>
+        <v>0.153562026399967</v>
       </c>
     </row>
     <row r="322">
@@ -41946,13 +41946,13 @@
         <v>44805</v>
       </c>
       <c r="B322" t="n">
-        <v>54742.8136785258</v>
+        <v>62804.9753541374</v>
       </c>
       <c r="C322" t="n">
         <v>3798.460005</v>
       </c>
       <c r="D322" t="n">
-        <v>119627.914176783</v>
+        <v>114919.643820101</v>
       </c>
       <c r="E322" t="n">
         <v>36189.776506</v>
@@ -41961,52 +41961,52 @@
         <v>86400.14876</v>
       </c>
       <c r="G322" t="n">
-        <v>233449.462595232</v>
+        <v>230855.158921852</v>
       </c>
       <c r="H322" t="n">
-        <v>79200.4600683206</v>
+        <v>79163.43139</v>
       </c>
       <c r="I322" t="n">
         <v>30544.1119120083</v>
       </c>
       <c r="J322" t="n">
-        <v>62656.5747542881</v>
+        <v>62656.378634</v>
       </c>
       <c r="K322" t="n">
-        <v>296443.285086835</v>
+        <v>296443.337254835</v>
       </c>
       <c r="L322" t="n">
-        <v>31199.5009516627</v>
+        <v>31198.76896</v>
       </c>
       <c r="M322" t="n">
-        <v>50567.3542726374</v>
+        <v>50401.743505</v>
       </c>
       <c r="N322" t="n">
-        <v>445565.816684563</v>
+        <v>445537.338794872</v>
       </c>
       <c r="O322" t="n">
         <v>65773.067975</v>
       </c>
       <c r="P322" t="n">
-        <v>379792.748709563</v>
+        <v>379764.270819872</v>
       </c>
       <c r="Q322" t="n">
-        <v>86142.5210395142</v>
+        <v>85567.4240917834</v>
       </c>
       <c r="R322" t="n">
-        <v>1741064.23686793</v>
+        <v>1740988.25639646</v>
       </c>
       <c r="S322" t="n">
         <v>321029.780308</v>
       </c>
       <c r="T322" t="n">
-        <v>2062094.01717593</v>
+        <v>2062018.03670446</v>
       </c>
       <c r="U322" t="n">
-        <v>1.24543177224001</v>
+        <v>1.24822768279047</v>
       </c>
       <c r="V322" t="n">
-        <v>16.4057738813949</v>
+        <v>16.4006939047954</v>
       </c>
       <c r="W322" t="n">
         <v>2.90778111062608</v>
@@ -42015,16 +42015,16 @@
         <v>29.3046222061123</v>
       </c>
       <c r="Y322" t="n">
-        <v>1.50069010908367</v>
+        <v>1.50307207008793</v>
       </c>
       <c r="Z322" t="n">
-        <v>18.2420831144194</v>
+        <v>18.2377263347827</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.844318553065949</v>
+        <v>0.844312816574062</v>
       </c>
       <c r="AB322" t="n">
-        <v>0.155681446934051</v>
+        <v>0.155687183425938</v>
       </c>
     </row>
     <row r="323">
@@ -42032,13 +42032,13 @@
         <v>44835</v>
       </c>
       <c r="B323" t="n">
-        <v>54838.1374500293</v>
+        <v>63071.8906228081</v>
       </c>
       <c r="C323" t="n">
         <v>4001.717958</v>
       </c>
       <c r="D323" t="n">
-        <v>124852.539164</v>
+        <v>120047.152322909</v>
       </c>
       <c r="E323" t="n">
         <v>35492.682164</v>
@@ -42047,52 +42047,52 @@
         <v>86292.555056</v>
       </c>
       <c r="G323" t="n">
-        <v>235467.827282738</v>
+        <v>232820.011463036</v>
       </c>
       <c r="H323" t="n">
-        <v>79311.9894449389</v>
+        <v>79274.196984</v>
       </c>
       <c r="I323" t="n">
         <v>31200.1514017623</v>
       </c>
       <c r="J323" t="n">
-        <v>62492.8520896192</v>
+        <v>62492.651924</v>
       </c>
       <c r="K323" t="n">
-        <v>299908.926247703</v>
+        <v>299908.973433703</v>
       </c>
       <c r="L323" t="n">
-        <v>30464.122826298</v>
+        <v>30463.375736</v>
       </c>
       <c r="M323" t="n">
-        <v>51635.6377146828</v>
+        <v>51447.444839</v>
       </c>
       <c r="N323" t="n">
-        <v>454055.796049339</v>
+        <v>454006.897549817</v>
       </c>
       <c r="O323" t="n">
         <v>67776.563931</v>
       </c>
       <c r="P323" t="n">
-        <v>386279.232118339</v>
+        <v>386230.333618817</v>
       </c>
       <c r="Q323" t="n">
-        <v>88900.015277027</v>
+        <v>88348.1204846508</v>
       </c>
       <c r="R323" t="n">
-        <v>1761146.83895148</v>
+        <v>1761050.8122655</v>
       </c>
       <c r="S323" t="n">
         <v>331823.907224</v>
       </c>
       <c r="T323" t="n">
-        <v>2092970.74617548</v>
+        <v>2092874.7194895</v>
       </c>
       <c r="U323" t="n">
-        <v>1.15346703804962</v>
+        <v>1.15236595050716</v>
       </c>
       <c r="V323" t="n">
-        <v>16.6498981176265</v>
+        <v>16.643537771693</v>
       </c>
       <c r="W323" t="n">
         <v>3.36234442351238</v>
@@ -42101,16 +42101,16 @@
         <v>31.5009527851203</v>
       </c>
       <c r="Y323" t="n">
-        <v>1.49734826551837</v>
+        <v>1.49643127440129</v>
       </c>
       <c r="Z323" t="n">
-        <v>18.7765859679467</v>
+        <v>18.7711364307553</v>
       </c>
       <c r="AA323" t="n">
-        <v>0.841457933499382</v>
+        <v>0.841450659165619</v>
       </c>
       <c r="AB323" t="n">
-        <v>0.158542066500618</v>
+        <v>0.158549340834381</v>
       </c>
     </row>
     <row r="324">
@@ -42118,13 +42118,13 @@
         <v>44866</v>
       </c>
       <c r="B324" t="n">
-        <v>55552.3508663087</v>
+        <v>64022.5505953227</v>
       </c>
       <c r="C324" t="n">
         <v>4189.60955967</v>
       </c>
       <c r="D324" t="n">
-        <v>125746.310394769</v>
+        <v>120817.215540406</v>
       </c>
       <c r="E324" t="n">
         <v>35726.64306728</v>
@@ -42133,52 +42133,52 @@
         <v>87050.52811038</v>
       </c>
       <c r="G324" t="n">
-        <v>241097.806687831</v>
+        <v>238381.826525611</v>
       </c>
       <c r="H324" t="n">
-        <v>80414.2087739814</v>
+        <v>80375.4433986</v>
       </c>
       <c r="I324" t="n">
         <v>31688.6038252217</v>
       </c>
       <c r="J324" t="n">
-        <v>62931.5715073552</v>
+        <v>62931.36618875</v>
       </c>
       <c r="K324" t="n">
-        <v>304073.325303054</v>
+        <v>304073.367457054</v>
       </c>
       <c r="L324" t="n">
-        <v>30554.3473486006</v>
+        <v>30553.5810255</v>
       </c>
       <c r="M324" t="n">
-        <v>53645.1065357086</v>
+        <v>53459.44929427</v>
       </c>
       <c r="N324" t="n">
-        <v>467365.052578717</v>
+        <v>467305.251387952</v>
       </c>
       <c r="O324" t="n">
         <v>73328.01964821</v>
       </c>
       <c r="P324" t="n">
-        <v>394037.032930507</v>
+        <v>393977.231739742</v>
       </c>
       <c r="Q324" t="n">
-        <v>88683.2020186275</v>
+        <v>88096.748813383</v>
       </c>
       <c r="R324" t="n">
-        <v>1793304.68178588</v>
+        <v>1793198.39880701</v>
       </c>
       <c r="S324" t="n">
         <v>342779.03737034</v>
       </c>
       <c r="T324" t="n">
-        <v>2136083.71915622</v>
+        <v>2135977.43617735</v>
       </c>
       <c r="U324" t="n">
-        <v>1.82596034147562</v>
+        <v>1.82547751135886</v>
       </c>
       <c r="V324" t="n">
-        <v>16.6143051279728</v>
+        <v>16.607393800604</v>
       </c>
       <c r="W324" t="n">
         <v>3.30148910546841</v>
@@ -42187,16 +42187,16 @@
         <v>31.1805586483905</v>
       </c>
       <c r="Y324" t="n">
-        <v>2.05989372090014</v>
+        <v>2.05949817666884</v>
       </c>
       <c r="Z324" t="n">
-        <v>18.7299097687041</v>
+        <v>18.7240022434615</v>
       </c>
       <c r="AA324" t="n">
-        <v>0.839529212129503</v>
+        <v>0.839521227347891</v>
       </c>
       <c r="AB324" t="n">
-        <v>0.160470787870497</v>
+        <v>0.160478772652109</v>
       </c>
     </row>
     <row r="325">
@@ -42204,13 +42204,13 @@
         <v>44896</v>
       </c>
       <c r="B325" t="n">
-        <v>55680.284894821</v>
+        <v>64055.7602851346</v>
       </c>
       <c r="C325" t="n">
         <v>4189.5002289</v>
       </c>
       <c r="D325" t="n">
-        <v>128318.648595272</v>
+        <v>123373.511138676</v>
       </c>
       <c r="E325" t="n">
         <v>35527.31431429</v>
@@ -42219,52 +42219,52 @@
         <v>87157.09103496</v>
       </c>
       <c r="G325" t="n">
-        <v>239789.703296977</v>
+        <v>237064.883501782</v>
       </c>
       <c r="H325" t="n">
-        <v>81519.5523823129</v>
+        <v>81480.66083823</v>
       </c>
       <c r="I325" t="n">
         <v>32063.1061748284</v>
       </c>
       <c r="J325" t="n">
-        <v>65312.9680219406</v>
+        <v>65312.76203509</v>
       </c>
       <c r="K325" t="n">
-        <v>306626.966130703</v>
+        <v>306627.003205703</v>
       </c>
       <c r="L325" t="n">
-        <v>31901.1952150133</v>
+        <v>31900.42639778</v>
       </c>
       <c r="M325" t="n">
-        <v>54887.9276673326</v>
+        <v>54780.71419277</v>
       </c>
       <c r="N325" t="n">
-        <v>467625.95442717</v>
+        <v>467605.507805088</v>
       </c>
       <c r="O325" t="n">
         <v>70652.67624779</v>
       </c>
       <c r="P325" t="n">
-        <v>396973.27817938</v>
+        <v>396952.831557298</v>
       </c>
       <c r="Q325" t="n">
-        <v>88794.6581565029</v>
+        <v>88235.9772213212</v>
       </c>
       <c r="R325" t="n">
-        <v>1797151.65585841</v>
+        <v>1797110.55706986</v>
       </c>
       <c r="S325" t="n">
         <v>349869.16910978</v>
       </c>
       <c r="T325" t="n">
-        <v>2147020.82496819</v>
+        <v>2146979.72617964</v>
       </c>
       <c r="U325" t="n">
-        <v>0.214518710155898</v>
+        <v>0.218166504356199</v>
       </c>
       <c r="V325" t="n">
-        <v>16.4365676675579</v>
+        <v>16.4339048973577</v>
       </c>
       <c r="W325" t="n">
         <v>2.06842629404427</v>
@@ -42273,16 +42273,16 @@
         <v>28.9253430766853</v>
       </c>
       <c r="Y325" t="n">
-        <v>0.512016720781561</v>
+        <v>0.515093924492893</v>
       </c>
       <c r="Z325" t="n">
-        <v>18.3040241670875</v>
+        <v>18.3017595630288</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.837044352322496</v>
+        <v>0.837041232926619</v>
       </c>
       <c r="AB325" t="n">
-        <v>0.162955647677504</v>
+        <v>0.162958767073381</v>
       </c>
     </row>
     <row r="326">
@@ -42290,13 +42290,13 @@
         <v>44927</v>
       </c>
       <c r="B326" t="n">
-        <v>51053.3612685873</v>
+        <v>59412.3771306568</v>
       </c>
       <c r="C326" t="n">
         <v>4808.16031675</v>
       </c>
       <c r="D326" t="n">
-        <v>127286.581830255</v>
+        <v>122366.915477728</v>
       </c>
       <c r="E326" t="n">
         <v>35396.0294751</v>
@@ -42305,52 +42305,52 @@
         <v>87431.24651272</v>
       </c>
       <c r="G326" t="n">
-        <v>239653.898537539</v>
+        <v>237305.451233989</v>
       </c>
       <c r="H326" t="n">
-        <v>78686.9180305312</v>
+        <v>78648.05973497</v>
       </c>
       <c r="I326" t="n">
-        <v>32473.7981358284</v>
+        <v>32505.9698808855</v>
       </c>
       <c r="J326" t="n">
-        <v>66040.8403596017</v>
+        <v>66040.63454885</v>
       </c>
       <c r="K326" t="n">
-        <v>308727.157671053</v>
+        <v>308970.070915188</v>
       </c>
       <c r="L326" t="n">
-        <v>34611.2858681586</v>
+        <v>34610.51770819</v>
       </c>
       <c r="M326" t="n">
-        <v>56926.6483927774</v>
+        <v>56820.92656797</v>
       </c>
       <c r="N326" t="n">
-        <v>474878.430821528</v>
+        <v>475216.774817504</v>
       </c>
       <c r="O326" t="n">
         <v>71176.02520721</v>
       </c>
       <c r="P326" t="n">
-        <v>403702.405614318</v>
+        <v>404040.749610294</v>
       </c>
       <c r="Q326" t="n">
-        <v>88891.9951713034</v>
+        <v>88547.7429733367</v>
       </c>
       <c r="R326" t="n">
-        <v>1810941.55293461</v>
+        <v>1812494.42183269</v>
       </c>
       <c r="S326" t="n">
         <v>350803.23027865</v>
       </c>
       <c r="T326" t="n">
-        <v>2161744.78321326</v>
+        <v>2163297.65211134</v>
       </c>
       <c r="U326" t="n">
-        <v>0.767319609964123</v>
+        <v>0.856033297579395</v>
       </c>
       <c r="V326" t="n">
-        <v>16.0494447300088</v>
+        <v>16.1493150090653</v>
       </c>
       <c r="W326" t="n">
         <v>0.266974415392673</v>
@@ -42359,16 +42359,16 @@
         <v>28.2410900917045</v>
       </c>
       <c r="Y326" t="n">
-        <v>0.685785534720429</v>
+        <v>0.760040988404587</v>
       </c>
       <c r="Z326" t="n">
-        <v>17.8678455973059</v>
+        <v>17.9528248248687</v>
       </c>
       <c r="AA326" t="n">
-        <v>0.837722180248674</v>
+        <v>0.837838667306706</v>
       </c>
       <c r="AB326" t="n">
-        <v>0.162277819751326</v>
+        <v>0.162161332693294</v>
       </c>
     </row>
     <row r="327">
@@ -42376,13 +42376,13 @@
         <v>44958</v>
       </c>
       <c r="B327" t="n">
-        <v>50870.0446823573</v>
+        <v>59094.2040670098</v>
       </c>
       <c r="C327" t="n">
         <v>4760.009642</v>
       </c>
       <c r="D327" t="n">
-        <v>123653.153329244</v>
+        <v>118721.318964155</v>
       </c>
       <c r="E327" t="n">
         <v>34968.697149</v>
@@ -42391,52 +42391,52 @@
         <v>89523.259123</v>
       </c>
       <c r="G327" t="n">
-        <v>241126.713871572</v>
+        <v>238409.224211766</v>
       </c>
       <c r="H327" t="n">
-        <v>77480.8080065463</v>
+        <v>77442.021086</v>
       </c>
       <c r="I327" t="n">
         <v>32025.2646905055</v>
       </c>
       <c r="J327" t="n">
-        <v>67507.529052718</v>
+        <v>67507.32362</v>
       </c>
       <c r="K327" t="n">
         <v>311957.939422696</v>
       </c>
       <c r="L327" t="n">
-        <v>34751.0698970105</v>
+        <v>34750.303148</v>
       </c>
       <c r="M327" t="n">
-        <v>58728.3660049674</v>
+        <v>58660.051077</v>
       </c>
       <c r="N327" t="n">
-        <v>481511.490664279</v>
+        <v>481478.90757438</v>
       </c>
       <c r="O327" t="n">
         <v>72475.559153</v>
       </c>
       <c r="P327" t="n">
-        <v>409035.931511279</v>
+        <v>409003.34842138</v>
       </c>
       <c r="Q327" t="n">
-        <v>90060.5684175926</v>
+        <v>89604.8855759717</v>
       </c>
       <c r="R327" t="n">
-        <v>1834417.36607177</v>
+        <v>1834363.27837986</v>
       </c>
       <c r="S327" t="n">
         <v>346019.038546</v>
       </c>
       <c r="T327" t="n">
-        <v>2180436.40461777</v>
+        <v>2180382.31692586</v>
       </c>
       <c r="U327" t="n">
-        <v>1.29633190530722</v>
+        <v>1.20656131592711</v>
       </c>
       <c r="V327" t="n">
-        <v>15.7787986353759</v>
+        <v>15.7757370949577</v>
       </c>
       <c r="W327" t="n">
         <v>-1.36378212049241</v>
@@ -42445,16 +42445,16 @@
         <v>34.0540718214504</v>
       </c>
       <c r="Y327" t="n">
-        <v>0.864654400910525</v>
+        <v>0.789750998797878</v>
       </c>
       <c r="Z327" t="n">
-        <v>18.3389651048958</v>
+        <v>18.3363391510711</v>
       </c>
       <c r="AA327" t="n">
-        <v>0.841307438358122</v>
+        <v>0.841303501748329</v>
       </c>
       <c r="AB327" t="n">
-        <v>0.158692561641878</v>
+        <v>0.158696498251671</v>
       </c>
     </row>
     <row r="328">
@@ -42462,13 +42462,13 @@
         <v>44986</v>
       </c>
       <c r="B328" t="n">
-        <v>50349.3008854772</v>
+        <v>58457.7086814553</v>
       </c>
       <c r="C328" t="n">
         <v>4774.23830511</v>
       </c>
       <c r="D328" t="n">
-        <v>123442.232567556</v>
+        <v>118498.15248464</v>
       </c>
       <c r="E328" t="n">
         <v>36267.39931458</v>
@@ -42477,52 +42477,52 @@
         <v>91291.28418439</v>
       </c>
       <c r="G328" t="n">
-        <v>248071.307811779</v>
+        <v>245347.07063997</v>
       </c>
       <c r="H328" t="n">
-        <v>75092.7775608685</v>
+        <v>75053.89433261</v>
       </c>
       <c r="I328" t="n">
         <v>31656.9011918792</v>
       </c>
       <c r="J328" t="n">
-        <v>69703.9305759563</v>
+        <v>69703.72463315</v>
       </c>
       <c r="K328" t="n">
         <v>316897.81103141</v>
       </c>
       <c r="L328" t="n">
-        <v>35113.3645534941</v>
+        <v>35112.59590065</v>
       </c>
       <c r="M328" t="n">
-        <v>60334.3670268745</v>
+        <v>60332.71536325</v>
       </c>
       <c r="N328" t="n">
-        <v>487324.456526539</v>
+        <v>487326.515728954</v>
       </c>
       <c r="O328" t="n">
         <v>71730.31727735</v>
       </c>
       <c r="P328" t="n">
-        <v>415594.139249189</v>
+        <v>415596.198451604</v>
       </c>
       <c r="Q328" t="n">
-        <v>92184.4590411835</v>
+        <v>91762.0501310279</v>
       </c>
       <c r="R328" t="n">
-        <v>1859645.41314513</v>
+        <v>1859625.70369352</v>
       </c>
       <c r="S328" t="n">
         <v>350182.87395851</v>
       </c>
       <c r="T328" t="n">
-        <v>2209828.28710364</v>
+        <v>2209808.57765203</v>
       </c>
       <c r="U328" t="n">
-        <v>1.37526211537031</v>
+        <v>1.37717678997424</v>
       </c>
       <c r="V328" t="n">
-        <v>15.3344715499694</v>
+        <v>15.3335939356977</v>
       </c>
       <c r="W328" t="n">
         <v>1.20335442523822</v>
@@ -42531,16 +42531,16 @@
         <v>31.2816520988632</v>
       </c>
       <c r="Y328" t="n">
-        <v>1.3479816436573</v>
+        <v>1.34959178937282</v>
       </c>
       <c r="Z328" t="n">
-        <v>17.59816065687</v>
+        <v>17.5974134257065</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.841533898356652</v>
+        <v>0.84153248498538</v>
       </c>
       <c r="AB328" t="n">
-        <v>0.158466101643348</v>
+        <v>0.15846751501462</v>
       </c>
     </row>
     <row r="329">
@@ -42563,7 +42563,7 @@
         <v>92388.3341763843</v>
       </c>
       <c r="G329" t="n">
-        <v>248125.634538147</v>
+        <v>245964.859643147</v>
       </c>
       <c r="H329" t="n">
         <v>73847.855461007</v>
@@ -42575,58 +42575,58 @@
         <v>68967.3120088249</v>
       </c>
       <c r="K329" t="n">
-        <v>320423.999696009</v>
+        <v>319949.143495009</v>
       </c>
       <c r="L329" t="n">
         <v>35292.7128625605</v>
       </c>
       <c r="M329" t="n">
-        <v>61483.5784123225</v>
+        <v>60740.7724323225</v>
       </c>
       <c r="N329" t="n">
-        <v>494313.34072894</v>
+        <v>493117.30235994</v>
       </c>
       <c r="O329" t="n">
         <v>73511.7200018623</v>
       </c>
       <c r="P329" t="n">
-        <v>420801.620727078</v>
+        <v>419605.582358078</v>
       </c>
       <c r="Q329" t="n">
-        <v>94155.7168985911</v>
+        <v>93960.3381095911</v>
       </c>
       <c r="R329" t="n">
-        <v>1880459.41374545</v>
+        <v>1874737.61526445</v>
       </c>
       <c r="S329" t="n">
-        <v>353899.194656038</v>
+        <v>353655.100534038</v>
       </c>
       <c r="T329" t="n">
-        <v>2234358.60840149</v>
+        <v>2228392.71579849</v>
       </c>
       <c r="U329" t="n">
-        <v>1.1192456611997</v>
+        <v>0.812631893661031</v>
       </c>
       <c r="V329" t="n">
-        <v>15.7233361354411</v>
+        <v>15.3715592755683</v>
       </c>
       <c r="W329" t="n">
-        <v>1.0612514128741</v>
+        <v>0.991546655688014</v>
       </c>
       <c r="X329" t="n">
-        <v>30.194931054703</v>
+        <v>30.1051319880068</v>
       </c>
       <c r="Y329" t="n">
-        <v>1.11005553874979</v>
+        <v>0.840984071398854</v>
       </c>
       <c r="Z329" t="n">
-        <v>17.79721818712</v>
+        <v>17.4829899657857</v>
       </c>
       <c r="AA329" t="n">
-        <v>0.841610387282807</v>
+        <v>0.841295881992993</v>
       </c>
       <c r="AB329" t="n">
-        <v>0.158389612717193</v>
+        <v>0.158704118007007</v>
       </c>
     </row>
     <row r="330">
@@ -42634,13 +42634,13 @@
         <v>45047</v>
       </c>
       <c r="B330" t="n">
-        <v>50887.9583563286</v>
+        <v>59332.7775534677</v>
       </c>
       <c r="C330" t="n">
         <v>4883.710808</v>
       </c>
       <c r="D330" t="n">
-        <v>127955.566193593</v>
+        <v>122834.211100723</v>
       </c>
       <c r="E330" t="n">
         <v>36789.346255</v>
@@ -42649,70 +42649,70 @@
         <v>93610.49583814</v>
       </c>
       <c r="G330" t="n">
-        <v>256467.894230479</v>
+        <v>253645.976769588</v>
       </c>
       <c r="H330" t="n">
-        <v>74284.4684098768</v>
+        <v>74244.190984</v>
       </c>
       <c r="I330" t="n">
         <v>31475.0252350713</v>
       </c>
       <c r="J330" t="n">
-        <v>69717.0869190947</v>
+        <v>69716.873592</v>
       </c>
       <c r="K330" t="n">
         <v>324645.955466881</v>
       </c>
       <c r="L330" t="n">
-        <v>35989.152470672</v>
+        <v>35988.356257</v>
       </c>
       <c r="M330" t="n">
-        <v>62384.3757074063</v>
+        <v>62308.273573</v>
       </c>
       <c r="N330" t="n">
-        <v>503647.206393066</v>
+        <v>503647.545147007</v>
       </c>
       <c r="O330" t="n">
         <v>75813.881765</v>
       </c>
       <c r="P330" t="n">
-        <v>427833.324628066</v>
+        <v>427833.663382007</v>
       </c>
       <c r="Q330" t="n">
-        <v>95546.1546815455</v>
+        <v>95155.5484280226</v>
       </c>
       <c r="R330" t="n">
-        <v>1911447.81533422</v>
+        <v>1911442.04413091</v>
       </c>
       <c r="S330" t="n">
         <v>360483.788024</v>
       </c>
       <c r="T330" t="n">
-        <v>2271931.60335822</v>
+        <v>2271925.83215491</v>
       </c>
       <c r="U330" t="n">
-        <v>1.64791653370735</v>
+        <v>1.95784351727943</v>
       </c>
       <c r="V330" t="n">
-        <v>15.5277661567896</v>
+        <v>15.527753888197</v>
       </c>
       <c r="W330" t="n">
-        <v>1.86058444534238</v>
+        <v>1.93088901578133</v>
       </c>
       <c r="X330" t="n">
         <v>28.259644728152</v>
       </c>
       <c r="Y330" t="n">
-        <v>1.6816009218686</v>
+        <v>1.95356572689287</v>
       </c>
       <c r="Z330" t="n">
-        <v>17.3764987214051</v>
+        <v>17.3764928378056</v>
       </c>
       <c r="AA330" t="n">
-        <v>0.841331584326237</v>
+        <v>0.841331181272725</v>
       </c>
       <c r="AB330" t="n">
-        <v>0.158668415673763</v>
+        <v>0.158668818727275</v>
       </c>
     </row>
     <row r="331">
@@ -42720,13 +42720,13 @@
         <v>45078</v>
       </c>
       <c r="B331" t="n">
-        <v>52139.8189985152</v>
+        <v>60913.0509992767</v>
       </c>
       <c r="C331" t="n">
         <v>5436.19738317</v>
       </c>
       <c r="D331" t="n">
-        <v>135228.109965993</v>
+        <v>129940.4963372</v>
       </c>
       <c r="E331" t="n">
         <v>38488.3141894</v>
@@ -42735,52 +42735,52 @@
         <v>103142.07613795</v>
       </c>
       <c r="G331" t="n">
-        <v>276502.693188501</v>
+        <v>273589.165625003</v>
       </c>
       <c r="H331" t="n">
-        <v>78264.1782607778</v>
+        <v>78222.59327748</v>
       </c>
       <c r="I331" t="n">
         <v>32704.2347153109</v>
       </c>
       <c r="J331" t="n">
-        <v>73233.6162701882</v>
+        <v>73233.39601769</v>
       </c>
       <c r="K331" t="n">
         <v>328863.214975899</v>
       </c>
       <c r="L331" t="n">
-        <v>36517.3085871861</v>
+        <v>36516.48652541</v>
       </c>
       <c r="M331" t="n">
-        <v>66852.4045071575</v>
+        <v>66737.61411966</v>
       </c>
       <c r="N331" t="n">
-        <v>515274.205515687</v>
+        <v>515264.661118221</v>
       </c>
       <c r="O331" t="n">
         <v>77403.79127953</v>
       </c>
       <c r="P331" t="n">
-        <v>437870.414236157</v>
+        <v>437860.869838691</v>
       </c>
       <c r="Q331" t="n">
-        <v>97295.7847427785</v>
+        <v>96885.9355045209</v>
       </c>
       <c r="R331" t="n">
-        <v>1981437.76825266</v>
+        <v>1981423.50334287</v>
       </c>
       <c r="S331" t="n">
         <v>373778.59470154</v>
       </c>
       <c r="T331" t="n">
-        <v>2355216.3629542</v>
+        <v>2355202.09804441</v>
       </c>
       <c r="U331" t="n">
-        <v>3.6616198651598</v>
+        <v>3.66118655947969</v>
       </c>
       <c r="V331" t="n">
-        <v>18.0109022420286</v>
+        <v>18.0181318638119</v>
       </c>
       <c r="W331" t="n">
         <v>3.68804565398511</v>
@@ -42789,16 +42789,16 @@
         <v>27.5481267000262</v>
       </c>
       <c r="Y331" t="n">
-        <v>3.66581280320566</v>
+        <v>3.66544826027697</v>
       </c>
       <c r="Z331" t="n">
-        <v>19.4281251076628</v>
+        <v>19.434362958829</v>
       </c>
       <c r="AA331" t="n">
-        <v>0.841297555256154</v>
+        <v>0.841296594032462</v>
       </c>
       <c r="AB331" t="n">
-        <v>0.158702444743845</v>
+        <v>0.158703405967538</v>
       </c>
     </row>
     <row r="332">
@@ -42806,13 +42806,13 @@
         <v>45108</v>
       </c>
       <c r="B332" t="n">
-        <v>52392.2497194948</v>
+        <v>61290.8464709959</v>
       </c>
       <c r="C332" t="n">
         <v>4630.012584</v>
       </c>
       <c r="D332" t="n">
-        <v>135478.07170587</v>
+        <v>130116.787446419</v>
       </c>
       <c r="E332" t="n">
         <v>40919.795296</v>
@@ -42821,52 +42821,52 @@
         <v>111435.211581</v>
       </c>
       <c r="G332" t="n">
-        <v>277033.890405316</v>
+        <v>274079.7695935</v>
       </c>
       <c r="H332" t="n">
-        <v>79564.1458275786</v>
+        <v>79521.981454</v>
       </c>
       <c r="I332" t="n">
         <v>33129.1515374015</v>
       </c>
       <c r="J332" t="n">
-        <v>72931.7843182058</v>
+        <v>72931.560997</v>
       </c>
       <c r="K332" t="n">
         <v>333488.188171627</v>
       </c>
       <c r="L332" t="n">
-        <v>36979.5511323001</v>
+        <v>36978.717617</v>
       </c>
       <c r="M332" t="n">
-        <v>69129.0470336903</v>
+        <v>69015.906947</v>
       </c>
       <c r="N332" t="n">
-        <v>526369.195490555</v>
+        <v>526347.089888982</v>
       </c>
       <c r="O332" t="n">
         <v>80329.811074</v>
       </c>
       <c r="P332" t="n">
-        <v>446039.384416555</v>
+        <v>446017.278814982</v>
       </c>
       <c r="Q332" t="n">
-        <v>100028.058721675</v>
+        <v>99619.2026346803</v>
       </c>
       <c r="R332" t="n">
-        <v>2015223.64214727</v>
+        <v>2015197.40524059</v>
       </c>
       <c r="S332" t="n">
         <v>384653.906868</v>
       </c>
       <c r="T332" t="n">
-        <v>2399877.54901527</v>
+        <v>2399851.31210859</v>
       </c>
       <c r="U332" t="n">
-        <v>1.70511910270097</v>
+        <v>1.70452716649099</v>
       </c>
       <c r="V332" t="n">
-        <v>18.3964799431655</v>
+        <v>18.4014723211209</v>
       </c>
       <c r="W332" t="n">
         <v>2.90955991611661</v>
@@ -42875,16 +42875,16 @@
         <v>27.6912620084605</v>
       </c>
       <c r="Y332" t="n">
-        <v>1.89626680433927</v>
+        <v>1.89576996815901</v>
       </c>
       <c r="Z332" t="n">
-        <v>19.7941175885878</v>
+        <v>19.7984247699398</v>
       </c>
       <c r="AA332" t="n">
-        <v>0.839719361087472</v>
+        <v>0.839717608783841</v>
       </c>
       <c r="AB332" t="n">
-        <v>0.160280638912528</v>
+        <v>0.160282391216158</v>
       </c>
     </row>
     <row r="333">
@@ -42892,13 +42892,13 @@
         <v>45139</v>
       </c>
       <c r="B333" t="n">
-        <v>53376.8619494601</v>
+        <v>62333.62345642</v>
       </c>
       <c r="C333" t="n">
         <v>4870.425066</v>
       </c>
       <c r="D333" t="n">
-        <v>132491.583769656</v>
+        <v>127066.271413687</v>
       </c>
       <c r="E333" t="n">
         <v>41528.425931</v>
@@ -42907,52 +42907,52 @@
         <v>106210.534506</v>
       </c>
       <c r="G333" t="n">
-        <v>279111.551455281</v>
+        <v>276122.150527114</v>
       </c>
       <c r="H333" t="n">
-        <v>80902.2660911542</v>
+        <v>80859.598162</v>
       </c>
       <c r="I333" t="n">
         <v>34340.6406501273</v>
       </c>
       <c r="J333" t="n">
-        <v>75977.1970512593</v>
+        <v>75976.971063</v>
       </c>
       <c r="K333" t="n">
         <v>340547.95213893</v>
       </c>
       <c r="L333" t="n">
-        <v>37606.9497547057</v>
+        <v>37606.106285</v>
       </c>
       <c r="M333" t="n">
-        <v>71430.9152028874</v>
+        <v>71309.070086</v>
       </c>
       <c r="N333" t="n">
-        <v>534685.412545399</v>
+        <v>534666.796824491</v>
       </c>
       <c r="O333" t="n">
         <v>82557.472932</v>
       </c>
       <c r="P333" t="n">
-        <v>452127.939613399</v>
+        <v>452109.323892491</v>
       </c>
       <c r="Q333" t="n">
-        <v>102161.024366522</v>
+        <v>101799.467560926</v>
       </c>
       <c r="R333" t="n">
-        <v>2040014.56086478</v>
+        <v>2039992.23833619</v>
       </c>
       <c r="S333" t="n">
         <v>389912.592159</v>
       </c>
       <c r="T333" t="n">
-        <v>2429927.15302378</v>
+        <v>2429904.83049519</v>
       </c>
       <c r="U333" t="n">
-        <v>1.23018201052343</v>
+        <v>1.23039226981525</v>
       </c>
       <c r="V333" t="n">
-        <v>18.6298303432892</v>
+        <v>18.6369855507816</v>
       </c>
       <c r="W333" t="n">
         <v>1.36712124772584</v>
@@ -42961,16 +42961,16 @@
         <v>24.9885280040958</v>
       </c>
       <c r="Y333" t="n">
-        <v>1.25213071895443</v>
+        <v>1.25230751734331</v>
       </c>
       <c r="Z333" t="n">
-        <v>19.60622594914</v>
+        <v>19.612341280678</v>
       </c>
       <c r="AA333" t="n">
-        <v>0.839537332765801</v>
+        <v>0.839535858661781</v>
       </c>
       <c r="AB333" t="n">
-        <v>0.160462667234199</v>
+        <v>0.160464141338219</v>
       </c>
     </row>
     <row r="334">
@@ -42978,13 +42978,13 @@
         <v>45170</v>
       </c>
       <c r="B334" t="n">
-        <v>52888.1739259939</v>
+        <v>61651.8189607785</v>
       </c>
       <c r="C334" t="n">
         <v>5226.12889303</v>
       </c>
       <c r="D334" t="n">
-        <v>124337.152546714</v>
+        <v>118996.480271511</v>
       </c>
       <c r="E334" t="n">
         <v>40355.92111146</v>
@@ -42993,52 +42993,52 @@
         <v>107949.4324657</v>
       </c>
       <c r="G334" t="n">
-        <v>283212.090652163</v>
+        <v>280269.327248142</v>
       </c>
       <c r="H334" t="n">
-        <v>80828.2974801605</v>
+        <v>80786.29521166</v>
       </c>
       <c r="I334" t="n">
         <v>34751.9532140549</v>
       </c>
       <c r="J334" t="n">
-        <v>77017.7523109655</v>
+        <v>77017.52984834</v>
       </c>
       <c r="K334" t="n">
         <v>346129.001582067</v>
       </c>
       <c r="L334" t="n">
-        <v>37547.9753434486</v>
+        <v>37547.14503268</v>
       </c>
       <c r="M334" t="n">
-        <v>72684.3479605505</v>
+        <v>72566.50183175</v>
       </c>
       <c r="N334" t="n">
-        <v>543824.887461824</v>
+        <v>543817.997395346</v>
       </c>
       <c r="O334" t="n">
         <v>84253.94924605</v>
       </c>
       <c r="P334" t="n">
-        <v>459570.938215774</v>
+        <v>459564.048149296</v>
       </c>
       <c r="Q334" t="n">
-        <v>105150.072173718</v>
+        <v>104832.956939014</v>
       </c>
       <c r="R334" t="n">
-        <v>2067598.50744202</v>
+        <v>2067586.92025923</v>
       </c>
       <c r="S334" t="n">
         <v>388129.56714165</v>
       </c>
       <c r="T334" t="n">
-        <v>2455728.07458367</v>
+        <v>2455716.48740088</v>
       </c>
       <c r="U334" t="n">
-        <v>1.35214459280875</v>
+        <v>1.35268563303694</v>
       </c>
       <c r="V334" t="n">
-        <v>18.7548663432146</v>
+        <v>18.7593835089255</v>
       </c>
       <c r="W334" t="n">
         <v>-0.457288390579313</v>
@@ -43047,16 +43047,16 @@
         <v>20.9014212853629</v>
       </c>
       <c r="Y334" t="n">
-        <v>1.06179815011276</v>
+        <v>1.06224970549289</v>
       </c>
       <c r="Z334" t="n">
-        <v>19.0890451225317</v>
+        <v>19.092871337131</v>
       </c>
       <c r="AA334" t="n">
-        <v>0.841949289435293</v>
+        <v>0.841948543680445</v>
       </c>
       <c r="AB334" t="n">
-        <v>0.158050710564707</v>
+        <v>0.158051456319555</v>
       </c>
     </row>
     <row r="335">
@@ -43064,13 +43064,13 @@
         <v>45200</v>
       </c>
       <c r="B335" t="n">
-        <v>53584.9154706664</v>
+        <v>62323.2768929711</v>
       </c>
       <c r="C335" t="n">
         <v>5750.238811</v>
       </c>
       <c r="D335" t="n">
-        <v>130910.221840202</v>
+        <v>125506.423670103</v>
       </c>
       <c r="E335" t="n">
         <v>43822.184047</v>
@@ -43079,52 +43079,52 @@
         <v>117011.426804</v>
       </c>
       <c r="G335" t="n">
-        <v>286040.071990424</v>
+        <v>283048.205844026</v>
       </c>
       <c r="H335" t="n">
-        <v>80815.0163558729</v>
+        <v>80772.52423</v>
       </c>
       <c r="I335" t="n">
-        <v>35957.6352862915</v>
+        <v>35956.36384439</v>
       </c>
       <c r="J335" t="n">
-        <v>79001.8021611272</v>
+        <v>79001.577104</v>
       </c>
       <c r="K335" t="n">
-        <v>350416.183395263</v>
+        <v>350406.584616457</v>
       </c>
       <c r="L335" t="n">
-        <v>38135.6720093849</v>
+        <v>38134.832015</v>
       </c>
       <c r="M335" t="n">
-        <v>74535.0663460225</v>
+        <v>74435.50496</v>
       </c>
       <c r="N335" t="n">
-        <v>551995.54234337</v>
+        <v>551974.301178487</v>
       </c>
       <c r="O335" t="n">
         <v>86653.36741</v>
       </c>
       <c r="P335" t="n">
-        <v>465342.17493337</v>
+        <v>465320.933768488</v>
       </c>
       <c r="Q335" t="n">
-        <v>106492.601699341</v>
+        <v>106272.013863927</v>
       </c>
       <c r="R335" t="n">
-        <v>2111994.74650434</v>
+        <v>2111920.38466085</v>
       </c>
       <c r="S335" t="n">
         <v>394469.374399</v>
       </c>
       <c r="T335" t="n">
-        <v>2506464.12090334</v>
+        <v>2506389.75905985</v>
       </c>
       <c r="U335" t="n">
-        <v>2.14723694675314</v>
+        <v>2.14421284867004</v>
       </c>
       <c r="V335" t="n">
-        <v>19.921559054198</v>
+        <v>19.9238755606358</v>
       </c>
       <c r="W335" t="n">
         <v>1.63342548315477</v>
@@ -43133,16 +43133,16 @@
         <v>18.8791301082206</v>
       </c>
       <c r="Y335" t="n">
-        <v>2.06602867983514</v>
+        <v>2.06348216168071</v>
       </c>
       <c r="Z335" t="n">
-        <v>19.7562902149227</v>
+        <v>19.7582318578157</v>
       </c>
       <c r="AA335" t="n">
-        <v>0.842619181695355</v>
+        <v>0.842614512378567</v>
       </c>
       <c r="AB335" t="n">
-        <v>0.157380818304645</v>
+        <v>0.157385487621433</v>
       </c>
     </row>
     <row r="336">
@@ -43150,13 +43150,13 @@
         <v>45231</v>
       </c>
       <c r="B336" t="n">
-        <v>54671.4255309624</v>
+        <v>63408.8440259592</v>
       </c>
       <c r="C336" t="n">
         <v>6083.341165</v>
       </c>
       <c r="D336" t="n">
-        <v>132241.411257139</v>
+        <v>126743.773163103</v>
       </c>
       <c r="E336" t="n">
         <v>39622.095577</v>
@@ -43165,52 +43165,52 @@
         <v>116229.539582</v>
       </c>
       <c r="G336" t="n">
-        <v>288608.643119069</v>
+        <v>285082.191831026</v>
       </c>
       <c r="H336" t="n">
-        <v>81342.857512458</v>
+        <v>81299.850025</v>
       </c>
       <c r="I336" t="n">
-        <v>36543.0165539194</v>
+        <v>36498.87062539</v>
       </c>
       <c r="J336" t="n">
-        <v>80513.5157337105</v>
+        <v>80513.287947</v>
       </c>
       <c r="K336" t="n">
-        <v>354766.789647027</v>
+        <v>354433.508981457</v>
       </c>
       <c r="L336" t="n">
-        <v>39305.9185141745</v>
+        <v>39305.068332</v>
       </c>
       <c r="M336" t="n">
-        <v>75240.8933267922</v>
+        <v>75104.358023</v>
       </c>
       <c r="N336" t="n">
-        <v>565226.642001196</v>
+        <v>564692.688492488</v>
       </c>
       <c r="O336" t="n">
         <v>93257.27568</v>
       </c>
       <c r="P336" t="n">
-        <v>471969.366321196</v>
+        <v>471435.412812488</v>
       </c>
       <c r="Q336" t="n">
-        <v>109279.054786244</v>
+        <v>108958.399197927</v>
       </c>
       <c r="R336" t="n">
-        <v>2152688.81111089</v>
+        <v>2150455.53026384</v>
       </c>
       <c r="S336" t="n">
         <v>392212.975197</v>
       </c>
       <c r="T336" t="n">
-        <v>2544901.78630789</v>
+        <v>2542668.50546084</v>
       </c>
       <c r="U336" t="n">
-        <v>1.92680709428406</v>
+        <v>1.82464954090475</v>
       </c>
       <c r="V336" t="n">
-        <v>20.0403273897166</v>
+        <v>19.92290042722</v>
       </c>
       <c r="W336" t="n">
         <v>-0.572008715616457</v>
@@ -43219,16 +43219,16 @@
         <v>14.4215171983377</v>
       </c>
       <c r="Y336" t="n">
-        <v>1.53354141732931</v>
+        <v>1.44745031254023</v>
       </c>
       <c r="Z336" t="n">
-        <v>19.1386724914113</v>
+        <v>19.0400451987601</v>
       </c>
       <c r="AA336" t="n">
-        <v>0.84588286380748</v>
+        <v>0.8457474993871</v>
       </c>
       <c r="AB336" t="n">
-        <v>0.15411713619252</v>
+        <v>0.1542525006129</v>
       </c>
     </row>
     <row r="337">
@@ -43293,10 +43293,10 @@
         <v>2575510.80871731</v>
       </c>
       <c r="U337" t="n">
-        <v>0.692038150917607</v>
+        <v>0.796608367361684</v>
       </c>
       <c r="V337" t="n">
-        <v>20.6123162665956</v>
+        <v>20.6150745944367</v>
       </c>
       <c r="W337" t="n">
         <v>4.00588342548036</v>
@@ -43305,10 +43305,10 @@
         <v>16.5934600070473</v>
       </c>
       <c r="Y337" t="n">
-        <v>1.20275849441835</v>
+        <v>1.29164707023111</v>
       </c>
       <c r="Z337" t="n">
-        <v>19.9574209418981</v>
+        <v>19.9597172396314</v>
       </c>
       <c r="AA337" t="n">
         <v>0.841614110730073</v>
@@ -43382,7 +43382,7 @@
         <v>1.31265550337536</v>
       </c>
       <c r="V338" t="n">
-        <v>21.2650499654003</v>
+        <v>21.1611551769544</v>
       </c>
       <c r="W338" t="n">
         <v>2.16480048630818</v>
@@ -43394,7 +43394,7 @@
         <v>1.44762324428409</v>
       </c>
       <c r="Z338" t="n">
-        <v>20.8650772344939</v>
+        <v>20.7783172737837</v>
       </c>
       <c r="AA338" t="n">
         <v>0.840494412193927</v>
@@ -43468,7 +43468,7 @@
         <v>1.24406749239681</v>
       </c>
       <c r="V339" t="n">
-        <v>21.2024825799502</v>
+        <v>21.2060563336407</v>
       </c>
       <c r="W339" t="n">
         <v>0.69919533245355</v>
@@ -43480,7 +43480,7 @@
         <v>1.15715733824586</v>
       </c>
       <c r="Z339" t="n">
-        <v>21.2155804937609</v>
+        <v>21.2185874301687</v>
       </c>
       <c r="AA339" t="n">
         <v>0.841216531130924</v>
@@ -43554,7 +43554,7 @@
         <v>1.30440436153034</v>
       </c>
       <c r="V340" t="n">
-        <v>21.1177662941795</v>
+        <v>21.1190499744108</v>
       </c>
       <c r="W340" t="n">
         <v>1.47525222628604</v>
@@ -43566,7 +43566,7 @@
         <v>1.33153217814515</v>
       </c>
       <c r="Z340" t="n">
-        <v>21.1959063820664</v>
+        <v>21.1969873376187</v>
       </c>
       <c r="AA340" t="n">
         <v>0.840991326130079</v>
@@ -43640,19 +43640,19 @@
         <v>0.758195749969448</v>
       </c>
       <c r="V341" t="n">
-        <v>20.6853109442313</v>
+        <v>21.0536489042835</v>
       </c>
       <c r="W341" t="n">
         <v>0.379280803051252</v>
       </c>
       <c r="X341" t="n">
-        <v>20.7902278354922</v>
+        <v>20.8735977192155</v>
       </c>
       <c r="Y341" t="n">
         <v>0.697944986750487</v>
       </c>
       <c r="Z341" t="n">
-        <v>20.7019286900056</v>
+        <v>21.0250740397612</v>
       </c>
       <c r="AA341" t="n">
         <v>0.841494517821493</v>
@@ -43726,7 +43726,7 @@
         <v>1.22453587007167</v>
       </c>
       <c r="V342" t="n">
-        <v>20.1826363318923</v>
+        <v>20.1829991984679</v>
       </c>
       <c r="W342" t="n">
         <v>4.09255067760357</v>
@@ -43738,7 +43738,7 @@
         <v>1.67913194003462</v>
       </c>
       <c r="Z342" t="n">
-        <v>20.6989978660752</v>
+        <v>20.6993044687145</v>
       </c>
       <c r="AA342" t="n">
         <v>0.837732289590408</v>
@@ -43812,7 +43812,7 @@
         <v>0.805440298320081</v>
       </c>
       <c r="V343" t="n">
-        <v>16.8712546399354</v>
+        <v>16.8720960339643</v>
       </c>
       <c r="W343" t="n">
         <v>1.55348429891724</v>
@@ -43824,7 +43824,7 @@
         <v>0.926823685582612</v>
       </c>
       <c r="Z343" t="n">
-        <v>17.5099692680863</v>
+        <v>17.5106809985626</v>
       </c>
       <c r="AA343" t="n">
         <v>0.836724759785978</v>
@@ -43898,7 +43898,7 @@
         <v>0.774516898073752</v>
       </c>
       <c r="V344" t="n">
-        <v>15.8018822407384</v>
+        <v>15.8033899258763</v>
       </c>
       <c r="W344" t="n">
         <v>2.97129045820628</v>
@@ -43910,7 +43910,7 @@
         <v>1.13319562880019</v>
       </c>
       <c r="Z344" t="n">
-        <v>16.6299716666124</v>
+        <v>16.6312467496425</v>
       </c>
       <c r="AA344" t="n">
         <v>0.833757233911398</v>
@@ -43984,7 +43984,7 @@
         <v>1.27025725997074</v>
       </c>
       <c r="V345" t="n">
-        <v>15.8477261701387</v>
+        <v>15.8489938289716</v>
       </c>
       <c r="W345" t="n">
         <v>2.17689373667798</v>
@@ -43996,7 +43996,7 @@
         <v>1.42097901569538</v>
       </c>
       <c r="Z345" t="n">
-        <v>16.8244640879079</v>
+        <v>16.825537305841</v>
       </c>
       <c r="AA345" t="n">
         <v>0.83251818696704</v>
@@ -44070,7 +44070,7 @@
         <v>0.518768188471741</v>
       </c>
       <c r="V346" t="n">
-        <v>14.8951586455524</v>
+        <v>14.8958025416771</v>
       </c>
       <c r="W346" t="n">
         <v>1.4997773175075</v>
@@ -44082,7 +44082,7 @@
         <v>0.68306937600453</v>
       </c>
       <c r="Z346" t="n">
-        <v>16.3866647722441</v>
+        <v>16.3872139372502</v>
       </c>
       <c r="AA346" t="n">
         <v>0.831159629588832</v>
@@ -44156,7 +44156,7 @@
         <v>0.815113999036354</v>
       </c>
       <c r="V347" t="n">
-        <v>13.3967874513018</v>
+        <v>13.400780212687</v>
       </c>
       <c r="W347" t="n">
         <v>2.69740211399569</v>
@@ -44168,7 +44168,7 @@
         <v>1.13292022158664</v>
       </c>
       <c r="Z347" t="n">
-        <v>15.322634137066</v>
+        <v>15.326055633519</v>
       </c>
       <c r="AA347" t="n">
         <v>0.828547743156233</v>
@@ -44242,7 +44242,7 @@
         <v>1.21951981986548</v>
       </c>
       <c r="V348" t="n">
-        <v>12.6099080521457</v>
+        <v>12.7268551581434</v>
       </c>
       <c r="W348" t="n">
         <v>2.44701316713325</v>
@@ -44254,7 +44254,7 @@
         <v>1.42997632451525</v>
       </c>
       <c r="Z348" t="n">
-        <v>15.2050040500894</v>
+        <v>15.3061911015973</v>
       </c>
       <c r="AA348" t="n">
         <v>0.826828593963077</v>
@@ -45558,85 +45558,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57387.6969802784</v>
+        <v>57308.3674632784</v>
       </c>
       <c r="C364" t="n">
-        <v>6542.638972</v>
+        <v>6547.093597</v>
       </c>
       <c r="D364" t="n">
-        <v>147076.172498673</v>
+        <v>147128.823394673</v>
       </c>
       <c r="E364" t="n">
-        <v>112295.537496</v>
+        <v>113216.332553</v>
       </c>
       <c r="F364" t="n">
-        <v>173016.358873</v>
+        <v>173103.45614</v>
       </c>
       <c r="G364" t="n">
-        <v>371427.565263897</v>
+        <v>371462.986348897</v>
       </c>
       <c r="H364" t="n">
-        <v>106091.630069</v>
+        <v>106719.749452</v>
       </c>
       <c r="I364" t="n">
-        <v>49339.9698875668</v>
+        <v>49329.6115015668</v>
       </c>
       <c r="J364" t="n">
-        <v>113458.516269</v>
+        <v>113509.390015</v>
       </c>
       <c r="K364" t="n">
-        <v>464112.884212015</v>
+        <v>464114.807657015</v>
       </c>
       <c r="L364" t="n">
-        <v>48700.712507</v>
+        <v>48688.495129</v>
       </c>
       <c r="M364" t="n">
-        <v>82620.275371</v>
+        <v>82592.419094</v>
       </c>
       <c r="N364" t="n">
-        <v>680718.582196629</v>
+        <v>682113.937579629</v>
       </c>
       <c r="O364" t="n">
-        <v>122278.707368</v>
+        <v>123681.506013</v>
       </c>
       <c r="P364" t="n">
-        <v>558439.874828629</v>
+        <v>558432.431566629</v>
       </c>
       <c r="Q364" t="n">
-        <v>99953.8252244537</v>
+        <v>100250.511790454</v>
       </c>
       <c r="R364" t="n">
-        <v>2628884.67241614</v>
+        <v>2630771.86843614</v>
       </c>
       <c r="S364" t="n">
-        <v>564576.275601</v>
+        <v>567428.050859</v>
       </c>
       <c r="T364" t="n">
-        <v>3193460.94801714</v>
+        <v>3198199.91929514</v>
       </c>
       <c r="U364" t="n">
-        <v>-0.308701758850261</v>
+        <v>-0.23713642042239</v>
       </c>
       <c r="V364" t="n">
-        <v>6.9881525798108</v>
+        <v>7.06495610712192</v>
       </c>
       <c r="W364" t="n">
-        <v>0.684288802836086</v>
+        <v>1.19286306655555</v>
       </c>
       <c r="X364" t="n">
-        <v>1.87069261612267</v>
+        <v>2.38525961667317</v>
       </c>
       <c r="Y364" t="n">
-        <v>-0.134577382933465</v>
+        <v>0.0136190024776273</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.04634557429928</v>
+        <v>6.20371420788959</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.823208648926315</v>
+        <v>0.822578930280238</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.176791351073685</v>
+        <v>0.177421069719762</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -41258,13 +41258,13 @@
         <v>44562</v>
       </c>
       <c r="B314" t="n">
-        <v>59751.403989751</v>
+        <v>53032.8666853723</v>
       </c>
       <c r="C314" t="n">
         <v>3088.559712</v>
       </c>
       <c r="D314" t="n">
-        <v>111363.393024108</v>
+        <v>115336.716178298</v>
       </c>
       <c r="E314" t="n">
         <v>29853.94119</v>
@@ -41273,52 +41273,52 @@
         <v>82508.82319714</v>
       </c>
       <c r="G314" t="n">
-        <v>205159.802464815</v>
+        <v>207349.14293882</v>
       </c>
       <c r="H314" t="n">
-        <v>74279.836042</v>
+        <v>74311.0846521677</v>
       </c>
       <c r="I314" t="n">
         <v>28728.5886093913</v>
       </c>
       <c r="J314" t="n">
-        <v>60146.39212058</v>
+        <v>60146.5576270659</v>
       </c>
       <c r="K314" t="n">
-        <v>264942.749060519</v>
+        <v>264942.615541379</v>
       </c>
       <c r="L314" t="n">
-        <v>29760.93067823</v>
+        <v>29761.5484081397</v>
       </c>
       <c r="M314" t="n">
-        <v>38500.478171</v>
+        <v>38573.2978820278</v>
       </c>
       <c r="N314" t="n">
-        <v>384256.597267264</v>
+        <v>384230.54596256</v>
       </c>
       <c r="O314" t="n">
         <v>55531.294064</v>
       </c>
       <c r="P314" t="n">
-        <v>328725.303203264</v>
+        <v>328699.25189856</v>
       </c>
       <c r="Q314" t="n">
-        <v>77438.2309000213</v>
+        <v>77946.3089544499</v>
       </c>
       <c r="R314" t="n">
-        <v>1560486.53553508</v>
+        <v>1560491.35534237</v>
       </c>
       <c r="S314" t="n">
         <v>273549.788159</v>
       </c>
       <c r="T314" t="n">
-        <v>1834036.32369408</v>
+        <v>1834041.14350137</v>
       </c>
       <c r="U314" t="n">
-        <v>1.1031514768604</v>
+        <v>1.1034637497928</v>
       </c>
       <c r="V314" t="n">
-        <v>12.8426306420735</v>
+        <v>12.8429791742277</v>
       </c>
       <c r="W314" t="n">
         <v>0.801966565643886</v>
@@ -41327,16 +41327,16 @@
         <v>16.8395535352565</v>
       </c>
       <c r="Y314" t="n">
-        <v>1.05811505802944</v>
+        <v>1.0583806365424</v>
       </c>
       <c r="Z314" t="n">
-        <v>13.4213381250935</v>
+        <v>13.4216361938859</v>
       </c>
       <c r="AA314" t="n">
-        <v>0.850848216785575</v>
+        <v>0.850848608752165</v>
       </c>
       <c r="AB314" t="n">
-        <v>0.149151783214425</v>
+        <v>0.149151391247835</v>
       </c>
     </row>
     <row r="315">
@@ -41344,13 +41344,13 @@
         <v>44593</v>
       </c>
       <c r="B315" t="n">
-        <v>60069.5788977393</v>
+        <v>53351.0415933606</v>
       </c>
       <c r="C315" t="n">
         <v>3025.956532</v>
       </c>
       <c r="D315" t="n">
-        <v>109290.492122159</v>
+        <v>113263.815276349</v>
       </c>
       <c r="E315" t="n">
         <v>27629.892877</v>
@@ -41359,52 +41359,52 @@
         <v>81291.41599814</v>
       </c>
       <c r="G315" t="n">
-        <v>202381.045162179</v>
+        <v>204570.385636184</v>
       </c>
       <c r="H315" t="n">
-        <v>72262.15648</v>
+        <v>72293.4050901677</v>
       </c>
       <c r="I315" t="n">
         <v>28399.3051571157</v>
       </c>
       <c r="J315" t="n">
-        <v>59894.93844158</v>
+        <v>59895.1039480659</v>
       </c>
       <c r="K315" t="n">
-        <v>267706.810830886</v>
+        <v>267706.677311746</v>
       </c>
       <c r="L315" t="n">
-        <v>29544.08892123</v>
+        <v>29544.7066511397</v>
       </c>
       <c r="M315" t="n">
-        <v>39255.511554</v>
+        <v>39328.3312650278</v>
       </c>
       <c r="N315" t="n">
-        <v>390961.365120067</v>
+        <v>390935.313815364</v>
       </c>
       <c r="O315" t="n">
         <v>56340.032166</v>
       </c>
       <c r="P315" t="n">
-        <v>334621.332954067</v>
+        <v>334595.281649364</v>
       </c>
       <c r="Q315" t="n">
-        <v>79855.880029398</v>
+        <v>80363.9580838267</v>
       </c>
       <c r="R315" t="n">
-        <v>1584410.79660356</v>
+        <v>1584415.61641085</v>
       </c>
       <c r="S315" t="n">
         <v>258119.00664</v>
       </c>
       <c r="T315" t="n">
-        <v>1842529.80324356</v>
+        <v>1842534.62305085</v>
       </c>
       <c r="U315" t="n">
-        <v>1.53312832399892</v>
+        <v>1.53312358870639</v>
       </c>
       <c r="V315" t="n">
-        <v>13.6633265572515</v>
+        <v>13.6636723232176</v>
       </c>
       <c r="W315" t="n">
         <v>-5.64094076725473</v>
@@ -41413,16 +41413,16 @@
         <v>10.6896235039097</v>
       </c>
       <c r="Y315" t="n">
-        <v>0.463103126134956</v>
+        <v>0.463101909113273</v>
       </c>
       <c r="Z315" t="n">
-        <v>13.2371543740824</v>
+        <v>13.2374505870724</v>
       </c>
       <c r="AA315" t="n">
-        <v>0.859910539202345</v>
+        <v>0.859910905656357</v>
       </c>
       <c r="AB315" t="n">
-        <v>0.140089460797655</v>
+        <v>0.140089094343643</v>
       </c>
     </row>
     <row r="316">
@@ -41430,13 +41430,13 @@
         <v>44621</v>
       </c>
       <c r="B316" t="n">
-        <v>58480.0178154955</v>
+        <v>51761.4805111168</v>
       </c>
       <c r="C316" t="n">
         <v>3042.460377</v>
       </c>
       <c r="D316" t="n">
-        <v>114929.569942505</v>
+        <v>118902.893096695</v>
       </c>
       <c r="E316" t="n">
         <v>29364.979116</v>
@@ -41445,52 +41445,52 @@
         <v>87992.29630114</v>
       </c>
       <c r="G316" t="n">
-        <v>204039.661354251</v>
+        <v>206229.001828256</v>
       </c>
       <c r="H316" t="n">
-        <v>72920.598888</v>
+        <v>72951.8474981677</v>
       </c>
       <c r="I316" t="n">
         <v>27621.6836080496</v>
       </c>
       <c r="J316" t="n">
-        <v>58984.75099258</v>
+        <v>58984.9164990659</v>
       </c>
       <c r="K316" t="n">
-        <v>271895.463055362</v>
+        <v>271895.329536222</v>
       </c>
       <c r="L316" t="n">
-        <v>28928.68059723</v>
+        <v>28929.2983271397</v>
       </c>
       <c r="M316" t="n">
-        <v>40771.894664</v>
+        <v>40844.7143750278</v>
       </c>
       <c r="N316" t="n">
-        <v>399715.866972354</v>
+        <v>399689.81566765</v>
       </c>
       <c r="O316" t="n">
         <v>56191.318388</v>
       </c>
       <c r="P316" t="n">
-        <v>343524.548584354</v>
+        <v>343498.49727965</v>
       </c>
       <c r="Q316" t="n">
-        <v>80726.4667860365</v>
+        <v>81234.5448404652</v>
       </c>
       <c r="R316" t="n">
-        <v>1612388.58535036</v>
+        <v>1612393.40515765</v>
       </c>
       <c r="S316" t="n">
         <v>266741.672092</v>
       </c>
       <c r="T316" t="n">
-        <v>1879130.25744236</v>
+        <v>1879135.07724965</v>
       </c>
       <c r="U316" t="n">
-        <v>1.76581659294235</v>
+        <v>1.76581122131159</v>
       </c>
       <c r="V316" t="n">
-        <v>14.1915310467052</v>
+        <v>14.1918723919484</v>
       </c>
       <c r="W316" t="n">
         <v>3.34057749727283</v>
@@ -41499,16 +41499,16 @@
         <v>16.0090898824449</v>
       </c>
       <c r="Y316" t="n">
-        <v>1.98642399891524</v>
+        <v>1.98641880271391</v>
       </c>
       <c r="Z316" t="n">
-        <v>14.446056532499</v>
+        <v>14.4463500767785</v>
       </c>
       <c r="AA316" t="n">
-        <v>0.858050461890249</v>
+        <v>0.858050825977656</v>
       </c>
       <c r="AB316" t="n">
-        <v>0.141949538109751</v>
+        <v>0.141949174022344</v>
       </c>
     </row>
     <row r="317">
@@ -41516,13 +41516,13 @@
         <v>44652</v>
       </c>
       <c r="B317" t="n">
-        <v>59842.6549764806</v>
+        <v>53124.1176721019</v>
       </c>
       <c r="C317" t="n">
         <v>2953.653841</v>
       </c>
       <c r="D317" t="n">
-        <v>117322.997897435</v>
+        <v>121296.321051625</v>
       </c>
       <c r="E317" t="n">
         <v>29377.542547</v>
@@ -41531,52 +41531,52 @@
         <v>85669.47730014</v>
       </c>
       <c r="G317" t="n">
-        <v>202955.979678191</v>
+        <v>205145.320152196</v>
       </c>
       <c r="H317" t="n">
-        <v>76058.409097</v>
+        <v>76089.6577071677</v>
       </c>
       <c r="I317" t="n">
         <v>28426.790062059</v>
       </c>
       <c r="J317" t="n">
-        <v>59527.19205758</v>
+        <v>59527.3575640659</v>
       </c>
       <c r="K317" t="n">
-        <v>275369.908905373</v>
+        <v>275369.775386233</v>
       </c>
       <c r="L317" t="n">
-        <v>29237.49039723</v>
+        <v>29238.1081271397</v>
       </c>
       <c r="M317" t="n">
-        <v>42477.309911</v>
+        <v>42550.1296220278</v>
       </c>
       <c r="N317" t="n">
-        <v>402989.555126419</v>
+        <v>402963.503821715</v>
       </c>
       <c r="O317" t="n">
         <v>57349.428334</v>
       </c>
       <c r="P317" t="n">
-        <v>345640.126792419</v>
+        <v>345614.075487715</v>
       </c>
       <c r="Q317" t="n">
-        <v>81580.5116385628</v>
+        <v>82088.5896929914</v>
       </c>
       <c r="R317" t="n">
-        <v>1624956.46850589</v>
+        <v>1624961.28831318</v>
       </c>
       <c r="S317" t="n">
         <v>271822.560056</v>
       </c>
       <c r="T317" t="n">
-        <v>1896779.02856189</v>
+        <v>1896783.84836918</v>
       </c>
       <c r="U317" t="n">
-        <v>0.779457462656308</v>
+        <v>0.779455132682294</v>
       </c>
       <c r="V317" t="n">
-        <v>14.1252070972309</v>
+        <v>14.1255456056868</v>
       </c>
       <c r="W317" t="n">
         <v>1.90479722352779</v>
@@ -41585,16 +41585,16 @@
         <v>17.3656897559533</v>
       </c>
       <c r="Y317" t="n">
-        <v>0.939198921928552</v>
+        <v>0.939196512970386</v>
       </c>
       <c r="Z317" t="n">
-        <v>14.5785644691908</v>
+        <v>14.5788556188671</v>
       </c>
       <c r="AA317" t="n">
-        <v>0.856692553026542</v>
+        <v>0.856692917176774</v>
       </c>
       <c r="AB317" t="n">
-        <v>0.143307446973458</v>
+        <v>0.143307082823226</v>
       </c>
     </row>
     <row r="318">
@@ -41602,13 +41602,13 @@
         <v>44682</v>
       </c>
       <c r="B318" t="n">
-        <v>62035.3533357207</v>
+        <v>55316.816031342</v>
       </c>
       <c r="C318" t="n">
         <v>3016.1436</v>
       </c>
       <c r="D318" t="n">
-        <v>119557.505286598</v>
+        <v>123530.828440787</v>
       </c>
       <c r="E318" t="n">
         <v>30598.601441</v>
@@ -41617,52 +41617,52 @@
         <v>86760.52349114</v>
       </c>
       <c r="G318" t="n">
-        <v>207342.586799492</v>
+        <v>209531.927273497</v>
       </c>
       <c r="H318" t="n">
-        <v>75179.981141</v>
+        <v>75211.2297511677</v>
       </c>
       <c r="I318" t="n">
         <v>28761.8233561185</v>
       </c>
       <c r="J318" t="n">
-        <v>60329.83180258</v>
+        <v>60329.9973090659</v>
       </c>
       <c r="K318" t="n">
-        <v>279708.803989455</v>
+        <v>279708.670470315</v>
       </c>
       <c r="L318" t="n">
-        <v>29237.91604823</v>
+        <v>29238.5337781397</v>
       </c>
       <c r="M318" t="n">
-        <v>44236.291465</v>
+        <v>44309.1111760278</v>
       </c>
       <c r="N318" t="n">
-        <v>413145.830919373</v>
+        <v>413119.77961467</v>
       </c>
       <c r="O318" t="n">
         <v>60142.33963</v>
       </c>
       <c r="P318" t="n">
-        <v>353003.491289373</v>
+        <v>352977.43998467</v>
       </c>
       <c r="Q318" t="n">
-        <v>82531.4210982901</v>
+        <v>83039.4991527188</v>
       </c>
       <c r="R318" t="n">
-        <v>1654530.60394537</v>
+        <v>1654535.42375266</v>
       </c>
       <c r="S318" t="n">
         <v>281057.840748</v>
       </c>
       <c r="T318" t="n">
-        <v>1935588.44469337</v>
+        <v>1935593.26450066</v>
       </c>
       <c r="U318" t="n">
-        <v>1.81999555143004</v>
+        <v>1.81999015313048</v>
       </c>
       <c r="V318" t="n">
-        <v>14.6659639040573</v>
+        <v>14.6662979370738</v>
       </c>
       <c r="W318" t="n">
         <v>3.39754017845222</v>
@@ -41671,16 +41671,16 @@
         <v>19.7147481805512</v>
       </c>
       <c r="Y318" t="n">
-        <v>2.0460694444153</v>
+        <v>2.04606424526705</v>
       </c>
       <c r="Z318" t="n">
-        <v>15.3724832911907</v>
+        <v>15.3727705801221</v>
       </c>
       <c r="AA318" t="n">
-        <v>0.854794627691361</v>
+        <v>0.854794989266246</v>
       </c>
       <c r="AB318" t="n">
-        <v>0.145205372308639</v>
+        <v>0.145205010733754</v>
       </c>
     </row>
     <row r="319">
@@ -41688,13 +41688,13 @@
         <v>44713</v>
       </c>
       <c r="B319" t="n">
-        <v>62387.7895519757</v>
+        <v>54548.499239595</v>
       </c>
       <c r="C319" t="n">
         <v>3339.735301</v>
       </c>
       <c r="D319" t="n">
-        <v>121261.461775464</v>
+        <v>125966.60744254</v>
       </c>
       <c r="E319" t="n">
         <v>32041.873818</v>
@@ -41703,52 +41703,52 @@
         <v>88870.89337714</v>
       </c>
       <c r="G319" t="n">
-        <v>212945.846370579</v>
+        <v>215538.428308989</v>
       </c>
       <c r="H319" t="n">
-        <v>77665.76672</v>
+        <v>77702.7708238766</v>
       </c>
       <c r="I319" t="n">
         <v>28408.448078981</v>
       </c>
       <c r="J319" t="n">
-        <v>59834.07078458</v>
+        <v>59834.2667747109</v>
       </c>
       <c r="K319" t="n">
-        <v>283523.810542522</v>
+        <v>283523.736007522</v>
       </c>
       <c r="L319" t="n">
-        <v>29772.80719123</v>
+        <v>29773.5386970993</v>
       </c>
       <c r="M319" t="n">
-        <v>45371.846148</v>
+        <v>45276.8355336994</v>
       </c>
       <c r="N319" t="n">
-        <v>421042.560620673</v>
+        <v>421073.930528191</v>
       </c>
       <c r="O319" t="n">
         <v>60877.840124</v>
       </c>
       <c r="P319" t="n">
-        <v>360164.720496673</v>
+        <v>360196.090404191</v>
       </c>
       <c r="Q319" t="n">
-        <v>84454.0743447733</v>
+        <v>85104.9927736929</v>
       </c>
       <c r="R319" t="n">
-        <v>1678914.47869159</v>
+        <v>1679029.42067923</v>
       </c>
       <c r="S319" t="n">
         <v>293049.066554</v>
       </c>
       <c r="T319" t="n">
-        <v>1971963.54524559</v>
+        <v>1972078.48723323</v>
       </c>
       <c r="U319" t="n">
-        <v>1.47376389944525</v>
+        <v>1.48041538276724</v>
       </c>
       <c r="V319" t="n">
-        <v>14.996387585435</v>
+        <v>15.0042604780259</v>
       </c>
       <c r="W319" t="n">
         <v>4.26646194039164</v>
@@ -41757,16 +41757,16 @@
         <v>22.7852461933471</v>
       </c>
       <c r="Y319" t="n">
-        <v>1.87927865822648</v>
+        <v>1.88496330307184</v>
       </c>
       <c r="Z319" t="n">
-        <v>16.0907641006653</v>
+        <v>16.0975308095145</v>
       </c>
       <c r="AA319" t="n">
-        <v>0.851392249486284</v>
+        <v>0.851400911043282</v>
       </c>
       <c r="AB319" t="n">
-        <v>0.148607750513716</v>
+        <v>0.148599088956718</v>
       </c>
     </row>
     <row r="320">
@@ -41774,13 +41774,13 @@
         <v>44743</v>
       </c>
       <c r="B320" t="n">
-        <v>62365.2764381016</v>
+        <v>54160.253295989</v>
       </c>
       <c r="C320" t="n">
         <v>3436.997793</v>
       </c>
       <c r="D320" t="n">
-        <v>121616.116244675</v>
+        <v>126391.780859079</v>
       </c>
       <c r="E320" t="n">
         <v>32685.603062</v>
@@ -41789,52 +41789,52 @@
         <v>89664.14552314</v>
       </c>
       <c r="G320" t="n">
-        <v>217662.352587013</v>
+        <v>220293.791164961</v>
       </c>
       <c r="H320" t="n">
-        <v>78577.98496</v>
+        <v>78615.5436674185</v>
       </c>
       <c r="I320" t="n">
         <v>29027.4446516128</v>
       </c>
       <c r="J320" t="n">
-        <v>61348.16475958</v>
+        <v>61348.363687137</v>
       </c>
       <c r="K320" t="n">
-        <v>287216.423924145</v>
+        <v>287216.371756145</v>
       </c>
       <c r="L320" t="n">
-        <v>30354.08258523</v>
+        <v>30354.8250546331</v>
       </c>
       <c r="M320" t="n">
-        <v>47235.089684</v>
+        <v>47410.6364722354</v>
       </c>
       <c r="N320" t="n">
-        <v>429295.091251454</v>
+        <v>429330.941105179</v>
       </c>
       <c r="O320" t="n">
         <v>62329.819894</v>
       </c>
       <c r="P320" t="n">
-        <v>366965.271357454</v>
+        <v>367001.121211179</v>
       </c>
       <c r="Q320" t="n">
-        <v>83461.2602970882</v>
+        <v>84067.4137447353</v>
       </c>
       <c r="R320" t="n">
-        <v>1702003.67084549</v>
+        <v>1702097.59877544</v>
       </c>
       <c r="S320" t="n">
         <v>301237.454167</v>
       </c>
       <c r="T320" t="n">
-        <v>2003241.12501249</v>
+        <v>2003335.05294244</v>
       </c>
       <c r="U320" t="n">
-        <v>1.37524528181425</v>
+        <v>1.37389957627334</v>
       </c>
       <c r="V320" t="n">
-        <v>16.0512544812111</v>
+        <v>16.0576589645199</v>
       </c>
       <c r="W320" t="n">
         <v>2.79420361555429</v>
@@ -41843,16 +41843,16 @@
         <v>21.9254441578109</v>
       </c>
       <c r="Y320" t="n">
-        <v>1.58611348786406</v>
+        <v>1.58495546255204</v>
       </c>
       <c r="Z320" t="n">
-        <v>16.8981640720886</v>
+        <v>16.9036451908762</v>
       </c>
       <c r="AA320" t="n">
-        <v>0.849624965059999</v>
+        <v>0.84963201551106</v>
       </c>
       <c r="AB320" t="n">
-        <v>0.150375034940001</v>
+        <v>0.15036798448894</v>
       </c>
     </row>
     <row r="321">
@@ -41860,13 +41860,13 @@
         <v>44774</v>
       </c>
       <c r="B321" t="n">
-        <v>62607.9427573849</v>
+        <v>54516.2168351685</v>
       </c>
       <c r="C321" t="n">
         <v>3397.6616</v>
       </c>
       <c r="D321" t="n">
-        <v>120374.886859805</v>
+        <v>125171.884143127</v>
       </c>
       <c r="E321" t="n">
         <v>35512.612282</v>
@@ -41875,52 +41875,52 @@
         <v>84297.50612114</v>
       </c>
       <c r="G321" t="n">
-        <v>223355.130031731</v>
+        <v>225998.323121876</v>
       </c>
       <c r="H321" t="n">
-        <v>78381.604223</v>
+        <v>78419.3307033957</v>
       </c>
       <c r="I321" t="n">
         <v>30244.6131245909</v>
       </c>
       <c r="J321" t="n">
-        <v>62788.08905058</v>
+        <v>62788.2888667371</v>
       </c>
       <c r="K321" t="n">
-        <v>292424.505731569</v>
+        <v>292424.44863057</v>
       </c>
       <c r="L321" t="n">
-        <v>30742.99537723</v>
+        <v>30743.741163209</v>
       </c>
       <c r="M321" t="n">
-        <v>48877.262599</v>
+        <v>48926.384704577</v>
       </c>
       <c r="N321" t="n">
-        <v>437016.697235</v>
+        <v>437055.361683373</v>
       </c>
       <c r="O321" t="n">
         <v>64244.414608</v>
       </c>
       <c r="P321" t="n">
-        <v>372772.282627</v>
+        <v>372810.947075373</v>
       </c>
       <c r="Q321" t="n">
-        <v>84445.1732215086</v>
+        <v>85054.1735920519</v>
       </c>
       <c r="R321" t="n">
-        <v>1719524.67341054</v>
+        <v>1719647.20421619</v>
       </c>
       <c r="S321" t="n">
         <v>311958.704039</v>
       </c>
       <c r="T321" t="n">
-        <v>2031483.37744954</v>
+        <v>2031605.90825519</v>
       </c>
       <c r="U321" t="n">
-        <v>1.02943388813854</v>
+        <v>1.0310575288615</v>
       </c>
       <c r="V321" t="n">
-        <v>16.1782399917979</v>
+        <v>16.1865186827438</v>
       </c>
       <c r="W321" t="n">
         <v>3.55906934004839</v>
@@ -41929,16 +41929,16 @@
         <v>25.862031708732</v>
       </c>
       <c r="Y321" t="n">
-        <v>1.40982790760495</v>
+        <v>1.41118956967392</v>
       </c>
       <c r="Z321" t="n">
-        <v>17.567300235875</v>
+        <v>17.5743914167214</v>
       </c>
       <c r="AA321" t="n">
-        <v>0.846437973600033</v>
+        <v>0.846447235277574</v>
       </c>
       <c r="AB321" t="n">
-        <v>0.153562026399967</v>
+        <v>0.153552764722426</v>
       </c>
     </row>
     <row r="322">
@@ -41946,13 +41946,13 @@
         <v>44805</v>
       </c>
       <c r="B322" t="n">
-        <v>62804.9753541374</v>
+        <v>54742.8136785258</v>
       </c>
       <c r="C322" t="n">
         <v>3798.460005</v>
       </c>
       <c r="D322" t="n">
-        <v>114919.643820101</v>
+        <v>119627.914176783</v>
       </c>
       <c r="E322" t="n">
         <v>36189.776506</v>
@@ -41961,52 +41961,52 @@
         <v>86400.14876</v>
       </c>
       <c r="G322" t="n">
-        <v>230855.158921852</v>
+        <v>233449.462595232</v>
       </c>
       <c r="H322" t="n">
-        <v>79163.43139</v>
+        <v>79200.4600683206</v>
       </c>
       <c r="I322" t="n">
         <v>30544.1119120083</v>
       </c>
       <c r="J322" t="n">
-        <v>62656.378634</v>
+        <v>62656.5747542881</v>
       </c>
       <c r="K322" t="n">
-        <v>296443.337254835</v>
+        <v>296443.285086835</v>
       </c>
       <c r="L322" t="n">
-        <v>31198.76896</v>
+        <v>31199.5009516627</v>
       </c>
       <c r="M322" t="n">
-        <v>50401.743505</v>
+        <v>50567.3542726374</v>
       </c>
       <c r="N322" t="n">
-        <v>445537.338794872</v>
+        <v>445565.816684563</v>
       </c>
       <c r="O322" t="n">
         <v>65773.067975</v>
       </c>
       <c r="P322" t="n">
-        <v>379764.270819872</v>
+        <v>379792.748709563</v>
       </c>
       <c r="Q322" t="n">
-        <v>85567.4240917834</v>
+        <v>86142.5210395142</v>
       </c>
       <c r="R322" t="n">
-        <v>1740988.25639646</v>
+        <v>1741064.23686793</v>
       </c>
       <c r="S322" t="n">
         <v>321029.780308</v>
       </c>
       <c r="T322" t="n">
-        <v>2062018.03670446</v>
+        <v>2062094.01717593</v>
       </c>
       <c r="U322" t="n">
-        <v>1.24822768279047</v>
+        <v>1.24543177224001</v>
       </c>
       <c r="V322" t="n">
-        <v>16.4006939047954</v>
+        <v>16.4057738813949</v>
       </c>
       <c r="W322" t="n">
         <v>2.90778111062608</v>
@@ -42015,16 +42015,16 @@
         <v>29.3046222061123</v>
       </c>
       <c r="Y322" t="n">
-        <v>1.50307207008793</v>
+        <v>1.50069010908367</v>
       </c>
       <c r="Z322" t="n">
-        <v>18.2377263347827</v>
+        <v>18.2420831144194</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.844312816574062</v>
+        <v>0.844318553065949</v>
       </c>
       <c r="AB322" t="n">
-        <v>0.155687183425938</v>
+        <v>0.155681446934051</v>
       </c>
     </row>
     <row r="323">
@@ -42032,13 +42032,13 @@
         <v>44835</v>
       </c>
       <c r="B323" t="n">
-        <v>63071.8906228081</v>
+        <v>54838.1374500293</v>
       </c>
       <c r="C323" t="n">
         <v>4001.717958</v>
       </c>
       <c r="D323" t="n">
-        <v>120047.152322909</v>
+        <v>124852.539164</v>
       </c>
       <c r="E323" t="n">
         <v>35492.682164</v>
@@ -42047,52 +42047,52 @@
         <v>86292.555056</v>
       </c>
       <c r="G323" t="n">
-        <v>232820.011463036</v>
+        <v>235467.827282738</v>
       </c>
       <c r="H323" t="n">
-        <v>79274.196984</v>
+        <v>79311.9894449389</v>
       </c>
       <c r="I323" t="n">
         <v>31200.1514017623</v>
       </c>
       <c r="J323" t="n">
-        <v>62492.651924</v>
+        <v>62492.8520896192</v>
       </c>
       <c r="K323" t="n">
-        <v>299908.973433703</v>
+        <v>299908.926247703</v>
       </c>
       <c r="L323" t="n">
-        <v>30463.375736</v>
+        <v>30464.122826298</v>
       </c>
       <c r="M323" t="n">
-        <v>51447.444839</v>
+        <v>51635.6377146828</v>
       </c>
       <c r="N323" t="n">
-        <v>454006.897549817</v>
+        <v>454055.796049339</v>
       </c>
       <c r="O323" t="n">
         <v>67776.563931</v>
       </c>
       <c r="P323" t="n">
-        <v>386230.333618817</v>
+        <v>386279.232118339</v>
       </c>
       <c r="Q323" t="n">
-        <v>88348.1204846508</v>
+        <v>88900.015277027</v>
       </c>
       <c r="R323" t="n">
-        <v>1761050.8122655</v>
+        <v>1761146.83895148</v>
       </c>
       <c r="S323" t="n">
         <v>331823.907224</v>
       </c>
       <c r="T323" t="n">
-        <v>2092874.7194895</v>
+        <v>2092970.74617548</v>
       </c>
       <c r="U323" t="n">
-        <v>1.15236595050716</v>
+        <v>1.15346703804962</v>
       </c>
       <c r="V323" t="n">
-        <v>16.643537771693</v>
+        <v>16.6498981176265</v>
       </c>
       <c r="W323" t="n">
         <v>3.36234442351238</v>
@@ -42101,16 +42101,16 @@
         <v>31.5009527851203</v>
       </c>
       <c r="Y323" t="n">
-        <v>1.49643127440129</v>
+        <v>1.49734826551837</v>
       </c>
       <c r="Z323" t="n">
-        <v>18.7711364307553</v>
+        <v>18.7765859679467</v>
       </c>
       <c r="AA323" t="n">
-        <v>0.841450659165619</v>
+        <v>0.841457933499382</v>
       </c>
       <c r="AB323" t="n">
-        <v>0.158549340834381</v>
+        <v>0.158542066500618</v>
       </c>
     </row>
     <row r="324">
@@ -42118,13 +42118,13 @@
         <v>44866</v>
       </c>
       <c r="B324" t="n">
-        <v>64022.5505953227</v>
+        <v>55552.3508663087</v>
       </c>
       <c r="C324" t="n">
         <v>4189.60955967</v>
       </c>
       <c r="D324" t="n">
-        <v>120817.215540406</v>
+        <v>125746.310394769</v>
       </c>
       <c r="E324" t="n">
         <v>35726.64306728</v>
@@ -42133,52 +42133,52 @@
         <v>87050.52811038</v>
       </c>
       <c r="G324" t="n">
-        <v>238381.826525611</v>
+        <v>241097.806687831</v>
       </c>
       <c r="H324" t="n">
-        <v>80375.4433986</v>
+        <v>80414.2087739814</v>
       </c>
       <c r="I324" t="n">
         <v>31688.6038252217</v>
       </c>
       <c r="J324" t="n">
-        <v>62931.36618875</v>
+        <v>62931.5715073552</v>
       </c>
       <c r="K324" t="n">
-        <v>304073.367457054</v>
+        <v>304073.325303054</v>
       </c>
       <c r="L324" t="n">
-        <v>30553.5810255</v>
+        <v>30554.3473486006</v>
       </c>
       <c r="M324" t="n">
-        <v>53459.44929427</v>
+        <v>53645.1065357086</v>
       </c>
       <c r="N324" t="n">
-        <v>467305.251387952</v>
+        <v>467365.052578717</v>
       </c>
       <c r="O324" t="n">
         <v>73328.01964821</v>
       </c>
       <c r="P324" t="n">
-        <v>393977.231739742</v>
+        <v>394037.032930507</v>
       </c>
       <c r="Q324" t="n">
-        <v>88096.748813383</v>
+        <v>88683.2020186275</v>
       </c>
       <c r="R324" t="n">
-        <v>1793198.39880701</v>
+        <v>1793304.68178588</v>
       </c>
       <c r="S324" t="n">
         <v>342779.03737034</v>
       </c>
       <c r="T324" t="n">
-        <v>2135977.43617735</v>
+        <v>2136083.71915622</v>
       </c>
       <c r="U324" t="n">
-        <v>1.82547751135886</v>
+        <v>1.82596034147562</v>
       </c>
       <c r="V324" t="n">
-        <v>16.607393800604</v>
+        <v>16.6143051279728</v>
       </c>
       <c r="W324" t="n">
         <v>3.30148910546841</v>
@@ -42187,16 +42187,16 @@
         <v>31.1805586483905</v>
       </c>
       <c r="Y324" t="n">
-        <v>2.05949817666884</v>
+        <v>2.05989372090014</v>
       </c>
       <c r="Z324" t="n">
-        <v>18.7240022434615</v>
+        <v>18.7299097687041</v>
       </c>
       <c r="AA324" t="n">
-        <v>0.839521227347891</v>
+        <v>0.839529212129503</v>
       </c>
       <c r="AB324" t="n">
-        <v>0.160478772652109</v>
+        <v>0.160470787870497</v>
       </c>
     </row>
     <row r="325">
@@ -42204,13 +42204,13 @@
         <v>44896</v>
       </c>
       <c r="B325" t="n">
-        <v>64055.7602851346</v>
+        <v>55680.284894821</v>
       </c>
       <c r="C325" t="n">
         <v>4189.5002289</v>
       </c>
       <c r="D325" t="n">
-        <v>123373.511138676</v>
+        <v>128318.648595272</v>
       </c>
       <c r="E325" t="n">
         <v>35527.31431429</v>
@@ -42219,52 +42219,52 @@
         <v>87157.09103496</v>
       </c>
       <c r="G325" t="n">
-        <v>237064.883501782</v>
+        <v>239789.703296977</v>
       </c>
       <c r="H325" t="n">
-        <v>81480.66083823</v>
+        <v>81519.5523823129</v>
       </c>
       <c r="I325" t="n">
         <v>32063.1061748284</v>
       </c>
       <c r="J325" t="n">
-        <v>65312.76203509</v>
+        <v>65312.9680219406</v>
       </c>
       <c r="K325" t="n">
-        <v>306627.003205703</v>
+        <v>306626.966130703</v>
       </c>
       <c r="L325" t="n">
-        <v>31900.42639778</v>
+        <v>31901.1952150133</v>
       </c>
       <c r="M325" t="n">
-        <v>54780.71419277</v>
+        <v>54887.9276673326</v>
       </c>
       <c r="N325" t="n">
-        <v>467605.507805088</v>
+        <v>467625.95442717</v>
       </c>
       <c r="O325" t="n">
         <v>70652.67624779</v>
       </c>
       <c r="P325" t="n">
-        <v>396952.831557298</v>
+        <v>396973.27817938</v>
       </c>
       <c r="Q325" t="n">
-        <v>88235.9772213212</v>
+        <v>88794.6581565029</v>
       </c>
       <c r="R325" t="n">
-        <v>1797110.55706986</v>
+        <v>1797151.65585841</v>
       </c>
       <c r="S325" t="n">
         <v>349869.16910978</v>
       </c>
       <c r="T325" t="n">
-        <v>2146979.72617964</v>
+        <v>2147020.82496819</v>
       </c>
       <c r="U325" t="n">
-        <v>0.218166504356199</v>
+        <v>0.214518710155898</v>
       </c>
       <c r="V325" t="n">
-        <v>16.4339048973577</v>
+        <v>16.4365676675579</v>
       </c>
       <c r="W325" t="n">
         <v>2.06842629404427</v>
@@ -42273,16 +42273,16 @@
         <v>28.9253430766853</v>
       </c>
       <c r="Y325" t="n">
-        <v>0.515093924492893</v>
+        <v>0.512016720781561</v>
       </c>
       <c r="Z325" t="n">
-        <v>18.3017595630288</v>
+        <v>18.3040241670875</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.837041232926619</v>
+        <v>0.837044352322496</v>
       </c>
       <c r="AB325" t="n">
-        <v>0.162958767073381</v>
+        <v>0.162955647677504</v>
       </c>
     </row>
     <row r="326">
@@ -42290,13 +42290,13 @@
         <v>44927</v>
       </c>
       <c r="B326" t="n">
-        <v>59412.3771306568</v>
+        <v>51053.3612685873</v>
       </c>
       <c r="C326" t="n">
         <v>4808.16031675</v>
       </c>
       <c r="D326" t="n">
-        <v>122366.915477728</v>
+        <v>127286.581830255</v>
       </c>
       <c r="E326" t="n">
         <v>35396.0294751</v>
@@ -42305,52 +42305,52 @@
         <v>87431.24651272</v>
       </c>
       <c r="G326" t="n">
-        <v>237305.451233989</v>
+        <v>239653.898537539</v>
       </c>
       <c r="H326" t="n">
-        <v>78648.05973497</v>
+        <v>78686.9180305312</v>
       </c>
       <c r="I326" t="n">
-        <v>32505.9698808855</v>
+        <v>32473.7981358284</v>
       </c>
       <c r="J326" t="n">
-        <v>66040.63454885</v>
+        <v>66040.8403596017</v>
       </c>
       <c r="K326" t="n">
-        <v>308970.070915188</v>
+        <v>308727.157671053</v>
       </c>
       <c r="L326" t="n">
-        <v>34610.51770819</v>
+        <v>34611.2858681586</v>
       </c>
       <c r="M326" t="n">
-        <v>56820.92656797</v>
+        <v>56926.6483927774</v>
       </c>
       <c r="N326" t="n">
-        <v>475216.774817504</v>
+        <v>474878.430821528</v>
       </c>
       <c r="O326" t="n">
         <v>71176.02520721</v>
       </c>
       <c r="P326" t="n">
-        <v>404040.749610294</v>
+        <v>403702.405614318</v>
       </c>
       <c r="Q326" t="n">
-        <v>88547.7429733367</v>
+        <v>88891.9951713034</v>
       </c>
       <c r="R326" t="n">
-        <v>1812494.42183269</v>
+        <v>1810941.55293461</v>
       </c>
       <c r="S326" t="n">
         <v>350803.23027865</v>
       </c>
       <c r="T326" t="n">
-        <v>2163297.65211134</v>
+        <v>2161744.78321326</v>
       </c>
       <c r="U326" t="n">
-        <v>0.856033297579395</v>
+        <v>0.767319609964123</v>
       </c>
       <c r="V326" t="n">
-        <v>16.1493150090653</v>
+        <v>16.0494447300088</v>
       </c>
       <c r="W326" t="n">
         <v>0.266974415392673</v>
@@ -42359,16 +42359,16 @@
         <v>28.2410900917045</v>
       </c>
       <c r="Y326" t="n">
-        <v>0.760040988404587</v>
+        <v>0.685785534720429</v>
       </c>
       <c r="Z326" t="n">
-        <v>17.9528248248687</v>
+        <v>17.8678455973059</v>
       </c>
       <c r="AA326" t="n">
-        <v>0.837838667306706</v>
+        <v>0.837722180248674</v>
       </c>
       <c r="AB326" t="n">
-        <v>0.162161332693294</v>
+        <v>0.162277819751326</v>
       </c>
     </row>
     <row r="327">
@@ -42376,13 +42376,13 @@
         <v>44958</v>
       </c>
       <c r="B327" t="n">
-        <v>59094.2040670098</v>
+        <v>50870.0446823573</v>
       </c>
       <c r="C327" t="n">
         <v>4760.009642</v>
       </c>
       <c r="D327" t="n">
-        <v>118721.318964155</v>
+        <v>123653.153329244</v>
       </c>
       <c r="E327" t="n">
         <v>34968.697149</v>
@@ -42391,52 +42391,52 @@
         <v>89523.259123</v>
       </c>
       <c r="G327" t="n">
-        <v>238409.224211766</v>
+        <v>241126.713871572</v>
       </c>
       <c r="H327" t="n">
-        <v>77442.021086</v>
+        <v>77480.8080065463</v>
       </c>
       <c r="I327" t="n">
         <v>32025.2646905055</v>
       </c>
       <c r="J327" t="n">
-        <v>67507.32362</v>
+        <v>67507.529052718</v>
       </c>
       <c r="K327" t="n">
         <v>311957.939422696</v>
       </c>
       <c r="L327" t="n">
-        <v>34750.303148</v>
+        <v>34751.0698970105</v>
       </c>
       <c r="M327" t="n">
-        <v>58660.051077</v>
+        <v>58728.3660049674</v>
       </c>
       <c r="N327" t="n">
-        <v>481478.90757438</v>
+        <v>481511.490664279</v>
       </c>
       <c r="O327" t="n">
         <v>72475.559153</v>
       </c>
       <c r="P327" t="n">
-        <v>409003.34842138</v>
+        <v>409035.931511279</v>
       </c>
       <c r="Q327" t="n">
-        <v>89604.8855759717</v>
+        <v>90060.5684175926</v>
       </c>
       <c r="R327" t="n">
-        <v>1834363.27837986</v>
+        <v>1834417.36607177</v>
       </c>
       <c r="S327" t="n">
         <v>346019.038546</v>
       </c>
       <c r="T327" t="n">
-        <v>2180382.31692586</v>
+        <v>2180436.40461777</v>
       </c>
       <c r="U327" t="n">
-        <v>1.20656131592711</v>
+        <v>1.29633190530722</v>
       </c>
       <c r="V327" t="n">
-        <v>15.7757370949577</v>
+        <v>15.7787986353759</v>
       </c>
       <c r="W327" t="n">
         <v>-1.36378212049241</v>
@@ -42445,16 +42445,16 @@
         <v>34.0540718214504</v>
       </c>
       <c r="Y327" t="n">
-        <v>0.789750998797878</v>
+        <v>0.864654400910525</v>
       </c>
       <c r="Z327" t="n">
-        <v>18.3363391510711</v>
+        <v>18.3389651048958</v>
       </c>
       <c r="AA327" t="n">
-        <v>0.841303501748329</v>
+        <v>0.841307438358122</v>
       </c>
       <c r="AB327" t="n">
-        <v>0.158696498251671</v>
+        <v>0.158692561641878</v>
       </c>
     </row>
     <row r="328">
@@ -42462,13 +42462,13 @@
         <v>44986</v>
       </c>
       <c r="B328" t="n">
-        <v>58457.7086814553</v>
+        <v>50349.3008854772</v>
       </c>
       <c r="C328" t="n">
         <v>4774.23830511</v>
       </c>
       <c r="D328" t="n">
-        <v>118498.15248464</v>
+        <v>123442.232567556</v>
       </c>
       <c r="E328" t="n">
         <v>36267.39931458</v>
@@ -42477,52 +42477,52 @@
         <v>91291.28418439</v>
       </c>
       <c r="G328" t="n">
-        <v>245347.07063997</v>
+        <v>248071.307811779</v>
       </c>
       <c r="H328" t="n">
-        <v>75053.89433261</v>
+        <v>75092.7775608685</v>
       </c>
       <c r="I328" t="n">
         <v>31656.9011918792</v>
       </c>
       <c r="J328" t="n">
-        <v>69703.72463315</v>
+        <v>69703.9305759563</v>
       </c>
       <c r="K328" t="n">
         <v>316897.81103141</v>
       </c>
       <c r="L328" t="n">
-        <v>35112.59590065</v>
+        <v>35113.3645534941</v>
       </c>
       <c r="M328" t="n">
-        <v>60332.71536325</v>
+        <v>60334.3670268745</v>
       </c>
       <c r="N328" t="n">
-        <v>487326.515728954</v>
+        <v>487324.456526539</v>
       </c>
       <c r="O328" t="n">
         <v>71730.31727735</v>
       </c>
       <c r="P328" t="n">
-        <v>415596.198451604</v>
+        <v>415594.139249189</v>
       </c>
       <c r="Q328" t="n">
-        <v>91762.0501310279</v>
+        <v>92184.4590411835</v>
       </c>
       <c r="R328" t="n">
-        <v>1859625.70369352</v>
+        <v>1859645.41314513</v>
       </c>
       <c r="S328" t="n">
         <v>350182.87395851</v>
       </c>
       <c r="T328" t="n">
-        <v>2209808.57765203</v>
+        <v>2209828.28710364</v>
       </c>
       <c r="U328" t="n">
-        <v>1.37717678997424</v>
+        <v>1.37526211537031</v>
       </c>
       <c r="V328" t="n">
-        <v>15.3335939356977</v>
+        <v>15.3344715499694</v>
       </c>
       <c r="W328" t="n">
         <v>1.20335442523822</v>
@@ -42531,16 +42531,16 @@
         <v>31.2816520988632</v>
       </c>
       <c r="Y328" t="n">
-        <v>1.34959178937282</v>
+        <v>1.3479816436573</v>
       </c>
       <c r="Z328" t="n">
-        <v>17.5974134257065</v>
+        <v>17.59816065687</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.84153248498538</v>
+        <v>0.841533898356652</v>
       </c>
       <c r="AB328" t="n">
-        <v>0.15846751501462</v>
+        <v>0.158466101643348</v>
       </c>
     </row>
     <row r="329">
@@ -42563,7 +42563,7 @@
         <v>92388.3341763843</v>
       </c>
       <c r="G329" t="n">
-        <v>245964.859643147</v>
+        <v>248125.634538147</v>
       </c>
       <c r="H329" t="n">
         <v>73847.855461007</v>
@@ -42575,58 +42575,58 @@
         <v>68967.3120088249</v>
       </c>
       <c r="K329" t="n">
-        <v>319949.143495009</v>
+        <v>320423.999696009</v>
       </c>
       <c r="L329" t="n">
         <v>35292.7128625605</v>
       </c>
       <c r="M329" t="n">
-        <v>60740.7724323225</v>
+        <v>61483.5784123225</v>
       </c>
       <c r="N329" t="n">
-        <v>493117.30235994</v>
+        <v>494313.34072894</v>
       </c>
       <c r="O329" t="n">
         <v>73511.7200018623</v>
       </c>
       <c r="P329" t="n">
-        <v>419605.582358078</v>
+        <v>420801.620727078</v>
       </c>
       <c r="Q329" t="n">
-        <v>93960.3381095911</v>
+        <v>94155.7168985911</v>
       </c>
       <c r="R329" t="n">
-        <v>1874737.61526445</v>
+        <v>1880459.41374545</v>
       </c>
       <c r="S329" t="n">
-        <v>353655.100534038</v>
+        <v>353899.194656038</v>
       </c>
       <c r="T329" t="n">
-        <v>2228392.71579849</v>
+        <v>2234358.60840149</v>
       </c>
       <c r="U329" t="n">
-        <v>0.812631893661031</v>
+        <v>1.1192456611997</v>
       </c>
       <c r="V329" t="n">
-        <v>15.3715592755683</v>
+        <v>15.7233361354411</v>
       </c>
       <c r="W329" t="n">
-        <v>0.991546655688014</v>
+        <v>1.0612514128741</v>
       </c>
       <c r="X329" t="n">
-        <v>30.1051319880068</v>
+        <v>30.194931054703</v>
       </c>
       <c r="Y329" t="n">
-        <v>0.840984071398854</v>
+        <v>1.11005553874979</v>
       </c>
       <c r="Z329" t="n">
-        <v>17.4829899657857</v>
+        <v>17.79721818712</v>
       </c>
       <c r="AA329" t="n">
-        <v>0.841295881992993</v>
+        <v>0.841610387282807</v>
       </c>
       <c r="AB329" t="n">
-        <v>0.158704118007007</v>
+        <v>0.158389612717193</v>
       </c>
     </row>
     <row r="330">
@@ -42634,13 +42634,13 @@
         <v>45047</v>
       </c>
       <c r="B330" t="n">
-        <v>59332.7775534677</v>
+        <v>50887.9583563286</v>
       </c>
       <c r="C330" t="n">
         <v>4883.710808</v>
       </c>
       <c r="D330" t="n">
-        <v>122834.211100723</v>
+        <v>127955.566193593</v>
       </c>
       <c r="E330" t="n">
         <v>36789.346255</v>
@@ -42649,70 +42649,70 @@
         <v>93610.49583814</v>
       </c>
       <c r="G330" t="n">
-        <v>253645.976769588</v>
+        <v>256467.894230479</v>
       </c>
       <c r="H330" t="n">
-        <v>74244.190984</v>
+        <v>74284.4684098768</v>
       </c>
       <c r="I330" t="n">
         <v>31475.0252350713</v>
       </c>
       <c r="J330" t="n">
-        <v>69716.873592</v>
+        <v>69717.0869190947</v>
       </c>
       <c r="K330" t="n">
         <v>324645.955466881</v>
       </c>
       <c r="L330" t="n">
-        <v>35988.356257</v>
+        <v>35989.152470672</v>
       </c>
       <c r="M330" t="n">
-        <v>62308.273573</v>
+        <v>62384.3757074063</v>
       </c>
       <c r="N330" t="n">
-        <v>503647.545147007</v>
+        <v>503647.206393066</v>
       </c>
       <c r="O330" t="n">
         <v>75813.881765</v>
       </c>
       <c r="P330" t="n">
-        <v>427833.663382007</v>
+        <v>427833.324628066</v>
       </c>
       <c r="Q330" t="n">
-        <v>95155.5484280226</v>
+        <v>95546.1546815455</v>
       </c>
       <c r="R330" t="n">
-        <v>1911442.04413091</v>
+        <v>1911447.81533422</v>
       </c>
       <c r="S330" t="n">
         <v>360483.788024</v>
       </c>
       <c r="T330" t="n">
-        <v>2271925.83215491</v>
+        <v>2271931.60335822</v>
       </c>
       <c r="U330" t="n">
-        <v>1.95784351727943</v>
+        <v>1.64791653370735</v>
       </c>
       <c r="V330" t="n">
-        <v>15.527753888197</v>
+        <v>15.5277661567896</v>
       </c>
       <c r="W330" t="n">
-        <v>1.93088901578133</v>
+        <v>1.86058444534238</v>
       </c>
       <c r="X330" t="n">
         <v>28.259644728152</v>
       </c>
       <c r="Y330" t="n">
-        <v>1.95356572689287</v>
+        <v>1.6816009218686</v>
       </c>
       <c r="Z330" t="n">
-        <v>17.3764928378056</v>
+        <v>17.3764987214051</v>
       </c>
       <c r="AA330" t="n">
-        <v>0.841331181272725</v>
+        <v>0.841331584326237</v>
       </c>
       <c r="AB330" t="n">
-        <v>0.158668818727275</v>
+        <v>0.158668415673763</v>
       </c>
     </row>
     <row r="331">
@@ -42720,13 +42720,13 @@
         <v>45078</v>
       </c>
       <c r="B331" t="n">
-        <v>60913.0509992767</v>
+        <v>52139.8189985152</v>
       </c>
       <c r="C331" t="n">
         <v>5436.19738317</v>
       </c>
       <c r="D331" t="n">
-        <v>129940.4963372</v>
+        <v>135228.109965993</v>
       </c>
       <c r="E331" t="n">
         <v>38488.3141894</v>
@@ -42735,52 +42735,52 @@
         <v>103142.07613795</v>
       </c>
       <c r="G331" t="n">
-        <v>273589.165625003</v>
+        <v>276502.693188501</v>
       </c>
       <c r="H331" t="n">
-        <v>78222.59327748</v>
+        <v>78264.1782607778</v>
       </c>
       <c r="I331" t="n">
         <v>32704.2347153109</v>
       </c>
       <c r="J331" t="n">
-        <v>73233.39601769</v>
+        <v>73233.6162701882</v>
       </c>
       <c r="K331" t="n">
         <v>328863.214975899</v>
       </c>
       <c r="L331" t="n">
-        <v>36516.48652541</v>
+        <v>36517.3085871861</v>
       </c>
       <c r="M331" t="n">
-        <v>66737.61411966</v>
+        <v>66852.4045071575</v>
       </c>
       <c r="N331" t="n">
-        <v>515264.661118221</v>
+        <v>515274.205515687</v>
       </c>
       <c r="O331" t="n">
         <v>77403.79127953</v>
       </c>
       <c r="P331" t="n">
-        <v>437860.869838691</v>
+        <v>437870.414236157</v>
       </c>
       <c r="Q331" t="n">
-        <v>96885.9355045209</v>
+        <v>97295.7847427785</v>
       </c>
       <c r="R331" t="n">
-        <v>1981423.50334287</v>
+        <v>1981437.76825266</v>
       </c>
       <c r="S331" t="n">
         <v>373778.59470154</v>
       </c>
       <c r="T331" t="n">
-        <v>2355202.09804441</v>
+        <v>2355216.3629542</v>
       </c>
       <c r="U331" t="n">
-        <v>3.66118655947969</v>
+        <v>3.6616198651598</v>
       </c>
       <c r="V331" t="n">
-        <v>18.0181318638119</v>
+        <v>18.0109022420286</v>
       </c>
       <c r="W331" t="n">
         <v>3.68804565398511</v>
@@ -42789,16 +42789,16 @@
         <v>27.5481267000262</v>
       </c>
       <c r="Y331" t="n">
-        <v>3.66544826027697</v>
+        <v>3.66581280320566</v>
       </c>
       <c r="Z331" t="n">
-        <v>19.434362958829</v>
+        <v>19.4281251076628</v>
       </c>
       <c r="AA331" t="n">
-        <v>0.841296594032462</v>
+        <v>0.841297555256154</v>
       </c>
       <c r="AB331" t="n">
-        <v>0.158703405967538</v>
+        <v>0.158702444743845</v>
       </c>
     </row>
     <row r="332">
@@ -42806,13 +42806,13 @@
         <v>45108</v>
       </c>
       <c r="B332" t="n">
-        <v>61290.8464709959</v>
+        <v>52392.2497194948</v>
       </c>
       <c r="C332" t="n">
         <v>4630.012584</v>
       </c>
       <c r="D332" t="n">
-        <v>130116.787446419</v>
+        <v>135478.07170587</v>
       </c>
       <c r="E332" t="n">
         <v>40919.795296</v>
@@ -42821,52 +42821,52 @@
         <v>111435.211581</v>
       </c>
       <c r="G332" t="n">
-        <v>274079.7695935</v>
+        <v>277033.890405316</v>
       </c>
       <c r="H332" t="n">
-        <v>79521.981454</v>
+        <v>79564.1458275786</v>
       </c>
       <c r="I332" t="n">
         <v>33129.1515374015</v>
       </c>
       <c r="J332" t="n">
-        <v>72931.560997</v>
+        <v>72931.7843182058</v>
       </c>
       <c r="K332" t="n">
         <v>333488.188171627</v>
       </c>
       <c r="L332" t="n">
-        <v>36978.717617</v>
+        <v>36979.5511323001</v>
       </c>
       <c r="M332" t="n">
-        <v>69015.906947</v>
+        <v>69129.0470336903</v>
       </c>
       <c r="N332" t="n">
-        <v>526347.089888982</v>
+        <v>526369.195490555</v>
       </c>
       <c r="O332" t="n">
         <v>80329.811074</v>
       </c>
       <c r="P332" t="n">
-        <v>446017.278814982</v>
+        <v>446039.384416555</v>
       </c>
       <c r="Q332" t="n">
-        <v>99619.2026346803</v>
+        <v>100028.058721675</v>
       </c>
       <c r="R332" t="n">
-        <v>2015197.40524059</v>
+        <v>2015223.64214727</v>
       </c>
       <c r="S332" t="n">
         <v>384653.906868</v>
       </c>
       <c r="T332" t="n">
-        <v>2399851.31210859</v>
+        <v>2399877.54901527</v>
       </c>
       <c r="U332" t="n">
-        <v>1.70452716649099</v>
+        <v>1.70511910270097</v>
       </c>
       <c r="V332" t="n">
-        <v>18.4014723211209</v>
+        <v>18.3964799431655</v>
       </c>
       <c r="W332" t="n">
         <v>2.90955991611661</v>
@@ -42875,16 +42875,16 @@
         <v>27.6912620084605</v>
       </c>
       <c r="Y332" t="n">
-        <v>1.89576996815901</v>
+        <v>1.89626680433927</v>
       </c>
       <c r="Z332" t="n">
-        <v>19.7984247699398</v>
+        <v>19.7941175885878</v>
       </c>
       <c r="AA332" t="n">
-        <v>0.839717608783841</v>
+        <v>0.839719361087472</v>
       </c>
       <c r="AB332" t="n">
-        <v>0.160282391216158</v>
+        <v>0.160280638912528</v>
       </c>
     </row>
     <row r="333">
@@ -42892,13 +42892,13 @@
         <v>45139</v>
       </c>
       <c r="B333" t="n">
-        <v>62333.62345642</v>
+        <v>53376.8619494601</v>
       </c>
       <c r="C333" t="n">
         <v>4870.425066</v>
       </c>
       <c r="D333" t="n">
-        <v>127066.271413687</v>
+        <v>132491.583769656</v>
       </c>
       <c r="E333" t="n">
         <v>41528.425931</v>
@@ -42907,52 +42907,52 @@
         <v>106210.534506</v>
       </c>
       <c r="G333" t="n">
-        <v>276122.150527114</v>
+        <v>279111.551455281</v>
       </c>
       <c r="H333" t="n">
-        <v>80859.598162</v>
+        <v>80902.2660911542</v>
       </c>
       <c r="I333" t="n">
         <v>34340.6406501273</v>
       </c>
       <c r="J333" t="n">
-        <v>75976.971063</v>
+        <v>75977.1970512593</v>
       </c>
       <c r="K333" t="n">
         <v>340547.95213893</v>
       </c>
       <c r="L333" t="n">
-        <v>37606.106285</v>
+        <v>37606.9497547057</v>
       </c>
       <c r="M333" t="n">
-        <v>71309.070086</v>
+        <v>71430.9152028874</v>
       </c>
       <c r="N333" t="n">
-        <v>534666.796824491</v>
+        <v>534685.412545399</v>
       </c>
       <c r="O333" t="n">
         <v>82557.472932</v>
       </c>
       <c r="P333" t="n">
-        <v>452109.323892491</v>
+        <v>452127.939613399</v>
       </c>
       <c r="Q333" t="n">
-        <v>101799.467560926</v>
+        <v>102161.024366522</v>
       </c>
       <c r="R333" t="n">
-        <v>2039992.23833619</v>
+        <v>2040014.56086478</v>
       </c>
       <c r="S333" t="n">
         <v>389912.592159</v>
       </c>
       <c r="T333" t="n">
-        <v>2429904.83049519</v>
+        <v>2429927.15302378</v>
       </c>
       <c r="U333" t="n">
-        <v>1.23039226981525</v>
+        <v>1.23018201052343</v>
       </c>
       <c r="V333" t="n">
-        <v>18.6369855507816</v>
+        <v>18.6298303432892</v>
       </c>
       <c r="W333" t="n">
         <v>1.36712124772584</v>
@@ -42961,16 +42961,16 @@
         <v>24.9885280040958</v>
       </c>
       <c r="Y333" t="n">
-        <v>1.25230751734331</v>
+        <v>1.25213071895443</v>
       </c>
       <c r="Z333" t="n">
-        <v>19.612341280678</v>
+        <v>19.60622594914</v>
       </c>
       <c r="AA333" t="n">
-        <v>0.839535858661781</v>
+        <v>0.839537332765801</v>
       </c>
       <c r="AB333" t="n">
-        <v>0.160464141338219</v>
+        <v>0.160462667234199</v>
       </c>
     </row>
     <row r="334">
@@ -42978,13 +42978,13 @@
         <v>45170</v>
       </c>
       <c r="B334" t="n">
-        <v>61651.8189607785</v>
+        <v>52888.1739259939</v>
       </c>
       <c r="C334" t="n">
         <v>5226.12889303</v>
       </c>
       <c r="D334" t="n">
-        <v>118996.480271511</v>
+        <v>124337.152546714</v>
       </c>
       <c r="E334" t="n">
         <v>40355.92111146</v>
@@ -42993,52 +42993,52 @@
         <v>107949.4324657</v>
       </c>
       <c r="G334" t="n">
-        <v>280269.327248142</v>
+        <v>283212.090652163</v>
       </c>
       <c r="H334" t="n">
-        <v>80786.29521166</v>
+        <v>80828.2974801605</v>
       </c>
       <c r="I334" t="n">
         <v>34751.9532140549</v>
       </c>
       <c r="J334" t="n">
-        <v>77017.52984834</v>
+        <v>77017.7523109655</v>
       </c>
       <c r="K334" t="n">
         <v>346129.001582067</v>
       </c>
       <c r="L334" t="n">
-        <v>37547.14503268</v>
+        <v>37547.9753434486</v>
       </c>
       <c r="M334" t="n">
-        <v>72566.50183175</v>
+        <v>72684.3479605505</v>
       </c>
       <c r="N334" t="n">
-        <v>543817.997395346</v>
+        <v>543824.887461824</v>
       </c>
       <c r="O334" t="n">
         <v>84253.94924605</v>
       </c>
       <c r="P334" t="n">
-        <v>459564.048149296</v>
+        <v>459570.938215774</v>
       </c>
       <c r="Q334" t="n">
-        <v>104832.956939014</v>
+        <v>105150.072173718</v>
       </c>
       <c r="R334" t="n">
-        <v>2067586.92025923</v>
+        <v>2067598.50744202</v>
       </c>
       <c r="S334" t="n">
         <v>388129.56714165</v>
       </c>
       <c r="T334" t="n">
-        <v>2455716.48740088</v>
+        <v>2455728.07458367</v>
       </c>
       <c r="U334" t="n">
-        <v>1.35268563303694</v>
+        <v>1.35214459280875</v>
       </c>
       <c r="V334" t="n">
-        <v>18.7593835089255</v>
+        <v>18.7548663432146</v>
       </c>
       <c r="W334" t="n">
         <v>-0.457288390579313</v>
@@ -43047,16 +43047,16 @@
         <v>20.9014212853629</v>
       </c>
       <c r="Y334" t="n">
-        <v>1.06224970549289</v>
+        <v>1.06179815011276</v>
       </c>
       <c r="Z334" t="n">
-        <v>19.092871337131</v>
+        <v>19.0890451225317</v>
       </c>
       <c r="AA334" t="n">
-        <v>0.841948543680445</v>
+        <v>0.841949289435293</v>
       </c>
       <c r="AB334" t="n">
-        <v>0.158051456319555</v>
+        <v>0.158050710564707</v>
       </c>
     </row>
     <row r="335">
@@ -43064,13 +43064,13 @@
         <v>45200</v>
       </c>
       <c r="B335" t="n">
-        <v>62323.2768929711</v>
+        <v>53584.9154706664</v>
       </c>
       <c r="C335" t="n">
         <v>5750.238811</v>
       </c>
       <c r="D335" t="n">
-        <v>125506.423670103</v>
+        <v>130910.221840202</v>
       </c>
       <c r="E335" t="n">
         <v>43822.184047</v>
@@ -43079,52 +43079,52 @@
         <v>117011.426804</v>
       </c>
       <c r="G335" t="n">
-        <v>283048.205844026</v>
+        <v>286040.071990424</v>
       </c>
       <c r="H335" t="n">
-        <v>80772.52423</v>
+        <v>80815.0163558729</v>
       </c>
       <c r="I335" t="n">
-        <v>35956.36384439</v>
+        <v>35957.6352862915</v>
       </c>
       <c r="J335" t="n">
-        <v>79001.577104</v>
+        <v>79001.8021611272</v>
       </c>
       <c r="K335" t="n">
-        <v>350406.584616457</v>
+        <v>350416.183395263</v>
       </c>
       <c r="L335" t="n">
-        <v>38134.832015</v>
+        <v>38135.6720093849</v>
       </c>
       <c r="M335" t="n">
-        <v>74435.50496</v>
+        <v>74535.0663460225</v>
       </c>
       <c r="N335" t="n">
-        <v>551974.301178487</v>
+        <v>551995.54234337</v>
       </c>
       <c r="O335" t="n">
         <v>86653.36741</v>
       </c>
       <c r="P335" t="n">
-        <v>465320.933768488</v>
+        <v>465342.17493337</v>
       </c>
       <c r="Q335" t="n">
-        <v>106272.013863927</v>
+        <v>106492.601699341</v>
       </c>
       <c r="R335" t="n">
-        <v>2111920.38466085</v>
+        <v>2111994.74650434</v>
       </c>
       <c r="S335" t="n">
         <v>394469.374399</v>
       </c>
       <c r="T335" t="n">
-        <v>2506389.75905985</v>
+        <v>2506464.12090334</v>
       </c>
       <c r="U335" t="n">
-        <v>2.14421284867004</v>
+        <v>2.14723694675314</v>
       </c>
       <c r="V335" t="n">
-        <v>19.9238755606358</v>
+        <v>19.921559054198</v>
       </c>
       <c r="W335" t="n">
         <v>1.63342548315477</v>
@@ -43133,16 +43133,16 @@
         <v>18.8791301082206</v>
       </c>
       <c r="Y335" t="n">
-        <v>2.06348216168071</v>
+        <v>2.06602867983514</v>
       </c>
       <c r="Z335" t="n">
-        <v>19.7582318578157</v>
+        <v>19.7562902149227</v>
       </c>
       <c r="AA335" t="n">
-        <v>0.842614512378567</v>
+        <v>0.842619181695355</v>
       </c>
       <c r="AB335" t="n">
-        <v>0.157385487621433</v>
+        <v>0.157380818304645</v>
       </c>
     </row>
     <row r="336">
@@ -43150,13 +43150,13 @@
         <v>45231</v>
       </c>
       <c r="B336" t="n">
-        <v>63408.8440259592</v>
+        <v>54671.4255309624</v>
       </c>
       <c r="C336" t="n">
         <v>6083.341165</v>
       </c>
       <c r="D336" t="n">
-        <v>126743.773163103</v>
+        <v>132241.411257139</v>
       </c>
       <c r="E336" t="n">
         <v>39622.095577</v>
@@ -43165,52 +43165,52 @@
         <v>116229.539582</v>
       </c>
       <c r="G336" t="n">
-        <v>285082.191831026</v>
+        <v>288608.643119069</v>
       </c>
       <c r="H336" t="n">
-        <v>81299.850025</v>
+        <v>81342.857512458</v>
       </c>
       <c r="I336" t="n">
-        <v>36498.87062539</v>
+        <v>36543.0165539194</v>
       </c>
       <c r="J336" t="n">
-        <v>80513.287947</v>
+        <v>80513.5157337105</v>
       </c>
       <c r="K336" t="n">
-        <v>354433.508981457</v>
+        <v>354766.789647027</v>
       </c>
       <c r="L336" t="n">
-        <v>39305.068332</v>
+        <v>39305.9185141745</v>
       </c>
       <c r="M336" t="n">
-        <v>75104.358023</v>
+        <v>75240.8933267922</v>
       </c>
       <c r="N336" t="n">
-        <v>564692.688492488</v>
+        <v>565226.642001196</v>
       </c>
       <c r="O336" t="n">
         <v>93257.27568</v>
       </c>
       <c r="P336" t="n">
-        <v>471435.412812488</v>
+        <v>471969.366321196</v>
       </c>
       <c r="Q336" t="n">
-        <v>108958.399197927</v>
+        <v>109279.054786244</v>
       </c>
       <c r="R336" t="n">
-        <v>2150455.53026384</v>
+        <v>2152688.81111089</v>
       </c>
       <c r="S336" t="n">
         <v>392212.975197</v>
       </c>
       <c r="T336" t="n">
-        <v>2542668.50546084</v>
+        <v>2544901.78630789</v>
       </c>
       <c r="U336" t="n">
-        <v>1.82464954090475</v>
+        <v>1.92680709428406</v>
       </c>
       <c r="V336" t="n">
-        <v>19.92290042722</v>
+        <v>20.0403273897166</v>
       </c>
       <c r="W336" t="n">
         <v>-0.572008715616457</v>
@@ -43219,16 +43219,16 @@
         <v>14.4215171983377</v>
       </c>
       <c r="Y336" t="n">
-        <v>1.44745031254023</v>
+        <v>1.53354141732931</v>
       </c>
       <c r="Z336" t="n">
-        <v>19.0400451987601</v>
+        <v>19.1386724914113</v>
       </c>
       <c r="AA336" t="n">
-        <v>0.8457474993871</v>
+        <v>0.84588286380748</v>
       </c>
       <c r="AB336" t="n">
-        <v>0.1542525006129</v>
+        <v>0.15411713619252</v>
       </c>
     </row>
     <row r="337">
@@ -43293,10 +43293,10 @@
         <v>2575510.80871731</v>
       </c>
       <c r="U337" t="n">
-        <v>0.796608367361684</v>
+        <v>0.692038150917607</v>
       </c>
       <c r="V337" t="n">
-        <v>20.6150745944367</v>
+        <v>20.6123162665956</v>
       </c>
       <c r="W337" t="n">
         <v>4.00588342548036</v>
@@ -43305,10 +43305,10 @@
         <v>16.5934600070473</v>
       </c>
       <c r="Y337" t="n">
-        <v>1.29164707023111</v>
+        <v>1.20275849441835</v>
       </c>
       <c r="Z337" t="n">
-        <v>19.9597172396314</v>
+        <v>19.9574209418981</v>
       </c>
       <c r="AA337" t="n">
         <v>0.841614110730073</v>
@@ -43382,7 +43382,7 @@
         <v>1.31265550337536</v>
       </c>
       <c r="V338" t="n">
-        <v>21.1611551769544</v>
+        <v>21.2650499654003</v>
       </c>
       <c r="W338" t="n">
         <v>2.16480048630818</v>
@@ -43394,7 +43394,7 @@
         <v>1.44762324428409</v>
       </c>
       <c r="Z338" t="n">
-        <v>20.7783172737837</v>
+        <v>20.8650772344939</v>
       </c>
       <c r="AA338" t="n">
         <v>0.840494412193927</v>
@@ -43468,7 +43468,7 @@
         <v>1.24406749239681</v>
       </c>
       <c r="V339" t="n">
-        <v>21.2060563336407</v>
+        <v>21.2024825799502</v>
       </c>
       <c r="W339" t="n">
         <v>0.69919533245355</v>
@@ -43480,7 +43480,7 @@
         <v>1.15715733824586</v>
       </c>
       <c r="Z339" t="n">
-        <v>21.2185874301687</v>
+        <v>21.2155804937609</v>
       </c>
       <c r="AA339" t="n">
         <v>0.841216531130924</v>
@@ -43554,7 +43554,7 @@
         <v>1.30440436153034</v>
       </c>
       <c r="V340" t="n">
-        <v>21.1190499744108</v>
+        <v>21.1177662941795</v>
       </c>
       <c r="W340" t="n">
         <v>1.47525222628604</v>
@@ -43566,7 +43566,7 @@
         <v>1.33153217814515</v>
       </c>
       <c r="Z340" t="n">
-        <v>21.1969873376187</v>
+        <v>21.1959063820664</v>
       </c>
       <c r="AA340" t="n">
         <v>0.840991326130079</v>
@@ -43640,19 +43640,19 @@
         <v>0.758195749969448</v>
       </c>
       <c r="V341" t="n">
-        <v>21.0536489042835</v>
+        <v>20.6853109442313</v>
       </c>
       <c r="W341" t="n">
         <v>0.379280803051252</v>
       </c>
       <c r="X341" t="n">
-        <v>20.8735977192155</v>
+        <v>20.7902278354922</v>
       </c>
       <c r="Y341" t="n">
         <v>0.697944986750487</v>
       </c>
       <c r="Z341" t="n">
-        <v>21.0250740397612</v>
+        <v>20.7019286900056</v>
       </c>
       <c r="AA341" t="n">
         <v>0.841494517821493</v>
@@ -43726,7 +43726,7 @@
         <v>1.22453587007167</v>
       </c>
       <c r="V342" t="n">
-        <v>20.1829991984679</v>
+        <v>20.1826363318923</v>
       </c>
       <c r="W342" t="n">
         <v>4.09255067760357</v>
@@ -43738,7 +43738,7 @@
         <v>1.67913194003462</v>
       </c>
       <c r="Z342" t="n">
-        <v>20.6993044687145</v>
+        <v>20.6989978660752</v>
       </c>
       <c r="AA342" t="n">
         <v>0.837732289590408</v>
@@ -43812,7 +43812,7 @@
         <v>0.805440298320081</v>
       </c>
       <c r="V343" t="n">
-        <v>16.8720960339643</v>
+        <v>16.8712546399354</v>
       </c>
       <c r="W343" t="n">
         <v>1.55348429891724</v>
@@ -43824,7 +43824,7 @@
         <v>0.926823685582612</v>
       </c>
       <c r="Z343" t="n">
-        <v>17.5106809985626</v>
+        <v>17.5099692680863</v>
       </c>
       <c r="AA343" t="n">
         <v>0.836724759785978</v>
@@ -43898,7 +43898,7 @@
         <v>0.774516898073752</v>
       </c>
       <c r="V344" t="n">
-        <v>15.8033899258763</v>
+        <v>15.8018822407384</v>
       </c>
       <c r="W344" t="n">
         <v>2.97129045820628</v>
@@ -43910,7 +43910,7 @@
         <v>1.13319562880019</v>
       </c>
       <c r="Z344" t="n">
-        <v>16.6312467496425</v>
+        <v>16.6299716666124</v>
       </c>
       <c r="AA344" t="n">
         <v>0.833757233911398</v>
@@ -43984,7 +43984,7 @@
         <v>1.27025725997074</v>
       </c>
       <c r="V345" t="n">
-        <v>15.8489938289716</v>
+        <v>15.8477261701387</v>
       </c>
       <c r="W345" t="n">
         <v>2.17689373667798</v>
@@ -43996,7 +43996,7 @@
         <v>1.42097901569538</v>
       </c>
       <c r="Z345" t="n">
-        <v>16.825537305841</v>
+        <v>16.8244640879079</v>
       </c>
       <c r="AA345" t="n">
         <v>0.83251818696704</v>
@@ -44070,7 +44070,7 @@
         <v>0.518768188471741</v>
       </c>
       <c r="V346" t="n">
-        <v>14.8958025416771</v>
+        <v>14.8951586455524</v>
       </c>
       <c r="W346" t="n">
         <v>1.4997773175075</v>
@@ -44082,7 +44082,7 @@
         <v>0.68306937600453</v>
       </c>
       <c r="Z346" t="n">
-        <v>16.3872139372502</v>
+        <v>16.3866647722441</v>
       </c>
       <c r="AA346" t="n">
         <v>0.831159629588832</v>
@@ -44156,7 +44156,7 @@
         <v>0.815113999036354</v>
       </c>
       <c r="V347" t="n">
-        <v>13.400780212687</v>
+        <v>13.3967874513018</v>
       </c>
       <c r="W347" t="n">
         <v>2.69740211399569</v>
@@ -44168,7 +44168,7 @@
         <v>1.13292022158664</v>
       </c>
       <c r="Z347" t="n">
-        <v>15.326055633519</v>
+        <v>15.322634137066</v>
       </c>
       <c r="AA347" t="n">
         <v>0.828547743156233</v>
@@ -44242,7 +44242,7 @@
         <v>1.21951981986548</v>
       </c>
       <c r="V348" t="n">
-        <v>12.7268551581434</v>
+        <v>12.6099080521457</v>
       </c>
       <c r="W348" t="n">
         <v>2.44701316713325</v>
@@ -44254,7 +44254,7 @@
         <v>1.42997632451525</v>
       </c>
       <c r="Z348" t="n">
-        <v>15.3061911015973</v>
+        <v>15.2050040500894</v>
       </c>
       <c r="AA348" t="n">
         <v>0.826828593963077</v>
@@ -45472,85 +45472,85 @@
         <v>46054</v>
       </c>
       <c r="B363" t="n">
-        <v>57442.1229722784</v>
+        <v>57093.9089582784</v>
       </c>
       <c r="C363" t="n">
-        <v>6562.121351</v>
+        <v>6560.018498</v>
       </c>
       <c r="D363" t="n">
-        <v>149229.906240673</v>
+        <v>149382.155540673</v>
       </c>
       <c r="E363" t="n">
-        <v>111357.96756</v>
+        <v>111405.4749</v>
       </c>
       <c r="F363" t="n">
-        <v>174444.064677</v>
+        <v>173028.328069</v>
       </c>
       <c r="G363" t="n">
-        <v>369624.112691897</v>
+        <v>369932.697172897</v>
       </c>
       <c r="H363" t="n">
-        <v>103878.862811</v>
+        <v>105040.624555</v>
       </c>
       <c r="I363" t="n">
-        <v>49315.5566525668</v>
+        <v>49292.8063305668</v>
       </c>
       <c r="J363" t="n">
-        <v>113339.3614</v>
+        <v>113289.576039</v>
       </c>
       <c r="K363" t="n">
-        <v>463729.956696015</v>
+        <v>463779.994959015</v>
       </c>
       <c r="L363" t="n">
-        <v>48585.400534</v>
+        <v>48623.885833</v>
       </c>
       <c r="M363" t="n">
-        <v>83313.000864</v>
+        <v>83069.229157</v>
       </c>
       <c r="N363" t="n">
-        <v>682865.682473629</v>
+        <v>683300.316861629</v>
       </c>
       <c r="O363" t="n">
-        <v>123451.201212</v>
+        <v>123895.495526</v>
       </c>
       <c r="P363" t="n">
-        <v>559414.481261629</v>
+        <v>559404.821335629</v>
       </c>
       <c r="Q363" t="n">
-        <v>101210.616282454</v>
+        <v>101244.516638454</v>
       </c>
       <c r="R363" t="n">
-        <v>2637025.21563814</v>
+        <v>2637520.39352214</v>
       </c>
       <c r="S363" t="n">
-        <v>560739.200042</v>
+        <v>560823.456852</v>
       </c>
       <c r="T363" t="n">
-        <v>3197764.41568014</v>
+        <v>3198343.85037414</v>
       </c>
       <c r="U363" t="n">
-        <v>1.20555722196638</v>
+        <v>1.2245614974572</v>
       </c>
       <c r="V363" t="n">
-        <v>7.89738596394034</v>
+        <v>7.91764682415279</v>
       </c>
       <c r="W363" t="n">
-        <v>-4.99173634102346</v>
+        <v>-4.97746037597777</v>
       </c>
       <c r="X363" t="n">
-        <v>3.73972158869211</v>
+        <v>3.75530954475207</v>
       </c>
       <c r="Y363" t="n">
-        <v>0.0610456786078739</v>
+        <v>0.0791767332596338</v>
       </c>
       <c r="Z363" t="n">
-        <v>7.14439759162191</v>
+        <v>7.16381214915713</v>
       </c>
       <c r="AA363" t="n">
-        <v>0.824646494503337</v>
+        <v>0.824651918902843</v>
       </c>
       <c r="AB363" t="n">
-        <v>0.175353505496663</v>
+        <v>0.175348081097157</v>
       </c>
     </row>
     <row r="364">
@@ -45558,85 +45558,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57308.3674632784</v>
+        <v>57356.5315252784</v>
       </c>
       <c r="C364" t="n">
-        <v>6547.093597</v>
+        <v>6593.926803</v>
       </c>
       <c r="D364" t="n">
-        <v>147128.823394673</v>
+        <v>147993.097234673</v>
       </c>
       <c r="E364" t="n">
-        <v>113216.332553</v>
+        <v>113799.736514</v>
       </c>
       <c r="F364" t="n">
-        <v>173103.45614</v>
+        <v>173644.145425</v>
       </c>
       <c r="G364" t="n">
-        <v>371462.986348897</v>
+        <v>374575.430254897</v>
       </c>
       <c r="H364" t="n">
-        <v>106719.749452</v>
+        <v>107631.57334</v>
       </c>
       <c r="I364" t="n">
-        <v>49329.6115015668</v>
+        <v>49516.3298275668</v>
       </c>
       <c r="J364" t="n">
-        <v>113509.390015</v>
+        <v>114443.954886</v>
       </c>
       <c r="K364" t="n">
-        <v>464114.807657015</v>
+        <v>464956.203970015</v>
       </c>
       <c r="L364" t="n">
-        <v>48688.495129</v>
+        <v>48766.22808</v>
       </c>
       <c r="M364" t="n">
-        <v>82592.419094</v>
+        <v>82608.814844</v>
       </c>
       <c r="N364" t="n">
-        <v>682113.937579629</v>
+        <v>683292.063900629</v>
       </c>
       <c r="O364" t="n">
-        <v>123681.506013</v>
+        <v>124169.381737</v>
       </c>
       <c r="P364" t="n">
-        <v>558432.431566629</v>
+        <v>559122.682163629</v>
       </c>
       <c r="Q364" t="n">
-        <v>100250.511790454</v>
+        <v>100026.008965454</v>
       </c>
       <c r="R364" t="n">
-        <v>2630771.86843614</v>
+        <v>2634079.75468214</v>
       </c>
       <c r="S364" t="n">
-        <v>567428.050859</v>
+        <v>574416.354789</v>
       </c>
       <c r="T364" t="n">
-        <v>3198199.91929514</v>
+        <v>3208496.10947114</v>
       </c>
       <c r="U364" t="n">
-        <v>-0.23713642042239</v>
+        <v>-0.130449753050266</v>
       </c>
       <c r="V364" t="n">
-        <v>7.06495610712192</v>
+        <v>7.19957769859649</v>
       </c>
       <c r="W364" t="n">
-        <v>1.19286306655555</v>
+        <v>2.42373919473684</v>
       </c>
       <c r="X364" t="n">
-        <v>2.38525961667317</v>
+        <v>3.64621122290787</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.0136190024776273</v>
+        <v>0.31742237770378</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.20371420788959</v>
+        <v>6.54562330252897</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.822578930280238</v>
+        <v>0.820970219320702</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.177421069719762</v>
+        <v>0.179029780679298</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45558,85 +45558,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57356.5315252784</v>
+        <v>57207.6709402784</v>
       </c>
       <c r="C364" t="n">
-        <v>6593.926803</v>
+        <v>6628.614807</v>
       </c>
       <c r="D364" t="n">
-        <v>147993.097234673</v>
+        <v>147968.612522673</v>
       </c>
       <c r="E364" t="n">
-        <v>113799.736514</v>
+        <v>113610.247273</v>
       </c>
       <c r="F364" t="n">
-        <v>173644.145425</v>
+        <v>174498.178047</v>
       </c>
       <c r="G364" t="n">
-        <v>374575.430254897</v>
+        <v>373574.575507897</v>
       </c>
       <c r="H364" t="n">
-        <v>107631.57334</v>
+        <v>106372.032589</v>
       </c>
       <c r="I364" t="n">
-        <v>49516.3298275668</v>
+        <v>49715.9945255668</v>
       </c>
       <c r="J364" t="n">
-        <v>114443.954886</v>
+        <v>114177.272412</v>
       </c>
       <c r="K364" t="n">
-        <v>464956.203970015</v>
+        <v>465147.950030015</v>
       </c>
       <c r="L364" t="n">
-        <v>48766.22808</v>
+        <v>48967.433365</v>
       </c>
       <c r="M364" t="n">
-        <v>82608.814844</v>
+        <v>82880.346181</v>
       </c>
       <c r="N364" t="n">
-        <v>683292.063900629</v>
+        <v>682909.971030629</v>
       </c>
       <c r="O364" t="n">
-        <v>124169.381737</v>
+        <v>123264.717041</v>
       </c>
       <c r="P364" t="n">
-        <v>559122.682163629</v>
+        <v>559645.253989629</v>
       </c>
       <c r="Q364" t="n">
-        <v>100026.008965454</v>
+        <v>101012.149904454</v>
       </c>
       <c r="R364" t="n">
-        <v>2634079.75468214</v>
+        <v>2638040.39554414</v>
       </c>
       <c r="S364" t="n">
-        <v>574416.354789</v>
+        <v>569540.624622</v>
       </c>
       <c r="T364" t="n">
-        <v>3208496.10947114</v>
+        <v>3207581.02016614</v>
       </c>
       <c r="U364" t="n">
-        <v>-0.130449753050266</v>
+        <v>0.0197155640304203</v>
       </c>
       <c r="V364" t="n">
-        <v>7.19957769859649</v>
+        <v>7.36076455220922</v>
       </c>
       <c r="W364" t="n">
-        <v>2.42373919473684</v>
+        <v>1.55435149216672</v>
       </c>
       <c r="X364" t="n">
-        <v>3.64621122290787</v>
+        <v>2.76644699867994</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.31742237770378</v>
+        <v>0.288811029211877</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.54562330252897</v>
+        <v>6.51523562024665</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.820970219320702</v>
+        <v>0.822439208537124</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.179029780679298</v>
+        <v>0.177560791462876</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45472,85 +45472,85 @@
         <v>46054</v>
       </c>
       <c r="B363" t="n">
-        <v>57093.9089582784</v>
+        <v>57092.3142342784</v>
       </c>
       <c r="C363" t="n">
         <v>6560.018498</v>
       </c>
       <c r="D363" t="n">
-        <v>149382.155540673</v>
+        <v>149381.979606673</v>
       </c>
       <c r="E363" t="n">
-        <v>111405.4749</v>
+        <v>111405.474897</v>
       </c>
       <c r="F363" t="n">
-        <v>173028.328069</v>
+        <v>173028.328062</v>
       </c>
       <c r="G363" t="n">
-        <v>369932.697172897</v>
+        <v>369932.610847897</v>
       </c>
       <c r="H363" t="n">
-        <v>105040.624555</v>
+        <v>105040.624554</v>
       </c>
       <c r="I363" t="n">
-        <v>49292.8063305668</v>
+        <v>49292.8063295668</v>
       </c>
       <c r="J363" t="n">
-        <v>113289.576039</v>
+        <v>113289.576035</v>
       </c>
       <c r="K363" t="n">
-        <v>463779.994959015</v>
+        <v>463779.994928015</v>
       </c>
       <c r="L363" t="n">
-        <v>48623.885833</v>
+        <v>48623.639338</v>
       </c>
       <c r="M363" t="n">
-        <v>83069.229157</v>
+        <v>83068.91589</v>
       </c>
       <c r="N363" t="n">
-        <v>683300.316861629</v>
+        <v>683300.116653629</v>
       </c>
       <c r="O363" t="n">
         <v>123895.495526</v>
       </c>
       <c r="P363" t="n">
-        <v>559404.821335629</v>
+        <v>559404.621127629</v>
       </c>
       <c r="Q363" t="n">
-        <v>101244.516638454</v>
+        <v>101258.312157454</v>
       </c>
       <c r="R363" t="n">
-        <v>2637520.39352214</v>
+        <v>2637531.37185414</v>
       </c>
       <c r="S363" t="n">
-        <v>560823.456852</v>
+        <v>560823.456831</v>
       </c>
       <c r="T363" t="n">
-        <v>3198343.85037414</v>
+        <v>3198354.82868514</v>
       </c>
       <c r="U363" t="n">
-        <v>1.2245614974572</v>
+        <v>1.22498283139092</v>
       </c>
       <c r="V363" t="n">
-        <v>7.91764682415279</v>
+        <v>7.91809601717455</v>
       </c>
       <c r="W363" t="n">
-        <v>-4.97746037597777</v>
+        <v>-4.97746037953587</v>
       </c>
       <c r="X363" t="n">
-        <v>3.75530954475207</v>
+        <v>3.75530954086698</v>
       </c>
       <c r="Y363" t="n">
-        <v>0.0791767332596338</v>
+        <v>0.079520254900256</v>
       </c>
       <c r="Z363" t="n">
-        <v>7.16381214915713</v>
+        <v>7.16417998879939</v>
       </c>
       <c r="AA363" t="n">
-        <v>0.824651918902843</v>
+        <v>0.824652520789397</v>
       </c>
       <c r="AB363" t="n">
-        <v>0.175348081097157</v>
+        <v>0.175347479210603</v>
       </c>
     </row>
     <row r="364">
@@ -45558,85 +45558,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57207.6709402784</v>
+        <v>57083.4709402784</v>
       </c>
       <c r="C364" t="n">
-        <v>6628.614807</v>
+        <v>6568.266292</v>
       </c>
       <c r="D364" t="n">
-        <v>147968.612522673</v>
+        <v>147377.373674673</v>
       </c>
       <c r="E364" t="n">
-        <v>113610.247273</v>
+        <v>112502.993533</v>
       </c>
       <c r="F364" t="n">
-        <v>174498.178047</v>
+        <v>174158.951035</v>
       </c>
       <c r="G364" t="n">
-        <v>373574.575507897</v>
+        <v>371146.836060897</v>
       </c>
       <c r="H364" t="n">
-        <v>106372.032589</v>
+        <v>105081.75748</v>
       </c>
       <c r="I364" t="n">
-        <v>49715.9945255668</v>
+        <v>49396.0762755668</v>
       </c>
       <c r="J364" t="n">
-        <v>114177.272412</v>
+        <v>113510.765336</v>
       </c>
       <c r="K364" t="n">
-        <v>465147.950030015</v>
+        <v>464526.437098015</v>
       </c>
       <c r="L364" t="n">
-        <v>48967.433365</v>
+        <v>48921.279907</v>
       </c>
       <c r="M364" t="n">
-        <v>82880.346181</v>
+        <v>82750.499551</v>
       </c>
       <c r="N364" t="n">
-        <v>682909.971030629</v>
+        <v>682986.601427629</v>
       </c>
       <c r="O364" t="n">
-        <v>123264.717041</v>
+        <v>123566.289834</v>
       </c>
       <c r="P364" t="n">
-        <v>559645.253989629</v>
+        <v>559420.311593629</v>
       </c>
       <c r="Q364" t="n">
-        <v>101012.149904454</v>
+        <v>100514.975750454</v>
       </c>
       <c r="R364" t="n">
-        <v>2638040.39554414</v>
+        <v>2639104.68846814</v>
       </c>
       <c r="S364" t="n">
-        <v>569540.624622</v>
+        <v>560408.197321</v>
       </c>
       <c r="T364" t="n">
-        <v>3207581.02016614</v>
+        <v>3199512.88578914</v>
       </c>
       <c r="U364" t="n">
-        <v>0.0197155640304203</v>
+        <v>0.0596511052262327</v>
       </c>
       <c r="V364" t="n">
-        <v>7.36076455220922</v>
+        <v>7.40407825666238</v>
       </c>
       <c r="W364" t="n">
-        <v>1.55435149216672</v>
+        <v>-0.0740446044012688</v>
       </c>
       <c r="X364" t="n">
-        <v>2.76644699867994</v>
+        <v>1.11861528023072</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.288811029211877</v>
+        <v>0.036207899561802</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.51523562024665</v>
+        <v>6.24731433352652</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.822439208537124</v>
+        <v>0.824845775802282</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.177560791462876</v>
+        <v>0.175154224197718</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45558,85 +45558,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57083.4709402784</v>
+        <v>57060.1638212784</v>
       </c>
       <c r="C364" t="n">
-        <v>6568.266292</v>
+        <v>6488.60605</v>
       </c>
       <c r="D364" t="n">
-        <v>147377.373674673</v>
+        <v>146765.910577673</v>
       </c>
       <c r="E364" t="n">
-        <v>112502.993533</v>
+        <v>111803.947034</v>
       </c>
       <c r="F364" t="n">
-        <v>174158.951035</v>
+        <v>173652.010689</v>
       </c>
       <c r="G364" t="n">
-        <v>371146.836060897</v>
+        <v>367936.306787897</v>
       </c>
       <c r="H364" t="n">
-        <v>105081.75748</v>
+        <v>104236.37597</v>
       </c>
       <c r="I364" t="n">
-        <v>49396.0762755668</v>
+        <v>48903.4844575668</v>
       </c>
       <c r="J364" t="n">
-        <v>113510.765336</v>
+        <v>112823.49609</v>
       </c>
       <c r="K364" t="n">
-        <v>464526.437098015</v>
+        <v>464095.642087015</v>
       </c>
       <c r="L364" t="n">
-        <v>48921.279907</v>
+        <v>49085.157411</v>
       </c>
       <c r="M364" t="n">
-        <v>82750.499551</v>
+        <v>82634.746512</v>
       </c>
       <c r="N364" t="n">
-        <v>682986.601427629</v>
+        <v>682347.065503629</v>
       </c>
       <c r="O364" t="n">
-        <v>123566.289834</v>
+        <v>122833.416909</v>
       </c>
       <c r="P364" t="n">
-        <v>559420.311593629</v>
+        <v>559513.648594629</v>
       </c>
       <c r="Q364" t="n">
-        <v>100514.975750454</v>
+        <v>99895.9015164537</v>
       </c>
       <c r="R364" t="n">
-        <v>2639104.68846814</v>
+        <v>2641882.17070514</v>
       </c>
       <c r="S364" t="n">
-        <v>560408.197321</v>
+        <v>548193.709306</v>
       </c>
       <c r="T364" t="n">
-        <v>3199512.88578914</v>
+        <v>3190075.88001114</v>
       </c>
       <c r="U364" t="n">
-        <v>0.0596511052262327</v>
+        <v>0.164957236051411</v>
       </c>
       <c r="V364" t="n">
-        <v>7.40407825666238</v>
+        <v>7.51711390880712</v>
       </c>
       <c r="W364" t="n">
-        <v>-0.0740446044012688</v>
+        <v>-2.25200058434893</v>
       </c>
       <c r="X364" t="n">
-        <v>1.11861528023072</v>
+        <v>-1.08533555478233</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.036207899561802</v>
+        <v>-0.258850225114127</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.24731433352652</v>
+        <v>5.93393646787834</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.824845775802282</v>
+        <v>0.828156529836499</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.175154224197718</v>
+        <v>0.171843470163501</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14380,8 +14380,12 @@
       <c r="C315" t="n">
         <v>137.7744</v>
       </c>
-      <c r="D315"/>
-      <c r="E315"/>
+      <c r="D315" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="E315" t="n">
+        <v>154.33</v>
+      </c>
       <c r="F315"/>
       <c r="G315" t="n">
         <v>4.76226814126008</v>
@@ -14395,10 +14399,18 @@
       <c r="J315" t="n">
         <v>0.0254103038056064</v>
       </c>
-      <c r="K315"/>
-      <c r="L315"/>
-      <c r="M315"/>
-      <c r="N315"/>
+      <c r="K315" t="n">
+        <v>4.24502955400321</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0.195955586740815</v>
+      </c>
+      <c r="M315" t="n">
+        <v>4.87224789344931</v>
+      </c>
+      <c r="N315" t="n">
+        <v>1.52226004387532</v>
+      </c>
       <c r="O315"/>
       <c r="P315"/>
     </row>
@@ -45558,85 +45570,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57060.1638212784</v>
+        <v>57397.9602052784</v>
       </c>
       <c r="C364" t="n">
-        <v>6488.60605</v>
+        <v>6546.772418</v>
       </c>
       <c r="D364" t="n">
-        <v>146765.910577673</v>
+        <v>147484.563151673</v>
       </c>
       <c r="E364" t="n">
-        <v>111803.947034</v>
+        <v>112480.115355</v>
       </c>
       <c r="F364" t="n">
-        <v>173652.010689</v>
+        <v>175082.857652</v>
       </c>
       <c r="G364" t="n">
-        <v>367936.306787897</v>
+        <v>372226.686237897</v>
       </c>
       <c r="H364" t="n">
-        <v>104236.37597</v>
+        <v>105992.497218</v>
       </c>
       <c r="I364" t="n">
-        <v>48903.4844575668</v>
+        <v>49472.5557225668</v>
       </c>
       <c r="J364" t="n">
-        <v>112823.49609</v>
+        <v>113717.880921</v>
       </c>
       <c r="K364" t="n">
-        <v>464095.642087015</v>
+        <v>465609.484999015</v>
       </c>
       <c r="L364" t="n">
-        <v>49085.157411</v>
+        <v>49127.628256</v>
       </c>
       <c r="M364" t="n">
-        <v>82634.746512</v>
+        <v>82812.753079</v>
       </c>
       <c r="N364" t="n">
-        <v>682347.065503629</v>
+        <v>682541.864677629</v>
       </c>
       <c r="O364" t="n">
-        <v>122833.416909</v>
+        <v>122897.459289</v>
       </c>
       <c r="P364" t="n">
-        <v>559513.648594629</v>
+        <v>559644.405388629</v>
       </c>
       <c r="Q364" t="n">
-        <v>99895.9015164537</v>
+        <v>101196.712922454</v>
       </c>
       <c r="R364" t="n">
-        <v>2641882.17070514</v>
+        <v>2644730.66612114</v>
       </c>
       <c r="S364" t="n">
-        <v>548193.709306</v>
+        <v>559501.531372</v>
       </c>
       <c r="T364" t="n">
-        <v>3190075.88001114</v>
+        <v>3204232.19749314</v>
       </c>
       <c r="U364" t="n">
-        <v>0.164957236051411</v>
+        <v>0.272955777657291</v>
       </c>
       <c r="V364" t="n">
-        <v>7.51711390880712</v>
+        <v>7.63303959599591</v>
       </c>
       <c r="W364" t="n">
-        <v>-2.25200058434893</v>
+        <v>-0.235711513649906</v>
       </c>
       <c r="X364" t="n">
-        <v>-1.08533555478233</v>
+        <v>0.955018805869901</v>
       </c>
       <c r="Y364" t="n">
-        <v>-0.258850225114127</v>
+        <v>0.183762250369712</v>
       </c>
       <c r="Z364" t="n">
-        <v>5.93393646787834</v>
+        <v>6.40403012494586</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.828156529836499</v>
+        <v>0.825386708301062</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.171843470163501</v>
+        <v>0.174613291698938</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45570,85 +45570,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57397.9602052784</v>
+        <v>57418.4292092784</v>
       </c>
       <c r="C364" t="n">
-        <v>6546.772418</v>
+        <v>6545.190551</v>
       </c>
       <c r="D364" t="n">
-        <v>147484.563151673</v>
+        <v>147265.841938673</v>
       </c>
       <c r="E364" t="n">
-        <v>112480.115355</v>
+        <v>112958.158876</v>
       </c>
       <c r="F364" t="n">
-        <v>175082.857652</v>
+        <v>175357.252957</v>
       </c>
       <c r="G364" t="n">
-        <v>372226.686237897</v>
+        <v>373549.481226897</v>
       </c>
       <c r="H364" t="n">
-        <v>105992.497218</v>
+        <v>106417.12816</v>
       </c>
       <c r="I364" t="n">
-        <v>49472.5557225668</v>
+        <v>49587.6226065668</v>
       </c>
       <c r="J364" t="n">
-        <v>113717.880921</v>
+        <v>113963.839496</v>
       </c>
       <c r="K364" t="n">
-        <v>465609.484999015</v>
+        <v>465950.731749015</v>
       </c>
       <c r="L364" t="n">
-        <v>49127.628256</v>
+        <v>49187.675479</v>
       </c>
       <c r="M364" t="n">
-        <v>82812.753079</v>
+        <v>82831.770591</v>
       </c>
       <c r="N364" t="n">
-        <v>682541.864677629</v>
+        <v>682777.230361629</v>
       </c>
       <c r="O364" t="n">
-        <v>122897.459289</v>
+        <v>123804.4175</v>
       </c>
       <c r="P364" t="n">
-        <v>559644.405388629</v>
+        <v>558972.812861629</v>
       </c>
       <c r="Q364" t="n">
-        <v>101196.712922454</v>
+        <v>100664.737981454</v>
       </c>
       <c r="R364" t="n">
-        <v>2644730.66612114</v>
+        <v>2644257.92711114</v>
       </c>
       <c r="S364" t="n">
-        <v>559501.531372</v>
+        <v>562994.394434</v>
       </c>
       <c r="T364" t="n">
-        <v>3204232.19749314</v>
+        <v>3207252.32154514</v>
       </c>
       <c r="U364" t="n">
-        <v>0.272955777657291</v>
+        <v>0.255032236915964</v>
       </c>
       <c r="V364" t="n">
-        <v>7.63303959599591</v>
+        <v>7.6138004586298</v>
       </c>
       <c r="W364" t="n">
-        <v>-0.235711513649906</v>
+        <v>0.387098217194248</v>
       </c>
       <c r="X364" t="n">
-        <v>0.955018805869901</v>
+        <v>1.58526204264147</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.183762250369712</v>
+        <v>0.278189673647256</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.40403012494586</v>
+        <v>6.50432041316575</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.825386708301062</v>
+        <v>0.824462082184177</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.174613291698938</v>
+        <v>0.175537917815823</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45570,85 +45570,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>57418.4292092784</v>
+        <v>56629.0990432784</v>
       </c>
       <c r="C364" t="n">
-        <v>6545.190551</v>
+        <v>6497.329666</v>
       </c>
       <c r="D364" t="n">
-        <v>147265.841938673</v>
+        <v>147022.706206673</v>
       </c>
       <c r="E364" t="n">
-        <v>112958.158876</v>
+        <v>112312.728759</v>
       </c>
       <c r="F364" t="n">
-        <v>175357.252957</v>
+        <v>175683.209821</v>
       </c>
       <c r="G364" t="n">
-        <v>373549.481226897</v>
+        <v>372719.615172897</v>
       </c>
       <c r="H364" t="n">
-        <v>106417.12816</v>
+        <v>102681.70145</v>
       </c>
       <c r="I364" t="n">
-        <v>49587.6226065668</v>
+        <v>49361.5604215668</v>
       </c>
       <c r="J364" t="n">
-        <v>113963.839496</v>
+        <v>112849.673266</v>
       </c>
       <c r="K364" t="n">
-        <v>465950.731749015</v>
+        <v>465929.780021015</v>
       </c>
       <c r="L364" t="n">
-        <v>49187.675479</v>
+        <v>49528.604799</v>
       </c>
       <c r="M364" t="n">
-        <v>82831.770591</v>
+        <v>82886.877225</v>
       </c>
       <c r="N364" t="n">
-        <v>682777.230361629</v>
+        <v>681513.791919629</v>
       </c>
       <c r="O364" t="n">
-        <v>123804.4175</v>
+        <v>122299.552872</v>
       </c>
       <c r="P364" t="n">
-        <v>558972.812861629</v>
+        <v>559214.239047629</v>
       </c>
       <c r="Q364" t="n">
-        <v>100664.737981454</v>
+        <v>99878.7169464537</v>
       </c>
       <c r="R364" t="n">
-        <v>2644257.92711114</v>
+        <v>2642844.27827414</v>
       </c>
       <c r="S364" t="n">
-        <v>562994.394434</v>
+        <v>554164.908363</v>
       </c>
       <c r="T364" t="n">
-        <v>3207252.32154514</v>
+        <v>3197009.18663714</v>
       </c>
       <c r="U364" t="n">
-        <v>0.255032236915964</v>
+        <v>0.201434814262136</v>
       </c>
       <c r="V364" t="n">
-        <v>7.6138004586298</v>
+        <v>7.5562689590345</v>
       </c>
       <c r="W364" t="n">
-        <v>0.387098217194248</v>
+        <v>-1.18728066504653</v>
       </c>
       <c r="X364" t="n">
-        <v>1.58526204264147</v>
+        <v>-0.00790773860674943</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.278189673647256</v>
+        <v>-0.042072944375382</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.50432041316575</v>
+        <v>6.16417314288447</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.824462082184177</v>
+        <v>0.826661458878724</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.175537917815823</v>
+        <v>0.173338541121276</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14337,7 +14337,7 @@
         <v>152.015922353681</v>
       </c>
       <c r="F314" t="n">
-        <v>129.96287646414</v>
+        <v>130.019707825944</v>
       </c>
       <c r="G314" t="n">
         <v>4.89226213151006</v>
@@ -14364,10 +14364,10 @@
         <v>0.99462644080861</v>
       </c>
       <c r="O314" t="n">
-        <v>3.48006152430886</v>
+        <v>3.52531223725103</v>
       </c>
       <c r="P314" t="n">
-        <v>-2.09683553036542</v>
+        <v>-2.05402353425441</v>
       </c>
     </row>
     <row r="315">
@@ -14386,7 +14386,9 @@
       <c r="E315" t="n">
         <v>154.33</v>
       </c>
-      <c r="F315"/>
+      <c r="F315" t="n">
+        <v>135.378889197075</v>
+      </c>
       <c r="G315" t="n">
         <v>4.76226814126008</v>
       </c>
@@ -14411,8 +14413,12 @@
       <c r="N315" t="n">
         <v>1.52226004387532</v>
       </c>
-      <c r="O315"/>
-      <c r="P315"/>
+      <c r="O315" t="n">
+        <v>3.86343838477858</v>
+      </c>
+      <c r="P315" t="n">
+        <v>4.12182234581271</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45576,85 +45576,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>56629.0990432784</v>
+        <v>56291.4831792784</v>
       </c>
       <c r="C364" t="n">
-        <v>6497.329666</v>
+        <v>6513.358471</v>
       </c>
       <c r="D364" t="n">
-        <v>147022.706206673</v>
+        <v>147787.426040673</v>
       </c>
       <c r="E364" t="n">
-        <v>112312.728759</v>
+        <v>112851.745302</v>
       </c>
       <c r="F364" t="n">
-        <v>175683.209821</v>
+        <v>176511.427933</v>
       </c>
       <c r="G364" t="n">
-        <v>372719.615172897</v>
+        <v>377600.214755897</v>
       </c>
       <c r="H364" t="n">
-        <v>102681.70145</v>
+        <v>103536.612753</v>
       </c>
       <c r="I364" t="n">
-        <v>49361.5604215668</v>
+        <v>49561.6308985668</v>
       </c>
       <c r="J364" t="n">
-        <v>112849.673266</v>
+        <v>113163.490463</v>
       </c>
       <c r="K364" t="n">
-        <v>465929.780021015</v>
+        <v>467131.455946015</v>
       </c>
       <c r="L364" t="n">
-        <v>49528.604799</v>
+        <v>49585.025528</v>
       </c>
       <c r="M364" t="n">
-        <v>82886.877225</v>
+        <v>82947.512599</v>
       </c>
       <c r="N364" t="n">
-        <v>681513.791919629</v>
+        <v>681176.596411629</v>
       </c>
       <c r="O364" t="n">
-        <v>122299.552872</v>
+        <v>121453.08981</v>
       </c>
       <c r="P364" t="n">
-        <v>559214.239047629</v>
+        <v>559723.506601629</v>
       </c>
       <c r="Q364" t="n">
-        <v>99878.7169464537</v>
+        <v>100629.763072454</v>
       </c>
       <c r="R364" t="n">
-        <v>2642844.27827414</v>
+        <v>2646862.15519014</v>
       </c>
       <c r="S364" t="n">
-        <v>554164.908363</v>
+        <v>559602.184575</v>
       </c>
       <c r="T364" t="n">
-        <v>3197009.18663714</v>
+        <v>3206464.33976514</v>
       </c>
       <c r="U364" t="n">
-        <v>0.201434814262136</v>
+        <v>0.353769567845585</v>
       </c>
       <c r="V364" t="n">
-        <v>7.5562689590345</v>
+        <v>7.71978515776557</v>
       </c>
       <c r="W364" t="n">
-        <v>-1.18728066504653</v>
+        <v>-0.217764118302222</v>
       </c>
       <c r="X364" t="n">
-        <v>-0.00790773860674943</v>
+        <v>0.973180411213148</v>
       </c>
       <c r="Y364" t="n">
-        <v>-0.042072944375382</v>
+        <v>0.253552576695615</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.16417314288447</v>
+        <v>6.47815363376611</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.826661458878724</v>
+        <v>0.825476872567999</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.173338541121276</v>
+        <v>0.174523127432001</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45576,85 +45576,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>56291.4831792784</v>
+        <v>55627.6870022784</v>
       </c>
       <c r="C364" t="n">
-        <v>6513.358471</v>
+        <v>6539.538373</v>
       </c>
       <c r="D364" t="n">
-        <v>147787.426040673</v>
+        <v>147879.177258673</v>
       </c>
       <c r="E364" t="n">
-        <v>112851.745302</v>
+        <v>112921.20762</v>
       </c>
       <c r="F364" t="n">
-        <v>176511.427933</v>
+        <v>177346.370633</v>
       </c>
       <c r="G364" t="n">
-        <v>377600.214755897</v>
+        <v>376541.437092897</v>
       </c>
       <c r="H364" t="n">
-        <v>103536.612753</v>
+        <v>109212.878902</v>
       </c>
       <c r="I364" t="n">
-        <v>49561.6308985668</v>
+        <v>49636.7757985668</v>
       </c>
       <c r="J364" t="n">
-        <v>113163.490463</v>
+        <v>113718.174861</v>
       </c>
       <c r="K364" t="n">
-        <v>467131.455946015</v>
+        <v>467772.455228015</v>
       </c>
       <c r="L364" t="n">
-        <v>49585.025528</v>
+        <v>49640.327099</v>
       </c>
       <c r="M364" t="n">
-        <v>82947.512599</v>
+        <v>83183.079586</v>
       </c>
       <c r="N364" t="n">
-        <v>681176.596411629</v>
+        <v>681862.736578629</v>
       </c>
       <c r="O364" t="n">
-        <v>121453.08981</v>
+        <v>122329.711596</v>
       </c>
       <c r="P364" t="n">
-        <v>559723.506601629</v>
+        <v>559533.024982629</v>
       </c>
       <c r="Q364" t="n">
-        <v>100629.763072454</v>
+        <v>99082.0937634537</v>
       </c>
       <c r="R364" t="n">
-        <v>2646862.15519014</v>
+        <v>2645562.05911014</v>
       </c>
       <c r="S364" t="n">
-        <v>559602.184575</v>
+        <v>567264.617265</v>
       </c>
       <c r="T364" t="n">
-        <v>3206464.33976514</v>
+        <v>3212826.67637514</v>
       </c>
       <c r="U364" t="n">
-        <v>0.353769567845585</v>
+        <v>0.304477411783521</v>
       </c>
       <c r="V364" t="n">
-        <v>7.71978515776557</v>
+        <v>7.66687493342788</v>
       </c>
       <c r="W364" t="n">
-        <v>-0.217764118302222</v>
+        <v>1.14851837160959</v>
       </c>
       <c r="X364" t="n">
-        <v>0.973180411213148</v>
+        <v>2.35577007887815</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.253552576695615</v>
+        <v>0.452477866439516</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.47815363376611</v>
+        <v>6.68942991294621</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.825476872567999</v>
+        <v>0.823437528878771</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.174523127432001</v>
+        <v>0.176562471121229</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -1119,6 +1119,9 @@
   <si>
     <t xml:space="preserve">126.974</t>
   </si>
+  <si>
+    <t xml:space="preserve">127.2749</t>
+  </si>
 </sst>
 </file>
 
@@ -14420,6 +14423,38 @@
         <v>4.12182234581271</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B316" t="n">
+        <v>134.8474</v>
+      </c>
+      <c r="C316" t="n">
+        <v>138.1495</v>
+      </c>
+      <c r="D316"/>
+      <c r="E316"/>
+      <c r="F316"/>
+      <c r="G316" t="n">
+        <v>4.58475522739963</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0.228482235766325</v>
+      </c>
+      <c r="I316" t="n">
+        <v>4.62914646088644</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0.272256674679738</v>
+      </c>
+      <c r="K316"/>
+      <c r="L316"/>
+      <c r="M316"/>
+      <c r="N316"/>
+      <c r="O316"/>
+      <c r="P316"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -45576,85 +45611,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>55627.6870022784</v>
+        <v>55678.5451902784</v>
       </c>
       <c r="C364" t="n">
-        <v>6539.538373</v>
+        <v>6700.586048</v>
       </c>
       <c r="D364" t="n">
-        <v>147879.177258673</v>
+        <v>148369.042126673</v>
       </c>
       <c r="E364" t="n">
-        <v>112921.20762</v>
+        <v>114406.621295</v>
       </c>
       <c r="F364" t="n">
-        <v>177346.370633</v>
+        <v>176894.977407</v>
       </c>
       <c r="G364" t="n">
-        <v>376541.437092897</v>
+        <v>378072.915948897</v>
       </c>
       <c r="H364" t="n">
-        <v>109212.878902</v>
+        <v>109356.688891</v>
       </c>
       <c r="I364" t="n">
-        <v>49636.7757985668</v>
+        <v>49948.1319535668</v>
       </c>
       <c r="J364" t="n">
-        <v>113718.174861</v>
+        <v>114202.094398</v>
       </c>
       <c r="K364" t="n">
-        <v>467772.455228015</v>
+        <v>469190.820205015</v>
       </c>
       <c r="L364" t="n">
-        <v>49640.327099</v>
+        <v>49857.525169</v>
       </c>
       <c r="M364" t="n">
-        <v>83183.079586</v>
+        <v>83412.737847</v>
       </c>
       <c r="N364" t="n">
-        <v>681862.736578629</v>
+        <v>682234.560821629</v>
       </c>
       <c r="O364" t="n">
-        <v>122329.711596</v>
+        <v>121528.87429</v>
       </c>
       <c r="P364" t="n">
-        <v>559533.024982629</v>
+        <v>560705.686531629</v>
       </c>
       <c r="Q364" t="n">
-        <v>99082.0937634537</v>
+        <v>98322.1283134537</v>
       </c>
       <c r="R364" t="n">
-        <v>2645562.05911014</v>
+        <v>2649016.79134314</v>
       </c>
       <c r="S364" t="n">
-        <v>567264.617265</v>
+        <v>569865.145093</v>
       </c>
       <c r="T364" t="n">
-        <v>3212826.67637514</v>
+        <v>3218881.93643614</v>
       </c>
       <c r="U364" t="n">
-        <v>0.304477411783521</v>
+        <v>0.435460962154366</v>
       </c>
       <c r="V364" t="n">
-        <v>7.66687493342788</v>
+        <v>7.80747274022586</v>
       </c>
       <c r="W364" t="n">
-        <v>1.14851837160959</v>
+        <v>1.61221649199395</v>
       </c>
       <c r="X364" t="n">
-        <v>2.35577007887815</v>
+        <v>2.8250026386839</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.452477866439516</v>
+        <v>0.641802077958897</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.68942991294621</v>
+        <v>6.89050899655606</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.823437528878771</v>
+        <v>0.822961774819259</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.176562471121229</v>
+        <v>0.177038225180741</v>
       </c>
     </row>
   </sheetData>
@@ -60473,6 +60508,53 @@
         <v>147.3267</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B316" t="n">
+        <v>138.1495</v>
+      </c>
+      <c r="C316" t="n">
+        <v>134.8474</v>
+      </c>
+      <c r="D316" t="n">
+        <v>153.4116</v>
+      </c>
+      <c r="E316" t="n">
+        <v>140.9768</v>
+      </c>
+      <c r="F316" t="n">
+        <v>96.5504</v>
+      </c>
+      <c r="G316" t="s">
+        <v>368</v>
+      </c>
+      <c r="H316" t="n">
+        <v>125.708</v>
+      </c>
+      <c r="I316" t="n">
+        <v>136.5448</v>
+      </c>
+      <c r="J316" t="n">
+        <v>141.3657</v>
+      </c>
+      <c r="K316" t="n">
+        <v>98.0346</v>
+      </c>
+      <c r="L316" t="n">
+        <v>121.7096</v>
+      </c>
+      <c r="M316" t="n">
+        <v>132.7154</v>
+      </c>
+      <c r="N316" t="n">
+        <v>153.51</v>
+      </c>
+      <c r="O316" t="n">
+        <v>147.8913</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45692,6 +45692,92 @@
         <v>0.177038225180741</v>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B365" t="n">
+        <v>55649.0148832784</v>
+      </c>
+      <c r="C365" t="n">
+        <v>6746.026238</v>
+      </c>
+      <c r="D365" t="n">
+        <v>148082.030254673</v>
+      </c>
+      <c r="E365" t="n">
+        <v>114608.306591</v>
+      </c>
+      <c r="F365" t="n">
+        <v>176742.232603</v>
+      </c>
+      <c r="G365" t="n">
+        <v>377723.930049897</v>
+      </c>
+      <c r="H365" t="n">
+        <v>109585.379043</v>
+      </c>
+      <c r="I365" t="n">
+        <v>50509.8333045668</v>
+      </c>
+      <c r="J365" t="n">
+        <v>113878.425114</v>
+      </c>
+      <c r="K365" t="n">
+        <v>469149.719283015</v>
+      </c>
+      <c r="L365" t="n">
+        <v>49740.958484</v>
+      </c>
+      <c r="M365" t="n">
+        <v>83087.50347</v>
+      </c>
+      <c r="N365" t="n">
+        <v>681373.089079629</v>
+      </c>
+      <c r="O365" t="n">
+        <v>121051.887669</v>
+      </c>
+      <c r="P365" t="n">
+        <v>560321.201410629</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>98082.5999084537</v>
+      </c>
+      <c r="R365" t="n">
+        <v>2643958.50217514</v>
+      </c>
+      <c r="S365" t="n">
+        <v>572373.635211</v>
+      </c>
+      <c r="T365" t="n">
+        <v>3216332.13738614</v>
+      </c>
+      <c r="U365" t="n">
+        <v>-0.190949683087327</v>
+      </c>
+      <c r="V365" t="n">
+        <v>6.83355994303116</v>
+      </c>
+      <c r="W365" t="n">
+        <v>0.44019012912091</v>
+      </c>
+      <c r="X365" t="n">
+        <v>9.69571601019605</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>-0.0792138108930751</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>7.33192927635153</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>0.822041502319422</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>0.177958497680578</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45697,85 +45697,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55649.0148832784</v>
+        <v>55649.4353932784</v>
       </c>
       <c r="C365" t="n">
-        <v>6746.026238</v>
+        <v>6714.889704</v>
       </c>
       <c r="D365" t="n">
-        <v>148082.030254673</v>
+        <v>148185.424027673</v>
       </c>
       <c r="E365" t="n">
-        <v>114608.306591</v>
+        <v>114345.500815</v>
       </c>
       <c r="F365" t="n">
-        <v>176742.232603</v>
+        <v>176185.18848</v>
       </c>
       <c r="G365" t="n">
-        <v>377723.930049897</v>
+        <v>377601.388853897</v>
       </c>
       <c r="H365" t="n">
-        <v>109585.379043</v>
+        <v>109368.057938</v>
       </c>
       <c r="I365" t="n">
-        <v>50509.8333045668</v>
+        <v>50387.5999205668</v>
       </c>
       <c r="J365" t="n">
-        <v>113878.425114</v>
+        <v>113315.922909</v>
       </c>
       <c r="K365" t="n">
-        <v>469149.719283015</v>
+        <v>468544.465867015</v>
       </c>
       <c r="L365" t="n">
-        <v>49740.958484</v>
+        <v>49573.5502</v>
       </c>
       <c r="M365" t="n">
-        <v>83087.50347</v>
+        <v>82641.034124</v>
       </c>
       <c r="N365" t="n">
-        <v>681373.089079629</v>
+        <v>682428.783601629</v>
       </c>
       <c r="O365" t="n">
-        <v>121051.887669</v>
+        <v>123174.992992</v>
       </c>
       <c r="P365" t="n">
-        <v>560321.201410629</v>
+        <v>559253.790609629</v>
       </c>
       <c r="Q365" t="n">
-        <v>98082.5999084537</v>
+        <v>99305.8497794537</v>
       </c>
       <c r="R365" t="n">
-        <v>2643958.50217514</v>
+        <v>2646565.36905714</v>
       </c>
       <c r="S365" t="n">
-        <v>572373.635211</v>
+        <v>570110.506158</v>
       </c>
       <c r="T365" t="n">
-        <v>3216332.13738614</v>
+        <v>3216675.87521514</v>
       </c>
       <c r="U365" t="n">
-        <v>-0.190949683087327</v>
+        <v>-0.092540836057009</v>
       </c>
       <c r="V365" t="n">
-        <v>6.83355994303116</v>
+        <v>6.93889475410046</v>
       </c>
       <c r="W365" t="n">
-        <v>0.44019012912091</v>
+        <v>0.0430559873880076</v>
       </c>
       <c r="X365" t="n">
-        <v>9.69571601019605</v>
+        <v>9.26198610612596</v>
       </c>
       <c r="Y365" t="n">
-        <v>-0.0792138108930751</v>
+        <v>-0.0685350150941733</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.33192927635153</v>
+        <v>7.34340012039869</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.822041502319422</v>
+        <v>0.82276408059924</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.177958497680578</v>
+        <v>0.17723591940076</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45697,85 +45697,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55649.4353932784</v>
+        <v>55506.3121512784</v>
       </c>
       <c r="C365" t="n">
-        <v>6714.889704</v>
+        <v>6688.718069</v>
       </c>
       <c r="D365" t="n">
-        <v>148185.424027673</v>
+        <v>148329.083860673</v>
       </c>
       <c r="E365" t="n">
-        <v>114345.500815</v>
+        <v>113697.543634</v>
       </c>
       <c r="F365" t="n">
-        <v>176185.18848</v>
+        <v>175997.263951</v>
       </c>
       <c r="G365" t="n">
-        <v>377601.388853897</v>
+        <v>376413.654662897</v>
       </c>
       <c r="H365" t="n">
-        <v>109368.057938</v>
+        <v>108440.988535</v>
       </c>
       <c r="I365" t="n">
-        <v>50387.5999205668</v>
+        <v>50870.9370685668</v>
       </c>
       <c r="J365" t="n">
-        <v>113315.922909</v>
+        <v>112295.145288</v>
       </c>
       <c r="K365" t="n">
-        <v>468544.465867015</v>
+        <v>468374.457945015</v>
       </c>
       <c r="L365" t="n">
-        <v>49573.5502</v>
+        <v>49532.384394</v>
       </c>
       <c r="M365" t="n">
-        <v>82641.034124</v>
+        <v>82528.580665</v>
       </c>
       <c r="N365" t="n">
-        <v>682428.783601629</v>
+        <v>681643.731988629</v>
       </c>
       <c r="O365" t="n">
-        <v>123174.992992</v>
+        <v>122052.495825</v>
       </c>
       <c r="P365" t="n">
-        <v>559253.790609629</v>
+        <v>559591.236163629</v>
       </c>
       <c r="Q365" t="n">
-        <v>99305.8497794537</v>
+        <v>100611.270008454</v>
       </c>
       <c r="R365" t="n">
-        <v>2646565.36905714</v>
+        <v>2647461.15914114</v>
       </c>
       <c r="S365" t="n">
-        <v>570110.506158</v>
+        <v>565112.645069</v>
       </c>
       <c r="T365" t="n">
-        <v>3216675.87521514</v>
+        <v>3212573.80421014</v>
       </c>
       <c r="U365" t="n">
-        <v>-0.092540836057009</v>
+        <v>-0.05872489019636</v>
       </c>
       <c r="V365" t="n">
-        <v>6.93889475410046</v>
+        <v>6.9750906488381</v>
       </c>
       <c r="W365" t="n">
-        <v>0.0430559873880076</v>
+        <v>-0.833969240779675</v>
       </c>
       <c r="X365" t="n">
-        <v>9.26198610612596</v>
+        <v>8.30414333184226</v>
       </c>
       <c r="Y365" t="n">
-        <v>-0.0685350150941733</v>
+        <v>-0.195972774105047</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.34340012039869</v>
+        <v>7.20651027936596</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.82276408059924</v>
+        <v>0.824093490294788</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.17723591940076</v>
+        <v>0.175906509705212</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45611,85 +45611,85 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>55678.5451902784</v>
+        <v>55673.7888672784</v>
       </c>
       <c r="C364" t="n">
-        <v>6700.586048</v>
+        <v>6700.952601</v>
       </c>
       <c r="D364" t="n">
-        <v>148369.042126673</v>
+        <v>148346.734202673</v>
       </c>
       <c r="E364" t="n">
-        <v>114406.621295</v>
+        <v>114183.676736</v>
       </c>
       <c r="F364" t="n">
-        <v>176894.977407</v>
+        <v>178366.216207</v>
       </c>
       <c r="G364" t="n">
-        <v>378072.915948897</v>
+        <v>378984.875609897</v>
       </c>
       <c r="H364" t="n">
-        <v>109356.688891</v>
+        <v>108166.213468</v>
       </c>
       <c r="I364" t="n">
-        <v>49948.1319535668</v>
+        <v>49691.7051315668</v>
       </c>
       <c r="J364" t="n">
-        <v>114202.094398</v>
+        <v>113565.918651</v>
       </c>
       <c r="K364" t="n">
-        <v>469190.820205015</v>
+        <v>469350.603929015</v>
       </c>
       <c r="L364" t="n">
-        <v>49857.525169</v>
+        <v>49903.790045</v>
       </c>
       <c r="M364" t="n">
-        <v>83412.737847</v>
+        <v>83182.145248</v>
       </c>
       <c r="N364" t="n">
-        <v>682234.560821629</v>
+        <v>682352.881240629</v>
       </c>
       <c r="O364" t="n">
-        <v>121528.87429</v>
+        <v>121617.585296</v>
       </c>
       <c r="P364" t="n">
-        <v>560705.686531629</v>
+        <v>560735.295944629</v>
       </c>
       <c r="Q364" t="n">
-        <v>98322.1283134537</v>
+        <v>98202.6832364537</v>
       </c>
       <c r="R364" t="n">
-        <v>2649016.79134314</v>
+        <v>2649137.49192114</v>
       </c>
       <c r="S364" t="n">
-        <v>569865.145093</v>
+        <v>569887.574493</v>
       </c>
       <c r="T364" t="n">
-        <v>3218881.93643614</v>
+        <v>3219025.06641414</v>
       </c>
       <c r="U364" t="n">
-        <v>0.435460962154366</v>
+        <v>0.440037232953983</v>
       </c>
       <c r="V364" t="n">
-        <v>7.80747274022586</v>
+        <v>7.81238491153222</v>
       </c>
       <c r="W364" t="n">
-        <v>1.61221649199395</v>
+        <v>1.61621586108718</v>
       </c>
       <c r="X364" t="n">
-        <v>2.8250026386839</v>
+        <v>2.82904974199256</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.641802077958897</v>
+        <v>0.646277190498523</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.89050899655606</v>
+        <v>6.89526196249368</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.822961774819259</v>
+        <v>0.822962678843681</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.177038225180741</v>
+        <v>0.177037321156319</v>
       </c>
     </row>
     <row r="365">
@@ -45697,85 +45697,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55506.3121512784</v>
+        <v>55692.8</v>
       </c>
       <c r="C365" t="n">
-        <v>6688.718069</v>
+        <v>6709.2</v>
       </c>
       <c r="D365" t="n">
-        <v>148329.083860673</v>
+        <v>148119.2</v>
       </c>
       <c r="E365" t="n">
-        <v>113697.543634</v>
+        <v>113689.7</v>
       </c>
       <c r="F365" t="n">
-        <v>175997.263951</v>
+        <v>175932</v>
       </c>
       <c r="G365" t="n">
-        <v>376413.654662897</v>
+        <v>378478.2</v>
       </c>
       <c r="H365" t="n">
-        <v>108440.988535</v>
+        <v>108383.1</v>
       </c>
       <c r="I365" t="n">
-        <v>50870.9370685668</v>
+        <v>50793.8</v>
       </c>
       <c r="J365" t="n">
-        <v>112295.145288</v>
+        <v>112245.5</v>
       </c>
       <c r="K365" t="n">
-        <v>468374.457945015</v>
+        <v>468456</v>
       </c>
       <c r="L365" t="n">
-        <v>49532.384394</v>
+        <v>49529.6</v>
       </c>
       <c r="M365" t="n">
-        <v>82528.580665</v>
+        <v>82439.5</v>
       </c>
       <c r="N365" t="n">
-        <v>681643.731988629</v>
+        <v>683814.3</v>
       </c>
       <c r="O365" t="n">
-        <v>122052.495825</v>
+        <v>124124.5</v>
       </c>
       <c r="P365" t="n">
-        <v>559591.236163629</v>
+        <v>559689.8</v>
       </c>
       <c r="Q365" t="n">
-        <v>100611.270008454</v>
+        <v>100223</v>
       </c>
       <c r="R365" t="n">
-        <v>2647461.15914114</v>
+        <v>2653783</v>
       </c>
       <c r="S365" t="n">
-        <v>565112.645069</v>
+        <v>564537.1</v>
       </c>
       <c r="T365" t="n">
-        <v>3212573.80421014</v>
+        <v>3218320.2</v>
       </c>
       <c r="U365" t="n">
-        <v>-0.05872489019636</v>
+        <v>0.17535926666794</v>
       </c>
       <c r="V365" t="n">
-        <v>6.9750906488381</v>
+        <v>7.23053518920795</v>
       </c>
       <c r="W365" t="n">
-        <v>-0.833969240779675</v>
+        <v>-0.938864915200177</v>
       </c>
       <c r="X365" t="n">
-        <v>8.30414333184226</v>
+        <v>8.19383980883528</v>
       </c>
       <c r="Y365" t="n">
-        <v>-0.195972774105047</v>
+        <v>-0.021896891126949</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.20651027936596</v>
+        <v>7.39827273428837</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.824093490294788</v>
+        <v>0.824586378943897</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.175906509705212</v>
+        <v>0.175413589983992</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45697,85 +45697,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55692.8</v>
+        <v>55756.9216852784</v>
       </c>
       <c r="C365" t="n">
-        <v>6709.2</v>
+        <v>6727.304734</v>
       </c>
       <c r="D365" t="n">
-        <v>148119.2</v>
+        <v>149297.908965673</v>
       </c>
       <c r="E365" t="n">
-        <v>113689.7</v>
+        <v>113797.75369</v>
       </c>
       <c r="F365" t="n">
-        <v>175932</v>
+        <v>176228.406805</v>
       </c>
       <c r="G365" t="n">
-        <v>378478.2</v>
+        <v>381650.643154897</v>
       </c>
       <c r="H365" t="n">
-        <v>108383.1</v>
+        <v>108629.378577</v>
       </c>
       <c r="I365" t="n">
-        <v>50793.8</v>
+        <v>51152.2838335668</v>
       </c>
       <c r="J365" t="n">
-        <v>112245.5</v>
+        <v>113333.229648</v>
       </c>
       <c r="K365" t="n">
-        <v>468456</v>
+        <v>469119.372524015</v>
       </c>
       <c r="L365" t="n">
-        <v>49529.6</v>
+        <v>49696.652859</v>
       </c>
       <c r="M365" t="n">
-        <v>82439.5</v>
+        <v>82484.254871</v>
       </c>
       <c r="N365" t="n">
-        <v>683814.3</v>
+        <v>683184.844943629</v>
       </c>
       <c r="O365" t="n">
-        <v>124124.5</v>
+        <v>123086.362459</v>
       </c>
       <c r="P365" t="n">
-        <v>559689.8</v>
+        <v>560098.482484629</v>
       </c>
       <c r="Q365" t="n">
-        <v>100223</v>
+        <v>100173.112770454</v>
       </c>
       <c r="R365" t="n">
-        <v>2653783</v>
+        <v>2656229.84276214</v>
       </c>
       <c r="S365" t="n">
-        <v>564537.1</v>
+        <v>568187.071243</v>
       </c>
       <c r="T365" t="n">
-        <v>3218320.2</v>
+        <v>3224416.91400514</v>
       </c>
       <c r="U365" t="n">
-        <v>0.17535926666794</v>
+        <v>0.2677230178739</v>
       </c>
       <c r="V365" t="n">
-        <v>7.23053518920795</v>
+        <v>7.32940395839832</v>
       </c>
       <c r="W365" t="n">
-        <v>-0.938864915200177</v>
+        <v>-0.298392757819455</v>
       </c>
       <c r="X365" t="n">
-        <v>8.19383980883528</v>
+        <v>8.89335876688426</v>
       </c>
       <c r="Y365" t="n">
-        <v>-0.021896891126949</v>
+        <v>0.167499397480797</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.39827273428837</v>
+        <v>7.60172562673429</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.824586378943897</v>
+        <v>0.823786102605064</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.175413589983992</v>
+        <v>0.176213897394937</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45697,85 +45697,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55756.9216852784</v>
+        <v>55617.5504092784</v>
       </c>
       <c r="C365" t="n">
-        <v>6727.304734</v>
+        <v>6737.999887</v>
       </c>
       <c r="D365" t="n">
-        <v>149297.908965673</v>
+        <v>149411.349253673</v>
       </c>
       <c r="E365" t="n">
-        <v>113797.75369</v>
+        <v>114620.293642</v>
       </c>
       <c r="F365" t="n">
-        <v>176228.406805</v>
+        <v>176835.04022</v>
       </c>
       <c r="G365" t="n">
-        <v>381650.643154897</v>
+        <v>382709.558829897</v>
       </c>
       <c r="H365" t="n">
-        <v>108629.378577</v>
+        <v>111064.158989</v>
       </c>
       <c r="I365" t="n">
-        <v>51152.2838335668</v>
+        <v>51233.1316155668</v>
       </c>
       <c r="J365" t="n">
-        <v>113333.229648</v>
+        <v>113553.634112</v>
       </c>
       <c r="K365" t="n">
-        <v>469119.372524015</v>
+        <v>469593.954059015</v>
       </c>
       <c r="L365" t="n">
-        <v>49696.652859</v>
+        <v>49809.608948</v>
       </c>
       <c r="M365" t="n">
-        <v>82484.254871</v>
+        <v>82456.632109</v>
       </c>
       <c r="N365" t="n">
-        <v>683184.844943629</v>
+        <v>683143.236801629</v>
       </c>
       <c r="O365" t="n">
-        <v>123086.362459</v>
+        <v>122683.623524</v>
       </c>
       <c r="P365" t="n">
-        <v>560098.482484629</v>
+        <v>560459.613277629</v>
       </c>
       <c r="Q365" t="n">
-        <v>100173.112770454</v>
+        <v>100978.677411454</v>
       </c>
       <c r="R365" t="n">
-        <v>2656229.84276214</v>
+        <v>2657608.66885914</v>
       </c>
       <c r="S365" t="n">
-        <v>568187.071243</v>
+        <v>573299.39423</v>
       </c>
       <c r="T365" t="n">
-        <v>3224416.91400514</v>
+        <v>3230908.06308914</v>
       </c>
       <c r="U365" t="n">
-        <v>0.2677230178739</v>
+        <v>0.319771131692259</v>
       </c>
       <c r="V365" t="n">
-        <v>7.32940395839832</v>
+        <v>7.38511773014008</v>
       </c>
       <c r="W365" t="n">
-        <v>-0.298392757819455</v>
+        <v>0.598682949007134</v>
       </c>
       <c r="X365" t="n">
-        <v>8.89335876688426</v>
+        <v>9.87313822567715</v>
       </c>
       <c r="Y365" t="n">
-        <v>0.167499397480797</v>
+        <v>0.369148932668506</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.60172562673429</v>
+        <v>7.81834117657372</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.823786102605064</v>
+        <v>0.82255781252969</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.176213897394937</v>
+        <v>0.17744218747031</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14340,7 +14340,7 @@
         <v>152.015922353681</v>
       </c>
       <c r="F314" t="n">
-        <v>130.019707825944</v>
+        <v>130.003551134733</v>
       </c>
       <c r="G314" t="n">
         <v>4.89226213151006</v>
@@ -14367,10 +14367,10 @@
         <v>0.99462644080861</v>
       </c>
       <c r="O314" t="n">
-        <v>3.52531223725103</v>
+        <v>3.51244782976698</v>
       </c>
       <c r="P314" t="n">
-        <v>-2.05402353425441</v>
+        <v>-2.066194634495</v>
       </c>
     </row>
     <row r="315">
@@ -14390,7 +14390,7 @@
         <v>154.33</v>
       </c>
       <c r="F315" t="n">
-        <v>135.378889197075</v>
+        <v>135.371359317312</v>
       </c>
       <c r="G315" t="n">
         <v>4.76226814126008</v>
@@ -14417,10 +14417,10 @@
         <v>1.52226004387532</v>
       </c>
       <c r="O315" t="n">
-        <v>3.86343838477858</v>
+        <v>3.85766141905393</v>
       </c>
       <c r="P315" t="n">
-        <v>4.12182234581271</v>
+        <v>4.12897042867446</v>
       </c>
     </row>
     <row r="316">
@@ -14435,7 +14435,9 @@
       </c>
       <c r="D316"/>
       <c r="E316"/>
-      <c r="F316"/>
+      <c r="F316" t="n">
+        <v>132.50618009064</v>
+      </c>
       <c r="G316" t="n">
         <v>4.58475522739963</v>
       </c>
@@ -14452,8 +14454,12 @@
       <c r="L316"/>
       <c r="M316"/>
       <c r="N316"/>
-      <c r="O316"/>
-      <c r="P316"/>
+      <c r="O316" t="n">
+        <v>5.05250094966285</v>
+      </c>
+      <c r="P316" t="n">
+        <v>-2.11653280363093</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45703,85 +45703,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55617.5504092784</v>
+        <v>55494.9496572784</v>
       </c>
       <c r="C365" t="n">
-        <v>6737.999887</v>
+        <v>6533.681171</v>
       </c>
       <c r="D365" t="n">
-        <v>149411.349253673</v>
+        <v>148989.314340673</v>
       </c>
       <c r="E365" t="n">
-        <v>114620.293642</v>
+        <v>114106.913902</v>
       </c>
       <c r="F365" t="n">
-        <v>176835.04022</v>
+        <v>176591.879996</v>
       </c>
       <c r="G365" t="n">
-        <v>382709.558829897</v>
+        <v>381272.388766897</v>
       </c>
       <c r="H365" t="n">
-        <v>111064.158989</v>
+        <v>110219.212077</v>
       </c>
       <c r="I365" t="n">
-        <v>51233.1316155668</v>
+        <v>51026.7177125668</v>
       </c>
       <c r="J365" t="n">
-        <v>113553.634112</v>
+        <v>113218.382355</v>
       </c>
       <c r="K365" t="n">
-        <v>469593.954059015</v>
+        <v>469338.696118015</v>
       </c>
       <c r="L365" t="n">
-        <v>49809.608948</v>
+        <v>49684.743333</v>
       </c>
       <c r="M365" t="n">
-        <v>82456.632109</v>
+        <v>82357.916773</v>
       </c>
       <c r="N365" t="n">
-        <v>683143.236801629</v>
+        <v>684021.714639629</v>
       </c>
       <c r="O365" t="n">
-        <v>122683.623524</v>
+        <v>123821.580584</v>
       </c>
       <c r="P365" t="n">
-        <v>560459.613277629</v>
+        <v>560200.134055629</v>
       </c>
       <c r="Q365" t="n">
-        <v>100978.677411454</v>
+        <v>100389.041897454</v>
       </c>
       <c r="R365" t="n">
-        <v>2657608.66885914</v>
+        <v>2658909.76757814</v>
       </c>
       <c r="S365" t="n">
-        <v>573299.39423</v>
+        <v>568357.499801</v>
       </c>
       <c r="T365" t="n">
-        <v>3230908.06308914</v>
+        <v>3227267.26737914</v>
       </c>
       <c r="U365" t="n">
-        <v>0.319771131692259</v>
+        <v>0.368885181943246</v>
       </c>
       <c r="V365" t="n">
-        <v>7.38511773014008</v>
+        <v>7.43769079733221</v>
       </c>
       <c r="W365" t="n">
-        <v>0.598682949007134</v>
+        <v>-0.268487112280225</v>
       </c>
       <c r="X365" t="n">
-        <v>9.87313822567715</v>
+        <v>8.92602149197905</v>
       </c>
       <c r="Y365" t="n">
-        <v>0.369148932668506</v>
+        <v>0.256046498394658</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.81834117657372</v>
+        <v>7.69684451175074</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.82255781252969</v>
+        <v>0.823888927469412</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.17744218747031</v>
+        <v>0.176111072530588</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14433,8 +14433,12 @@
       <c r="C316" t="n">
         <v>138.1495</v>
       </c>
-      <c r="D316"/>
-      <c r="E316"/>
+      <c r="D316" t="n">
+        <v>173.68</v>
+      </c>
+      <c r="E316" t="n">
+        <v>154.66</v>
+      </c>
       <c r="F316" t="n">
         <v>132.50618009064</v>
       </c>
@@ -14450,10 +14454,18 @@
       <c r="J316" t="n">
         <v>0.272256674679738</v>
       </c>
-      <c r="K316"/>
-      <c r="L316"/>
-      <c r="M316"/>
-      <c r="N316"/>
+      <c r="K316" t="n">
+        <v>2.97640222933713</v>
+      </c>
+      <c r="L316" t="n">
+        <v>-0.526918671248566</v>
+      </c>
+      <c r="M316" t="n">
+        <v>4.84712900820283</v>
+      </c>
+      <c r="N316" t="n">
+        <v>0.213827512473252</v>
+      </c>
       <c r="O316" t="n">
         <v>5.05250094966285</v>
       </c>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45715,85 +45715,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55494.9496572784</v>
+        <v>55722.8598192784</v>
       </c>
       <c r="C365" t="n">
-        <v>6533.681171</v>
+        <v>6534.102929</v>
       </c>
       <c r="D365" t="n">
-        <v>148989.314340673</v>
+        <v>148515.741252673</v>
       </c>
       <c r="E365" t="n">
-        <v>114106.913902</v>
+        <v>113882.017772</v>
       </c>
       <c r="F365" t="n">
-        <v>176591.879996</v>
+        <v>176523.072026</v>
       </c>
       <c r="G365" t="n">
-        <v>381272.388766897</v>
+        <v>380014.692700897</v>
       </c>
       <c r="H365" t="n">
-        <v>110219.212077</v>
+        <v>109983.806455</v>
       </c>
       <c r="I365" t="n">
-        <v>51026.7177125668</v>
+        <v>50878.7940025668</v>
       </c>
       <c r="J365" t="n">
-        <v>113218.382355</v>
+        <v>113286.180933</v>
       </c>
       <c r="K365" t="n">
-        <v>469338.696118015</v>
+        <v>469699.444786015</v>
       </c>
       <c r="L365" t="n">
-        <v>49684.743333</v>
+        <v>49787.26406</v>
       </c>
       <c r="M365" t="n">
-        <v>82357.916773</v>
+        <v>82063.674374</v>
       </c>
       <c r="N365" t="n">
-        <v>684021.714639629</v>
+        <v>682980.628453629</v>
       </c>
       <c r="O365" t="n">
-        <v>123821.580584</v>
+        <v>123021.388707</v>
       </c>
       <c r="P365" t="n">
-        <v>560200.134055629</v>
+        <v>559959.239746629</v>
       </c>
       <c r="Q365" t="n">
-        <v>100389.041897454</v>
+        <v>99719.7865524537</v>
       </c>
       <c r="R365" t="n">
-        <v>2658909.76757814</v>
+        <v>2657955.62756614</v>
       </c>
       <c r="S365" t="n">
-        <v>568357.499801</v>
+        <v>564617.067004</v>
       </c>
       <c r="T365" t="n">
-        <v>3227267.26737914</v>
+        <v>3222572.69457014</v>
       </c>
       <c r="U365" t="n">
-        <v>0.368885181943246</v>
+        <v>0.332868175845591</v>
       </c>
       <c r="V365" t="n">
-        <v>7.43769079733221</v>
+        <v>7.39913717628173</v>
       </c>
       <c r="W365" t="n">
-        <v>-0.268487112280225</v>
+        <v>-0.924832848599833</v>
       </c>
       <c r="X365" t="n">
-        <v>8.92602149197905</v>
+        <v>8.20916552829776</v>
       </c>
       <c r="Y365" t="n">
-        <v>0.256046498394658</v>
+        <v>0.110208155662206</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.69684451175074</v>
+        <v>7.54018234652805</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.823888927469412</v>
+        <v>0.824793070469644</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.176111072530588</v>
+        <v>0.175206929530356</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45715,85 +45715,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55722.8598192784</v>
+        <v>55559.8667772784</v>
       </c>
       <c r="C365" t="n">
-        <v>6534.102929</v>
+        <v>6496.490374</v>
       </c>
       <c r="D365" t="n">
-        <v>148515.741252673</v>
+        <v>148753.950874673</v>
       </c>
       <c r="E365" t="n">
-        <v>113882.017772</v>
+        <v>113814.698275</v>
       </c>
       <c r="F365" t="n">
-        <v>176523.072026</v>
+        <v>176816.506444</v>
       </c>
       <c r="G365" t="n">
-        <v>380014.692700897</v>
+        <v>380304.062529897</v>
       </c>
       <c r="H365" t="n">
-        <v>109983.806455</v>
+        <v>109325.334651</v>
       </c>
       <c r="I365" t="n">
-        <v>50878.7940025668</v>
+        <v>50698.5302035668</v>
       </c>
       <c r="J365" t="n">
-        <v>113286.180933</v>
+        <v>112897.493155</v>
       </c>
       <c r="K365" t="n">
-        <v>469699.444786015</v>
+        <v>469980.486082015</v>
       </c>
       <c r="L365" t="n">
-        <v>49787.26406</v>
+        <v>51554.559389</v>
       </c>
       <c r="M365" t="n">
-        <v>82063.674374</v>
+        <v>81715.401373</v>
       </c>
       <c r="N365" t="n">
-        <v>682980.628453629</v>
+        <v>680939.808947629</v>
       </c>
       <c r="O365" t="n">
-        <v>123021.388707</v>
+        <v>121584.928747</v>
       </c>
       <c r="P365" t="n">
-        <v>559959.239746629</v>
+        <v>559354.880200629</v>
       </c>
       <c r="Q365" t="n">
-        <v>99719.7865524537</v>
+        <v>99390.2446644537</v>
       </c>
       <c r="R365" t="n">
-        <v>2657955.62756614</v>
+        <v>2658969.48742314</v>
       </c>
       <c r="S365" t="n">
-        <v>564617.067004</v>
+        <v>560217.755265</v>
       </c>
       <c r="T365" t="n">
-        <v>3222572.69457014</v>
+        <v>3219187.24268814</v>
       </c>
       <c r="U365" t="n">
-        <v>0.332868175845591</v>
+        <v>0.371139494721717</v>
       </c>
       <c r="V365" t="n">
-        <v>7.39913717628173</v>
+        <v>7.44010387742984</v>
       </c>
       <c r="W365" t="n">
-        <v>-0.924832848599833</v>
+        <v>-1.69679418552034</v>
       </c>
       <c r="X365" t="n">
-        <v>8.20916552829776</v>
+        <v>7.36603505988658</v>
       </c>
       <c r="Y365" t="n">
-        <v>0.110208155662206</v>
+        <v>0.00503805564273652</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.54018234652805</v>
+        <v>7.4272067375281</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.824793070469644</v>
+        <v>0.825975405271177</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.175206929530356</v>
+        <v>0.174024594728823</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45715,85 +45715,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55559.8667772784</v>
+        <v>55807.9073872784</v>
       </c>
       <c r="C365" t="n">
-        <v>6496.490374</v>
+        <v>6526.958395</v>
       </c>
       <c r="D365" t="n">
-        <v>148753.950874673</v>
+        <v>149991.332503673</v>
       </c>
       <c r="E365" t="n">
-        <v>113814.698275</v>
+        <v>114101.947969</v>
       </c>
       <c r="F365" t="n">
-        <v>176816.506444</v>
+        <v>178439.555536</v>
       </c>
       <c r="G365" t="n">
-        <v>380304.062529897</v>
+        <v>384117.987442897</v>
       </c>
       <c r="H365" t="n">
-        <v>109325.334651</v>
+        <v>110248.208248</v>
       </c>
       <c r="I365" t="n">
-        <v>50698.5302035668</v>
+        <v>50939.5024665668</v>
       </c>
       <c r="J365" t="n">
-        <v>112897.493155</v>
+        <v>113526.594695</v>
       </c>
       <c r="K365" t="n">
-        <v>469980.486082015</v>
+        <v>471753.149502015</v>
       </c>
       <c r="L365" t="n">
-        <v>51554.559389</v>
+        <v>51737.399558</v>
       </c>
       <c r="M365" t="n">
-        <v>81715.401373</v>
+        <v>81978.227817</v>
       </c>
       <c r="N365" t="n">
-        <v>680939.808947629</v>
+        <v>681176.895649629</v>
       </c>
       <c r="O365" t="n">
-        <v>121584.928747</v>
+        <v>121290.316811</v>
       </c>
       <c r="P365" t="n">
-        <v>559354.880200629</v>
+        <v>559886.578838629</v>
       </c>
       <c r="Q365" t="n">
-        <v>99390.2446644537</v>
+        <v>98982.2404604537</v>
       </c>
       <c r="R365" t="n">
-        <v>2658969.48742314</v>
+        <v>2663921.93601314</v>
       </c>
       <c r="S365" t="n">
-        <v>560217.755265</v>
+        <v>566582.867267</v>
       </c>
       <c r="T365" t="n">
-        <v>3219187.24268814</v>
+        <v>3230504.80328014</v>
       </c>
       <c r="U365" t="n">
-        <v>0.371139494721717</v>
+        <v>0.558085193278446</v>
       </c>
       <c r="V365" t="n">
-        <v>7.44010387742984</v>
+        <v>7.64021583564298</v>
       </c>
       <c r="W365" t="n">
-        <v>-1.69679418552034</v>
+        <v>-0.579887573253379</v>
       </c>
       <c r="X365" t="n">
-        <v>7.36603505988658</v>
+        <v>8.58591220934175</v>
       </c>
       <c r="Y365" t="n">
-        <v>0.00503805564273652</v>
+        <v>0.356621543142799</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.4272067375281</v>
+        <v>7.80488402990767</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.825975405271177</v>
+        <v>0.824614757826173</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.174024594728823</v>
+        <v>0.175385242173827</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45715,85 +45715,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55807.9073872784</v>
+        <v>55839.1738002784</v>
       </c>
       <c r="C365" t="n">
-        <v>6526.958395</v>
+        <v>6507.034023</v>
       </c>
       <c r="D365" t="n">
-        <v>149991.332503673</v>
+        <v>149442.215251673</v>
       </c>
       <c r="E365" t="n">
-        <v>114101.947969</v>
+        <v>114365.665392</v>
       </c>
       <c r="F365" t="n">
-        <v>178439.555536</v>
+        <v>179425.70168</v>
       </c>
       <c r="G365" t="n">
-        <v>384117.987442897</v>
+        <v>384957.908167897</v>
       </c>
       <c r="H365" t="n">
-        <v>110248.208248</v>
+        <v>109965.2698</v>
       </c>
       <c r="I365" t="n">
-        <v>50939.5024665668</v>
+        <v>50905.7100505668</v>
       </c>
       <c r="J365" t="n">
-        <v>113526.594695</v>
+        <v>113847.271202</v>
       </c>
       <c r="K365" t="n">
-        <v>471753.149502015</v>
+        <v>472913.879369015</v>
       </c>
       <c r="L365" t="n">
-        <v>51737.399558</v>
+        <v>53396.790344</v>
       </c>
       <c r="M365" t="n">
-        <v>81978.227817</v>
+        <v>82241.564638</v>
       </c>
       <c r="N365" t="n">
-        <v>681176.895649629</v>
+        <v>681313.569557629</v>
       </c>
       <c r="O365" t="n">
-        <v>121290.316811</v>
+        <v>120460.170944</v>
       </c>
       <c r="P365" t="n">
-        <v>559886.578838629</v>
+        <v>560853.398613629</v>
       </c>
       <c r="Q365" t="n">
-        <v>98982.2404604537</v>
+        <v>98758.4257304537</v>
       </c>
       <c r="R365" t="n">
-        <v>2663921.93601314</v>
+        <v>2669999.89539214</v>
       </c>
       <c r="S365" t="n">
-        <v>566582.867267</v>
+        <v>565193.853172</v>
       </c>
       <c r="T365" t="n">
-        <v>3230504.80328014</v>
+        <v>3235193.74856414</v>
       </c>
       <c r="U365" t="n">
-        <v>0.558085193278446</v>
+        <v>0.787516825178836</v>
       </c>
       <c r="V365" t="n">
-        <v>7.64021583564298</v>
+        <v>7.88580593742163</v>
       </c>
       <c r="W365" t="n">
-        <v>-0.579887573253379</v>
+        <v>-0.823622330277296</v>
       </c>
       <c r="X365" t="n">
-        <v>8.58591220934175</v>
+        <v>8.31970690859776</v>
       </c>
       <c r="Y365" t="n">
-        <v>0.356621543142799</v>
+        <v>0.502285065086827</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.80488402990767</v>
+        <v>7.96135839950185</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.824614757826173</v>
+        <v>0.825298298309692</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.175385242173827</v>
+        <v>0.174701701690307</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45796,6 +45796,92 @@
         <v>0.174701701690307</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B366" t="n">
+        <v>55865.1125112784</v>
+      </c>
+      <c r="C366" t="n">
+        <v>6523.556</v>
+      </c>
+      <c r="D366" t="n">
+        <v>149339.938641673</v>
+      </c>
+      <c r="E366" t="n">
+        <v>114343.205809</v>
+      </c>
+      <c r="F366" t="n">
+        <v>178929.609191</v>
+      </c>
+      <c r="G366" t="n">
+        <v>385170.372480897</v>
+      </c>
+      <c r="H366" t="n">
+        <v>110073.946498</v>
+      </c>
+      <c r="I366" t="n">
+        <v>51329.3436385668</v>
+      </c>
+      <c r="J366" t="n">
+        <v>113987.187851</v>
+      </c>
+      <c r="K366" t="n">
+        <v>472809.693115015</v>
+      </c>
+      <c r="L366" t="n">
+        <v>53318.195184</v>
+      </c>
+      <c r="M366" t="n">
+        <v>81847.762589</v>
+      </c>
+      <c r="N366" t="n">
+        <v>679893.586148629</v>
+      </c>
+      <c r="O366" t="n">
+        <v>119511.772372</v>
+      </c>
+      <c r="P366" t="n">
+        <v>560381.813776629</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>100166.625325454</v>
+      </c>
+      <c r="R366" t="n">
+        <v>2667633.49350314</v>
+      </c>
+      <c r="S366" t="n">
+        <v>565858.227629</v>
+      </c>
+      <c r="T366" t="n">
+        <v>3233491.72113214</v>
+      </c>
+      <c r="U366" t="n">
+        <v>-0.0886292877046002</v>
+      </c>
+      <c r="V366" t="n">
+        <v>6.75177883320499</v>
+      </c>
+      <c r="W366" t="n">
+        <v>0.117548068378892</v>
+      </c>
+      <c r="X366" t="n">
+        <v>8.26281380979566</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>-0.0526097527468239</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>7.01315637082438</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>0.825000873226026</v>
+      </c>
+      <c r="AB366" t="n">
+        <v>0.174999126773974</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45801,85 +45801,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55865.1125112784</v>
+        <v>55786.8359112784</v>
       </c>
       <c r="C366" t="n">
-        <v>6523.556</v>
+        <v>6515.608299</v>
       </c>
       <c r="D366" t="n">
-        <v>149339.938641673</v>
+        <v>149398.931215673</v>
       </c>
       <c r="E366" t="n">
-        <v>114343.205809</v>
+        <v>114279.76661</v>
       </c>
       <c r="F366" t="n">
-        <v>178929.609191</v>
+        <v>178797.068173</v>
       </c>
       <c r="G366" t="n">
-        <v>385170.372480897</v>
+        <v>385155.849943897</v>
       </c>
       <c r="H366" t="n">
-        <v>110073.946498</v>
+        <v>109949.600733</v>
       </c>
       <c r="I366" t="n">
-        <v>51329.3436385668</v>
+        <v>51245.0173895668</v>
       </c>
       <c r="J366" t="n">
-        <v>113987.187851</v>
+        <v>113727.893583</v>
       </c>
       <c r="K366" t="n">
-        <v>472809.693115015</v>
+        <v>472511.105652015</v>
       </c>
       <c r="L366" t="n">
-        <v>53318.195184</v>
+        <v>52799.923081</v>
       </c>
       <c r="M366" t="n">
-        <v>81847.762589</v>
+        <v>81324.385392</v>
       </c>
       <c r="N366" t="n">
-        <v>679893.586148629</v>
+        <v>680610.997507629</v>
       </c>
       <c r="O366" t="n">
-        <v>119511.772372</v>
+        <v>121029.255585</v>
       </c>
       <c r="P366" t="n">
-        <v>560381.813776629</v>
+        <v>559581.741922629</v>
       </c>
       <c r="Q366" t="n">
-        <v>100166.625325454</v>
+        <v>99464.1439044537</v>
       </c>
       <c r="R366" t="n">
-        <v>2667633.49350314</v>
+        <v>2666720.61896914</v>
       </c>
       <c r="S366" t="n">
-        <v>565858.227629</v>
+        <v>565457.505934</v>
       </c>
       <c r="T366" t="n">
-        <v>3233491.72113214</v>
+        <v>3232178.12490314</v>
       </c>
       <c r="U366" t="n">
-        <v>-0.0886292877046002</v>
+        <v>-0.122819346497305</v>
       </c>
       <c r="V366" t="n">
-        <v>6.75177883320499</v>
+        <v>6.71524796020713</v>
       </c>
       <c r="W366" t="n">
-        <v>0.117548068378892</v>
+        <v>0.0466482005280655</v>
       </c>
       <c r="X366" t="n">
-        <v>8.26281380979566</v>
+        <v>8.18614573970837</v>
       </c>
       <c r="Y366" t="n">
-        <v>-0.0526097527468239</v>
+        <v>-0.0932130776507223</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.01315637082438</v>
+        <v>6.96968259980979</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.825000873226026</v>
+        <v>0.825053730307347</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.174999126773974</v>
+        <v>0.174946269692653</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45801,85 +45801,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55786.8359112784</v>
+        <v>55572.3910092784</v>
       </c>
       <c r="C366" t="n">
-        <v>6515.608299</v>
+        <v>6489.912403</v>
       </c>
       <c r="D366" t="n">
-        <v>149398.931215673</v>
+        <v>149147.065375673</v>
       </c>
       <c r="E366" t="n">
-        <v>114279.76661</v>
+        <v>113549.879058</v>
       </c>
       <c r="F366" t="n">
-        <v>178797.068173</v>
+        <v>180562.386488</v>
       </c>
       <c r="G366" t="n">
-        <v>385155.849943897</v>
+        <v>384082.594260897</v>
       </c>
       <c r="H366" t="n">
-        <v>109949.600733</v>
+        <v>108784.314268</v>
       </c>
       <c r="I366" t="n">
-        <v>51245.0173895668</v>
+        <v>50969.1753865668</v>
       </c>
       <c r="J366" t="n">
-        <v>113727.893583</v>
+        <v>112331.001092</v>
       </c>
       <c r="K366" t="n">
-        <v>472511.105652015</v>
+        <v>472422.437090015</v>
       </c>
       <c r="L366" t="n">
-        <v>52799.923081</v>
+        <v>52589.175092</v>
       </c>
       <c r="M366" t="n">
-        <v>81324.385392</v>
+        <v>81934.21834</v>
       </c>
       <c r="N366" t="n">
-        <v>680610.997507629</v>
+        <v>680230.391276629</v>
       </c>
       <c r="O366" t="n">
-        <v>121029.255585</v>
+        <v>120413.863864</v>
       </c>
       <c r="P366" t="n">
-        <v>559581.741922629</v>
+        <v>559816.527412629</v>
       </c>
       <c r="Q366" t="n">
-        <v>99464.1439044537</v>
+        <v>100999.880432454</v>
       </c>
       <c r="R366" t="n">
-        <v>2666720.61896914</v>
+        <v>2669648.46921214</v>
       </c>
       <c r="S366" t="n">
-        <v>565457.505934</v>
+        <v>560246.743637</v>
       </c>
       <c r="T366" t="n">
-        <v>3232178.12490314</v>
+        <v>3229895.21284914</v>
       </c>
       <c r="U366" t="n">
-        <v>-0.122819346497305</v>
+        <v>-0.0131620297291413</v>
       </c>
       <c r="V366" t="n">
-        <v>6.71524796020713</v>
+        <v>6.83241293896402</v>
       </c>
       <c r="W366" t="n">
-        <v>0.0466482005280655</v>
+        <v>-0.875294291902806</v>
       </c>
       <c r="X366" t="n">
-        <v>8.18614573970837</v>
+        <v>7.18919674997469</v>
       </c>
       <c r="Y366" t="n">
-        <v>-0.0932130776507223</v>
+        <v>-0.163778003013015</v>
       </c>
       <c r="Z366" t="n">
-        <v>6.96968259980979</v>
+        <v>6.89412909737805</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.825053730307347</v>
+        <v>0.826543368525322</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.174946269692653</v>
+        <v>0.173456631474678</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14473,6 +14473,38 @@
         <v>-2.11653280363093</v>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B317" t="n">
+        <v>135.433</v>
+      </c>
+      <c r="C317" t="n">
+        <v>138.8249</v>
+      </c>
+      <c r="D317"/>
+      <c r="E317"/>
+      <c r="F317"/>
+      <c r="G317" t="n">
+        <v>4.86594135287464</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0.434268662206305</v>
+      </c>
+      <c r="I317" t="n">
+        <v>5.11431781837566</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0.488890658308594</v>
+      </c>
+      <c r="K317"/>
+      <c r="L317"/>
+      <c r="M317"/>
+      <c r="N317"/>
+      <c r="O317"/>
+      <c r="P317"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14480,9 +14480,7 @@
       <c r="B317" t="n">
         <v>135.433</v>
       </c>
-      <c r="C317" t="n">
-        <v>138.8249</v>
-      </c>
+      <c r="C317"/>
       <c r="D317"/>
       <c r="E317"/>
       <c r="F317"/>
@@ -14492,12 +14490,8 @@
       <c r="H317" t="n">
         <v>0.434268662206305</v>
       </c>
-      <c r="I317" t="n">
-        <v>5.11431781837566</v>
-      </c>
-      <c r="J317" t="n">
-        <v>0.488890658308594</v>
-      </c>
+      <c r="I317"/>
+      <c r="J317"/>
       <c r="K317"/>
       <c r="L317"/>
       <c r="M317"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -1122,6 +1122,9 @@
   <si>
     <t xml:space="preserve">127.2749</t>
   </si>
+  <si>
+    <t xml:space="preserve">127.50369999999999</t>
+  </si>
 </sst>
 </file>
 
@@ -14480,7 +14483,9 @@
       <c r="B317" t="n">
         <v>135.433</v>
       </c>
-      <c r="C317"/>
+      <c r="C317" t="n">
+        <v>138.8249</v>
+      </c>
       <c r="D317"/>
       <c r="E317"/>
       <c r="F317"/>
@@ -14490,8 +14495,12 @@
       <c r="H317" t="n">
         <v>0.434268662206305</v>
       </c>
-      <c r="I317"/>
-      <c r="J317"/>
+      <c r="I317" t="n">
+        <v>5.11431781837566</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0.488890658308594</v>
+      </c>
       <c r="K317"/>
       <c r="L317"/>
       <c r="M317"/>
@@ -45827,85 +45836,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55572.3910092784</v>
+        <v>55519.6857622784</v>
       </c>
       <c r="C366" t="n">
-        <v>6489.912403</v>
+        <v>6481.920176</v>
       </c>
       <c r="D366" t="n">
-        <v>149147.065375673</v>
+        <v>148752.286731673</v>
       </c>
       <c r="E366" t="n">
-        <v>113549.879058</v>
+        <v>113379.868671</v>
       </c>
       <c r="F366" t="n">
-        <v>180562.386488</v>
+        <v>180380.933431</v>
       </c>
       <c r="G366" t="n">
-        <v>384082.594260897</v>
+        <v>383538.467628897</v>
       </c>
       <c r="H366" t="n">
-        <v>108784.314268</v>
+        <v>108582.436834</v>
       </c>
       <c r="I366" t="n">
-        <v>50969.1753865668</v>
+        <v>50846.5361985668</v>
       </c>
       <c r="J366" t="n">
-        <v>112331.001092</v>
+        <v>112451.784126</v>
       </c>
       <c r="K366" t="n">
-        <v>472422.437090015</v>
+        <v>472285.473593015</v>
       </c>
       <c r="L366" t="n">
-        <v>52589.175092</v>
+        <v>52530.600225</v>
       </c>
       <c r="M366" t="n">
-        <v>81934.21834</v>
+        <v>81964.935885</v>
       </c>
       <c r="N366" t="n">
-        <v>680230.391276629</v>
+        <v>681768.159101629</v>
       </c>
       <c r="O366" t="n">
-        <v>120413.863864</v>
+        <v>121947.338149</v>
       </c>
       <c r="P366" t="n">
-        <v>559816.527412629</v>
+        <v>559820.820952629</v>
       </c>
       <c r="Q366" t="n">
-        <v>100999.880432454</v>
+        <v>100751.930291454</v>
       </c>
       <c r="R366" t="n">
-        <v>2669648.46921214</v>
+        <v>2672068.45909914</v>
       </c>
       <c r="S366" t="n">
-        <v>560246.743637</v>
+        <v>558934.718658</v>
       </c>
       <c r="T366" t="n">
-        <v>3229895.21284914</v>
+        <v>3231003.17775714</v>
       </c>
       <c r="U366" t="n">
-        <v>-0.0131620297291413</v>
+        <v>0.0774742991776822</v>
       </c>
       <c r="V366" t="n">
-        <v>6.83241293896402</v>
+        <v>6.92925466247092</v>
       </c>
       <c r="W366" t="n">
-        <v>-0.875294291902806</v>
+        <v>-1.10743145539752</v>
       </c>
       <c r="X366" t="n">
-        <v>7.18919674997469</v>
+        <v>6.93817359774369</v>
       </c>
       <c r="Y366" t="n">
-        <v>-0.163778003013015</v>
+        <v>-0.129530752489249</v>
       </c>
       <c r="Z366" t="n">
-        <v>6.89412909737805</v>
+        <v>6.93079745226459</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.826543368525322</v>
+        <v>0.82700892326389</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.173456631474678</v>
+        <v>0.17299107673611</v>
       </c>
     </row>
   </sheetData>
@@ -60771,6 +60780,53 @@
         <v>147.8913</v>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B317" t="n">
+        <v>138.8249</v>
+      </c>
+      <c r="C317" t="n">
+        <v>135.433</v>
+      </c>
+      <c r="D317" t="n">
+        <v>153.3094</v>
+      </c>
+      <c r="E317" t="n">
+        <v>141.2634</v>
+      </c>
+      <c r="F317" t="n">
+        <v>96.5271</v>
+      </c>
+      <c r="G317" t="s">
+        <v>369</v>
+      </c>
+      <c r="H317" t="n">
+        <v>126.0799</v>
+      </c>
+      <c r="I317" t="n">
+        <v>137.1184</v>
+      </c>
+      <c r="J317" t="n">
+        <v>143.8788</v>
+      </c>
+      <c r="K317" t="n">
+        <v>97.9289</v>
+      </c>
+      <c r="L317" t="n">
+        <v>122.9818</v>
+      </c>
+      <c r="M317" t="n">
+        <v>132.7154</v>
+      </c>
+      <c r="N317" t="n">
+        <v>154.2589</v>
+      </c>
+      <c r="O317" t="n">
+        <v>148.8784</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45750,85 +45750,85 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55839.1738002784</v>
+        <v>55879.6528772784</v>
       </c>
       <c r="C365" t="n">
-        <v>6507.034023</v>
+        <v>6506.435252</v>
       </c>
       <c r="D365" t="n">
-        <v>149442.215251673</v>
+        <v>149445.968778673</v>
       </c>
       <c r="E365" t="n">
-        <v>114365.665392</v>
+        <v>114088.220543</v>
       </c>
       <c r="F365" t="n">
-        <v>179425.70168</v>
+        <v>180773.744496</v>
       </c>
       <c r="G365" t="n">
-        <v>384957.908167897</v>
+        <v>386112.749019897</v>
       </c>
       <c r="H365" t="n">
-        <v>109965.2698</v>
+        <v>109315.368448</v>
       </c>
       <c r="I365" t="n">
-        <v>50905.7100505668</v>
+        <v>50824.2013285668</v>
       </c>
       <c r="J365" t="n">
-        <v>113847.271202</v>
+        <v>112557.817685</v>
       </c>
       <c r="K365" t="n">
-        <v>472913.879369015</v>
+        <v>473128.666056015</v>
       </c>
       <c r="L365" t="n">
-        <v>53396.790344</v>
+        <v>53322.242909</v>
       </c>
       <c r="M365" t="n">
-        <v>82241.564638</v>
+        <v>82005.887614</v>
       </c>
       <c r="N365" t="n">
-        <v>681313.569557629</v>
+        <v>681425.124617629</v>
       </c>
       <c r="O365" t="n">
-        <v>120460.170944</v>
+        <v>120538.566978</v>
       </c>
       <c r="P365" t="n">
-        <v>560853.398613629</v>
+        <v>560886.557639629</v>
       </c>
       <c r="Q365" t="n">
-        <v>98758.4257304537</v>
+        <v>98682.0910644537</v>
       </c>
       <c r="R365" t="n">
-        <v>2669999.89539214</v>
+        <v>2670268.46339714</v>
       </c>
       <c r="S365" t="n">
-        <v>565193.853172</v>
+        <v>565224.83191</v>
       </c>
       <c r="T365" t="n">
-        <v>3235193.74856414</v>
+        <v>3235493.29530714</v>
       </c>
       <c r="U365" t="n">
-        <v>0.787516825178836</v>
+        <v>0.79765476652085</v>
       </c>
       <c r="V365" t="n">
-        <v>7.88580593742163</v>
+        <v>7.89665787629941</v>
       </c>
       <c r="W365" t="n">
-        <v>-0.823622330277296</v>
+        <v>-0.818186391789344</v>
       </c>
       <c r="X365" t="n">
-        <v>8.31970690859776</v>
+        <v>8.32564400044988</v>
       </c>
       <c r="Y365" t="n">
-        <v>0.502285065086827</v>
+        <v>0.51159057643948</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.96135839950185</v>
+        <v>7.97135454680917</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.825298298309692</v>
+        <v>0.825304897794157</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.174701701690307</v>
+        <v>0.174695102205843</v>
       </c>
     </row>
     <row r="366">
@@ -45836,85 +45836,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55519.6857622784</v>
+        <v>55705.4587482784</v>
       </c>
       <c r="C366" t="n">
-        <v>6481.920176</v>
+        <v>6528.981633</v>
       </c>
       <c r="D366" t="n">
-        <v>148752.286731673</v>
+        <v>149520.232712673</v>
       </c>
       <c r="E366" t="n">
-        <v>113379.868671</v>
+        <v>114340.785426</v>
       </c>
       <c r="F366" t="n">
-        <v>180380.933431</v>
+        <v>180823.375416</v>
       </c>
       <c r="G366" t="n">
-        <v>383538.467628897</v>
+        <v>386519.864562897</v>
       </c>
       <c r="H366" t="n">
-        <v>108582.436834</v>
+        <v>110088.284769</v>
       </c>
       <c r="I366" t="n">
-        <v>50846.5361985668</v>
+        <v>51030.5446625668</v>
       </c>
       <c r="J366" t="n">
-        <v>112451.784126</v>
+        <v>113023.68707</v>
       </c>
       <c r="K366" t="n">
-        <v>472285.473593015</v>
+        <v>473255.289856015</v>
       </c>
       <c r="L366" t="n">
-        <v>52530.600225</v>
+        <v>52401.650511</v>
       </c>
       <c r="M366" t="n">
-        <v>81964.935885</v>
+        <v>81822.048108</v>
       </c>
       <c r="N366" t="n">
-        <v>681768.159101629</v>
+        <v>682800.190123629</v>
       </c>
       <c r="O366" t="n">
-        <v>121947.338149</v>
+        <v>122471.142941</v>
       </c>
       <c r="P366" t="n">
-        <v>559820.820952629</v>
+        <v>560329.047182629</v>
       </c>
       <c r="Q366" t="n">
-        <v>100751.930291454</v>
+        <v>101052.564688454</v>
       </c>
       <c r="R366" t="n">
-        <v>2672068.45909914</v>
+        <v>2673732.32283514</v>
       </c>
       <c r="S366" t="n">
-        <v>558934.718658</v>
+        <v>567980.825576</v>
       </c>
       <c r="T366" t="n">
-        <v>3231003.17775714</v>
+        <v>3241713.14841114</v>
       </c>
       <c r="U366" t="n">
-        <v>0.0774742991776822</v>
+        <v>0.129719520171157</v>
       </c>
       <c r="V366" t="n">
-        <v>6.92925466247092</v>
+        <v>6.99583817703042</v>
       </c>
       <c r="W366" t="n">
-        <v>-1.10743145539752</v>
+        <v>0.487592460629704</v>
       </c>
       <c r="X366" t="n">
-        <v>6.93817359774369</v>
+        <v>8.66891981852507</v>
       </c>
       <c r="Y366" t="n">
-        <v>-0.129530752489249</v>
+        <v>0.192238170081249</v>
       </c>
       <c r="Z366" t="n">
-        <v>6.93079745226459</v>
+        <v>7.28524640812034</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.82700892326389</v>
+        <v>0.824789918301567</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.17299107673611</v>
+        <v>0.175210081698433</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45836,85 +45836,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55705.4587482784</v>
+        <v>55841.0186142784</v>
       </c>
       <c r="C366" t="n">
-        <v>6528.981633</v>
+        <v>6481.941985</v>
       </c>
       <c r="D366" t="n">
-        <v>149520.232712673</v>
+        <v>149102.047996673</v>
       </c>
       <c r="E366" t="n">
-        <v>114340.785426</v>
+        <v>113362.840703</v>
       </c>
       <c r="F366" t="n">
-        <v>180823.375416</v>
+        <v>180593.203463</v>
       </c>
       <c r="G366" t="n">
-        <v>386519.864562897</v>
+        <v>385223.019677897</v>
       </c>
       <c r="H366" t="n">
-        <v>110088.284769</v>
+        <v>109060.806234</v>
       </c>
       <c r="I366" t="n">
-        <v>51030.5446625668</v>
+        <v>50852.1568115668</v>
       </c>
       <c r="J366" t="n">
-        <v>113023.68707</v>
+        <v>113412.558058</v>
       </c>
       <c r="K366" t="n">
-        <v>473255.289856015</v>
+        <v>473298.514126015</v>
       </c>
       <c r="L366" t="n">
-        <v>52401.650511</v>
+        <v>52506.116566</v>
       </c>
       <c r="M366" t="n">
-        <v>81822.048108</v>
+        <v>81846.422022</v>
       </c>
       <c r="N366" t="n">
-        <v>682800.190123629</v>
+        <v>681404.345378629</v>
       </c>
       <c r="O366" t="n">
-        <v>122471.142941</v>
+        <v>121348.581719</v>
       </c>
       <c r="P366" t="n">
-        <v>560329.047182629</v>
+        <v>560055.763659629</v>
       </c>
       <c r="Q366" t="n">
-        <v>101052.564688454</v>
+        <v>101952.699317454</v>
       </c>
       <c r="R366" t="n">
-        <v>2673732.32283514</v>
+        <v>2675090.13910014</v>
       </c>
       <c r="S366" t="n">
-        <v>567980.825576</v>
+        <v>561251.897232</v>
       </c>
       <c r="T366" t="n">
-        <v>3241713.14841114</v>
+        <v>3236342.03633214</v>
       </c>
       <c r="U366" t="n">
-        <v>0.129719520171157</v>
+        <v>0.180568949118554</v>
       </c>
       <c r="V366" t="n">
-        <v>6.99583817703042</v>
+        <v>7.05017446496894</v>
       </c>
       <c r="W366" t="n">
-        <v>0.487592460629704</v>
+        <v>-0.702894574637614</v>
       </c>
       <c r="X366" t="n">
-        <v>8.66891981852507</v>
+        <v>7.38150774094801</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.192238170081249</v>
+        <v>0.026232198540832</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.28524640812034</v>
+        <v>7.10748821160516</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.824789918301567</v>
+        <v>0.826578312511095</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.175210081698433</v>
+        <v>0.173421687488905</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45836,85 +45836,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55841.0186142784</v>
+        <v>55663.6161962784</v>
       </c>
       <c r="C366" t="n">
-        <v>6481.941985</v>
+        <v>6479.979991</v>
       </c>
       <c r="D366" t="n">
-        <v>149102.047996673</v>
+        <v>149343.429749673</v>
       </c>
       <c r="E366" t="n">
-        <v>113362.840703</v>
+        <v>113575.622215</v>
       </c>
       <c r="F366" t="n">
-        <v>180593.203463</v>
+        <v>181027.101761</v>
       </c>
       <c r="G366" t="n">
-        <v>385223.019677897</v>
+        <v>384629.105652897</v>
       </c>
       <c r="H366" t="n">
-        <v>109060.806234</v>
+        <v>108919.392</v>
       </c>
       <c r="I366" t="n">
-        <v>50852.1568115668</v>
+        <v>50819.4221745668</v>
       </c>
       <c r="J366" t="n">
-        <v>113412.558058</v>
+        <v>113289.710668</v>
       </c>
       <c r="K366" t="n">
-        <v>473298.514126015</v>
+        <v>473204.906329015</v>
       </c>
       <c r="L366" t="n">
-        <v>52506.116566</v>
+        <v>52476.168151</v>
       </c>
       <c r="M366" t="n">
-        <v>81846.422022</v>
+        <v>81774.772417</v>
       </c>
       <c r="N366" t="n">
-        <v>681404.345378629</v>
+        <v>682523.250692629</v>
       </c>
       <c r="O366" t="n">
-        <v>121348.581719</v>
+        <v>122516.016966</v>
       </c>
       <c r="P366" t="n">
-        <v>560055.763659629</v>
+        <v>560007.233726629</v>
       </c>
       <c r="Q366" t="n">
-        <v>101952.699317454</v>
+        <v>101295.114236454</v>
       </c>
       <c r="R366" t="n">
-        <v>2675090.13910014</v>
+        <v>2676299.07421114</v>
       </c>
       <c r="S366" t="n">
-        <v>561251.897232</v>
+        <v>561245.768716</v>
       </c>
       <c r="T366" t="n">
-        <v>3236342.03633214</v>
+        <v>3237544.84292714</v>
       </c>
       <c r="U366" t="n">
-        <v>0.180568949118554</v>
+        <v>0.225842865489545</v>
       </c>
       <c r="V366" t="n">
-        <v>7.05017446496894</v>
+        <v>7.09855291497246</v>
       </c>
       <c r="W366" t="n">
-        <v>-0.702894574637614</v>
+        <v>-0.703978836271923</v>
       </c>
       <c r="X366" t="n">
-        <v>7.38150774094801</v>
+        <v>7.38033520274985</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.026232198540832</v>
+        <v>0.0634075682671265</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.10748821160516</v>
+        <v>7.14729537405847</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.826578312511095</v>
+        <v>0.826644634763247</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.173421687488905</v>
+        <v>0.173355365236753</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14486,8 +14486,12 @@
       <c r="C317" t="n">
         <v>138.8249</v>
       </c>
-      <c r="D317"/>
-      <c r="E317"/>
+      <c r="D317" t="n">
+        <v>176.05</v>
+      </c>
+      <c r="E317" t="n">
+        <v>155.18</v>
+      </c>
       <c r="F317"/>
       <c r="G317" t="n">
         <v>4.86594135287464</v>
@@ -14501,10 +14505,18 @@
       <c r="J317" t="n">
         <v>0.488890658308594</v>
       </c>
-      <c r="K317"/>
-      <c r="L317"/>
-      <c r="M317"/>
-      <c r="N317"/>
+      <c r="K317" t="n">
+        <v>4.58001663300465</v>
+      </c>
+      <c r="L317" t="n">
+        <v>1.36457853523722</v>
+      </c>
+      <c r="M317" t="n">
+        <v>4.89387589563337</v>
+      </c>
+      <c r="N317" t="n">
+        <v>0.336221388852964</v>
+      </c>
       <c r="O317"/>
       <c r="P317"/>
     </row>
@@ -45836,85 +45848,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55663.6161962784</v>
+        <v>55808.4399182784</v>
       </c>
       <c r="C366" t="n">
-        <v>6479.979991</v>
+        <v>6464.322627</v>
       </c>
       <c r="D366" t="n">
-        <v>149343.429749673</v>
+        <v>149310.023030673</v>
       </c>
       <c r="E366" t="n">
-        <v>113575.622215</v>
+        <v>113732.096508</v>
       </c>
       <c r="F366" t="n">
-        <v>181027.101761</v>
+        <v>181712.919207</v>
       </c>
       <c r="G366" t="n">
-        <v>384629.105652897</v>
+        <v>385703.539742897</v>
       </c>
       <c r="H366" t="n">
-        <v>108919.392</v>
+        <v>108477.637473</v>
       </c>
       <c r="I366" t="n">
-        <v>50819.4221745668</v>
+        <v>50874.5277985668</v>
       </c>
       <c r="J366" t="n">
-        <v>113289.710668</v>
+        <v>113456.577146</v>
       </c>
       <c r="K366" t="n">
-        <v>473204.906329015</v>
+        <v>473613.714264015</v>
       </c>
       <c r="L366" t="n">
-        <v>52476.168151</v>
+        <v>52856.527962</v>
       </c>
       <c r="M366" t="n">
-        <v>81774.772417</v>
+        <v>81675.456421</v>
       </c>
       <c r="N366" t="n">
-        <v>682523.250692629</v>
+        <v>682490.346832629</v>
       </c>
       <c r="O366" t="n">
-        <v>122516.016966</v>
+        <v>122342.363054</v>
       </c>
       <c r="P366" t="n">
-        <v>560007.233726629</v>
+        <v>560147.983778629</v>
       </c>
       <c r="Q366" t="n">
-        <v>101295.114236454</v>
+        <v>101125.100597454</v>
       </c>
       <c r="R366" t="n">
-        <v>2676299.07421114</v>
+        <v>2677564.03318614</v>
       </c>
       <c r="S366" t="n">
-        <v>561245.768716</v>
+        <v>562227.543175</v>
       </c>
       <c r="T366" t="n">
-        <v>3237544.84292714</v>
+        <v>3239791.57636114</v>
       </c>
       <c r="U366" t="n">
-        <v>0.225842865489545</v>
+        <v>0.273214842964453</v>
       </c>
       <c r="V366" t="n">
-        <v>7.09855291497246</v>
+        <v>7.1491732948189</v>
       </c>
       <c r="W366" t="n">
-        <v>-0.703978836271923</v>
+        <v>-0.530282564704665</v>
       </c>
       <c r="X366" t="n">
-        <v>7.38033520274985</v>
+        <v>7.56817318100687</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.0634075682671265</v>
+        <v>0.132847781209566</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.14729537405847</v>
+        <v>7.22165153669372</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.826644634763247</v>
+        <v>0.826461817088098</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.173355365236753</v>
+        <v>0.173538182911902</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45848,85 +45848,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55808.4399182784</v>
+        <v>55950.1640582784</v>
       </c>
       <c r="C366" t="n">
-        <v>6464.322627</v>
+        <v>6433.576231</v>
       </c>
       <c r="D366" t="n">
-        <v>149310.023030673</v>
+        <v>149816.186542673</v>
       </c>
       <c r="E366" t="n">
-        <v>113732.096508</v>
+        <v>113713.149429</v>
       </c>
       <c r="F366" t="n">
-        <v>181712.919207</v>
+        <v>181639.326442</v>
       </c>
       <c r="G366" t="n">
-        <v>385703.539742897</v>
+        <v>385808.229072897</v>
       </c>
       <c r="H366" t="n">
-        <v>108477.637473</v>
+        <v>108720.507299</v>
       </c>
       <c r="I366" t="n">
-        <v>50874.5277985668</v>
+        <v>50952.6045855668</v>
       </c>
       <c r="J366" t="n">
-        <v>113456.577146</v>
+        <v>115723.885074</v>
       </c>
       <c r="K366" t="n">
-        <v>473613.714264015</v>
+        <v>474172.807524015</v>
       </c>
       <c r="L366" t="n">
-        <v>52856.527962</v>
+        <v>53432.233476</v>
       </c>
       <c r="M366" t="n">
-        <v>81675.456421</v>
+        <v>81740.467549</v>
       </c>
       <c r="N366" t="n">
-        <v>682490.346832629</v>
+        <v>681977.732444629</v>
       </c>
       <c r="O366" t="n">
-        <v>122342.363054</v>
+        <v>121505.228845</v>
       </c>
       <c r="P366" t="n">
-        <v>560147.983778629</v>
+        <v>560472.503599629</v>
       </c>
       <c r="Q366" t="n">
-        <v>101125.100597454</v>
+        <v>101704.730543454</v>
       </c>
       <c r="R366" t="n">
-        <v>2677564.03318614</v>
+        <v>2681269.28440514</v>
       </c>
       <c r="S366" t="n">
-        <v>562227.543175</v>
+        <v>562494.048311</v>
       </c>
       <c r="T366" t="n">
-        <v>3239791.57636114</v>
+        <v>3243763.33271614</v>
       </c>
       <c r="U366" t="n">
-        <v>0.273214842964453</v>
+        <v>0.411974344856869</v>
       </c>
       <c r="V366" t="n">
-        <v>7.1491732948189</v>
+        <v>7.2974478458828</v>
       </c>
       <c r="W366" t="n">
-        <v>-0.530282564704665</v>
+        <v>-0.483132276721132</v>
       </c>
       <c r="X366" t="n">
-        <v>7.56817318100687</v>
+        <v>7.61916227069284</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.132847781209566</v>
+        <v>0.255603602115184</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.22165153669372</v>
+        <v>7.35309773187234</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.826461817088098</v>
+        <v>0.826592142947741</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.173538182911902</v>
+        <v>0.173407857052259</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14343,7 +14343,7 @@
         <v>152.015922353681</v>
       </c>
       <c r="F314" t="n">
-        <v>130.003551134733</v>
+        <v>129.96941444808</v>
       </c>
       <c r="G314" t="n">
         <v>4.89226213151006</v>
@@ -14370,10 +14370,10 @@
         <v>0.99462644080861</v>
       </c>
       <c r="O314" t="n">
-        <v>3.51244782976698</v>
+        <v>3.48526724919511</v>
       </c>
       <c r="P314" t="n">
-        <v>-2.066194634495</v>
+        <v>-2.09191035992954</v>
       </c>
     </row>
     <row r="315">
@@ -14393,7 +14393,7 @@
         <v>154.33</v>
       </c>
       <c r="F315" t="n">
-        <v>135.371359317312</v>
+        <v>135.379690676363</v>
       </c>
       <c r="G315" t="n">
         <v>4.76226814126008</v>
@@ -14420,10 +14420,10 @@
         <v>1.52226004387532</v>
       </c>
       <c r="O315" t="n">
-        <v>3.85766141905393</v>
+        <v>3.86405328415582</v>
       </c>
       <c r="P315" t="n">
-        <v>4.12897042867446</v>
+        <v>4.16273032486767</v>
       </c>
     </row>
     <row r="316">
@@ -14443,7 +14443,7 @@
         <v>154.66</v>
       </c>
       <c r="F316" t="n">
-        <v>132.50618009064</v>
+        <v>132.531985418243</v>
       </c>
       <c r="G316" t="n">
         <v>4.58475522739963</v>
@@ -14470,10 +14470,10 @@
         <v>0.213827512473252</v>
       </c>
       <c r="O316" t="n">
-        <v>5.05250094966285</v>
+        <v>5.07295972525066</v>
       </c>
       <c r="P316" t="n">
-        <v>-2.11653280363093</v>
+        <v>-2.10349517264563</v>
       </c>
     </row>
     <row r="317">
@@ -14492,7 +14492,9 @@
       <c r="E317" t="n">
         <v>155.18</v>
       </c>
-      <c r="F317"/>
+      <c r="F317" t="n">
+        <v>127.488522830683</v>
+      </c>
       <c r="G317" t="n">
         <v>4.86594135287464</v>
       </c>
@@ -14517,8 +14519,12 @@
       <c r="N317" t="n">
         <v>0.336221388852964</v>
       </c>
-      <c r="O317"/>
-      <c r="P317"/>
+      <c r="O317" t="n">
+        <v>3.76550522481476</v>
+      </c>
+      <c r="P317" t="n">
+        <v>-3.80546822085501</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45854,85 +45854,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55950.1640582784</v>
+        <v>55926.6261922784</v>
       </c>
       <c r="C366" t="n">
-        <v>6433.576231</v>
+        <v>6414.036724</v>
       </c>
       <c r="D366" t="n">
-        <v>149816.186542673</v>
+        <v>149667.839013673</v>
       </c>
       <c r="E366" t="n">
-        <v>113713.149429</v>
+        <v>113139.710617</v>
       </c>
       <c r="F366" t="n">
-        <v>181639.326442</v>
+        <v>181623.142413</v>
       </c>
       <c r="G366" t="n">
-        <v>385808.229072897</v>
+        <v>384155.338967897</v>
       </c>
       <c r="H366" t="n">
-        <v>108720.507299</v>
+        <v>108131.65877</v>
       </c>
       <c r="I366" t="n">
-        <v>50952.6045855668</v>
+        <v>50738.6629025668</v>
       </c>
       <c r="J366" t="n">
-        <v>115723.885074</v>
+        <v>114183.542206</v>
       </c>
       <c r="K366" t="n">
-        <v>474172.807524015</v>
+        <v>473882.974192015</v>
       </c>
       <c r="L366" t="n">
-        <v>53432.233476</v>
+        <v>53450.626954</v>
       </c>
       <c r="M366" t="n">
-        <v>81740.467549</v>
+        <v>81632.200795</v>
       </c>
       <c r="N366" t="n">
-        <v>681977.732444629</v>
+        <v>682160.348823629</v>
       </c>
       <c r="O366" t="n">
-        <v>121505.228845</v>
+        <v>122333.188565</v>
       </c>
       <c r="P366" t="n">
-        <v>560472.503599629</v>
+        <v>559827.160258629</v>
       </c>
       <c r="Q366" t="n">
-        <v>101704.730543454</v>
+        <v>100172.523779454</v>
       </c>
       <c r="R366" t="n">
-        <v>2681269.28440514</v>
+        <v>2680061.05986314</v>
       </c>
       <c r="S366" t="n">
-        <v>562494.048311</v>
+        <v>557378.521311</v>
       </c>
       <c r="T366" t="n">
-        <v>3243763.33271614</v>
+        <v>3237439.58117414</v>
       </c>
       <c r="U366" t="n">
-        <v>0.411974344856869</v>
+        <v>0.366727038881409</v>
       </c>
       <c r="V366" t="n">
-        <v>7.2974478458828</v>
+        <v>7.24909783100911</v>
       </c>
       <c r="W366" t="n">
-        <v>-0.483132276721132</v>
+        <v>-1.38817513952559</v>
       </c>
       <c r="X366" t="n">
-        <v>7.61916227069284</v>
+        <v>6.64043417220683</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.255603602115184</v>
+        <v>0.0601542234633268</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.35309773187234</v>
+        <v>7.14381171199741</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.826592142947741</v>
+        <v>0.827833537171726</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.173407857052259</v>
+        <v>0.172166462828274</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45854,85 +45854,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55926.6261922784</v>
+        <v>55965.5580972784</v>
       </c>
       <c r="C366" t="n">
-        <v>6414.036724</v>
+        <v>6383.011542</v>
       </c>
       <c r="D366" t="n">
-        <v>149667.839013673</v>
+        <v>150651.000427673</v>
       </c>
       <c r="E366" t="n">
-        <v>113139.710617</v>
+        <v>113436.960117</v>
       </c>
       <c r="F366" t="n">
-        <v>181623.142413</v>
+        <v>181355.067327</v>
       </c>
       <c r="G366" t="n">
-        <v>384155.338967897</v>
+        <v>383142.302918897</v>
       </c>
       <c r="H366" t="n">
-        <v>108131.65877</v>
+        <v>107739.669195</v>
       </c>
       <c r="I366" t="n">
-        <v>50738.6629025668</v>
+        <v>50678.0599695668</v>
       </c>
       <c r="J366" t="n">
-        <v>114183.542206</v>
+        <v>113901.716444</v>
       </c>
       <c r="K366" t="n">
-        <v>473882.974192015</v>
+        <v>474362.477426015</v>
       </c>
       <c r="L366" t="n">
-        <v>53450.626954</v>
+        <v>53414.230243</v>
       </c>
       <c r="M366" t="n">
-        <v>81632.200795</v>
+        <v>81642.583968</v>
       </c>
       <c r="N366" t="n">
-        <v>682160.348823629</v>
+        <v>682021.992892629</v>
       </c>
       <c r="O366" t="n">
-        <v>122333.188565</v>
+        <v>121654.545833</v>
       </c>
       <c r="P366" t="n">
-        <v>559827.160258629</v>
+        <v>560367.447059629</v>
       </c>
       <c r="Q366" t="n">
-        <v>100172.523779454</v>
+        <v>100082.088236454</v>
       </c>
       <c r="R366" t="n">
-        <v>2680061.05986314</v>
+        <v>2682614.23064714</v>
       </c>
       <c r="S366" t="n">
-        <v>557378.521311</v>
+        <v>554184.48105</v>
       </c>
       <c r="T366" t="n">
-        <v>3237439.58117414</v>
+        <v>3236798.71169714</v>
       </c>
       <c r="U366" t="n">
-        <v>0.366727038881409</v>
+        <v>0.462341798932586</v>
       </c>
       <c r="V366" t="n">
-        <v>7.24909783100911</v>
+        <v>7.35126910885546</v>
       </c>
       <c r="W366" t="n">
-        <v>-1.38817513952559</v>
+        <v>-1.95326713136301</v>
       </c>
       <c r="X366" t="n">
-        <v>6.64043417220683</v>
+        <v>6.02933448469936</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.0601542234633268</v>
+        <v>0.0403467499652477</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.14381171199741</v>
+        <v>7.12260198843224</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.827833537171726</v>
+        <v>0.828786238993704</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.172166462828274</v>
+        <v>0.171213761006296</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45854,85 +45854,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55965.5580972784</v>
+        <v>55800.5413592784</v>
       </c>
       <c r="C366" t="n">
-        <v>6383.011542</v>
+        <v>6364.858966</v>
       </c>
       <c r="D366" t="n">
-        <v>150651.000427673</v>
+        <v>150522.677580673</v>
       </c>
       <c r="E366" t="n">
-        <v>113436.960117</v>
+        <v>113131.500792</v>
       </c>
       <c r="F366" t="n">
-        <v>181355.067327</v>
+        <v>182877.988271</v>
       </c>
       <c r="G366" t="n">
-        <v>383142.302918897</v>
+        <v>382144.115595897</v>
       </c>
       <c r="H366" t="n">
-        <v>107739.669195</v>
+        <v>107519.743191</v>
       </c>
       <c r="I366" t="n">
-        <v>50678.0599695668</v>
+        <v>51023.7811725668</v>
       </c>
       <c r="J366" t="n">
-        <v>113901.716444</v>
+        <v>114408.34576</v>
       </c>
       <c r="K366" t="n">
-        <v>474362.477426015</v>
+        <v>475492.886434015</v>
       </c>
       <c r="L366" t="n">
-        <v>53414.230243</v>
+        <v>53700.173388</v>
       </c>
       <c r="M366" t="n">
-        <v>81642.583968</v>
+        <v>82071.610198</v>
       </c>
       <c r="N366" t="n">
-        <v>682021.992892629</v>
+        <v>683439.614860629</v>
       </c>
       <c r="O366" t="n">
-        <v>121654.545833</v>
+        <v>121386.752727</v>
       </c>
       <c r="P366" t="n">
-        <v>560367.447059629</v>
+        <v>562052.862133629</v>
       </c>
       <c r="Q366" t="n">
-        <v>100082.088236454</v>
+        <v>101036.372793454</v>
       </c>
       <c r="R366" t="n">
-        <v>2682614.23064714</v>
+        <v>2688992.21557114</v>
       </c>
       <c r="S366" t="n">
-        <v>554184.48105</v>
+        <v>553981.609652</v>
       </c>
       <c r="T366" t="n">
-        <v>3236798.71169714</v>
+        <v>3242973.82522314</v>
       </c>
       <c r="U366" t="n">
-        <v>0.462341798932586</v>
+        <v>0.70119362268839</v>
       </c>
       <c r="V366" t="n">
-        <v>7.35126910885546</v>
+        <v>7.60649953599868</v>
       </c>
       <c r="W366" t="n">
-        <v>-1.95326713136301</v>
+        <v>-1.98915929082716</v>
       </c>
       <c r="X366" t="n">
-        <v>6.02933448469936</v>
+        <v>5.9905201186327</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.0403467499652477</v>
+        <v>0.231202145492015</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.12260198843224</v>
+        <v>7.32696879878982</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.828786238993704</v>
+        <v>0.829174813147349</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.171213761006296</v>
+        <v>0.170825186852651</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45935,6 +45935,92 @@
         <v>0.170825186852651</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B367" t="n">
+        <v>55744.4941422784</v>
+      </c>
+      <c r="C367" t="n">
+        <v>6369.224467</v>
+      </c>
+      <c r="D367" t="n">
+        <v>150000.249323673</v>
+      </c>
+      <c r="E367" t="n">
+        <v>113013.897598</v>
+      </c>
+      <c r="F367" t="n">
+        <v>182496.203238</v>
+      </c>
+      <c r="G367" t="n">
+        <v>380912.129016897</v>
+      </c>
+      <c r="H367" t="n">
+        <v>107475.306609</v>
+      </c>
+      <c r="I367" t="n">
+        <v>50875.8404015668</v>
+      </c>
+      <c r="J367" t="n">
+        <v>114350.264314</v>
+      </c>
+      <c r="K367" t="n">
+        <v>475278.839011015</v>
+      </c>
+      <c r="L367" t="n">
+        <v>53548.813892</v>
+      </c>
+      <c r="M367" t="n">
+        <v>81850.104089</v>
+      </c>
+      <c r="N367" t="n">
+        <v>683722.122363629</v>
+      </c>
+      <c r="O367" t="n">
+        <v>121916.402498</v>
+      </c>
+      <c r="P367" t="n">
+        <v>561805.719865629</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>99802.5246874537</v>
+      </c>
+      <c r="R367" t="n">
+        <v>2686296.93146414</v>
+      </c>
+      <c r="S367" t="n">
+        <v>552865.204053</v>
+      </c>
+      <c r="T367" t="n">
+        <v>3239162.13551714</v>
+      </c>
+      <c r="U367" t="n">
+        <v>-0.100233986970755</v>
+      </c>
+      <c r="V367" t="n">
+        <v>6.79690955783177</v>
+      </c>
+      <c r="W367" t="n">
+        <v>-0.201523945840254</v>
+      </c>
+      <c r="X367" t="n">
+        <v>4.4320871624709</v>
+      </c>
+      <c r="Y367" t="n">
+        <v>-0.117536863120937</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>6.38572716597847</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>0.829318453068194</v>
+      </c>
+      <c r="AB367" t="n">
+        <v>0.170681546931807</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="371">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -1125,6 +1125,9 @@
   <si>
     <t xml:space="preserve">127.50369999999999</t>
   </si>
+  <si>
+    <t xml:space="preserve">127.6391</t>
+  </si>
 </sst>
 </file>
 
@@ -14526,6 +14529,38 @@
         <v>-3.80546822085501</v>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B318" t="n">
+        <v>135.8179</v>
+      </c>
+      <c r="C318" t="n">
+        <v>139.2489</v>
+      </c>
+      <c r="D318"/>
+      <c r="E318"/>
+      <c r="F318"/>
+      <c r="G318" t="n">
+        <v>4.86135881792507</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0.284199567313737</v>
+      </c>
+      <c r="I318" t="n">
+        <v>5.34610155822677</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0.30542071343107</v>
+      </c>
+      <c r="K318"/>
+      <c r="L318"/>
+      <c r="M318"/>
+      <c r="N318"/>
+      <c r="O318"/>
+      <c r="P318"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -45940,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>55744.4941422784</v>
+        <v>55646.7473892784</v>
       </c>
       <c r="C367" t="n">
-        <v>6369.224467</v>
+        <v>6382.82283</v>
       </c>
       <c r="D367" t="n">
-        <v>150000.249323673</v>
+        <v>149873.177161673</v>
       </c>
       <c r="E367" t="n">
-        <v>113013.897598</v>
+        <v>115180.110931</v>
       </c>
       <c r="F367" t="n">
-        <v>182496.203238</v>
+        <v>182708.547645</v>
       </c>
       <c r="G367" t="n">
-        <v>380912.129016897</v>
+        <v>381236.565077897</v>
       </c>
       <c r="H367" t="n">
-        <v>107475.306609</v>
+        <v>108626.230389</v>
       </c>
       <c r="I367" t="n">
-        <v>50875.8404015668</v>
+        <v>50991.0589935668</v>
       </c>
       <c r="J367" t="n">
-        <v>114350.264314</v>
+        <v>114614.073719</v>
       </c>
       <c r="K367" t="n">
-        <v>475278.839011015</v>
+        <v>475531.212542015</v>
       </c>
       <c r="L367" t="n">
-        <v>53548.813892</v>
+        <v>53491.215214</v>
       </c>
       <c r="M367" t="n">
-        <v>81850.104089</v>
+        <v>81610.693582</v>
       </c>
       <c r="N367" t="n">
-        <v>683722.122363629</v>
+        <v>684287.293898629</v>
       </c>
       <c r="O367" t="n">
-        <v>121916.402498</v>
+        <v>122126.689381</v>
       </c>
       <c r="P367" t="n">
-        <v>561805.719865629</v>
+        <v>562160.604517629</v>
       </c>
       <c r="Q367" t="n">
-        <v>99802.5246874537</v>
+        <v>100474.078154454</v>
       </c>
       <c r="R367" t="n">
-        <v>2686296.93146414</v>
+        <v>2685949.65485114</v>
       </c>
       <c r="S367" t="n">
-        <v>552865.204053</v>
+        <v>558991.466575</v>
       </c>
       <c r="T367" t="n">
-        <v>3239162.13551714</v>
+        <v>3244941.12142614</v>
       </c>
       <c r="U367" t="n">
-        <v>-0.100233986970755</v>
+        <v>-0.113148736630075</v>
       </c>
       <c r="V367" t="n">
-        <v>6.79690955783177</v>
+        <v>6.7831031656211</v>
       </c>
       <c r="W367" t="n">
-        <v>-0.201523945840254</v>
+        <v>0.904336323753974</v>
       </c>
       <c r="X367" t="n">
-        <v>4.4320871624709</v>
+        <v>5.58929216829787</v>
       </c>
       <c r="Y367" t="n">
-        <v>-0.117536863120937</v>
+        <v>0.0606633389298006</v>
       </c>
       <c r="Z367" t="n">
-        <v>6.38572716597847</v>
+        <v>6.57552983484451</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.829318453068194</v>
+        <v>0.827734480948201</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.170681546931807</v>
+        <v>0.172265519051799</v>
       </c>
     </row>
   </sheetData>
@@ -60931,6 +60966,53 @@
         <v>148.8784</v>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B318" t="n">
+        <v>139.2489</v>
+      </c>
+      <c r="C318" t="n">
+        <v>135.8179</v>
+      </c>
+      <c r="D318" t="n">
+        <v>152.4179</v>
+      </c>
+      <c r="E318" t="n">
+        <v>141.5185</v>
+      </c>
+      <c r="F318" t="n">
+        <v>96.4347</v>
+      </c>
+      <c r="G318" t="s">
+        <v>370</v>
+      </c>
+      <c r="H318" t="n">
+        <v>126.0295</v>
+      </c>
+      <c r="I318" t="n">
+        <v>137.6188</v>
+      </c>
+      <c r="J318" t="n">
+        <v>146.9912</v>
+      </c>
+      <c r="K318" t="n">
+        <v>97.7694</v>
+      </c>
+      <c r="L318" t="n">
+        <v>121.7763</v>
+      </c>
+      <c r="M318" t="n">
+        <v>132.8489</v>
+      </c>
+      <c r="N318" t="n">
+        <v>154.8883</v>
+      </c>
+      <c r="O318" t="n">
+        <v>149.497</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45975,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>55646.7473892784</v>
+        <v>55633.0532602784</v>
       </c>
       <c r="C367" t="n">
-        <v>6382.82283</v>
+        <v>6351.023649</v>
       </c>
       <c r="D367" t="n">
-        <v>149873.177161673</v>
+        <v>150345.108179673</v>
       </c>
       <c r="E367" t="n">
-        <v>115180.110931</v>
+        <v>114868.485906</v>
       </c>
       <c r="F367" t="n">
-        <v>182708.547645</v>
+        <v>182499.250195</v>
       </c>
       <c r="G367" t="n">
-        <v>381236.565077897</v>
+        <v>381145.864398897</v>
       </c>
       <c r="H367" t="n">
-        <v>108626.230389</v>
+        <v>108413.196818</v>
       </c>
       <c r="I367" t="n">
-        <v>50991.0589935668</v>
+        <v>50909.4139405668</v>
       </c>
       <c r="J367" t="n">
-        <v>114614.073719</v>
+        <v>114658.598336</v>
       </c>
       <c r="K367" t="n">
-        <v>475531.212542015</v>
+        <v>475496.336370015</v>
       </c>
       <c r="L367" t="n">
-        <v>53491.215214</v>
+        <v>53542.92941</v>
       </c>
       <c r="M367" t="n">
-        <v>81610.693582</v>
+        <v>81389.847135</v>
       </c>
       <c r="N367" t="n">
-        <v>684287.293898629</v>
+        <v>684719.938884629</v>
       </c>
       <c r="O367" t="n">
-        <v>122126.689381</v>
+        <v>122605.80581</v>
       </c>
       <c r="P367" t="n">
-        <v>562160.604517629</v>
+        <v>562114.133074629</v>
       </c>
       <c r="Q367" t="n">
-        <v>100474.078154454</v>
+        <v>100941.154881454</v>
       </c>
       <c r="R367" t="n">
-        <v>2685949.65485114</v>
+        <v>2687553.78850114</v>
       </c>
       <c r="S367" t="n">
-        <v>558991.466575</v>
+        <v>558080.351748</v>
       </c>
       <c r="T367" t="n">
-        <v>3244941.12142614</v>
+        <v>3245634.14024914</v>
       </c>
       <c r="U367" t="n">
-        <v>-0.113148736630075</v>
+        <v>-0.0534931660147842</v>
       </c>
       <c r="V367" t="n">
-        <v>6.7831031656211</v>
+        <v>6.84687739486995</v>
       </c>
       <c r="W367" t="n">
-        <v>0.904336323753974</v>
+        <v>0.739869704081819</v>
       </c>
       <c r="X367" t="n">
-        <v>5.58929216829787</v>
+        <v>5.41718941643223</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.0606633389298006</v>
+        <v>0.0820331945114106</v>
       </c>
       <c r="Z367" t="n">
-        <v>6.57552983484451</v>
+        <v>6.59829106393399</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.827734480948201</v>
+        <v>0.828051983793478</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.172265519051799</v>
+        <v>0.171948016206522</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45889,85 +45889,85 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55800.5413592784</v>
+        <v>55807.5911762784</v>
       </c>
       <c r="C366" t="n">
-        <v>6364.858966</v>
+        <v>6372.703946</v>
       </c>
       <c r="D366" t="n">
-        <v>150522.677580673</v>
+        <v>150087.012827673</v>
       </c>
       <c r="E366" t="n">
-        <v>113131.500792</v>
+        <v>113061.442669</v>
       </c>
       <c r="F366" t="n">
-        <v>182877.988271</v>
+        <v>180082.056306</v>
       </c>
       <c r="G366" t="n">
-        <v>382144.115595897</v>
+        <v>381422.501902897</v>
       </c>
       <c r="H366" t="n">
-        <v>107519.743191</v>
+        <v>110132.565726</v>
       </c>
       <c r="I366" t="n">
-        <v>51023.7811725668</v>
+        <v>51657.5166875668</v>
       </c>
       <c r="J366" t="n">
-        <v>114408.34576</v>
+        <v>114868.621509</v>
       </c>
       <c r="K366" t="n">
-        <v>475492.886434015</v>
+        <v>475706.717032015</v>
       </c>
       <c r="L366" t="n">
-        <v>53700.173388</v>
+        <v>53685.543524</v>
       </c>
       <c r="M366" t="n">
-        <v>82071.610198</v>
+        <v>81918.321283</v>
       </c>
       <c r="N366" t="n">
-        <v>683439.614860629</v>
+        <v>684135.131062629</v>
       </c>
       <c r="O366" t="n">
-        <v>121386.752727</v>
+        <v>121926.615668</v>
       </c>
       <c r="P366" t="n">
-        <v>562052.862133629</v>
+        <v>562208.515394629</v>
       </c>
       <c r="Q366" t="n">
-        <v>101036.372793454</v>
+        <v>100875.605274454</v>
       </c>
       <c r="R366" t="n">
-        <v>2688992.21557114</v>
+        <v>2689549.03058814</v>
       </c>
       <c r="S366" t="n">
-        <v>553981.609652</v>
+        <v>554399.431401</v>
       </c>
       <c r="T366" t="n">
-        <v>3242973.82522314</v>
+        <v>3243948.46198914</v>
       </c>
       <c r="U366" t="n">
-        <v>0.70119362268839</v>
+        <v>0.722046021038314</v>
       </c>
       <c r="V366" t="n">
-        <v>7.60649953599868</v>
+        <v>7.62878182990845</v>
       </c>
       <c r="W366" t="n">
-        <v>-1.98915929082716</v>
+        <v>-1.91523795450014</v>
       </c>
       <c r="X366" t="n">
-        <v>5.9905201186327</v>
+        <v>6.07045985620127</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.231202145492015</v>
+        <v>0.261325427385795</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.32696879878982</v>
+        <v>7.35922462798</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.829174813147349</v>
+        <v>0.829097336811248</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.170825186852651</v>
+        <v>0.170902663188752</v>
       </c>
     </row>
     <row r="367">
@@ -45975,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>55633.0532602784</v>
+        <v>55553.2994952784</v>
       </c>
       <c r="C367" t="n">
-        <v>6351.023649</v>
+        <v>6333.875539</v>
       </c>
       <c r="D367" t="n">
-        <v>150345.108179673</v>
+        <v>149451.133729673</v>
       </c>
       <c r="E367" t="n">
-        <v>114868.485906</v>
+        <v>114835.596113</v>
       </c>
       <c r="F367" t="n">
-        <v>182499.250195</v>
+        <v>180019.762276</v>
       </c>
       <c r="G367" t="n">
-        <v>381145.864398897</v>
+        <v>380028.708381897</v>
       </c>
       <c r="H367" t="n">
-        <v>108413.196818</v>
+        <v>111030.09715</v>
       </c>
       <c r="I367" t="n">
-        <v>50909.4139405668</v>
+        <v>51510.9116855668</v>
       </c>
       <c r="J367" t="n">
-        <v>114658.598336</v>
+        <v>114982.636716</v>
       </c>
       <c r="K367" t="n">
-        <v>475496.336370015</v>
+        <v>475456.702098015</v>
       </c>
       <c r="L367" t="n">
-        <v>53542.92941</v>
+        <v>53503.997157</v>
       </c>
       <c r="M367" t="n">
-        <v>81389.847135</v>
+        <v>81707.905189</v>
       </c>
       <c r="N367" t="n">
-        <v>684719.938884629</v>
+        <v>686064.594530629</v>
       </c>
       <c r="O367" t="n">
-        <v>122605.80581</v>
+        <v>123935.490517</v>
       </c>
       <c r="P367" t="n">
-        <v>562114.133074629</v>
+        <v>562129.104013629</v>
       </c>
       <c r="Q367" t="n">
-        <v>100941.154881454</v>
+        <v>101144.138035454</v>
       </c>
       <c r="R367" t="n">
-        <v>2687553.78850114</v>
+        <v>2688540.41215514</v>
       </c>
       <c r="S367" t="n">
-        <v>558080.351748</v>
+        <v>559147.540472</v>
       </c>
       <c r="T367" t="n">
-        <v>3245634.14024914</v>
+        <v>3247687.95262714</v>
       </c>
       <c r="U367" t="n">
-        <v>-0.0534931660147842</v>
+        <v>-0.0375013960158044</v>
       </c>
       <c r="V367" t="n">
-        <v>6.84687739486995</v>
+        <v>6.88610178436677</v>
       </c>
       <c r="W367" t="n">
-        <v>0.739869704081819</v>
+        <v>0.856441908499295</v>
       </c>
       <c r="X367" t="n">
-        <v>5.41718941643223</v>
+        <v>5.6187733559288</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.0820331945114106</v>
+        <v>0.115275895465583</v>
       </c>
       <c r="Z367" t="n">
-        <v>6.59829106393399</v>
+        <v>6.66574564451836</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.828051983793478</v>
+        <v>0.827832122843055</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.171948016206522</v>
+        <v>0.172167877156945</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45459,13 +45459,13 @@
         <v>45992</v>
       </c>
       <c r="B361" t="n">
-        <v>58642.5451262784</v>
+        <v>58116.8367866938</v>
       </c>
       <c r="C361" t="n">
         <v>6792.944137</v>
       </c>
       <c r="D361" t="n">
-        <v>146934.314206673</v>
+        <v>148643.202920438</v>
       </c>
       <c r="E361" t="n">
         <v>109565.342563</v>
@@ -45474,19 +45474,19 @@
         <v>167401.351336</v>
       </c>
       <c r="G361" t="n">
-        <v>376309.878111897</v>
+        <v>370632.106567849</v>
       </c>
       <c r="H361" t="n">
         <v>111736.78418</v>
       </c>
       <c r="I361" t="n">
-        <v>48902.1027905668</v>
+        <v>50103.1259526799</v>
       </c>
       <c r="J361" t="n">
         <v>113013.780635</v>
       </c>
       <c r="K361" t="n">
-        <v>461356.466416015</v>
+        <v>463704.405771236</v>
       </c>
       <c r="L361" t="n">
         <v>47954.55983</v>
@@ -45495,31 +45495,31 @@
         <v>84025.302035</v>
       </c>
       <c r="N361" t="n">
-        <v>676050.698294629</v>
+        <v>675780.101959025</v>
       </c>
       <c r="O361" t="n">
         <v>125578.277228</v>
       </c>
       <c r="P361" t="n">
-        <v>550472.421066629</v>
+        <v>550201.824731025</v>
       </c>
       <c r="Q361" t="n">
-        <v>100730.333392454</v>
+        <v>101946.55838059</v>
       </c>
       <c r="R361" t="n">
-        <v>2594553.05574414</v>
+        <v>2594282.45940854</v>
       </c>
       <c r="S361" t="n">
         <v>590914.045605</v>
       </c>
       <c r="T361" t="n">
-        <v>3185467.10134914</v>
+        <v>3185196.50501354</v>
       </c>
       <c r="U361" t="n">
-        <v>-0.562123058943731</v>
+        <v>-0.572493833617593</v>
       </c>
       <c r="V361" t="n">
-        <v>7.3396306505328</v>
+        <v>7.32843577029907</v>
       </c>
       <c r="W361" t="n">
         <v>1.35005778749251</v>
@@ -45528,16 +45528,16 @@
         <v>15.0095129731572</v>
       </c>
       <c r="Y361" t="n">
-        <v>-0.212877694542846</v>
+        <v>-0.221354325685841</v>
       </c>
       <c r="Z361" t="n">
-        <v>8.68416655620494</v>
+        <v>8.67493414655431</v>
       </c>
       <c r="AA361" t="n">
-        <v>0.814496892667725</v>
+        <v>0.81448113336967</v>
       </c>
       <c r="AB361" t="n">
-        <v>0.185503107332275</v>
+        <v>0.18551886663033</v>
       </c>
     </row>
     <row r="362">
@@ -45545,13 +45545,13 @@
         <v>46023</v>
       </c>
       <c r="B362" t="n">
-        <v>58850.3722232784</v>
+        <v>58279.360246129</v>
       </c>
       <c r="C362" t="n">
         <v>6770.43739</v>
       </c>
       <c r="D362" t="n">
-        <v>147317.833824673</v>
+        <v>148981.577288899</v>
       </c>
       <c r="E362" t="n">
         <v>111629.220653</v>
@@ -45560,19 +45560,19 @@
         <v>166121.723833</v>
       </c>
       <c r="G362" t="n">
-        <v>375622.078352897</v>
+        <v>369535.611295477</v>
       </c>
       <c r="H362" t="n">
         <v>112264.706558</v>
       </c>
       <c r="I362" t="n">
-        <v>48558.3089095668</v>
+        <v>49705.93870017</v>
       </c>
       <c r="J362" t="n">
         <v>113376.854688</v>
       </c>
       <c r="K362" t="n">
-        <v>462525.406099015</v>
+        <v>464542.802235703</v>
       </c>
       <c r="L362" t="n">
         <v>48112.946054</v>
@@ -45581,31 +45581,31 @@
         <v>83431.795498</v>
       </c>
       <c r="N362" t="n">
-        <v>680067.373106629</v>
+        <v>679319.17289657</v>
       </c>
       <c r="O362" t="n">
         <v>123980.352047</v>
       </c>
       <c r="P362" t="n">
-        <v>556087.021059629</v>
+        <v>555338.82084957</v>
       </c>
       <c r="Q362" t="n">
-        <v>101097.079339454</v>
+        <v>102121.404658955</v>
       </c>
       <c r="R362" t="n">
-        <v>2605613.05922614</v>
+        <v>2603312.27448247</v>
       </c>
       <c r="S362" t="n">
         <v>590200.45041</v>
       </c>
       <c r="T362" t="n">
-        <v>3195813.50963614</v>
+        <v>3193512.72489247</v>
       </c>
       <c r="U362" t="n">
-        <v>0.426277792142815</v>
+        <v>0.34806599571251</v>
       </c>
       <c r="V362" t="n">
-        <v>7.23545283168325</v>
+        <v>7.14076275750593</v>
       </c>
       <c r="W362" t="n">
         <v>-0.120761251201829</v>
@@ -45614,16 +45614,16 @@
         <v>11.8979380429352</v>
       </c>
       <c r="Y362" t="n">
-        <v>0.324800349770316</v>
+        <v>0.261089696219541</v>
       </c>
       <c r="Z362" t="n">
-        <v>8.06703800959865</v>
+        <v>7.98923653851897</v>
       </c>
       <c r="AA362" t="n">
-        <v>0.815320747399557</v>
+        <v>0.815187694162117</v>
       </c>
       <c r="AB362" t="n">
-        <v>0.184679252600443</v>
+        <v>0.184812305837883</v>
       </c>
     </row>
     <row r="363">
@@ -45631,13 +45631,13 @@
         <v>46054</v>
       </c>
       <c r="B363" t="n">
-        <v>57092.3142342784</v>
+        <v>56553.6626607719</v>
       </c>
       <c r="C363" t="n">
         <v>6560.018498</v>
       </c>
       <c r="D363" t="n">
-        <v>149381.979606673</v>
+        <v>151077.970337922</v>
       </c>
       <c r="E363" t="n">
         <v>111405.474897</v>
@@ -45646,19 +45646,19 @@
         <v>173028.328062</v>
       </c>
       <c r="G363" t="n">
-        <v>369932.610847897</v>
+        <v>364138.075133978</v>
       </c>
       <c r="H363" t="n">
         <v>105040.624554</v>
       </c>
       <c r="I363" t="n">
-        <v>49292.8063295668</v>
+        <v>50478.5750235074</v>
       </c>
       <c r="J363" t="n">
         <v>113289.576035</v>
       </c>
       <c r="K363" t="n">
-        <v>463779.994928015</v>
+        <v>466033.498197554</v>
       </c>
       <c r="L363" t="n">
         <v>48623.639338</v>
@@ -45667,31 +45667,31 @@
         <v>83068.91589</v>
       </c>
       <c r="N363" t="n">
-        <v>683300.116653629</v>
+        <v>682893.069052711</v>
       </c>
       <c r="O363" t="n">
         <v>123895.495526</v>
       </c>
       <c r="P363" t="n">
-        <v>559404.621127629</v>
+        <v>558997.573526711</v>
       </c>
       <c r="Q363" t="n">
-        <v>101258.312157454</v>
+        <v>102419.711475198</v>
       </c>
       <c r="R363" t="n">
-        <v>2637531.37185414</v>
+        <v>2636680.75137735</v>
       </c>
       <c r="S363" t="n">
         <v>560823.456831</v>
       </c>
       <c r="T363" t="n">
-        <v>3198354.82868514</v>
+        <v>3197504.20820835</v>
       </c>
       <c r="U363" t="n">
-        <v>1.22498283139092</v>
+        <v>1.2817700443376</v>
       </c>
       <c r="V363" t="n">
-        <v>7.91809601717455</v>
+        <v>7.88329175161477</v>
       </c>
       <c r="W363" t="n">
         <v>-4.97746037953587</v>
@@ -45700,16 +45700,16 @@
         <v>3.75530954086698</v>
       </c>
       <c r="Y363" t="n">
-        <v>0.079520254900256</v>
+        <v>0.124987236930929</v>
       </c>
       <c r="Z363" t="n">
-        <v>7.16417998879939</v>
+        <v>7.13567907168442</v>
       </c>
       <c r="AA363" t="n">
-        <v>0.824652520789397</v>
+        <v>0.824605873733863</v>
       </c>
       <c r="AB363" t="n">
-        <v>0.175347479210603</v>
+        <v>0.175394126266137</v>
       </c>
     </row>
     <row r="364">
@@ -45717,13 +45717,13 @@
         <v>46082</v>
       </c>
       <c r="B364" t="n">
-        <v>55673.7888672784</v>
+        <v>55181.2244564345</v>
       </c>
       <c r="C364" t="n">
         <v>6700.952601</v>
       </c>
       <c r="D364" t="n">
-        <v>148346.734202673</v>
+        <v>150088.650969243</v>
       </c>
       <c r="E364" t="n">
         <v>114183.676736</v>
@@ -45732,19 +45732,19 @@
         <v>178366.216207</v>
       </c>
       <c r="G364" t="n">
-        <v>378984.875609897</v>
+        <v>373606.103786401</v>
       </c>
       <c r="H364" t="n">
         <v>108166.213468</v>
       </c>
       <c r="I364" t="n">
-        <v>49691.7051315668</v>
+        <v>50931.7906338291</v>
       </c>
       <c r="J364" t="n">
         <v>113565.918651</v>
       </c>
       <c r="K364" t="n">
-        <v>469350.603929015</v>
+        <v>471940.367152466</v>
       </c>
       <c r="L364" t="n">
         <v>49903.790045</v>
@@ -45753,31 +45753,31 @@
         <v>83182.145248</v>
       </c>
       <c r="N364" t="n">
-        <v>682352.881240629</v>
+        <v>682431.697659323</v>
       </c>
       <c r="O364" t="n">
         <v>121617.585296</v>
       </c>
       <c r="P364" t="n">
-        <v>560735.295944629</v>
+        <v>560814.112363323</v>
       </c>
       <c r="Q364" t="n">
-        <v>98202.6832364537</v>
+        <v>99559.3011220372</v>
       </c>
       <c r="R364" t="n">
-        <v>2649137.49192114</v>
+        <v>2650352.17190206</v>
       </c>
       <c r="S364" t="n">
         <v>569887.574493</v>
       </c>
       <c r="T364" t="n">
-        <v>3219025.06641414</v>
+        <v>3220239.74639506</v>
       </c>
       <c r="U364" t="n">
-        <v>0.440037232953983</v>
+        <v>0.518508754522529</v>
       </c>
       <c r="V364" t="n">
-        <v>7.81238491153222</v>
+        <v>7.86181894281448</v>
       </c>
       <c r="W364" t="n">
         <v>1.61621586108718</v>
@@ -45786,16 +45786,16 @@
         <v>2.82904974199256</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.646277190498523</v>
+        <v>0.711040133374574</v>
       </c>
       <c r="Z364" t="n">
-        <v>6.89526196249368</v>
+        <v>6.93559825440861</v>
       </c>
       <c r="AA364" t="n">
-        <v>0.822962678843681</v>
+        <v>0.823029457626262</v>
       </c>
       <c r="AB364" t="n">
-        <v>0.177037321156319</v>
+        <v>0.176970542373738</v>
       </c>
     </row>
     <row r="365">
@@ -45803,13 +45803,13 @@
         <v>46113</v>
       </c>
       <c r="B365" t="n">
-        <v>55879.6528772784</v>
+        <v>55387.0884664345</v>
       </c>
       <c r="C365" t="n">
         <v>6506.435252</v>
       </c>
       <c r="D365" t="n">
-        <v>149445.968778673</v>
+        <v>151187.885545243</v>
       </c>
       <c r="E365" t="n">
         <v>114088.220543</v>
@@ -45818,19 +45818,19 @@
         <v>180773.744496</v>
       </c>
       <c r="G365" t="n">
-        <v>386112.749019897</v>
+        <v>380733.977196401</v>
       </c>
       <c r="H365" t="n">
         <v>109315.368448</v>
       </c>
       <c r="I365" t="n">
-        <v>50824.2013285668</v>
+        <v>52064.2868308291</v>
       </c>
       <c r="J365" t="n">
         <v>112557.817685</v>
       </c>
       <c r="K365" t="n">
-        <v>473128.666056015</v>
+        <v>475718.429279466</v>
       </c>
       <c r="L365" t="n">
         <v>53322.242909</v>
@@ -45839,31 +45839,31 @@
         <v>82005.887614</v>
       </c>
       <c r="N365" t="n">
-        <v>681425.124617629</v>
+        <v>681503.941036323</v>
       </c>
       <c r="O365" t="n">
         <v>120538.566978</v>
       </c>
       <c r="P365" t="n">
-        <v>560886.557639629</v>
+        <v>560965.374058323</v>
       </c>
       <c r="Q365" t="n">
-        <v>98682.0910644537</v>
+        <v>100038.708950037</v>
       </c>
       <c r="R365" t="n">
-        <v>2670268.46339714</v>
+        <v>2671483.14337806</v>
       </c>
       <c r="S365" t="n">
         <v>565224.83191</v>
       </c>
       <c r="T365" t="n">
-        <v>3235493.29530714</v>
+        <v>3236707.97528806</v>
       </c>
       <c r="U365" t="n">
-        <v>0.79765476652085</v>
+        <v>0.797289194244533</v>
       </c>
       <c r="V365" t="n">
-        <v>7.89665787629941</v>
+        <v>7.94573905001896</v>
       </c>
       <c r="W365" t="n">
         <v>-0.818186391789344</v>
@@ -45872,16 +45872,16 @@
         <v>8.32564400044988</v>
       </c>
       <c r="Y365" t="n">
-        <v>0.51159057643948</v>
+        <v>0.511397603592578</v>
       </c>
       <c r="Z365" t="n">
-        <v>7.97135454680917</v>
+        <v>8.01188952274943</v>
       </c>
       <c r="AA365" t="n">
-        <v>0.825304897794157</v>
+        <v>0.825370457815337</v>
       </c>
       <c r="AB365" t="n">
-        <v>0.174695102205843</v>
+        <v>0.174629542184663</v>
       </c>
     </row>
     <row r="366">
@@ -45889,13 +45889,13 @@
         <v>46143</v>
       </c>
       <c r="B366" t="n">
-        <v>55807.5911762784</v>
+        <v>55315.0267654345</v>
       </c>
       <c r="C366" t="n">
         <v>6372.703946</v>
       </c>
       <c r="D366" t="n">
-        <v>150087.012827673</v>
+        <v>151828.929594243</v>
       </c>
       <c r="E366" t="n">
         <v>113061.442669</v>
@@ -45904,19 +45904,19 @@
         <v>180082.056306</v>
       </c>
       <c r="G366" t="n">
-        <v>381422.501902897</v>
+        <v>376043.730079401</v>
       </c>
       <c r="H366" t="n">
         <v>110132.565726</v>
       </c>
       <c r="I366" t="n">
-        <v>51657.5166875668</v>
+        <v>52897.6021898291</v>
       </c>
       <c r="J366" t="n">
         <v>114868.621509</v>
       </c>
       <c r="K366" t="n">
-        <v>475706.717032015</v>
+        <v>478296.480255466</v>
       </c>
       <c r="L366" t="n">
         <v>53685.543524</v>
@@ -45925,31 +45925,31 @@
         <v>81918.321283</v>
       </c>
       <c r="N366" t="n">
-        <v>684135.131062629</v>
+        <v>684213.947481323</v>
       </c>
       <c r="O366" t="n">
         <v>121926.615668</v>
       </c>
       <c r="P366" t="n">
-        <v>562208.515394629</v>
+        <v>562287.331813323</v>
       </c>
       <c r="Q366" t="n">
-        <v>100875.605274454</v>
+        <v>102232.223160037</v>
       </c>
       <c r="R366" t="n">
-        <v>2689549.03058814</v>
+        <v>2690763.71056906</v>
       </c>
       <c r="S366" t="n">
         <v>554399.431401</v>
       </c>
       <c r="T366" t="n">
-        <v>3243948.46198914</v>
+        <v>3245163.14197006</v>
       </c>
       <c r="U366" t="n">
-        <v>0.722046021038314</v>
+        <v>0.721717718443848</v>
       </c>
       <c r="V366" t="n">
-        <v>7.62878182990845</v>
+        <v>7.67739017471725</v>
       </c>
       <c r="W366" t="n">
         <v>-1.91523795450014</v>
@@ -45958,16 +45958,16 @@
         <v>6.07045985620127</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.261325427385795</v>
+        <v>0.261227356516391</v>
       </c>
       <c r="Z366" t="n">
-        <v>7.35922462798</v>
+        <v>7.39942474288631</v>
       </c>
       <c r="AA366" t="n">
-        <v>0.829097336811248</v>
+        <v>0.829161306489991</v>
       </c>
       <c r="AB366" t="n">
-        <v>0.170902663188752</v>
+        <v>0.170838693510009</v>
       </c>
     </row>
     <row r="367">
@@ -45975,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>55553.2994952784</v>
+        <v>54800.5837174345</v>
       </c>
       <c r="C367" t="n">
-        <v>6333.875539</v>
+        <v>6357.174939</v>
       </c>
       <c r="D367" t="n">
-        <v>149451.133729673</v>
+        <v>150957.530692243</v>
       </c>
       <c r="E367" t="n">
-        <v>114835.596113</v>
+        <v>115145.778238</v>
       </c>
       <c r="F367" t="n">
-        <v>180019.762276</v>
+        <v>180103.104618</v>
       </c>
       <c r="G367" t="n">
-        <v>380028.708381897</v>
+        <v>376540.025620401</v>
       </c>
       <c r="H367" t="n">
-        <v>111030.09715</v>
+        <v>111893.185663</v>
       </c>
       <c r="I367" t="n">
-        <v>51510.9116855668</v>
+        <v>52859.8793538291</v>
       </c>
       <c r="J367" t="n">
-        <v>114982.636716</v>
+        <v>115542.24534</v>
       </c>
       <c r="K367" t="n">
-        <v>475456.702098015</v>
+        <v>478409.785842466</v>
       </c>
       <c r="L367" t="n">
-        <v>53503.997157</v>
+        <v>54448.48621</v>
       </c>
       <c r="M367" t="n">
-        <v>81707.905189</v>
+        <v>81867.185148</v>
       </c>
       <c r="N367" t="n">
-        <v>686064.594530629</v>
+        <v>686440.481406323</v>
       </c>
       <c r="O367" t="n">
-        <v>123935.490517</v>
+        <v>123625.988877</v>
       </c>
       <c r="P367" t="n">
-        <v>562129.104013629</v>
+        <v>562814.492529323</v>
       </c>
       <c r="Q367" t="n">
-        <v>101144.138035454</v>
+        <v>102352.297831037</v>
       </c>
       <c r="R367" t="n">
-        <v>2688540.41215514</v>
+        <v>2691707.69254406</v>
       </c>
       <c r="S367" t="n">
-        <v>559147.540472</v>
+        <v>562450.533482</v>
       </c>
       <c r="T367" t="n">
-        <v>3247687.95262714</v>
+        <v>3254158.22602606</v>
       </c>
       <c r="U367" t="n">
-        <v>-0.0375013960158044</v>
+        <v>0.0350823066065598</v>
       </c>
       <c r="V367" t="n">
-        <v>6.88610178436677</v>
+        <v>7.01202075977012</v>
       </c>
       <c r="W367" t="n">
-        <v>0.856441908499295</v>
+        <v>1.45222047949334</v>
       </c>
       <c r="X367" t="n">
-        <v>5.6187733559288</v>
+        <v>6.2426839427927</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.115275895465583</v>
+        <v>0.277184340585701</v>
       </c>
       <c r="Z367" t="n">
-        <v>6.66574564451836</v>
+        <v>6.87825267927233</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.827832122843055</v>
+        <v>0.827159438965309</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.172167877156945</v>
+        <v>0.172840561034692</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45975,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54800.5837174345</v>
+        <v>54774.3910944345</v>
       </c>
       <c r="C367" t="n">
-        <v>6357.174939</v>
+        <v>6375.357777</v>
       </c>
       <c r="D367" t="n">
-        <v>150957.530692243</v>
+        <v>151538.422846243</v>
       </c>
       <c r="E367" t="n">
-        <v>115145.778238</v>
+        <v>116543.007163</v>
       </c>
       <c r="F367" t="n">
-        <v>180103.104618</v>
+        <v>180918.227833</v>
       </c>
       <c r="G367" t="n">
-        <v>376540.025620401</v>
+        <v>379587.388799401</v>
       </c>
       <c r="H367" t="n">
-        <v>111893.185663</v>
+        <v>112561.159216</v>
       </c>
       <c r="I367" t="n">
-        <v>52859.8793538291</v>
+        <v>52957.1825358291</v>
       </c>
       <c r="J367" t="n">
-        <v>115542.24534</v>
+        <v>116174.651943</v>
       </c>
       <c r="K367" t="n">
-        <v>478409.785842466</v>
+        <v>479011.594243466</v>
       </c>
       <c r="L367" t="n">
-        <v>54448.48621</v>
+        <v>54673.45539</v>
       </c>
       <c r="M367" t="n">
-        <v>81867.185148</v>
+        <v>81952.329689</v>
       </c>
       <c r="N367" t="n">
-        <v>686440.481406323</v>
+        <v>686888.134075323</v>
       </c>
       <c r="O367" t="n">
-        <v>123625.988877</v>
+        <v>123622.811755</v>
       </c>
       <c r="P367" t="n">
-        <v>562814.492529323</v>
+        <v>563265.322320323</v>
       </c>
       <c r="Q367" t="n">
-        <v>102352.297831037</v>
+        <v>103482.666484037</v>
       </c>
       <c r="R367" t="n">
-        <v>2691707.69254406</v>
+        <v>2696500.72006506</v>
       </c>
       <c r="S367" t="n">
-        <v>562450.533482</v>
+        <v>567825.3831</v>
       </c>
       <c r="T367" t="n">
-        <v>3254158.22602606</v>
+        <v>3264326.10316506</v>
       </c>
       <c r="U367" t="n">
-        <v>0.0350823066065598</v>
+        <v>0.213211196266139</v>
       </c>
       <c r="V367" t="n">
-        <v>7.01202075977012</v>
+        <v>7.20257323394855</v>
       </c>
       <c r="W367" t="n">
-        <v>1.45222047949334</v>
+        <v>2.42171094315011</v>
       </c>
       <c r="X367" t="n">
-        <v>6.2426839427927</v>
+        <v>7.25795269126388</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.277184340585701</v>
+        <v>0.590508407640988</v>
       </c>
       <c r="Z367" t="n">
-        <v>6.87825267927233</v>
+        <v>7.2122023112793</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.827159438965309</v>
+        <v>0.826051269035455</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.172840561034692</v>
+        <v>0.173948730964545</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45975,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54774.3910944345</v>
+        <v>54692.6112984345</v>
       </c>
       <c r="C367" t="n">
-        <v>6375.357777</v>
+        <v>6333.36766</v>
       </c>
       <c r="D367" t="n">
-        <v>151538.422846243</v>
+        <v>151181.976137243</v>
       </c>
       <c r="E367" t="n">
-        <v>116543.007163</v>
+        <v>115883.587651</v>
       </c>
       <c r="F367" t="n">
-        <v>180918.227833</v>
+        <v>180656.743555</v>
       </c>
       <c r="G367" t="n">
-        <v>379587.388799401</v>
+        <v>377246.264828401</v>
       </c>
       <c r="H367" t="n">
-        <v>112561.159216</v>
+        <v>111603.080206</v>
       </c>
       <c r="I367" t="n">
-        <v>52957.1825358291</v>
+        <v>52696.7534468291</v>
       </c>
       <c r="J367" t="n">
-        <v>116174.651943</v>
+        <v>115692.775212</v>
       </c>
       <c r="K367" t="n">
-        <v>479011.594243466</v>
+        <v>478721.358021466</v>
       </c>
       <c r="L367" t="n">
-        <v>54673.45539</v>
+        <v>54724.337901</v>
       </c>
       <c r="M367" t="n">
-        <v>81952.329689</v>
+        <v>81709.410102</v>
       </c>
       <c r="N367" t="n">
-        <v>686888.134075323</v>
+        <v>686907.933612323</v>
       </c>
       <c r="O367" t="n">
-        <v>123622.811755</v>
+        <v>124130.35453</v>
       </c>
       <c r="P367" t="n">
-        <v>563265.322320323</v>
+        <v>562777.579082323</v>
       </c>
       <c r="Q367" t="n">
-        <v>103482.666484037</v>
+        <v>102952.428998037</v>
       </c>
       <c r="R367" t="n">
-        <v>2696500.72006506</v>
+        <v>2696157.37043806</v>
       </c>
       <c r="S367" t="n">
-        <v>567825.3831</v>
+        <v>561753.191804</v>
       </c>
       <c r="T367" t="n">
-        <v>3264326.10316506</v>
+        <v>3257910.56224206</v>
       </c>
       <c r="U367" t="n">
-        <v>0.213211196266139</v>
+        <v>0.200450892354986</v>
       </c>
       <c r="V367" t="n">
-        <v>7.20257323394855</v>
+        <v>7.18892296370779</v>
       </c>
       <c r="W367" t="n">
-        <v>2.42171094315011</v>
+        <v>1.3264372195362</v>
       </c>
       <c r="X367" t="n">
-        <v>7.25795269126388</v>
+        <v>6.11096133416216</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.590508407640988</v>
+        <v>0.392812925400765</v>
       </c>
       <c r="Z367" t="n">
-        <v>7.2122023112793</v>
+        <v>7.00149288776122</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.826051269035455</v>
+        <v>0.827572555761811</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.173948730964545</v>
+        <v>0.172427444238189</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45975,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54692.6112984345</v>
+        <v>54628.2915894345</v>
       </c>
       <c r="C367" t="n">
-        <v>6333.36766</v>
+        <v>6305.251594</v>
       </c>
       <c r="D367" t="n">
-        <v>151181.976137243</v>
+        <v>150981.588367243</v>
       </c>
       <c r="E367" t="n">
-        <v>115883.587651</v>
+        <v>115912.900453</v>
       </c>
       <c r="F367" t="n">
-        <v>180656.743555</v>
+        <v>180285.933611</v>
       </c>
       <c r="G367" t="n">
-        <v>377246.264828401</v>
+        <v>377263.517884401</v>
       </c>
       <c r="H367" t="n">
-        <v>111603.080206</v>
+        <v>111653.185385</v>
       </c>
       <c r="I367" t="n">
-        <v>52696.7534468291</v>
+        <v>52731.4774088291</v>
       </c>
       <c r="J367" t="n">
-        <v>115692.775212</v>
+        <v>116068.77867</v>
       </c>
       <c r="K367" t="n">
-        <v>478721.358021466</v>
+        <v>479050.677189466</v>
       </c>
       <c r="L367" t="n">
-        <v>54724.337901</v>
+        <v>54818.937234</v>
       </c>
       <c r="M367" t="n">
-        <v>81709.410102</v>
+        <v>81882.127301</v>
       </c>
       <c r="N367" t="n">
-        <v>686907.933612323</v>
+        <v>687214.649297323</v>
       </c>
       <c r="O367" t="n">
-        <v>124130.35453</v>
+        <v>123669.405416</v>
       </c>
       <c r="P367" t="n">
-        <v>562777.579082323</v>
+        <v>563545.243881323</v>
       </c>
       <c r="Q367" t="n">
-        <v>102952.428998037</v>
+        <v>103019.173313037</v>
       </c>
       <c r="R367" t="n">
-        <v>2696157.37043806</v>
+        <v>2696768.06902006</v>
       </c>
       <c r="S367" t="n">
-        <v>561753.191804</v>
+        <v>562263.069575</v>
       </c>
       <c r="T367" t="n">
-        <v>3257910.56224206</v>
+        <v>3259031.13859506</v>
       </c>
       <c r="U367" t="n">
-        <v>0.200450892354986</v>
+        <v>0.223146998282142</v>
       </c>
       <c r="V367" t="n">
-        <v>7.18892296370779</v>
+        <v>7.21320200764557</v>
       </c>
       <c r="W367" t="n">
-        <v>1.3264372195362</v>
+        <v>1.41840660877448</v>
       </c>
       <c r="X367" t="n">
-        <v>6.11096133416216</v>
+        <v>6.20727341789058</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.392812925400765</v>
+        <v>0.427343588543949</v>
       </c>
       <c r="Z367" t="n">
-        <v>7.00149288776122</v>
+        <v>7.03829664292117</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.827572555761811</v>
+        <v>0.827475392021757</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.172427444238189</v>
+        <v>0.172524607978243</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45975,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54628.2915894345</v>
+        <v>54692.6112984345</v>
       </c>
       <c r="C367" t="n">
-        <v>6305.251594</v>
+        <v>6333.36766</v>
       </c>
       <c r="D367" t="n">
-        <v>150981.588367243</v>
+        <v>151181.976137243</v>
       </c>
       <c r="E367" t="n">
-        <v>115912.900453</v>
+        <v>115883.587651</v>
       </c>
       <c r="F367" t="n">
-        <v>180285.933611</v>
+        <v>180656.743555</v>
       </c>
       <c r="G367" t="n">
-        <v>377263.517884401</v>
+        <v>377246.264828401</v>
       </c>
       <c r="H367" t="n">
-        <v>111653.185385</v>
+        <v>111603.080206</v>
       </c>
       <c r="I367" t="n">
-        <v>52731.4774088291</v>
+        <v>52696.7534468291</v>
       </c>
       <c r="J367" t="n">
-        <v>116068.77867</v>
+        <v>115692.775212</v>
       </c>
       <c r="K367" t="n">
-        <v>479050.677189466</v>
+        <v>478721.358021466</v>
       </c>
       <c r="L367" t="n">
-        <v>54818.937234</v>
+        <v>54724.337901</v>
       </c>
       <c r="M367" t="n">
-        <v>81882.127301</v>
+        <v>81709.410102</v>
       </c>
       <c r="N367" t="n">
-        <v>687214.649297323</v>
+        <v>686907.933612323</v>
       </c>
       <c r="O367" t="n">
-        <v>123669.405416</v>
+        <v>124130.35453</v>
       </c>
       <c r="P367" t="n">
-        <v>563545.243881323</v>
+        <v>562777.579082323</v>
       </c>
       <c r="Q367" t="n">
-        <v>103019.173313037</v>
+        <v>102952.428998037</v>
       </c>
       <c r="R367" t="n">
-        <v>2696768.06902006</v>
+        <v>2696157.37043806</v>
       </c>
       <c r="S367" t="n">
-        <v>562263.069575</v>
+        <v>561753.191804</v>
       </c>
       <c r="T367" t="n">
-        <v>3259031.13859506</v>
+        <v>3257910.56224206</v>
       </c>
       <c r="U367" t="n">
-        <v>0.223146998282142</v>
+        <v>0.200450892354986</v>
       </c>
       <c r="V367" t="n">
-        <v>7.21320200764557</v>
+        <v>7.18892296370779</v>
       </c>
       <c r="W367" t="n">
-        <v>1.41840660877448</v>
+        <v>1.3264372195362</v>
       </c>
       <c r="X367" t="n">
-        <v>6.20727341789058</v>
+        <v>6.11096133416216</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.427343588543949</v>
+        <v>0.392812925400765</v>
       </c>
       <c r="Z367" t="n">
-        <v>7.03829664292117</v>
+        <v>7.00149288776122</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.827475392021757</v>
+        <v>0.827572555761811</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.172524607978243</v>
+        <v>0.172427444238189</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45975,85 +45975,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54628.2915894345</v>
+        <v>54226.4298024345</v>
       </c>
       <c r="C367" t="n">
-        <v>6305.251594</v>
+        <v>6291.26342</v>
       </c>
       <c r="D367" t="n">
-        <v>150981.588367243</v>
+        <v>150675.775423243</v>
       </c>
       <c r="E367" t="n">
-        <v>115912.900453</v>
+        <v>115638.372189</v>
       </c>
       <c r="F367" t="n">
-        <v>180285.933611</v>
+        <v>180565.090637</v>
       </c>
       <c r="G367" t="n">
-        <v>377263.517884401</v>
+        <v>376492.715785401</v>
       </c>
       <c r="H367" t="n">
-        <v>111653.185385</v>
+        <v>111454.984747</v>
       </c>
       <c r="I367" t="n">
-        <v>52731.4774088291</v>
+        <v>52761.8845908291</v>
       </c>
       <c r="J367" t="n">
-        <v>116068.77867</v>
+        <v>116008.178536</v>
       </c>
       <c r="K367" t="n">
-        <v>479050.677189466</v>
+        <v>479382.544709466</v>
       </c>
       <c r="L367" t="n">
-        <v>54818.937234</v>
+        <v>54931.597926</v>
       </c>
       <c r="M367" t="n">
-        <v>81882.127301</v>
+        <v>82040.314609</v>
       </c>
       <c r="N367" t="n">
-        <v>687214.649297323</v>
+        <v>687459.001685323</v>
       </c>
       <c r="O367" t="n">
-        <v>123669.405416</v>
+        <v>123272.066937</v>
       </c>
       <c r="P367" t="n">
-        <v>563545.243881323</v>
+        <v>564186.934748323</v>
       </c>
       <c r="Q367" t="n">
-        <v>103019.173313037</v>
+        <v>104251.382866037</v>
       </c>
       <c r="R367" t="n">
-        <v>2696768.06902006</v>
+        <v>2699002.02505006</v>
       </c>
       <c r="S367" t="n">
-        <v>562263.069575</v>
+        <v>560636.513562</v>
       </c>
       <c r="T367" t="n">
-        <v>3259031.13859506</v>
+        <v>3259638.53861206</v>
       </c>
       <c r="U367" t="n">
-        <v>0.223146998282142</v>
+        <v>0.306170119978955</v>
       </c>
       <c r="V367" t="n">
-        <v>7.21320200764557</v>
+        <v>7.30201557002492</v>
       </c>
       <c r="W367" t="n">
-        <v>1.41840660877448</v>
+        <v>1.12501597363448</v>
       </c>
       <c r="X367" t="n">
-        <v>6.20727341789058</v>
+        <v>5.90002919619061</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.427343588543949</v>
+        <v>0.446060675803572</v>
       </c>
       <c r="Z367" t="n">
-        <v>7.03829664292117</v>
+        <v>7.05824584267891</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.827475392021757</v>
+        <v>0.828006539092915</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.172524607978243</v>
+        <v>0.171993460907085</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -14346,7 +14346,7 @@
         <v>152.015922353681</v>
       </c>
       <c r="F314" t="n">
-        <v>129.96941444808</v>
+        <v>129.971496722426</v>
       </c>
       <c r="G314" t="n">
         <v>4.89226213151006</v>
@@ -14373,10 +14373,10 @@
         <v>0.99462644080861</v>
       </c>
       <c r="O314" t="n">
-        <v>3.48526724919511</v>
+        <v>3.48692521401781</v>
       </c>
       <c r="P314" t="n">
-        <v>-2.09191035992954</v>
+        <v>-2.09034174854364</v>
       </c>
     </row>
     <row r="315">
@@ -14396,7 +14396,7 @@
         <v>154.33</v>
       </c>
       <c r="F315" t="n">
-        <v>135.379690676363</v>
+        <v>135.38036768505</v>
       </c>
       <c r="G315" t="n">
         <v>4.76226814126008</v>
@@ -14423,10 +14423,10 @@
         <v>1.52226004387532</v>
       </c>
       <c r="O315" t="n">
-        <v>3.86405328415582</v>
+        <v>3.86457268899414</v>
       </c>
       <c r="P315" t="n">
-        <v>4.16273032486767</v>
+        <v>4.16158242308753</v>
       </c>
     </row>
     <row r="316">
@@ -14446,7 +14446,7 @@
         <v>154.66</v>
       </c>
       <c r="F316" t="n">
-        <v>132.531985418243</v>
+        <v>132.52922613521</v>
       </c>
       <c r="G316" t="n">
         <v>4.58475522739963</v>
@@ -14473,10 +14473,10 @@
         <v>0.213827512473252</v>
       </c>
       <c r="O316" t="n">
-        <v>5.07295972525066</v>
+        <v>5.07077213231533</v>
       </c>
       <c r="P316" t="n">
-        <v>-2.10349517264563</v>
+        <v>-2.10602290316786</v>
       </c>
     </row>
     <row r="317">
@@ -14496,7 +14496,7 @@
         <v>155.18</v>
       </c>
       <c r="F317" t="n">
-        <v>127.488522830683</v>
+        <v>127.497036188006</v>
       </c>
       <c r="G317" t="n">
         <v>4.86594135287464</v>
@@ -14523,10 +14523,10 @@
         <v>0.336221388852964</v>
       </c>
       <c r="O317" t="n">
-        <v>3.76550522481476</v>
+        <v>3.77243441972632</v>
       </c>
       <c r="P317" t="n">
-        <v>-3.80546822085501</v>
+        <v>-3.79704167446835</v>
       </c>
     </row>
     <row r="318">
@@ -14539,9 +14539,15 @@
       <c r="C318" t="n">
         <v>139.2489</v>
       </c>
-      <c r="D318"/>
-      <c r="E318"/>
-      <c r="F318"/>
+      <c r="D318" t="n">
+        <v>175.29</v>
+      </c>
+      <c r="E318" t="n">
+        <v>153.81</v>
+      </c>
+      <c r="F318" t="n">
+        <v>139.205036803449</v>
+      </c>
       <c r="G318" t="n">
         <v>4.86135881792507</v>
       </c>
@@ -14554,12 +14560,24 @@
       <c r="J318" t="n">
         <v>0.30542071343107</v>
       </c>
-      <c r="K318"/>
-      <c r="L318"/>
-      <c r="M318"/>
-      <c r="N318"/>
-      <c r="O318"/>
-      <c r="P318"/>
+      <c r="K318" t="n">
+        <v>5.14666186791433</v>
+      </c>
+      <c r="L318" t="n">
+        <v>-0.43169554103949</v>
+      </c>
+      <c r="M318" t="n">
+        <v>4.02407682943324</v>
+      </c>
+      <c r="N318" t="n">
+        <v>-0.882845727542214</v>
+      </c>
+      <c r="O318" t="n">
+        <v>4.72735986300814</v>
+      </c>
+      <c r="P318" t="n">
+        <v>9.18295904398849</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45993,85 +45993,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54226.4298024345</v>
+        <v>54278.9334374345</v>
       </c>
       <c r="C367" t="n">
-        <v>6291.26342</v>
+        <v>6260.814338</v>
       </c>
       <c r="D367" t="n">
-        <v>150675.775423243</v>
+        <v>150535.008621243</v>
       </c>
       <c r="E367" t="n">
-        <v>115638.372189</v>
+        <v>115324.951909</v>
       </c>
       <c r="F367" t="n">
-        <v>180565.090637</v>
+        <v>180482.541106</v>
       </c>
       <c r="G367" t="n">
-        <v>376492.715785401</v>
+        <v>376126.716889401</v>
       </c>
       <c r="H367" t="n">
-        <v>111454.984747</v>
+        <v>111345.615679</v>
       </c>
       <c r="I367" t="n">
-        <v>52761.8845908291</v>
+        <v>52770.9740658291</v>
       </c>
       <c r="J367" t="n">
-        <v>116008.178536</v>
+        <v>115830.377034</v>
       </c>
       <c r="K367" t="n">
-        <v>479382.544709466</v>
+        <v>479381.609133466</v>
       </c>
       <c r="L367" t="n">
-        <v>54931.597926</v>
+        <v>54868.927164</v>
       </c>
       <c r="M367" t="n">
-        <v>82040.314609</v>
+        <v>81926.906207</v>
       </c>
       <c r="N367" t="n">
-        <v>687459.001685323</v>
+        <v>688983.527878323</v>
       </c>
       <c r="O367" t="n">
-        <v>123272.066937</v>
+        <v>124576.519161</v>
       </c>
       <c r="P367" t="n">
-        <v>564186.934748323</v>
+        <v>564407.008717323</v>
       </c>
       <c r="Q367" t="n">
-        <v>104251.382866037</v>
+        <v>103339.645025037</v>
       </c>
       <c r="R367" t="n">
-        <v>2699002.02505006</v>
+        <v>2700054.76996706</v>
       </c>
       <c r="S367" t="n">
-        <v>560636.513562</v>
+        <v>560385.306399</v>
       </c>
       <c r="T367" t="n">
-        <v>3259638.53861206</v>
+        <v>3260440.07636606</v>
       </c>
       <c r="U367" t="n">
-        <v>0.306170119978955</v>
+        <v>0.34529451105294</v>
       </c>
       <c r="V367" t="n">
-        <v>7.30201557002492</v>
+        <v>7.34386868848382</v>
       </c>
       <c r="W367" t="n">
-        <v>1.12501597363448</v>
+        <v>1.07970438982474</v>
       </c>
       <c r="X367" t="n">
-        <v>5.90002919619061</v>
+        <v>5.85257804869583</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.446060675803572</v>
+        <v>0.470760135243187</v>
       </c>
       <c r="Z367" t="n">
-        <v>7.05824584267891</v>
+        <v>7.08457122351591</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.828006539092915</v>
+        <v>0.828125868510492</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.171993460907085</v>
+        <v>0.171874131489508</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -45993,85 +45993,85 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54278.9334374345</v>
+        <v>54356.3415924345</v>
       </c>
       <c r="C367" t="n">
-        <v>6260.814338</v>
+        <v>6309.483124</v>
       </c>
       <c r="D367" t="n">
-        <v>150535.008621243</v>
+        <v>151357.316071243</v>
       </c>
       <c r="E367" t="n">
-        <v>115324.951909</v>
+        <v>115912.038143</v>
       </c>
       <c r="F367" t="n">
-        <v>180482.541106</v>
+        <v>182730.320597</v>
       </c>
       <c r="G367" t="n">
-        <v>376126.716889401</v>
+        <v>380246.828650401</v>
       </c>
       <c r="H367" t="n">
-        <v>111345.615679</v>
+        <v>112830.348033</v>
       </c>
       <c r="I367" t="n">
-        <v>52770.9740658291</v>
+        <v>53677.4476548291</v>
       </c>
       <c r="J367" t="n">
-        <v>115830.377034</v>
+        <v>115922.928495</v>
       </c>
       <c r="K367" t="n">
-        <v>479381.609133466</v>
+        <v>480689.121041466</v>
       </c>
       <c r="L367" t="n">
-        <v>54868.927164</v>
+        <v>54869.682377</v>
       </c>
       <c r="M367" t="n">
-        <v>81926.906207</v>
+        <v>81931.431094</v>
       </c>
       <c r="N367" t="n">
-        <v>688983.527878323</v>
+        <v>689220.701374323</v>
       </c>
       <c r="O367" t="n">
-        <v>124576.519161</v>
+        <v>124119.815548</v>
       </c>
       <c r="P367" t="n">
-        <v>564407.008717323</v>
+        <v>565100.885826323</v>
       </c>
       <c r="Q367" t="n">
-        <v>103339.645025037</v>
+        <v>103230.362699037</v>
       </c>
       <c r="R367" t="n">
-        <v>2700054.76996706</v>
+        <v>2698947.92506506</v>
       </c>
       <c r="S367" t="n">
-        <v>560385.306399</v>
+        <v>573557.127256</v>
       </c>
       <c r="T367" t="n">
-        <v>3260440.07636606</v>
+        <v>3272505.05232106</v>
       </c>
       <c r="U367" t="n">
-        <v>0.34529451105294</v>
+        <v>0.304159538938809</v>
       </c>
       <c r="V367" t="n">
-        <v>7.34386868848382</v>
+        <v>7.29986476117821</v>
       </c>
       <c r="W367" t="n">
-        <v>1.07970438982474</v>
+        <v>3.45557638949725</v>
       </c>
       <c r="X367" t="n">
-        <v>5.85257804869583</v>
+        <v>8.3406361390632</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.470760135243187</v>
+        <v>0.842543476393653</v>
       </c>
       <c r="Z367" t="n">
-        <v>7.08457122351591</v>
+        <v>7.48082839945003</v>
       </c>
       <c r="AA367" t="n">
-        <v>0.828125868510492</v>
+        <v>0.82473453269409</v>
       </c>
       <c r="AB367" t="n">
-        <v>0.171874131489508</v>
+        <v>0.17526546730591</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -9,12 +9,13 @@
     <sheet name="índices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="préstamos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="IPC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="sipen" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="372">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -1122,6 +1123,15 @@
   <si>
     <t xml:space="preserve">127.6391</t>
   </si>
+  <si>
+    <t xml:space="preserve">mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cotizantes</t>
+  </si>
 </sst>
 </file>
 
@@ -58827,4 +58837,3047 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>37833</v>
+      </c>
+      <c r="B2" t="n">
+        <v>7088.2099609375</v>
+      </c>
+      <c r="C2"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>37864</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6637.5498046875</v>
+      </c>
+      <c r="C3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>37894</v>
+      </c>
+      <c r="B4" t="n">
+        <v>6983.14990234375</v>
+      </c>
+      <c r="C4" t="n">
+        <v>570119</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>37925</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7067.77978515625</v>
+      </c>
+      <c r="C5" t="n">
+        <v>571062</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>37955</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7229.75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>573216</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>37986</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7407.06005859375</v>
+      </c>
+      <c r="C7" t="n">
+        <v>576869</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>38017</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7641.8798828125</v>
+      </c>
+      <c r="C8" t="n">
+        <v>510977</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>38046</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7657.759765625</v>
+      </c>
+      <c r="C9" t="n">
+        <v>577717</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>38077</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7944.47998046875</v>
+      </c>
+      <c r="C10" t="n">
+        <v>589862</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>38107</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7914.669921875</v>
+      </c>
+      <c r="C11" t="n">
+        <v>750512</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>38138</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8174.35986328125</v>
+      </c>
+      <c r="C12" t="n">
+        <v>673738</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>38168</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8083.31005859375</v>
+      </c>
+      <c r="C13" t="n">
+        <v>737226</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>38199</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8223.4296875</v>
+      </c>
+      <c r="C14" t="n">
+        <v>741387</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>38230</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8672.0595703125</v>
+      </c>
+      <c r="C15" t="n">
+        <v>604016</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>38260</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8397.08984375</v>
+      </c>
+      <c r="C16" t="n">
+        <v>622183</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>38291</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8651.76953125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>624582</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>38321</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8748.4296875</v>
+      </c>
+      <c r="C18" t="n">
+        <v>753666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>38352</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8956.1298828125</v>
+      </c>
+      <c r="C19" t="n">
+        <v>593286</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>38383</v>
+      </c>
+      <c r="B20" t="n">
+        <v>9309.8603515625</v>
+      </c>
+      <c r="C20" t="n">
+        <v>581267</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>38411</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9817.8095703125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>835032</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>38442</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9696.830078125</v>
+      </c>
+      <c r="C22" t="n">
+        <v>725929</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>38472</v>
+      </c>
+      <c r="B23" t="n">
+        <v>11461.1298828125</v>
+      </c>
+      <c r="C23" t="n">
+        <v>733936</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>38503</v>
+      </c>
+      <c r="B24" t="n">
+        <v>10158.509765625</v>
+      </c>
+      <c r="C24" t="n">
+        <v>706720</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>38533</v>
+      </c>
+      <c r="B25" t="n">
+        <v>9867.830078125</v>
+      </c>
+      <c r="C25" t="n">
+        <v>720862</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>38564</v>
+      </c>
+      <c r="B26" t="n">
+        <v>10542.509765625</v>
+      </c>
+      <c r="C26" t="n">
+        <v>773186</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>38595</v>
+      </c>
+      <c r="B27" t="n">
+        <v>10274.6904296875</v>
+      </c>
+      <c r="C27" t="n">
+        <v>757575</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>38625</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10369.2197265625</v>
+      </c>
+      <c r="C28" t="n">
+        <v>678912</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>38656</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10308.76953125</v>
+      </c>
+      <c r="C29" t="n">
+        <v>733909</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>38686</v>
+      </c>
+      <c r="B30" t="n">
+        <v>10598.8603515625</v>
+      </c>
+      <c r="C30" t="n">
+        <v>657018</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>38717</v>
+      </c>
+      <c r="B31" t="n">
+        <v>10717.259765625</v>
+      </c>
+      <c r="C31" t="n">
+        <v>626615</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>38748</v>
+      </c>
+      <c r="B32" t="n">
+        <v>11213.490234375</v>
+      </c>
+      <c r="C32" t="n">
+        <v>555033</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>38776</v>
+      </c>
+      <c r="B33" t="n">
+        <v>10484.8701171875</v>
+      </c>
+      <c r="C33" t="n">
+        <v>637018</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>38807</v>
+      </c>
+      <c r="B34" t="n">
+        <v>10866.509765625</v>
+      </c>
+      <c r="C34" t="n">
+        <v>639878</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>38837</v>
+      </c>
+      <c r="B35" t="n">
+        <v>11217.73046875</v>
+      </c>
+      <c r="C35" t="n">
+        <v>742746</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>38868</v>
+      </c>
+      <c r="B36" t="n">
+        <v>10995.240234375</v>
+      </c>
+      <c r="C36" t="n">
+        <v>769270</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>38898</v>
+      </c>
+      <c r="B37" t="n">
+        <v>10919</v>
+      </c>
+      <c r="C37" t="n">
+        <v>761772</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>38929</v>
+      </c>
+      <c r="B38" t="n">
+        <v>11146.3701171875</v>
+      </c>
+      <c r="C38" t="n">
+        <v>763820</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38960</v>
+      </c>
+      <c r="B39" t="n">
+        <v>11141.2001953125</v>
+      </c>
+      <c r="C39" t="n">
+        <v>772056</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38990</v>
+      </c>
+      <c r="B40" t="n">
+        <v>11358.5703125</v>
+      </c>
+      <c r="C40" t="n">
+        <v>768990</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39021</v>
+      </c>
+      <c r="B41" t="n">
+        <v>11298.08984375</v>
+      </c>
+      <c r="C41" t="n">
+        <v>790384</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>39051</v>
+      </c>
+      <c r="B42" t="n">
+        <v>11352.8896484375</v>
+      </c>
+      <c r="C42" t="n">
+        <v>785133</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>39082</v>
+      </c>
+      <c r="B43" t="n">
+        <v>11557.1396484375</v>
+      </c>
+      <c r="C43" t="n">
+        <v>808496</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>39113</v>
+      </c>
+      <c r="B44" t="n">
+        <v>11875.330078125</v>
+      </c>
+      <c r="C44" t="n">
+        <v>742001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>39141</v>
+      </c>
+      <c r="B45" t="n">
+        <v>11335.23046875</v>
+      </c>
+      <c r="C45" t="n">
+        <v>790414</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>39172</v>
+      </c>
+      <c r="B46" t="n">
+        <v>11695.1201171875</v>
+      </c>
+      <c r="C46" t="n">
+        <v>821887</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>39202</v>
+      </c>
+      <c r="B47" t="n">
+        <v>11909.580078125</v>
+      </c>
+      <c r="C47" t="n">
+        <v>809789</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>39233</v>
+      </c>
+      <c r="B48" t="n">
+        <v>11926.08984375</v>
+      </c>
+      <c r="C48" t="n">
+        <v>838413</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>39263</v>
+      </c>
+      <c r="B49" t="n">
+        <v>12357.4697265625</v>
+      </c>
+      <c r="C49" t="n">
+        <v>837302</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>39294</v>
+      </c>
+      <c r="B50" t="n">
+        <v>12491.990234375</v>
+      </c>
+      <c r="C50" t="n">
+        <v>826642</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>39325</v>
+      </c>
+      <c r="B51" t="n">
+        <v>12455.3701171875</v>
+      </c>
+      <c r="C51" t="n">
+        <v>804054</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>39355</v>
+      </c>
+      <c r="B52" t="n">
+        <v>12426.830078125</v>
+      </c>
+      <c r="C52" t="n">
+        <v>833676</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>39386</v>
+      </c>
+      <c r="B53" t="n">
+        <v>12161.259765625</v>
+      </c>
+      <c r="C53" t="n">
+        <v>867962</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>39416</v>
+      </c>
+      <c r="B54" t="n">
+        <v>12078.1796875</v>
+      </c>
+      <c r="C54" t="n">
+        <v>876418</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>39447</v>
+      </c>
+      <c r="B55" t="n">
+        <v>12156.5595703125</v>
+      </c>
+      <c r="C55" t="n">
+        <v>913203</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>39478</v>
+      </c>
+      <c r="B56" t="n">
+        <v>12422.0302734375</v>
+      </c>
+      <c r="C56" t="n">
+        <v>832677</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>39507</v>
+      </c>
+      <c r="B57" t="n">
+        <v>12129.8203125</v>
+      </c>
+      <c r="C57" t="n">
+        <v>858797</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>39538</v>
+      </c>
+      <c r="B58" t="n">
+        <v>12360.25</v>
+      </c>
+      <c r="C58" t="n">
+        <v>901599</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>39568</v>
+      </c>
+      <c r="B59" t="n">
+        <v>12437.3896484375</v>
+      </c>
+      <c r="C59" t="n">
+        <v>882878</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>39599</v>
+      </c>
+      <c r="B60" t="n">
+        <v>12543.6298828125</v>
+      </c>
+      <c r="C60" t="n">
+        <v>908331</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>39629</v>
+      </c>
+      <c r="B61" t="n">
+        <v>12538.51953125</v>
+      </c>
+      <c r="C61" t="n">
+        <v>915787</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>39660</v>
+      </c>
+      <c r="B62" t="n">
+        <v>12592.73046875</v>
+      </c>
+      <c r="C62" t="n">
+        <v>928221</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>39691</v>
+      </c>
+      <c r="B63" t="n">
+        <v>12771.330078125</v>
+      </c>
+      <c r="C63" t="n">
+        <v>896435</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>39721</v>
+      </c>
+      <c r="B64" t="n">
+        <v>13222.98046875</v>
+      </c>
+      <c r="C64" t="n">
+        <v>921225</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>39752</v>
+      </c>
+      <c r="B65" t="n">
+        <v>13290.7099609375</v>
+      </c>
+      <c r="C65" t="n">
+        <v>928195</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>39782</v>
+      </c>
+      <c r="B66" t="n">
+        <v>13429.5</v>
+      </c>
+      <c r="C66" t="n">
+        <v>901909</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>39813</v>
+      </c>
+      <c r="B67" t="n">
+        <v>13418.419921875</v>
+      </c>
+      <c r="C67" t="n">
+        <v>929743</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>39844</v>
+      </c>
+      <c r="B68" t="n">
+        <v>13702.2001953125</v>
+      </c>
+      <c r="C68" t="n">
+        <v>855267</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>39872</v>
+      </c>
+      <c r="B69" t="n">
+        <v>13286.0400390625</v>
+      </c>
+      <c r="C69" t="n">
+        <v>920721</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="B70" t="n">
+        <v>13401.5498046875</v>
+      </c>
+      <c r="C70" t="n">
+        <v>938933</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>39933</v>
+      </c>
+      <c r="B71" t="n">
+        <v>13526.759765625</v>
+      </c>
+      <c r="C71" t="n">
+        <v>998192</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>39964</v>
+      </c>
+      <c r="B72" t="n">
+        <v>13608.16015625</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1017529</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>39994</v>
+      </c>
+      <c r="B73" t="n">
+        <v>13580.3095703125</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1019428</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>40025</v>
+      </c>
+      <c r="B74" t="n">
+        <v>13572.4501953125</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1034463</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>40056</v>
+      </c>
+      <c r="B75" t="n">
+        <v>13634.8798828125</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1076120</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>40086</v>
+      </c>
+      <c r="B76" t="n">
+        <v>13318.5</v>
+      </c>
+      <c r="C76" t="n">
+        <v>995191</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>40117</v>
+      </c>
+      <c r="B77" t="n">
+        <v>13419.5595703125</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1094295</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>40147</v>
+      </c>
+      <c r="B78" t="n">
+        <v>13600.7001953125</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1096297</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>40178</v>
+      </c>
+      <c r="B79" t="n">
+        <v>13525.5</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1118293</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>40209</v>
+      </c>
+      <c r="B80" t="n">
+        <v>14882.5302734375</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1026752</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>40237</v>
+      </c>
+      <c r="B81" t="n">
+        <v>14254.3095703125</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1115426</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>40268</v>
+      </c>
+      <c r="B82" t="n">
+        <v>15364.1396484375</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1148486</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>40298</v>
+      </c>
+      <c r="B83" t="n">
+        <v>14719.7001953125</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1109033</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>40329</v>
+      </c>
+      <c r="B84" t="n">
+        <v>15021.6103515625</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1126585</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>40359</v>
+      </c>
+      <c r="B85" t="n">
+        <v>14929.6396484375</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1145754</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>40390</v>
+      </c>
+      <c r="B86" t="n">
+        <v>15079.26953125</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1148113</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>40421</v>
+      </c>
+      <c r="B87" t="n">
+        <v>15291.8603515625</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1144919</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>40451</v>
+      </c>
+      <c r="B88" t="n">
+        <v>15155.400390625</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1145836</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>40482</v>
+      </c>
+      <c r="B89" t="n">
+        <v>15378.2802734375</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1153219</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>40512</v>
+      </c>
+      <c r="B90" t="n">
+        <v>15556.33984375</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1176723</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>40543</v>
+      </c>
+      <c r="B91" t="n">
+        <v>16596.25</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1189601</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>40574</v>
+      </c>
+      <c r="B92" t="n">
+        <v>15588.830078125</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1077595</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>40602</v>
+      </c>
+      <c r="B93" t="n">
+        <v>15002.0703125</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1178397</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>40633</v>
+      </c>
+      <c r="B94" t="n">
+        <v>15710.1201171875</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1212258</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>40663</v>
+      </c>
+      <c r="B95" t="n">
+        <v>15402.3203125</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1178755</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>40694</v>
+      </c>
+      <c r="B96" t="n">
+        <v>15975.0703125</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1197970</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>40724</v>
+      </c>
+      <c r="B97" t="n">
+        <v>15728.650390625</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1220579</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>40755</v>
+      </c>
+      <c r="B98" t="n">
+        <v>15965.7998046875</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1216389</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>40786</v>
+      </c>
+      <c r="B99" t="n">
+        <v>16506.669921875</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1232426</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>40816</v>
+      </c>
+      <c r="B100" t="n">
+        <v>16322.650390625</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1208846</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>40847</v>
+      </c>
+      <c r="B101" t="n">
+        <v>16479.380859375</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1223060</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>40877</v>
+      </c>
+      <c r="B102" t="n">
+        <v>16545.009765625</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1232680</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>40908</v>
+      </c>
+      <c r="B103" t="n">
+        <v>17531.41015625</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1242780</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>40939</v>
+      </c>
+      <c r="B104" t="n">
+        <v>16687.779296875</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1160674</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>40968</v>
+      </c>
+      <c r="B105" t="n">
+        <v>16394.810546875</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1242050</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>40999</v>
+      </c>
+      <c r="B106" t="n">
+        <v>17035.400390625</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1263326</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>41029</v>
+      </c>
+      <c r="B107" t="n">
+        <v>16662.970703125</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1232216</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>41060</v>
+      </c>
+      <c r="B108" t="n">
+        <v>17325.439453125</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1281168</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>41090</v>
+      </c>
+      <c r="B109" t="n">
+        <v>16576.4296875</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1236530</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>41121</v>
+      </c>
+      <c r="B110" t="n">
+        <v>17303.890625</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1279009</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>41152</v>
+      </c>
+      <c r="B111" t="n">
+        <v>16912.400390625</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1260233</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>41182</v>
+      </c>
+      <c r="B112" t="n">
+        <v>17003.939453125</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1240431</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>41213</v>
+      </c>
+      <c r="B113" t="n">
+        <v>17164.490234375</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1287611</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>41243</v>
+      </c>
+      <c r="B114" t="n">
+        <v>17049.80078125</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1273247</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>41274</v>
+      </c>
+      <c r="B115" t="n">
+        <v>17911.509765625</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1291137</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>41305</v>
+      </c>
+      <c r="B116" t="n">
+        <v>17312.80078125</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1241113</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>41333</v>
+      </c>
+      <c r="B117" t="n">
+        <v>16726.099609375</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1284535</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>41364</v>
+      </c>
+      <c r="B118" t="n">
+        <v>17331.2890625</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1316873</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>41394</v>
+      </c>
+      <c r="B119" t="n">
+        <v>17347.390625</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1304070</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>41425</v>
+      </c>
+      <c r="B120" t="n">
+        <v>17789.939453125</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1345058</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>41455</v>
+      </c>
+      <c r="B121" t="n">
+        <v>17510.73046875</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1333316</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>41486</v>
+      </c>
+      <c r="B122" t="n">
+        <v>18007.08984375</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1349327</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>41517</v>
+      </c>
+      <c r="B123" t="n">
+        <v>18175.720703125</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1336030</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>41547</v>
+      </c>
+      <c r="B124" t="n">
+        <v>18219.75</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1335886</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>41578</v>
+      </c>
+      <c r="B125" t="n">
+        <v>18393.08984375</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1366703</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>41608</v>
+      </c>
+      <c r="B126" t="n">
+        <v>18212.75</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1338335</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>41639</v>
+      </c>
+      <c r="B127" t="n">
+        <v>19197.720703125</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1376966</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>41670</v>
+      </c>
+      <c r="B128" t="n">
+        <v>18608.91015625</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1324202</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>41698</v>
+      </c>
+      <c r="B129" t="n">
+        <v>18234.91015625</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1363785</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>41729</v>
+      </c>
+      <c r="B130" t="n">
+        <v>18693.470703125</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1406908</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>41759</v>
+      </c>
+      <c r="B131" t="n">
+        <v>18480.0703125</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1414140</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>41790</v>
+      </c>
+      <c r="B132" t="n">
+        <v>18618.80078125</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1417833</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>41820</v>
+      </c>
+      <c r="B133" t="n">
+        <v>19004.880859375</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1429452</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>41851</v>
+      </c>
+      <c r="B134" t="n">
+        <v>18900.359375</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1449141</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>41882</v>
+      </c>
+      <c r="B135" t="n">
+        <v>18828.599609375</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1420010</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>41912</v>
+      </c>
+      <c r="B136" t="n">
+        <v>18930.939453125</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1451258</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>41943</v>
+      </c>
+      <c r="B137" t="n">
+        <v>19075.529296875</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1472311</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>41973</v>
+      </c>
+      <c r="B138" t="n">
+        <v>18789.01953125</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1444579</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>42004</v>
+      </c>
+      <c r="B139" t="n">
+        <v>19893.30078125</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1508392</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>42035</v>
+      </c>
+      <c r="B140" t="n">
+        <v>18812.330078125</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1423196</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>42063</v>
+      </c>
+      <c r="B141" t="n">
+        <v>18772.26953125</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1490792</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>42094</v>
+      </c>
+      <c r="B142" t="n">
+        <v>19508.41015625</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1539313</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>42124</v>
+      </c>
+      <c r="B143" t="n">
+        <v>19340.98046875</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1513581</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>42155</v>
+      </c>
+      <c r="B144" t="n">
+        <v>19231.6796875</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1530988</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>42185</v>
+      </c>
+      <c r="B145" t="n">
+        <v>19301.900390625</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1553760</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>42216</v>
+      </c>
+      <c r="B146" t="n">
+        <v>19932.05078125</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1571146</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>42247</v>
+      </c>
+      <c r="B147" t="n">
+        <v>19601.869140625</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1520245</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>42277</v>
+      </c>
+      <c r="B148" t="n">
+        <v>20045.330078125</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1562475</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>42308</v>
+      </c>
+      <c r="B149" t="n">
+        <v>19896.400390625</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1578120</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>42338</v>
+      </c>
+      <c r="B150" t="n">
+        <v>20120.26953125</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1569766</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>42369</v>
+      </c>
+      <c r="B151" t="n">
+        <v>21370.580078125</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1617107</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>42400</v>
+      </c>
+      <c r="B152" t="n">
+        <v>20194.390625</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1501053</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>42429</v>
+      </c>
+      <c r="B153" t="n">
+        <v>20243.2109375</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1605919</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>42460</v>
+      </c>
+      <c r="B154" t="n">
+        <v>20249.990234375</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1671280</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>42490</v>
+      </c>
+      <c r="B155" t="n">
+        <v>20211.7890625</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1646516</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>42521</v>
+      </c>
+      <c r="B156" t="n">
+        <v>20359.6796875</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1679894</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>42551</v>
+      </c>
+      <c r="B157" t="n">
+        <v>20460.560546875</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1643218</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>42582</v>
+      </c>
+      <c r="B158" t="n">
+        <v>20080.279296875</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1668107</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>42613</v>
+      </c>
+      <c r="B159" t="n">
+        <v>20397.470703125</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1683902</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>42643</v>
+      </c>
+      <c r="B160" t="n">
+        <v>20362.029296875</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1684907</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>42674</v>
+      </c>
+      <c r="B161" t="n">
+        <v>20348.55078125</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1685991</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>42704</v>
+      </c>
+      <c r="B162" t="n">
+        <v>20186.41015625</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1695262</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>42735</v>
+      </c>
+      <c r="B163" t="n">
+        <v>21472.9296875</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1725802</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>42766</v>
+      </c>
+      <c r="B164" t="n">
+        <v>20745.7109375</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1624220</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>42794</v>
+      </c>
+      <c r="B165" t="n">
+        <v>20573.6796875</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1682495</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>42825</v>
+      </c>
+      <c r="B166" t="n">
+        <v>21448.220703125</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1727425</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>42855</v>
+      </c>
+      <c r="B167" t="n">
+        <v>20497.5390625</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1716399</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>42886</v>
+      </c>
+      <c r="B168" t="n">
+        <v>20666.23046875</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1793446</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>42916</v>
+      </c>
+      <c r="B169" t="n">
+        <v>20974.73046875</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1774273</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>42947</v>
+      </c>
+      <c r="B170" t="n">
+        <v>20958.5</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1779808</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>42978</v>
+      </c>
+      <c r="B171" t="n">
+        <v>20888.650390625</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1786508</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>43008</v>
+      </c>
+      <c r="B172" t="n">
+        <v>21436.48046875</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1775018</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>43039</v>
+      </c>
+      <c r="B173" t="n">
+        <v>21406.630859375</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1807106</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>43069</v>
+      </c>
+      <c r="B174" t="n">
+        <v>21556.5</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1804014</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>43100</v>
+      </c>
+      <c r="B175" t="n">
+        <v>22355.630859375</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1837104</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>43131</v>
+      </c>
+      <c r="B176" t="n">
+        <v>22157.859375</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1777342</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>43159</v>
+      </c>
+      <c r="B177" t="n">
+        <v>21732.689453125</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1807468</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>43190</v>
+      </c>
+      <c r="B178" t="n">
+        <v>22385.140625</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1860698</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>43220</v>
+      </c>
+      <c r="B179" t="n">
+        <v>22098.220703125</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1830789</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>43251</v>
+      </c>
+      <c r="B180" t="n">
+        <v>22404.859375</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1890857</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>43281</v>
+      </c>
+      <c r="B181" t="n">
+        <v>22203.880859375</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1813834</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>43312</v>
+      </c>
+      <c r="B182" t="n">
+        <v>22751.119140625</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1894599</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>43343</v>
+      </c>
+      <c r="B183" t="n">
+        <v>22543.369140625</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1888021</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>43373</v>
+      </c>
+      <c r="B184" t="n">
+        <v>22496.490234375</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1857705</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>43404</v>
+      </c>
+      <c r="B185" t="n">
+        <v>22681.169921875</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1922130</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>43434</v>
+      </c>
+      <c r="B186" t="n">
+        <v>22436.900390625</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1902380</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>43465</v>
+      </c>
+      <c r="B187" t="n">
+        <v>23772.9296875</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1935968</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>43496</v>
+      </c>
+      <c r="B188" t="n">
+        <v>22738.30078125</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1872444</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>43524</v>
+      </c>
+      <c r="B189" t="n">
+        <v>22215.599609375</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1914717</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>43555</v>
+      </c>
+      <c r="B190" t="n">
+        <v>22811.759765625</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1969696</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>43585</v>
+      </c>
+      <c r="B191" t="n">
+        <v>22564.490234375</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1962253</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>43616</v>
+      </c>
+      <c r="B192" t="n">
+        <v>23959.439453125</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1931882</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>43646</v>
+      </c>
+      <c r="B193" t="n">
+        <v>23806.099609375</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1885197</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>43677</v>
+      </c>
+      <c r="B194" t="n">
+        <v>23839.30078125</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1939817</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>43708</v>
+      </c>
+      <c r="B195" t="n">
+        <v>23658.130859375</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1917355</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>43738</v>
+      </c>
+      <c r="B196" t="n">
+        <v>24165.1796875</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1924512</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>43769</v>
+      </c>
+      <c r="B197" t="n">
+        <v>24530.16015625</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1959668</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>43799</v>
+      </c>
+      <c r="B198" t="n">
+        <v>23898.529296875</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1910515</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>43830</v>
+      </c>
+      <c r="B199" t="n">
+        <v>27018.470703125</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1924919</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="B200" t="n">
+        <v>25826.4609375</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1861696</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="B201" t="n">
+        <v>25609.560546875</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1903195</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>43921</v>
+      </c>
+      <c r="B202" t="n">
+        <v>25611.650390625</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1962593</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="B203" t="n">
+        <v>26372.369140625</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1569809</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>43982</v>
+      </c>
+      <c r="B204" t="n">
+        <v>28120.939453125</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1460091</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>44012</v>
+      </c>
+      <c r="B205" t="n">
+        <v>26703.55078125</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1397937</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>44043</v>
+      </c>
+      <c r="B206" t="n">
+        <v>26135.630859375</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1597113</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>44074</v>
+      </c>
+      <c r="B207" t="n">
+        <v>25878.669921875</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1624478</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>44104</v>
+      </c>
+      <c r="B208" t="n">
+        <v>25852.01953125</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1653032</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>44135</v>
+      </c>
+      <c r="B209" t="n">
+        <v>25828.41015625</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1674668</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>44165</v>
+      </c>
+      <c r="B210" t="n">
+        <v>25905.830078125</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1658616</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="B211" t="n">
+        <v>26362.7109375</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1747440</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>44227</v>
+      </c>
+      <c r="B212" t="n">
+        <v>26257.8203125</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1652224</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>44255</v>
+      </c>
+      <c r="B213" t="n">
+        <v>26059.05078125</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1756519</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>44286</v>
+      </c>
+      <c r="B214" t="n">
+        <v>27364.029296875</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1803984</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>44316</v>
+      </c>
+      <c r="B215" t="n">
+        <v>26667.630859375</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1740784</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>44347</v>
+      </c>
+      <c r="B216" t="n">
+        <v>26777.76953125</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1803412</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>44377</v>
+      </c>
+      <c r="B217" t="n">
+        <v>26312.55078125</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1831156</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="B218" t="n">
+        <v>27005.400390625</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1866512</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="B219" t="n">
+        <v>27988.060546875</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1872658</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="B220" t="n">
+        <v>27847.69921875</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1879053</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B221" t="n">
+        <v>28020.4296875</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1913789</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="B222" t="n">
+        <v>28049.9296875</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1939371</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B223" t="n">
+        <v>29547.439453125</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1972032</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B224" t="n">
+        <v>28563.509765625</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1864996</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B225" t="n">
+        <v>28044.1796875</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1956958</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B226" t="n">
+        <v>29497.359375</v>
+      </c>
+      <c r="C226" t="n">
+        <v>2031036</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>44681</v>
+      </c>
+      <c r="B227" t="n">
+        <v>28757.5</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1977626</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="B228" t="n">
+        <v>29622.970703125</v>
+      </c>
+      <c r="C228" t="n">
+        <v>2038706</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B229" t="n">
+        <v>28993.16015625</v>
+      </c>
+      <c r="C229" t="n">
+        <v>2018402</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="B230" t="n">
+        <v>29888.73046875</v>
+      </c>
+      <c r="C230" t="n">
+        <v>2054737</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>44804</v>
+      </c>
+      <c r="B231" t="n">
+        <v>29965.650390625</v>
+      </c>
+      <c r="C231" t="n">
+        <v>2077092</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B232" t="n">
+        <v>29790.119140625</v>
+      </c>
+      <c r="C232" t="n">
+        <v>2044732</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>44865</v>
+      </c>
+      <c r="B233" t="n">
+        <v>29994.880859375</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1985841</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B234" t="n">
+        <v>29607.4296875</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1996282</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B235" t="n">
+        <v>30054.5</v>
+      </c>
+      <c r="C235" t="n">
+        <v>2020997</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B236" t="n">
+        <v>30440.259765625</v>
+      </c>
+      <c r="C236" t="n">
+        <v>2020338</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B237" t="n">
+        <v>29792.869140625</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2105974</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B238" t="n">
+        <v>31154.310546875</v>
+      </c>
+      <c r="C238" t="n">
+        <v>2159049</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B239" t="n">
+        <v>30464.609375</v>
+      </c>
+      <c r="C239" t="n">
+        <v>2071926</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B240" t="n">
+        <v>32248.720703125</v>
+      </c>
+      <c r="C240" t="n">
+        <v>2138001</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B241" t="n">
+        <v>31695.740234375</v>
+      </c>
+      <c r="C241" t="n">
+        <v>2099920</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B242" t="n">
+        <v>33184.578125</v>
+      </c>
+      <c r="C242" t="n">
+        <v>2107284</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B243" t="n">
+        <v>32704.9296875</v>
+      </c>
+      <c r="C243" t="n">
+        <v>2094278</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B244" t="n">
+        <v>33114.21875</v>
+      </c>
+      <c r="C244" t="n">
+        <v>2103843</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B245" t="n">
+        <v>33275.75</v>
+      </c>
+      <c r="C245" t="n">
+        <v>2133925</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>33329.828125</v>
+      </c>
+      <c r="C246" t="n">
+        <v>2105433</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B247" t="n">
+        <v>34159.8984375</v>
+      </c>
+      <c r="C247" t="n">
+        <v>2138144</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B248" t="n">
+        <v>33880.3515625</v>
+      </c>
+      <c r="C248" t="n">
+        <v>2093134</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B249" t="n">
+        <v>33285.8203125</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2138524</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B250" t="n">
+        <v>34355.55859375</v>
+      </c>
+      <c r="C250" t="n">
+        <v>2158279</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B251" t="n">
+        <v>34291.9296875</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2128643</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B252" t="n">
+        <v>34827.9609375</v>
+      </c>
+      <c r="C252" t="n">
+        <v>2176498</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B253" t="n">
+        <v>34632.37890625</v>
+      </c>
+      <c r="C253" t="n">
+        <v>2146387</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B254" t="n">
+        <v>35385.1015625</v>
+      </c>
+      <c r="C254" t="n">
+        <v>2184125</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B255" t="n">
+        <v>35193.578125</v>
+      </c>
+      <c r="C255" t="n">
+        <v>2144976</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B256" t="n">
+        <v>35375.8984375</v>
+      </c>
+      <c r="C256" t="n">
+        <v>2160783</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B257" t="n">
+        <v>35588.25</v>
+      </c>
+      <c r="C257" t="n">
+        <v>2206846</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B258" t="n">
+        <v>35348.12890625</v>
+      </c>
+      <c r="C258" t="n">
+        <v>2157762</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B259" t="n">
+        <v>36905.26953125</v>
+      </c>
+      <c r="C259" t="n">
+        <v>2219499</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B260" t="n">
+        <v>35750.5390625</v>
+      </c>
+      <c r="C260" t="n">
+        <v>2123418</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B261" t="n">
+        <v>35698.19921875</v>
+      </c>
+      <c r="C261" t="n">
+        <v>2158065</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B262" t="n">
+        <v>36120.87890625</v>
+      </c>
+      <c r="C262" t="n">
+        <v>2230869</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B263" t="n">
+        <v>35102.921875</v>
+      </c>
+      <c r="C263" t="n">
+        <v>2226931</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B264" t="n">
+        <v>36328.25</v>
+      </c>
+      <c r="C264" t="n">
+        <v>2242332</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B265" t="n">
+        <v>36419.63062428</v>
+      </c>
+      <c r="C265" t="n">
+        <v>2226937</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B266" t="n">
+        <v>36635.05495667</v>
+      </c>
+      <c r="C266" t="n">
+        <v>2260926</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B267" t="n">
+        <v>37422.94386606</v>
+      </c>
+      <c r="C267" t="n">
+        <v>2192103</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B268" t="n">
+        <v>37122.61066755</v>
+      </c>
+      <c r="C268" t="n">
+        <v>2255383</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B269" t="n">
+        <v>36931.49068016</v>
+      </c>
+      <c r="C269" t="n">
+        <v>2281237</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B270" t="n">
+        <v>37448.0298499</v>
+      </c>
+      <c r="C270" t="n">
+        <v>2243854</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B271" t="n">
+        <v>37201.39659823</v>
+      </c>
+      <c r="C271" t="n">
+        <v>2308549</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B272" t="n">
+        <v>37576.78317798</v>
+      </c>
+      <c r="C272" t="n">
+        <v>2181704</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B273" t="n">
+        <v>37780.78510248</v>
+      </c>
+      <c r="C273" t="n">
+        <v>2272743</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B274" t="n">
+        <v>38092.43616123</v>
+      </c>
+      <c r="C274" t="n">
+        <v>2325278</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B275" t="n">
+        <v>38216.971436</v>
+      </c>
+      <c r="C275" t="n">
+        <v>2256214</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B276" t="n">
+        <v>39021.55552756</v>
+      </c>
+      <c r="C276" t="n">
+        <v>2306128</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -10,12 +10,13 @@
     <sheet name="préstamos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="IPC" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="sipen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="transacciones" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -1132,6 +1133,21 @@
   <si>
     <t xml:space="preserve">cotizantes</t>
   </si>
+  <si>
+    <t xml:space="preserve">periodo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l_tc_val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_tc_val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l_td_val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_td_val</t>
+  </si>
 </sst>
 </file>
 
@@ -61880,4 +61896,3789 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>39448</v>
+      </c>
+      <c r="B2" t="n">
+        <v>5868.17204372001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1441.46933358784</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1340.79017396</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.388847604271</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>39479</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5385.23285033</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1284.79481817707</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1228.60809352</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27.253761318986</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>39508</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5922.22373533</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1400.74862278178</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1355.40440605</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32.13474595872</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>39539</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6228.67216879</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1401.35023426604</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1356.80745171</v>
+      </c>
+      <c r="E5" t="n">
+        <v>33.3738117157825</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>39569</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6427.03762566</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1304.22713700093</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1308.45928703</v>
+      </c>
+      <c r="E6" t="n">
+        <v>33.434621033003</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>39600</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6339.99646513</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1430.2674292348</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1425.91573739</v>
+      </c>
+      <c r="E7" t="n">
+        <v>36.142092930776</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>39630</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6897.80969427</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1489.91187387824</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1362.76949934</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48.589854597125</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>39661</v>
+      </c>
+      <c r="B9" t="n">
+        <v>6678.79339501</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1480.16843776943</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1305.34500557</v>
+      </c>
+      <c r="E9" t="n">
+        <v>43.720874103258</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="B10" t="n">
+        <v>6600.8477251</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1402.0049103645</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1320.51052174</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42.096221283</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>39722</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6869.20819073</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1698.78866886429</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1349.82411003</v>
+      </c>
+      <c r="E11" t="n">
+        <v>42.465689839044</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>39753</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6345.06950026</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1461.7565911045</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1157.37785350998</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40.802943870566</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>39783</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7624.96130727</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2041.96156306046</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2154.68932865</v>
+      </c>
+      <c r="E13" t="n">
+        <v>70.301011356888</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>39814</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6184.99644213</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1467.73839341485</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1324.84391672</v>
+      </c>
+      <c r="E14" t="n">
+        <v>31.7659111806311</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>39845</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5824.67699626</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1503.57593462371</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1218.02601546</v>
+      </c>
+      <c r="E15" t="n">
+        <v>37.2885447436893</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>39873</v>
+      </c>
+      <c r="B16" t="n">
+        <v>6314.07241536</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1359.24408061886</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1402.72912865</v>
+      </c>
+      <c r="E16" t="n">
+        <v>45.3946687597674</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>39904</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5967.35058972</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1304.0200607084</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1225.902471084</v>
+      </c>
+      <c r="E17" t="n">
+        <v>35.7669364059302</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>39934</v>
+      </c>
+      <c r="B18" t="n">
+        <v>6078.43054048</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1213.52975703217</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1469.16532603</v>
+      </c>
+      <c r="E18" t="n">
+        <v>40.5769158223094</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>39965</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6316.56536517</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1308.52529847999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1404.71889458</v>
+      </c>
+      <c r="E19" t="n">
+        <v>31.8045339294071</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>39995</v>
+      </c>
+      <c r="B20" t="n">
+        <v>6672.15334323</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1520.22277614154</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1350.79792363</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37.188112490118</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>40026</v>
+      </c>
+      <c r="B21" t="n">
+        <v>6634.80402671</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1529.16816221407</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1665.78187261</v>
+      </c>
+      <c r="E21" t="n">
+        <v>37.6629074902987</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>40057</v>
+      </c>
+      <c r="B22" t="n">
+        <v>6648.11597229</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1369.22201603152</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1255.71117755</v>
+      </c>
+      <c r="E22" t="n">
+        <v>33.7513158379869</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>40087</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6726.76760136</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1524.20079699449</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1329.31668668</v>
+      </c>
+      <c r="E23" t="n">
+        <v>37.6151549445546</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>40118</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6582.11157081</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1509.17856739113</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1405.50449959</v>
+      </c>
+      <c r="E24" t="n">
+        <v>39.8514869415176</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>40148</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8080.30418398</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1574.94474888283</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2234.08685099</v>
+      </c>
+      <c r="E25" t="n">
+        <v>45.3531461624914</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>40179</v>
+      </c>
+      <c r="B26" t="n">
+        <v>6167.29364899</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1484.26632995817</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1402.36709922</v>
+      </c>
+      <c r="E26" t="n">
+        <v>38.1296696138722</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>40210</v>
+      </c>
+      <c r="B27" t="n">
+        <v>6149.08845339</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1292.04828655961</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1371.38294512</v>
+      </c>
+      <c r="E27" t="n">
+        <v>31.1647821624985</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>40238</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7750.96493353</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1527.68261951521</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1687.92658965</v>
+      </c>
+      <c r="E28" t="n">
+        <v>42.2121238368282</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>40269</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7475.44819874</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1500.62984166285</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1477.74366747</v>
+      </c>
+      <c r="E29" t="n">
+        <v>37.0626013055084</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>40299</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8342.14489752001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1597.36022230525</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1696.35591445</v>
+      </c>
+      <c r="E30" t="n">
+        <v>46.6729810007672</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>40330</v>
+      </c>
+      <c r="B31" t="n">
+        <v>7807.22804311</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1629.03105940341</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1438.40511881</v>
+      </c>
+      <c r="E31" t="n">
+        <v>41.2081339068008</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>40360</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8317.11607937001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1801.26602951486</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1558.68674781</v>
+      </c>
+      <c r="E32" t="n">
+        <v>55.5632729717803</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>40391</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8453.70441824</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1718.71134824944</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1755.80024884</v>
+      </c>
+      <c r="E33" t="n">
+        <v>48.680269072584</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>40422</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8065.23283068001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1683.36079509602</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1484.857314811</v>
+      </c>
+      <c r="E34" t="n">
+        <v>48.1244478456845</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>40452</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8140.58286866001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1736.83516783534</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1712.59539803</v>
+      </c>
+      <c r="E35" t="n">
+        <v>44.344262749715</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>40483</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8579.36055734001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1847.12812542573</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1694.91507439</v>
+      </c>
+      <c r="E36" t="n">
+        <v>58.0496910185758</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>40513</v>
+      </c>
+      <c r="B37" t="n">
+        <v>9831.225308</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1708.90294851773</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2643.94669356</v>
+      </c>
+      <c r="E37" t="n">
+        <v>79.8526334835802</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>40544</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8357.55572494</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1794.50235978098</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1814.93040463</v>
+      </c>
+      <c r="E38" t="n">
+        <v>71.0339643371881</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>40575</v>
+      </c>
+      <c r="B39" t="n">
+        <v>7894.05683496001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1539.34010302141</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1645.50579385</v>
+      </c>
+      <c r="E39" t="n">
+        <v>56.8277073581353</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>40603</v>
+      </c>
+      <c r="B40" t="n">
+        <v>9248.53054579</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1776.39308931774</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1808.76445508</v>
+      </c>
+      <c r="E40" t="n">
+        <v>54.6780452749206</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40634</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8807.15988699</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1718.2076434465</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1751.38773996</v>
+      </c>
+      <c r="E41" t="n">
+        <v>63.8340427550687</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40664</v>
+      </c>
+      <c r="B42" t="n">
+        <v>11457.092406</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1822.85647590742</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1997.77292135</v>
+      </c>
+      <c r="E42" t="n">
+        <v>78.7775878683762</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>40695</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8829.19818</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1723.06729353899</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1713.35444589</v>
+      </c>
+      <c r="E43" t="n">
+        <v>70.1073847350524</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>40725</v>
+      </c>
+      <c r="B44" t="n">
+        <v>9712.62762218</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1891.29611923428</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1721.1212028</v>
+      </c>
+      <c r="E44" t="n">
+        <v>76.1293521434202</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>40756</v>
+      </c>
+      <c r="B45" t="n">
+        <v>10371.38474445</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1990.93285983937</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2057.1996306</v>
+      </c>
+      <c r="E45" t="n">
+        <v>74.5318125242829</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>40787</v>
+      </c>
+      <c r="B46" t="n">
+        <v>9578.92029121</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1858.57982636784</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1735.52288386</v>
+      </c>
+      <c r="E46" t="n">
+        <v>82.3012601036459</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>40817</v>
+      </c>
+      <c r="B47" t="n">
+        <v>10137.459817</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2022.35872627762</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1895.89738475</v>
+      </c>
+      <c r="E47" t="n">
+        <v>66.2686558340667</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>40848</v>
+      </c>
+      <c r="B48" t="n">
+        <v>9905.94736765</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2104.92662106946</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1799.90700972</v>
+      </c>
+      <c r="E48" t="n">
+        <v>79.9867868768607</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>40878</v>
+      </c>
+      <c r="B49" t="n">
+        <v>11519.94258154</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1841.51257264768</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2718.93383751</v>
+      </c>
+      <c r="E49" t="n">
+        <v>86.9500712751476</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>40909</v>
+      </c>
+      <c r="B50" t="n">
+        <v>9712.22530701</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2093.83876660318</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2133.87755707</v>
+      </c>
+      <c r="E50" t="n">
+        <v>78.7207013197256</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>40940</v>
+      </c>
+      <c r="B51" t="n">
+        <v>9484.6390347</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1810.69281679725</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1850.05626638</v>
+      </c>
+      <c r="E51" t="n">
+        <v>60.4486277995917</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>40969</v>
+      </c>
+      <c r="B52" t="n">
+        <v>10548.97236126</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2064.64581574996</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2196.70660326</v>
+      </c>
+      <c r="E52" t="n">
+        <v>67.4437492481222</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>41000</v>
+      </c>
+      <c r="B53" t="n">
+        <v>9595.12179306</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1963.670747827</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1936.17780904</v>
+      </c>
+      <c r="E53" t="n">
+        <v>67.3679213998425</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>41030</v>
+      </c>
+      <c r="B54" t="n">
+        <v>11613.50355706</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2087.04420514498</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2292.32957587</v>
+      </c>
+      <c r="E54" t="n">
+        <v>93.1547317437953</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>41061</v>
+      </c>
+      <c r="B55" t="n">
+        <v>10315.4143532</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2112.40180264351</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1817.15337644</v>
+      </c>
+      <c r="E55" t="n">
+        <v>74.2716170580991</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>41091</v>
+      </c>
+      <c r="B56" t="n">
+        <v>11332.93041466</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2453.10523996601</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2204.85874689</v>
+      </c>
+      <c r="E56" t="n">
+        <v>87.9519997273358</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>41122</v>
+      </c>
+      <c r="B57" t="n">
+        <v>11085.16337064</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2213.85117820288</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1917.86411277</v>
+      </c>
+      <c r="E57" t="n">
+        <v>83.928064462588</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>41153</v>
+      </c>
+      <c r="B58" t="n">
+        <v>10263.27675728</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2075.45345975339</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1764.00704938</v>
+      </c>
+      <c r="E58" t="n">
+        <v>77.79724515533</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>41183</v>
+      </c>
+      <c r="B59" t="n">
+        <v>11782.07294683</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2281.22585374792</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2155.26949309</v>
+      </c>
+      <c r="E59" t="n">
+        <v>94.455135867342</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>41214</v>
+      </c>
+      <c r="B60" t="n">
+        <v>11457.15278331</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2505.33647151663</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2012.09559643</v>
+      </c>
+      <c r="E60" t="n">
+        <v>94.146074405815</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>41244</v>
+      </c>
+      <c r="B61" t="n">
+        <v>13314.77965758</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2224.14262206616</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3446.50859198</v>
+      </c>
+      <c r="E61" t="n">
+        <v>109.882832989638</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>41275</v>
+      </c>
+      <c r="B62" t="n">
+        <v>10899.9110658</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2435.3910493739</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2233.459431152</v>
+      </c>
+      <c r="E62" t="n">
+        <v>101.261311764589</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>41306</v>
+      </c>
+      <c r="B63" t="n">
+        <v>10424.416587</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2023.76977212864</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2059.632864332</v>
+      </c>
+      <c r="E63" t="n">
+        <v>90.169676397562</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>41334</v>
+      </c>
+      <c r="B64" t="n">
+        <v>11600.02597633</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2332.38597776424</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2134.943439926</v>
+      </c>
+      <c r="E64" t="n">
+        <v>94.155015155992</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>41365</v>
+      </c>
+      <c r="B65" t="n">
+        <v>11384.87509736</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2326.25633651666</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2402.1890314</v>
+      </c>
+      <c r="E65" t="n">
+        <v>116.610777539663</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>41395</v>
+      </c>
+      <c r="B66" t="n">
+        <v>12792.87437178</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2446.21645221857</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2333.72570559</v>
+      </c>
+      <c r="E66" t="n">
+        <v>133.856366038021</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>41426</v>
+      </c>
+      <c r="B67" t="n">
+        <v>11513.04469758</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2338.0437395095</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2074.62460322</v>
+      </c>
+      <c r="E67" t="n">
+        <v>120.988314560745</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>41456</v>
+      </c>
+      <c r="B68" t="n">
+        <v>12492.71763676</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2727.36273529228</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2698.63915505</v>
+      </c>
+      <c r="E68" t="n">
+        <v>367.117238380101</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>41487</v>
+      </c>
+      <c r="B69" t="n">
+        <v>12863.04631898</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2690.87010743151</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2544.6438204</v>
+      </c>
+      <c r="E69" t="n">
+        <v>390.390222662657</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>41518</v>
+      </c>
+      <c r="B70" t="n">
+        <v>11913.12597861</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2473.0136169196</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2505.60256767</v>
+      </c>
+      <c r="E70" t="n">
+        <v>355.873088391098</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>41548</v>
+      </c>
+      <c r="B71" t="n">
+        <v>13050.37421422</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2682.33136197663</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2480.43018147</v>
+      </c>
+      <c r="E71" t="n">
+        <v>146.681426563044</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>41579</v>
+      </c>
+      <c r="B72" t="n">
+        <v>12357.92990553</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2654.28161755714</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2434.6041390613</v>
+      </c>
+      <c r="E72" t="n">
+        <v>121.827940319788</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>41609</v>
+      </c>
+      <c r="B73" t="n">
+        <v>14798.36578963</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2735.48593621401</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4124.18526742</v>
+      </c>
+      <c r="E73" t="n">
+        <v>212.143529171557</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>41640</v>
+      </c>
+      <c r="B74" t="n">
+        <v>11418.57699752</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2167.36883446741</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2760.45470062</v>
+      </c>
+      <c r="E74" t="n">
+        <v>147.590624146801</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>41671</v>
+      </c>
+      <c r="B75" t="n">
+        <v>11459.14775827</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1912.9421195558</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2819.53684958</v>
+      </c>
+      <c r="E75" t="n">
+        <v>225.330399102472</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>41699</v>
+      </c>
+      <c r="B76" t="n">
+        <v>12745.28881218</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2132.45514452933</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3123.13242417</v>
+      </c>
+      <c r="E76" t="n">
+        <v>196.630803843952</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>41730</v>
+      </c>
+      <c r="B77" t="n">
+        <v>11940.5198687814</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2208.58387995882</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3035.50007107863</v>
+      </c>
+      <c r="E77" t="n">
+        <v>140.619824678097</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>41760</v>
+      </c>
+      <c r="B78" t="n">
+        <v>13421.0183486362</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2279.01434543638</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3245.20847961</v>
+      </c>
+      <c r="E78" t="n">
+        <v>154.425136085511</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>41791</v>
+      </c>
+      <c r="B79" t="n">
+        <v>12560.7644057507</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2196.98191819917</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3089.3793668</v>
+      </c>
+      <c r="E79" t="n">
+        <v>139.540681189011</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>41821</v>
+      </c>
+      <c r="B80" t="n">
+        <v>13637.647180633</v>
+      </c>
+      <c r="C80" t="n">
+        <v>2602.47761724962</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3328.68951641</v>
+      </c>
+      <c r="E80" t="n">
+        <v>180.02697669915</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>41852</v>
+      </c>
+      <c r="B81" t="n">
+        <v>13520.2343590424</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2492.09025882715</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3317.52472336</v>
+      </c>
+      <c r="E81" t="n">
+        <v>176.357916471181</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>41883</v>
+      </c>
+      <c r="B82" t="n">
+        <v>13566.3204840326</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2437.70210592737</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3394.71808666</v>
+      </c>
+      <c r="E82" t="n">
+        <v>183.249431925618</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>41913</v>
+      </c>
+      <c r="B83" t="n">
+        <v>14375.498623007</v>
+      </c>
+      <c r="C83" t="n">
+        <v>2725.77708133187</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3198.5375242</v>
+      </c>
+      <c r="E83" t="n">
+        <v>186.350547846656</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>41944</v>
+      </c>
+      <c r="B84" t="n">
+        <v>14137.5708959065</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2735.86403450644</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3056.29440648</v>
+      </c>
+      <c r="E84" t="n">
+        <v>151.61631253716</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>41974</v>
+      </c>
+      <c r="B85" t="n">
+        <v>16764.2969883081</v>
+      </c>
+      <c r="C85" t="n">
+        <v>2749.88288178214</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4974.06421837</v>
+      </c>
+      <c r="E85" t="n">
+        <v>255.370649194053</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>42005</v>
+      </c>
+      <c r="B86" t="n">
+        <v>13225.4056142302</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2651.90833354497</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3589.47870885</v>
+      </c>
+      <c r="E86" t="n">
+        <v>288.347960543127</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>42036</v>
+      </c>
+      <c r="B87" t="n">
+        <v>12899.7198161644</v>
+      </c>
+      <c r="C87" t="n">
+        <v>2122.13674573836</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3073.30088057</v>
+      </c>
+      <c r="E87" t="n">
+        <v>169.452139588721</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>42064</v>
+      </c>
+      <c r="B88" t="n">
+        <v>15003.2959332265</v>
+      </c>
+      <c r="C88" t="n">
+        <v>2515.14106433916</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3787.00166257</v>
+      </c>
+      <c r="E88" t="n">
+        <v>199.80465933882</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>42095</v>
+      </c>
+      <c r="B89" t="n">
+        <v>14252.2277585441</v>
+      </c>
+      <c r="C89" t="n">
+        <v>2630.52020585851</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3534.1615244349</v>
+      </c>
+      <c r="E89" t="n">
+        <v>209.00777823779</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>42125</v>
+      </c>
+      <c r="B90" t="n">
+        <v>15307.8820914282</v>
+      </c>
+      <c r="C90" t="n">
+        <v>2775.98904979635</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3749.9256489649</v>
+      </c>
+      <c r="E90" t="n">
+        <v>208.344069368269</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>42156</v>
+      </c>
+      <c r="B91" t="n">
+        <v>15254.6095427757</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2656.70662246366</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3711.77246818585</v>
+      </c>
+      <c r="E91" t="n">
+        <v>220.364565024295</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>42186</v>
+      </c>
+      <c r="B92" t="n">
+        <v>16065.333167733</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3310.57427612272</v>
+      </c>
+      <c r="D92" t="n">
+        <v>4092.69813040377</v>
+      </c>
+      <c r="E92" t="n">
+        <v>251.085415962964</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>42217</v>
+      </c>
+      <c r="B93" t="n">
+        <v>15801.4357158102</v>
+      </c>
+      <c r="C93" t="n">
+        <v>2908.35652245063</v>
+      </c>
+      <c r="D93" t="n">
+        <v>4386.37971647</v>
+      </c>
+      <c r="E93" t="n">
+        <v>247.49543910116</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>42248</v>
+      </c>
+      <c r="B94" t="n">
+        <v>14821.1834859135</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2793.54513660902</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3709.94080457</v>
+      </c>
+      <c r="E94" t="n">
+        <v>234.596398631637</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>42278</v>
+      </c>
+      <c r="B95" t="n">
+        <v>15769.6106845151</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3106.59402139384</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4145.0450613</v>
+      </c>
+      <c r="E95" t="n">
+        <v>253.862468843573</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>42309</v>
+      </c>
+      <c r="B96" t="n">
+        <v>16857.5205175055</v>
+      </c>
+      <c r="C96" t="n">
+        <v>3172.06086351752</v>
+      </c>
+      <c r="D96" t="n">
+        <v>4293.80214417</v>
+      </c>
+      <c r="E96" t="n">
+        <v>237.993701850862</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B97" t="n">
+        <v>18521.2195840006</v>
+      </c>
+      <c r="C97" t="n">
+        <v>3072.28892720951</v>
+      </c>
+      <c r="D97" t="n">
+        <v>5951.75514479</v>
+      </c>
+      <c r="E97" t="n">
+        <v>284.447247902917</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>42370</v>
+      </c>
+      <c r="B98" t="n">
+        <v>14199.2553185413</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2890.05626844998</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3900.15816595</v>
+      </c>
+      <c r="E98" t="n">
+        <v>205.234237884166</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>42401</v>
+      </c>
+      <c r="B99" t="n">
+        <v>15374.0350893067</v>
+      </c>
+      <c r="C99" t="n">
+        <v>2632.41287273518</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3934.79974598</v>
+      </c>
+      <c r="E99" t="n">
+        <v>213.543534200515</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>42430</v>
+      </c>
+      <c r="B100" t="n">
+        <v>16072.8770166178</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3025.39236285279</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4126.42845979</v>
+      </c>
+      <c r="E100" t="n">
+        <v>220.133303446864</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>42461</v>
+      </c>
+      <c r="B101" t="n">
+        <v>16137.2691442111</v>
+      </c>
+      <c r="C101" t="n">
+        <v>2945.39739110776</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4236.37313628</v>
+      </c>
+      <c r="E101" t="n">
+        <v>234.234627257923</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>42491</v>
+      </c>
+      <c r="B102" t="n">
+        <v>17792.4575166178</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3266.65790638311</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4632.32749186789</v>
+      </c>
+      <c r="E102" t="n">
+        <v>253.281413293337</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>42522</v>
+      </c>
+      <c r="B103" t="n">
+        <v>16224.5706672277</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3181.409933117</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4188.3496566</v>
+      </c>
+      <c r="E103" t="n">
+        <v>267.846937212075</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>42552</v>
+      </c>
+      <c r="B104" t="n">
+        <v>17189.1964819775</v>
+      </c>
+      <c r="C104" t="n">
+        <v>3763.86508683492</v>
+      </c>
+      <c r="D104" t="n">
+        <v>4213.47230983</v>
+      </c>
+      <c r="E104" t="n">
+        <v>248.081496409978</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>42583</v>
+      </c>
+      <c r="B105" t="n">
+        <v>17963.8929894819</v>
+      </c>
+      <c r="C105" t="n">
+        <v>3561.35384221257</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4737.8790351003</v>
+      </c>
+      <c r="E105" t="n">
+        <v>273.10575337612</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>42614</v>
+      </c>
+      <c r="B106" t="n">
+        <v>16769.375426499</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3169.6477957296</v>
+      </c>
+      <c r="D106" t="n">
+        <v>4249.68067162</v>
+      </c>
+      <c r="E106" t="n">
+        <v>261.356836599177</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>42644</v>
+      </c>
+      <c r="B107" t="n">
+        <v>17276.7579913748</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3483.4952195193</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4502.55508752</v>
+      </c>
+      <c r="E107" t="n">
+        <v>272.342271270652</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>42675</v>
+      </c>
+      <c r="B108" t="n">
+        <v>18378.0728802539</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3528.07924911725</v>
+      </c>
+      <c r="D108" t="n">
+        <v>4777.45974282024</v>
+      </c>
+      <c r="E108" t="n">
+        <v>272.609566588112</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B109" t="n">
+        <v>19824.4465253824</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3020.77742752979</v>
+      </c>
+      <c r="D109" t="n">
+        <v>6548.97403084224</v>
+      </c>
+      <c r="E109" t="n">
+        <v>303.552605740309</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>42736</v>
+      </c>
+      <c r="B110" t="n">
+        <v>16226.3387255849</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3216.34616379113</v>
+      </c>
+      <c r="D110" t="n">
+        <v>5132.2212630896</v>
+      </c>
+      <c r="E110" t="n">
+        <v>286.777647255648</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>42767</v>
+      </c>
+      <c r="B111" t="n">
+        <v>15433.9649880957</v>
+      </c>
+      <c r="C111" t="n">
+        <v>2493.36429505381</v>
+      </c>
+      <c r="D111" t="n">
+        <v>4416.62087936</v>
+      </c>
+      <c r="E111" t="n">
+        <v>243.01517472196</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>42795</v>
+      </c>
+      <c r="B112" t="n">
+        <v>17340.8741471206</v>
+      </c>
+      <c r="C112" t="n">
+        <v>2919.6044253728</v>
+      </c>
+      <c r="D112" t="n">
+        <v>4898.38747378031</v>
+      </c>
+      <c r="E112" t="n">
+        <v>252.18101362301</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>42826</v>
+      </c>
+      <c r="B113" t="n">
+        <v>15309.570891144</v>
+      </c>
+      <c r="C113" t="n">
+        <v>2749.71072049181</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4743.3706555383</v>
+      </c>
+      <c r="E113" t="n">
+        <v>285.795191447185</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>42856</v>
+      </c>
+      <c r="B114" t="n">
+        <v>18120.0751536938</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2853.60082369953</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5346.23041959628</v>
+      </c>
+      <c r="E114" t="n">
+        <v>305.807708508456</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>42887</v>
+      </c>
+      <c r="B115" t="n">
+        <v>16079.4042831644</v>
+      </c>
+      <c r="C115" t="n">
+        <v>2728.10708579889</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4746.079824946</v>
+      </c>
+      <c r="E115" t="n">
+        <v>291.146312113703</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>42917</v>
+      </c>
+      <c r="B116" t="n">
+        <v>17231.4885432812</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3497.00202506638</v>
+      </c>
+      <c r="D116" t="n">
+        <v>5358.3335466</v>
+      </c>
+      <c r="E116" t="n">
+        <v>327.517741228614</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>42948</v>
+      </c>
+      <c r="B117" t="n">
+        <v>19725.27563908</v>
+      </c>
+      <c r="C117" t="n">
+        <v>3249.0086194719</v>
+      </c>
+      <c r="D117" t="n">
+        <v>5519.14345873037</v>
+      </c>
+      <c r="E117" t="n">
+        <v>341.002829216412</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>42979</v>
+      </c>
+      <c r="B118" t="n">
+        <v>15830.0852533811</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2639.02045112462</v>
+      </c>
+      <c r="D118" t="n">
+        <v>4752.65470534</v>
+      </c>
+      <c r="E118" t="n">
+        <v>282.19186037625</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>43009</v>
+      </c>
+      <c r="B119" t="n">
+        <v>18048.4060408197</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3450.67715253343</v>
+      </c>
+      <c r="D119" t="n">
+        <v>5390.09228054011</v>
+      </c>
+      <c r="E119" t="n">
+        <v>319.584966601925</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>43040</v>
+      </c>
+      <c r="B120" t="n">
+        <v>19534.4752109249</v>
+      </c>
+      <c r="C120" t="n">
+        <v>3608.63563676841</v>
+      </c>
+      <c r="D120" t="n">
+        <v>5984.36851557</v>
+      </c>
+      <c r="E120" t="n">
+        <v>267.406113106668</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B121" t="n">
+        <v>20211.1341671021</v>
+      </c>
+      <c r="C121" t="n">
+        <v>3353.54424744592</v>
+      </c>
+      <c r="D121" t="n">
+        <v>7708.85870681016</v>
+      </c>
+      <c r="E121" t="n">
+        <v>278.989651948018</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>43101</v>
+      </c>
+      <c r="B122" t="n">
+        <v>16532.0476400853</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2057.60335583479</v>
+      </c>
+      <c r="D122" t="n">
+        <v>5943.93881865994</v>
+      </c>
+      <c r="E122" t="n">
+        <v>332.732292331561</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>43132</v>
+      </c>
+      <c r="B123" t="n">
+        <v>16151.1532513057</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2166.60088800341</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5509.43366081996</v>
+      </c>
+      <c r="E123" t="n">
+        <v>279.88986978981</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="B124" t="n">
+        <v>18153.578745759</v>
+      </c>
+      <c r="C124" t="n">
+        <v>2491.77101666072</v>
+      </c>
+      <c r="D124" t="n">
+        <v>6122.08576169996</v>
+      </c>
+      <c r="E124" t="n">
+        <v>170.152306850477</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>43191</v>
+      </c>
+      <c r="B125" t="n">
+        <v>17130.0772674563</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2336.86860640187</v>
+      </c>
+      <c r="D125" t="n">
+        <v>6021.45400606999</v>
+      </c>
+      <c r="E125" t="n">
+        <v>167.704180073934</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>43221</v>
+      </c>
+      <c r="B126" t="n">
+        <v>19456.1443454351</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2847.81811605514</v>
+      </c>
+      <c r="D126" t="n">
+        <v>6478.69892923998</v>
+      </c>
+      <c r="E126" t="n">
+        <v>194.683077277823</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>43252</v>
+      </c>
+      <c r="B127" t="n">
+        <v>17641.5693676747</v>
+      </c>
+      <c r="C127" t="n">
+        <v>2492.43898400815</v>
+      </c>
+      <c r="D127" t="n">
+        <v>5703.74360826992</v>
+      </c>
+      <c r="E127" t="n">
+        <v>187.617146674314</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>43282</v>
+      </c>
+      <c r="B128" t="n">
+        <v>18350.1747148658</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2967.36838964212</v>
+      </c>
+      <c r="D128" t="n">
+        <v>6509.28180626002</v>
+      </c>
+      <c r="E128" t="n">
+        <v>230.710360791404</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>43313</v>
+      </c>
+      <c r="B129" t="n">
+        <v>19349.3391195308</v>
+      </c>
+      <c r="C129" t="n">
+        <v>2991.50436631136</v>
+      </c>
+      <c r="D129" t="n">
+        <v>6796.37534720001</v>
+      </c>
+      <c r="E129" t="n">
+        <v>249.347739839378</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>43344</v>
+      </c>
+      <c r="B130" t="n">
+        <v>17498.1013116793</v>
+      </c>
+      <c r="C130" t="n">
+        <v>2770.73777433286</v>
+      </c>
+      <c r="D130" t="n">
+        <v>6190.15619777</v>
+      </c>
+      <c r="E130" t="n">
+        <v>234.411134982344</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>43374</v>
+      </c>
+      <c r="B131" t="n">
+        <v>18999.4007421796</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3000.908730894</v>
+      </c>
+      <c r="D131" t="n">
+        <v>6499.89521470003</v>
+      </c>
+      <c r="E131" t="n">
+        <v>239.782911543791</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>43405</v>
+      </c>
+      <c r="B132" t="n">
+        <v>20921.0591921156</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3051.77351225057</v>
+      </c>
+      <c r="D132" t="n">
+        <v>6877.99094288005</v>
+      </c>
+      <c r="E132" t="n">
+        <v>271.270331842436</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B133" t="n">
+        <v>21830.4216456802</v>
+      </c>
+      <c r="C133" t="n">
+        <v>2655.91408331772</v>
+      </c>
+      <c r="D133" t="n">
+        <v>9459.78274532015</v>
+      </c>
+      <c r="E133" t="n">
+        <v>306.11916566176</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="B134" t="n">
+        <v>17823.3436037256</v>
+      </c>
+      <c r="C134" t="n">
+        <v>2780.37768075291</v>
+      </c>
+      <c r="D134" t="n">
+        <v>7073.29906977004</v>
+      </c>
+      <c r="E134" t="n">
+        <v>271.194347613615</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>43497</v>
+      </c>
+      <c r="B135" t="n">
+        <v>17397.1013080553</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2122.57308030648</v>
+      </c>
+      <c r="D135" t="n">
+        <v>6446.66830582</v>
+      </c>
+      <c r="E135" t="n">
+        <v>231.795608190963</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>43525</v>
+      </c>
+      <c r="B136" t="n">
+        <v>19356.9058143703</v>
+      </c>
+      <c r="C136" t="n">
+        <v>2342.33574802067</v>
+      </c>
+      <c r="D136" t="n">
+        <v>7113.10700902807</v>
+      </c>
+      <c r="E136" t="n">
+        <v>255.840621908254</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>43556</v>
+      </c>
+      <c r="B137" t="n">
+        <v>18469.5441572452</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2870.2280920584</v>
+      </c>
+      <c r="D137" t="n">
+        <v>7148.43179898999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>290.688460147378</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>43586</v>
+      </c>
+      <c r="B138" t="n">
+        <v>19598.2816442091</v>
+      </c>
+      <c r="C138" t="n">
+        <v>2515.99059719146</v>
+      </c>
+      <c r="D138" t="n">
+        <v>7901.71207615015</v>
+      </c>
+      <c r="E138" t="n">
+        <v>299.065652973012</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>43617</v>
+      </c>
+      <c r="B139" t="n">
+        <v>18901.0523316106</v>
+      </c>
+      <c r="C139" t="n">
+        <v>2646.46189276718</v>
+      </c>
+      <c r="D139" t="n">
+        <v>7341.02067374005</v>
+      </c>
+      <c r="E139" t="n">
+        <v>303.109444280346</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>43647</v>
+      </c>
+      <c r="B140" t="n">
+        <v>20629.9853260505</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3235.99725288493</v>
+      </c>
+      <c r="D140" t="n">
+        <v>7567.12524853014</v>
+      </c>
+      <c r="E140" t="n">
+        <v>332.228051291248</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>43678</v>
+      </c>
+      <c r="B141" t="n">
+        <v>20968.8688638255</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3038.30398087979</v>
+      </c>
+      <c r="D141" t="n">
+        <v>7859.50183001006</v>
+      </c>
+      <c r="E141" t="n">
+        <v>337.582672777867</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>43709</v>
+      </c>
+      <c r="B142" t="n">
+        <v>18490.641178489</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2795.6772389498</v>
+      </c>
+      <c r="D142" t="n">
+        <v>6782.46117515889</v>
+      </c>
+      <c r="E142" t="n">
+        <v>293.547423916026</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>43739</v>
+      </c>
+      <c r="B143" t="n">
+        <v>19889.5153371674</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3022.26867954061</v>
+      </c>
+      <c r="D143" t="n">
+        <v>6801.20750504012</v>
+      </c>
+      <c r="E143" t="n">
+        <v>309.052352343916</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>43770</v>
+      </c>
+      <c r="B144" t="n">
+        <v>22109.4945403211</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3338.03704858483</v>
+      </c>
+      <c r="D144" t="n">
+        <v>8109.51780732689</v>
+      </c>
+      <c r="E144" t="n">
+        <v>341.899224685146</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="B145" t="n">
+        <v>24875.4260070592</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3038.4720039129</v>
+      </c>
+      <c r="D145" t="n">
+        <v>11519.9620603305</v>
+      </c>
+      <c r="E145" t="n">
+        <v>414.443346694115</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="B146" t="n">
+        <v>19623.819790054</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2914.24076367523</v>
+      </c>
+      <c r="D146" t="n">
+        <v>8325.62803983</v>
+      </c>
+      <c r="E146" t="n">
+        <v>342.595697519438</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="B147" t="n">
+        <v>19820.7411000762</v>
+      </c>
+      <c r="C147" t="n">
+        <v>2391.65568785949</v>
+      </c>
+      <c r="D147" t="n">
+        <v>7820.81594912</v>
+      </c>
+      <c r="E147" t="n">
+        <v>283.127375312093</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>43891</v>
+      </c>
+      <c r="B148" t="n">
+        <v>16696.0529200525</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1596.26490088762</v>
+      </c>
+      <c r="D148" t="n">
+        <v>7557.92337484</v>
+      </c>
+      <c r="E148" t="n">
+        <v>204.5413257364</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>43922</v>
+      </c>
+      <c r="B149" t="n">
+        <v>8597.78920138846</v>
+      </c>
+      <c r="C149" t="n">
+        <v>715.223489257426</v>
+      </c>
+      <c r="D149" t="n">
+        <v>5153.4317862</v>
+      </c>
+      <c r="E149" t="n">
+        <v>95.207399670557</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>43952</v>
+      </c>
+      <c r="B150" t="n">
+        <v>12831.6069269796</v>
+      </c>
+      <c r="C150" t="n">
+        <v>617.710460690769</v>
+      </c>
+      <c r="D150" t="n">
+        <v>6862.48610152</v>
+      </c>
+      <c r="E150" t="n">
+        <v>132.728539689219</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>43983</v>
+      </c>
+      <c r="B151" t="n">
+        <v>15232.1206187276</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1477.15249420135</v>
+      </c>
+      <c r="D151" t="n">
+        <v>8068.71896808</v>
+      </c>
+      <c r="E151" t="n">
+        <v>170.8313510642</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>44013</v>
+      </c>
+      <c r="B152" t="n">
+        <v>16478.5289209491</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1053.06204273092</v>
+      </c>
+      <c r="D152" t="n">
+        <v>8884.24466714</v>
+      </c>
+      <c r="E152" t="n">
+        <v>206.015006319471</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="B153" t="n">
+        <v>16692.7278052216</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1185.35998646935</v>
+      </c>
+      <c r="D153" t="n">
+        <v>8481.80340738999</v>
+      </c>
+      <c r="E153" t="n">
+        <v>230.808556362202</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>44075</v>
+      </c>
+      <c r="B154" t="n">
+        <v>16938.8856377257</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1315.17074812237</v>
+      </c>
+      <c r="D154" t="n">
+        <v>8836.83568548999</v>
+      </c>
+      <c r="E154" t="n">
+        <v>236.57546250698</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B155" t="n">
+        <v>19316.3766134352</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1777.59062901007</v>
+      </c>
+      <c r="D155" t="n">
+        <v>9761.67379235499</v>
+      </c>
+      <c r="E155" t="n">
+        <v>277.008888438266</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>44136</v>
+      </c>
+      <c r="B156" t="n">
+        <v>21111.2398789228</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1981.26046947622</v>
+      </c>
+      <c r="D156" t="n">
+        <v>10197.732054022</v>
+      </c>
+      <c r="E156" t="n">
+        <v>279.585187537644</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B157" t="n">
+        <v>22189.6284121876</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1876.62231938802</v>
+      </c>
+      <c r="D157" t="n">
+        <v>13719.28111821</v>
+      </c>
+      <c r="E157" t="n">
+        <v>351.116503337804</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B158" t="n">
+        <v>16928.4595324808</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1941.53753434747</v>
+      </c>
+      <c r="D158" t="n">
+        <v>9296.67326085703</v>
+      </c>
+      <c r="E158" t="n">
+        <v>292.94058986476</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B159" t="n">
+        <v>18846.7920794013</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1617.55579237653</v>
+      </c>
+      <c r="D159" t="n">
+        <v>9897.87793447398</v>
+      </c>
+      <c r="E159" t="n">
+        <v>289.793195440688</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B160" t="n">
+        <v>22282.6073038691</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2141.98286365868</v>
+      </c>
+      <c r="D160" t="n">
+        <v>11456.233125722</v>
+      </c>
+      <c r="E160" t="n">
+        <v>383.609240225398</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B161" t="n">
+        <v>20816.9304044596</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2398.79776638389</v>
+      </c>
+      <c r="D161" t="n">
+        <v>10845.621381018</v>
+      </c>
+      <c r="E161" t="n">
+        <v>366.984674446762</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B162" t="n">
+        <v>24190.9186858836</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2453.70700010225</v>
+      </c>
+      <c r="D162" t="n">
+        <v>12712.947699793</v>
+      </c>
+      <c r="E162" t="n">
+        <v>427.218222650126</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B163" t="n">
+        <v>20685.644083848</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2421.72195447572</v>
+      </c>
+      <c r="D163" t="n">
+        <v>10544.799192112</v>
+      </c>
+      <c r="E163" t="n">
+        <v>411.47895118008</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B164" t="n">
+        <v>24008.3041164081</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2913.49302973869</v>
+      </c>
+      <c r="D164" t="n">
+        <v>12594.5703918415</v>
+      </c>
+      <c r="E164" t="n">
+        <v>485.816186112752</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B165" t="n">
+        <v>23927.963214576</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3056.32294708638</v>
+      </c>
+      <c r="D165" t="n">
+        <v>12887.56127545</v>
+      </c>
+      <c r="E165" t="n">
+        <v>530.898628759443</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B166" t="n">
+        <v>24481.8888991822</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3131.34308805549</v>
+      </c>
+      <c r="D166" t="n">
+        <v>13073.897269192</v>
+      </c>
+      <c r="E166" t="n">
+        <v>529.607223160316</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B167" t="n">
+        <v>24739.6540070585</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3554.50385539017</v>
+      </c>
+      <c r="D167" t="n">
+        <v>13028.5686750649</v>
+      </c>
+      <c r="E167" t="n">
+        <v>554.480504496353</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B168" t="n">
+        <v>28239.2954638199</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3842.97318158606</v>
+      </c>
+      <c r="D168" t="n">
+        <v>13984.4995802935</v>
+      </c>
+      <c r="E168" t="n">
+        <v>596.015276039192</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B169" t="n">
+        <v>29845.0251098344</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3647.24985585138</v>
+      </c>
+      <c r="D169" t="n">
+        <v>18847.7912774542</v>
+      </c>
+      <c r="E169" t="n">
+        <v>681.76676694093</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B170" t="n">
+        <v>23506.5820511158</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3629.14252033552</v>
+      </c>
+      <c r="D170" t="n">
+        <v>13966.195035712</v>
+      </c>
+      <c r="E170" t="n">
+        <v>650.420518461477</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B171" t="n">
+        <v>25010.0838185005</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2860.92308305635</v>
+      </c>
+      <c r="D171" t="n">
+        <v>13466.864933623</v>
+      </c>
+      <c r="E171" t="n">
+        <v>577.926962590948</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B172" t="n">
+        <v>27707.9357598713</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3322.49755041477</v>
+      </c>
+      <c r="D172" t="n">
+        <v>14965.28018109</v>
+      </c>
+      <c r="E172" t="n">
+        <v>601.244601293</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B173" t="n">
+        <v>26083.0437836905</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3899.89238554982</v>
+      </c>
+      <c r="D173" t="n">
+        <v>15439.10303455</v>
+      </c>
+      <c r="E173" t="n">
+        <v>636.60123874</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B174" t="n">
+        <v>30056.2582439835</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3891.92504460912</v>
+      </c>
+      <c r="D174" t="n">
+        <v>15648.971104</v>
+      </c>
+      <c r="E174" t="n">
+        <v>647.8694696278</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B175" t="n">
+        <v>26253.438003465</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3757.63349831596</v>
+      </c>
+      <c r="D175" t="n">
+        <v>14725.35981936</v>
+      </c>
+      <c r="E175" t="n">
+        <v>623.4838179072</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B176" t="n">
+        <v>29588.8684638456</v>
+      </c>
+      <c r="C176" t="n">
+        <v>4154.44867950409</v>
+      </c>
+      <c r="D176" t="n">
+        <v>16593.21143258</v>
+      </c>
+      <c r="E176" t="n">
+        <v>730.8831782617</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B177" t="n">
+        <v>30411.0515455217</v>
+      </c>
+      <c r="C177" t="n">
+        <v>4265.8432809197</v>
+      </c>
+      <c r="D177" t="n">
+        <v>16332.27834833</v>
+      </c>
+      <c r="E177" t="n">
+        <v>710.4874856365</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B178" t="n">
+        <v>28860.4160236024</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3893.64235185396</v>
+      </c>
+      <c r="D178" t="n">
+        <v>15771.9254888394</v>
+      </c>
+      <c r="E178" t="n">
+        <v>645.8013394512</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B179" t="n">
+        <v>30429.3190968596</v>
+      </c>
+      <c r="C179" t="n">
+        <v>4495.71509236553</v>
+      </c>
+      <c r="D179" t="n">
+        <v>16385.1203424299</v>
+      </c>
+      <c r="E179" t="n">
+        <v>722.6363740003</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B180" t="n">
+        <v>34170.6626436717</v>
+      </c>
+      <c r="C180" t="n">
+        <v>4651.93803290591</v>
+      </c>
+      <c r="D180" t="n">
+        <v>16596.9339283691</v>
+      </c>
+      <c r="E180" t="n">
+        <v>702.9083805463</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B181" t="n">
+        <v>37646.0056258744</v>
+      </c>
+      <c r="C181" t="n">
+        <v>4657.84667411853</v>
+      </c>
+      <c r="D181" t="n">
+        <v>23148.7218738496</v>
+      </c>
+      <c r="E181" t="n">
+        <v>866.633904692891</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B182" t="n">
+        <v>30157.9815253935</v>
+      </c>
+      <c r="C182" t="n">
+        <v>4905.8704168559</v>
+      </c>
+      <c r="D182" t="n">
+        <v>17564.8979796186</v>
+      </c>
+      <c r="E182" t="n">
+        <v>765.184828164382</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B183" t="n">
+        <v>29989.7309857684</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3577.49747164857</v>
+      </c>
+      <c r="D183" t="n">
+        <v>15845.075139811</v>
+      </c>
+      <c r="E183" t="n">
+        <v>642.865982890768</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B184" t="n">
+        <v>33385.2703671702</v>
+      </c>
+      <c r="C184" t="n">
+        <v>4590.68119655609</v>
+      </c>
+      <c r="D184" t="n">
+        <v>16754.3183788247</v>
+      </c>
+      <c r="E184" t="n">
+        <v>703.50767737007</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B185" t="n">
+        <v>32074.7439624506</v>
+      </c>
+      <c r="C185" t="n">
+        <v>4615.5731017543</v>
+      </c>
+      <c r="D185" t="n">
+        <v>17191.3653227799</v>
+      </c>
+      <c r="E185" t="n">
+        <v>721.480096472207</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B186" t="n">
+        <v>35992.3411352724</v>
+      </c>
+      <c r="C186" t="n">
+        <v>4612.98471362137</v>
+      </c>
+      <c r="D186" t="n">
+        <v>18538.905559106</v>
+      </c>
+      <c r="E186" t="n">
+        <v>778.730073475215</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B187" t="n">
+        <v>33701.5509408053</v>
+      </c>
+      <c r="C187" t="n">
+        <v>4598.66058373758</v>
+      </c>
+      <c r="D187" t="n">
+        <v>17170.4831541196</v>
+      </c>
+      <c r="E187" t="n">
+        <v>758.786109841475</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B188" t="n">
+        <v>35912.3210734216</v>
+      </c>
+      <c r="C188" t="n">
+        <v>5306.46014789437</v>
+      </c>
+      <c r="D188" t="n">
+        <v>18742.4247369223</v>
+      </c>
+      <c r="E188" t="n">
+        <v>859.296532970782</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B189" t="n">
+        <v>36289.4769478088</v>
+      </c>
+      <c r="C189" t="n">
+        <v>5256.33586119655</v>
+      </c>
+      <c r="D189" t="n">
+        <v>18595.2705826959</v>
+      </c>
+      <c r="E189" t="n">
+        <v>851.896337052191</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B190" t="n">
+        <v>35885.574244846</v>
+      </c>
+      <c r="C190" t="n">
+        <v>4942.23453196869</v>
+      </c>
+      <c r="D190" t="n">
+        <v>18229.9209984527</v>
+      </c>
+      <c r="E190" t="n">
+        <v>801.018313478008</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B191" t="n">
+        <v>37510.0242052544</v>
+      </c>
+      <c r="C191" t="n">
+        <v>5475.85352329767</v>
+      </c>
+      <c r="D191" t="n">
+        <v>19000.1867491723</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1004.18082751836</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B192" t="n">
+        <v>40870.1263497254</v>
+      </c>
+      <c r="C192" t="n">
+        <v>5819.20409417848</v>
+      </c>
+      <c r="D192" t="n">
+        <v>19543.2652688198</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1220.53329059614</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B193" t="n">
+        <v>44482.1138104796</v>
+      </c>
+      <c r="C193" t="n">
+        <v>5416.64821876506</v>
+      </c>
+      <c r="D193" t="n">
+        <v>26459.0282340251</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1385.16987573856</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B194" t="n">
+        <v>37268.5099487906</v>
+      </c>
+      <c r="C194" t="n">
+        <v>5875.63909322779</v>
+      </c>
+      <c r="D194" t="n">
+        <v>19950.5687848354</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1230.31018748416</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B195" t="n">
+        <v>37412.0224802738</v>
+      </c>
+      <c r="C195" t="n">
+        <v>4427.82100708715</v>
+      </c>
+      <c r="D195" t="n">
+        <v>17704.004843366</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1064.54082328967</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B196" t="n">
+        <v>39773.843860776</v>
+      </c>
+      <c r="C196" t="n">
+        <v>5528.24969541909</v>
+      </c>
+      <c r="D196" t="n">
+        <v>19470.5597153061</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1201.58369991782</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B197" t="n">
+        <v>39052.3745102478</v>
+      </c>
+      <c r="C197" t="n">
+        <v>5271.64428173299</v>
+      </c>
+      <c r="D197" t="n">
+        <v>19198.9034339417</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1188.71309912248</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B198" t="n">
+        <v>43484.0828049629</v>
+      </c>
+      <c r="C198" t="n">
+        <v>5529.98039793895</v>
+      </c>
+      <c r="D198" t="n">
+        <v>21041.1723549328</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1303.16007952001</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B199" t="n">
+        <v>40765.6609713792</v>
+      </c>
+      <c r="C199" t="n">
+        <v>5732.79662634075</v>
+      </c>
+      <c r="D199" t="n">
+        <v>19418.5778021472</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1209.15695213259</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B200" t="n">
+        <v>43262.9956245142</v>
+      </c>
+      <c r="C200" t="n">
+        <v>6489.7436954707</v>
+      </c>
+      <c r="D200" t="n">
+        <v>20587.1091135891</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1344.31953053684</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B201" t="n">
+        <v>44860.2025162428</v>
+      </c>
+      <c r="C201" t="n">
+        <v>6268.01436860748</v>
+      </c>
+      <c r="D201" t="n">
+        <v>21634.1568858642</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1339.37268003629</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B202" t="n">
+        <v>41027.4679348445</v>
+      </c>
+      <c r="C202" t="n">
+        <v>5746.14959950706</v>
+      </c>
+      <c r="D202" t="n">
+        <v>20242.9365013712</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1280.81602962867</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B203" t="n">
+        <v>44117.2927914446</v>
+      </c>
+      <c r="C203" t="n">
+        <v>6312.36319700455</v>
+      </c>
+      <c r="D203" t="n">
+        <v>20582.262377715</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1300.97454787452</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B204" t="n">
+        <v>48120.4929959288</v>
+      </c>
+      <c r="C204" t="n">
+        <v>6324.72084809954</v>
+      </c>
+      <c r="D204" t="n">
+        <v>21413.1866487773</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1396.55137298359</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B205" t="n">
+        <v>50652.5659449124</v>
+      </c>
+      <c r="C205" t="n">
+        <v>6249.98728763009</v>
+      </c>
+      <c r="D205" t="n">
+        <v>29276.0412955649</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1503.07244400676</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B206" t="n">
+        <v>42865.23452274</v>
+      </c>
+      <c r="C206" t="n">
+        <v>6341.51027001</v>
+      </c>
+      <c r="D206" t="n">
+        <v>21448.29399655</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1310.01460155</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B207" t="n">
+        <v>41511.03837014</v>
+      </c>
+      <c r="C207" t="n">
+        <v>4859.11571</v>
+      </c>
+      <c r="D207" t="n">
+        <v>19871.803879</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1159.89068296</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B208" t="n">
+        <v>45871.97313447</v>
+      </c>
+      <c r="C208" t="n">
+        <v>5754.82756607</v>
+      </c>
+      <c r="D208" t="n">
+        <v>21431.62039364</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1254.50415186</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B209" t="n">
+        <v>43485.31983842</v>
+      </c>
+      <c r="C209" t="n">
+        <v>6477.77868402</v>
+      </c>
+      <c r="D209" t="n">
+        <v>20667.67521284</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1230.80886996</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B210" t="n">
+        <v>49845.2508116</v>
+      </c>
+      <c r="C210" t="n">
+        <v>6394.50905563</v>
+      </c>
+      <c r="D210" t="n">
+        <v>23587.74634015</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1319.29611711</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B211" t="n">
+        <v>44810.14255457</v>
+      </c>
+      <c r="C211" t="n">
+        <v>6189.26641521</v>
+      </c>
+      <c r="D211" t="n">
+        <v>21461.4335638</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1305.35926644</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B212" t="n">
+        <v>48447.80827683</v>
+      </c>
+      <c r="C212" t="n">
+        <v>7164.4182227</v>
+      </c>
+      <c r="D212" t="n">
+        <v>23340.79673814</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1470.51958267</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B213" t="n">
+        <v>49251.63335944</v>
+      </c>
+      <c r="C213" t="n">
+        <v>6857.36198616</v>
+      </c>
+      <c r="D213" t="n">
+        <v>24097.17059244</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1407.757743</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B214" t="n">
+        <v>44511.31237721</v>
+      </c>
+      <c r="C214" t="n">
+        <v>6532.20566254</v>
+      </c>
+      <c r="D214" t="n">
+        <v>21788.07865917</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1311.47487549</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B215" t="n">
+        <v>46241.66415331</v>
+      </c>
+      <c r="C215" t="n">
+        <v>7139.24711022</v>
+      </c>
+      <c r="D215" t="n">
+        <v>22998.46679442</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1398.45320806</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B216" t="n">
+        <v>51848.33126206</v>
+      </c>
+      <c r="C216" t="n">
+        <v>6975.48858347</v>
+      </c>
+      <c r="D216" t="n">
+        <v>24668.94613004</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1438.55751687</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B217" t="n">
+        <v>56508.77221688</v>
+      </c>
+      <c r="C217" t="n">
+        <v>7190.85719846</v>
+      </c>
+      <c r="D217" t="n">
+        <v>33855.33742453</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1704.7401211</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B218" t="n">
+        <v>46126.57130855</v>
+      </c>
+      <c r="C218" t="n">
+        <v>7215.74936357</v>
+      </c>
+      <c r="D218" t="n">
+        <v>24082.8859023</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1391.59803774</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B219" t="n">
+        <v>46325.2612569</v>
+      </c>
+      <c r="C219" t="n">
+        <v>5209.52303078</v>
+      </c>
+      <c r="D219" t="n">
+        <v>23347.72352615</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1241.09015422</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B220" t="n">
+        <v>50126.53369923</v>
+      </c>
+      <c r="C220" t="n">
+        <v>7014.28747603</v>
+      </c>
+      <c r="D220" t="n">
+        <v>25554.29284173</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1415.02733823</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B221" t="n">
+        <v>47139.07046005</v>
+      </c>
+      <c r="C221" t="n">
+        <v>6587.04821862</v>
+      </c>
+      <c r="D221" t="n">
+        <v>24308.75137059</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1359.63810246</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B222" t="n">
+        <v>54568.98057027</v>
+      </c>
+      <c r="C222" t="n">
+        <v>6708.61461045</v>
+      </c>
+      <c r="D222" t="n">
+        <v>27630.1262109</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1433.70043025</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -43817,79 +43817,79 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54356.3415924345</v>
+        <v>54346.2401604345</v>
       </c>
       <c r="C367" t="n">
-        <v>6309.483124</v>
+        <v>6316.749941</v>
       </c>
       <c r="D367" t="n">
-        <v>151357.316071243</v>
+        <v>152876.543571243</v>
       </c>
       <c r="E367" t="n">
-        <v>115912.038143</v>
+        <v>116178.513145</v>
       </c>
       <c r="F367" t="n">
-        <v>182730.320597</v>
+        <v>182823.578148</v>
       </c>
       <c r="G367" t="n">
-        <v>380246.828650401</v>
+        <v>381048.757698401</v>
       </c>
       <c r="H367" t="n">
-        <v>112830.348033</v>
+        <v>113575.68635</v>
       </c>
       <c r="I367" t="n">
-        <v>53677.4476548291</v>
+        <v>53846.4832088291</v>
       </c>
       <c r="J367" t="n">
-        <v>115922.928495</v>
+        <v>116169.65646</v>
       </c>
       <c r="K367" t="n">
-        <v>480689.121041466</v>
+        <v>481733.018407466</v>
       </c>
       <c r="L367" t="n">
-        <v>54869.682377</v>
+        <v>55102.665965</v>
       </c>
       <c r="M367" t="n">
-        <v>81931.431094</v>
+        <v>82051.395217</v>
       </c>
       <c r="N367" t="n">
-        <v>689220.701374323</v>
+        <v>687990.956617323</v>
       </c>
       <c r="O367" t="n">
-        <v>124119.815548</v>
+        <v>123194.470614</v>
       </c>
       <c r="P367" t="n">
-        <v>565100.885826323</v>
+        <v>564796.486003323</v>
       </c>
       <c r="Q367" t="n">
-        <v>103230.362699037</v>
+        <v>103823.618100037</v>
       </c>
       <c r="R367" t="n">
-        <v>2040295.92933373</v>
+        <v>2039758.20591073</v>
       </c>
       <c r="S367" t="n">
-        <v>542988.421613</v>
+        <v>548125.657079</v>
       </c>
       <c r="T367" t="n">
-        <v>2583284.35094673</v>
+        <v>2587883.86298973</v>
       </c>
       <c r="U367" t="n">
-        <v>0.186988852044245</v>
+        <v>0.160584402664576</v>
       </c>
       <c r="V367" t="n">
-        <v>8.524613565511</v>
+        <v>8.49601172111811</v>
       </c>
       <c r="W367" t="n">
-        <v>3.53260614415092</v>
+        <v>4.51213232740022</v>
       </c>
       <c r="X367" t="n">
-        <v>8.95938993774343</v>
+        <v>9.99025914242944</v>
       </c>
       <c r="Y367" t="n">
-        <v>0.87214367649564</v>
+        <v>1.05174552306482</v>
       </c>
       <c r="Z367" t="n">
-        <v>8.61571228701452</v>
+        <v>8.80910148032579</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -43875,79 +43875,79 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54346.2401604345</v>
+        <v>54292.8662054345</v>
       </c>
       <c r="C367" t="n">
-        <v>6316.749941</v>
+        <v>6289.979245</v>
       </c>
       <c r="D367" t="n">
-        <v>152876.543571243</v>
+        <v>152556.065937243</v>
       </c>
       <c r="E367" t="n">
-        <v>116178.513145</v>
+        <v>117292.889877</v>
       </c>
       <c r="F367" t="n">
-        <v>182823.578148</v>
+        <v>182558.486148</v>
       </c>
       <c r="G367" t="n">
-        <v>381048.757698401</v>
+        <v>379565.061618401</v>
       </c>
       <c r="H367" t="n">
-        <v>113575.68635</v>
+        <v>112958.692488</v>
       </c>
       <c r="I367" t="n">
-        <v>53846.4832088291</v>
+        <v>53794.5341958291</v>
       </c>
       <c r="J367" t="n">
-        <v>116169.65646</v>
+        <v>116766.574892</v>
       </c>
       <c r="K367" t="n">
-        <v>481733.018407466</v>
+        <v>481616.390416466</v>
       </c>
       <c r="L367" t="n">
-        <v>55102.665965</v>
+        <v>55262.536467</v>
       </c>
       <c r="M367" t="n">
-        <v>82051.395217</v>
+        <v>82295.066029</v>
       </c>
       <c r="N367" t="n">
-        <v>687990.956617323</v>
+        <v>689397.191679323</v>
       </c>
       <c r="O367" t="n">
-        <v>123194.470614</v>
+        <v>124293.592067</v>
       </c>
       <c r="P367" t="n">
-        <v>564796.486003323</v>
+        <v>565103.599612323</v>
       </c>
       <c r="Q367" t="n">
-        <v>103823.618100037</v>
+        <v>102479.632982037</v>
       </c>
       <c r="R367" t="n">
-        <v>2039758.20591073</v>
+        <v>2040005.88340073</v>
       </c>
       <c r="S367" t="n">
-        <v>548125.657079</v>
+        <v>547120.08478</v>
       </c>
       <c r="T367" t="n">
-        <v>2587883.86298973</v>
+        <v>2587125.96818073</v>
       </c>
       <c r="U367" t="n">
-        <v>0.160584402664576</v>
+        <v>0.172746394252576</v>
       </c>
       <c r="V367" t="n">
-        <v>8.49601172111811</v>
+        <v>8.50918584135465</v>
       </c>
       <c r="W367" t="n">
-        <v>4.51213232740022</v>
+        <v>4.3203979981993</v>
       </c>
       <c r="X367" t="n">
-        <v>9.99025914242944</v>
+        <v>9.78847483197978</v>
       </c>
       <c r="Y367" t="n">
-        <v>1.05174552306482</v>
+        <v>1.02215123003351</v>
       </c>
       <c r="Z367" t="n">
-        <v>8.80910148032579</v>
+        <v>8.77723534662353</v>
       </c>
     </row>
   </sheetData>

--- a/data-coyuntura.xlsx
+++ b/data-coyuntura.xlsx
@@ -43875,79 +43875,79 @@
         <v>46174</v>
       </c>
       <c r="B367" t="n">
-        <v>54292.8662054345</v>
+        <v>54184.0738894345</v>
       </c>
       <c r="C367" t="n">
-        <v>6289.979245</v>
+        <v>6310.816742</v>
       </c>
       <c r="D367" t="n">
-        <v>152556.065937243</v>
+        <v>153207.726577243</v>
       </c>
       <c r="E367" t="n">
-        <v>117292.889877</v>
+        <v>119549.795499</v>
       </c>
       <c r="F367" t="n">
-        <v>182558.486148</v>
+        <v>182867.78546</v>
       </c>
       <c r="G367" t="n">
-        <v>379565.061618401</v>
+        <v>381485.330651401</v>
       </c>
       <c r="H367" t="n">
-        <v>112958.692488</v>
+        <v>114200.803855</v>
       </c>
       <c r="I367" t="n">
-        <v>53794.5341958291</v>
+        <v>53906.3121748291</v>
       </c>
       <c r="J367" t="n">
-        <v>116766.574892</v>
+        <v>118556.08159</v>
       </c>
       <c r="K367" t="n">
-        <v>481616.390416466</v>
+        <v>482836.746558466</v>
       </c>
       <c r="L367" t="n">
-        <v>55262.536467</v>
+        <v>55383.507737</v>
       </c>
       <c r="M367" t="n">
-        <v>82295.066029</v>
+        <v>82503.858564</v>
       </c>
       <c r="N367" t="n">
-        <v>689397.191679323</v>
+        <v>689248.027181323</v>
       </c>
       <c r="O367" t="n">
-        <v>124293.592067</v>
+        <v>123401.41405</v>
       </c>
       <c r="P367" t="n">
-        <v>565103.599612323</v>
+        <v>565846.613131323</v>
       </c>
       <c r="Q367" t="n">
-        <v>102479.632982037</v>
+        <v>100724.947747037</v>
       </c>
       <c r="R367" t="n">
-        <v>2040005.88340073</v>
+        <v>2042348.22895673</v>
       </c>
       <c r="S367" t="n">
-        <v>547120.08478</v>
+        <v>552617.58527</v>
       </c>
       <c r="T367" t="n">
-        <v>2587125.96818073</v>
+        <v>2594965.81422673</v>
       </c>
       <c r="U367" t="n">
-        <v>0.172746394252576</v>
+        <v>0.287765272020568</v>
       </c>
       <c r="V367" t="n">
-        <v>8.50918584135465</v>
+        <v>8.63377666303256</v>
       </c>
       <c r="W367" t="n">
-        <v>4.3203979981993</v>
+        <v>5.36861657957839</v>
       </c>
       <c r="X367" t="n">
-        <v>9.78847483197978</v>
+        <v>10.8916370279497</v>
       </c>
       <c r="Y367" t="n">
-        <v>1.02215123003351</v>
+        <v>1.32828170942263</v>
       </c>
       <c r="Z367" t="n">
-        <v>8.77723534662353</v>
+        <v>9.10686629189472</v>
       </c>
     </row>
   </sheetData>
